--- a/Lib/hardware/data/tokopedia_products_latest.xlsx
+++ b/Lib/hardware/data/tokopedia_products_latest.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/1/7aeb95bc-e841-4938-b4bc-170c843ec092.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=JJ%2BopeCN5yYlw2aaZmmCeCBbHRg%3D&amp;x-signature-webp=5GwQt1OXgQksK0igZrUdD4ClkpA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/1/7aeb95bc-e841-4938-b4bc-170c843ec092.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=%2BktrB0oEulTaNOpU31fpvgqJCGs%3D&amp;x-signature-webp=EtvSRsjmskN5RvNjiTqcZxR%2Fkpo%3D</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d1c57722b70e4b7a864178ab8d5b07aa.jpeg</t>
+          <t>Lib\hardware\data\images\400ef9cef96741dc8ee756ade3d9d281.jpeg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomppurwokerto/speaker-gaming-pc-dan-laptop-nyk-sp-n02?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomppurwokerto/speaker-gaming-pc-dan-laptop-nyk-sp-n02?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/df0f4a61aed14dcb8da81f3c4f338f43~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=FcKejrNkp6i%2F5AB%2F%2FexbrYlvMxU%3D&amp;x-signature-webp=qFt76k2g5WJnwrVE3Ymkarwd9oE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/df0f4a61aed14dcb8da81f3c4f338f43~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=%2Fl9He6a%2BET5mKbgpHV9uvogdQYQ%3D&amp;x-signature-webp=hlyw4QYn%2FyU%2FuETiTvEzk8jwaQg%3D</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\18c5efcd853d49babb393f5d3a5ea1fe.jpeg</t>
+          <t>Lib\hardware\data\images\b549dd7c928c406a9fbcfae4de1eda14.jpeg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomppurwokerto/coolingpad-nyk-x6-thunderstorm-gaming-cooling-pad-laptop-2-fan-x-6-x-6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomppurwokerto/coolingpad-nyk-x6-thunderstorm-gaming-cooling-pad-laptop-2-fan-x-6-x-6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -606,17 +606,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/22/cc4b9584-80b6-44d6-87d5-f4611d98002d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=6%2BFL9zT0SKV%2B%2BSJ2ggsiZyB3bnU%3D&amp;x-signature-webp=VM7M%2B4nUm30ThkP5b9OYW0dvgQY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/22/cc4b9584-80b6-44d6-87d5-f4611d98002d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=7YbZqQJ3FeP%2B3uvEngQYU6cPRRc%3D&amp;x-signature-webp=EzwSu2qTRdHeZ1SJhk9bofFCqdQ%3D</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f596ad0108c84ea78b861c7c24f0ce0a.png</t>
+          <t>Lib\hardware\data\images\9254ac7cf1f34bc7897f20fd50cecde5.png</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomp-semarang/rexus-gladius-gx2-gaming-pro-gamepad-joystick-laptop-pc-hitam-95b39?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomp-semarang/rexus-gladius-gx2-gaming-pro-gamepad-joystick-laptop-pc-hitam-95b39?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -655,17 +655,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/3/c0410e6b-f108-42d2-9b67-ea029ba1ab29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=zFzNd7lOXyLXeCemc2i3mtpFDpc%3D&amp;x-signature-webp=M8IvDM1vHpxQ6LE%2FBefkHur2DNs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/3/c0410e6b-f108-42d2-9b67-ea029ba1ab29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=1cJp1R%2BH%2B0NRombyCb6u3cscwAk%3D&amp;x-signature-webp=TxZUs2XlVsmq%2FL1uJBalPAQ00xc%3D</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5695550a96db40ac9b0dec97a73af966.png</t>
+          <t>Lib\hardware\data\images\2a161342d2e344cc8a618244f3e2728c.png</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomp-semarang/nyk-x6-thunderstorm-gaming-coolingpad-laptop-2-fan-x-6-x6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomp-semarang/nyk-x6-thunderstorm-gaming-coolingpad-laptop-2-fan-x-6-x6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/13/35945633-babb-4760-81cb-d4986d80ec0f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=dPorr1xZVc2Rzs3EHBqgmityAIM%3D&amp;x-signature-webp=QdOjQDGjZqWYYViWFzUIsmUvlk4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/13/35945633-babb-4760-81cb-d4986d80ec0f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=8T3WvF%2BaQHRVrH8M1a80EOR3Kwo%3D&amp;x-signature-webp=5rm4GHhccpzl0tMJkTWDK85cQNY%3D</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7e1c837bacb042869942b7b2be0dd3e5.jpeg</t>
+          <t>Lib\hardware\data\images\4ec34475fb4d4ee3af9580c600d59fe8.jpeg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/oceanbike/headset-headphone-gaming-power-full-bass-hs04su-mic-3-5mm-earphone-komputer-laptop-pc?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/oceanbike/headset-headphone-gaming-power-full-bass-hs04su-mic-3-5mm-earphone-komputer-laptop-pc?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/16/f7f0720b-7ffd-4402-9d19-9a8e519ea683.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=rA6wK8n0xpmAGAKeCYu0RMSvr7s%3D&amp;x-signature-webp=AHGGoVi1Grp3v4JhQ%2F3csMrp4c8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/16/f7f0720b-7ffd-4402-9d19-9a8e519ea683.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=7zP0OEnhXekHA%2BvK9lNztGVzJ2E%3D&amp;x-signature-webp=5e7Fq7FPHPHrYtRXiu%2BuPnSmp%2Bo%3D</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f55c8098a41b468485dace1e542be45a.png</t>
+          <t>Lib\hardware\data\images\6e36443c92384599a6b8fb70547c1104.png</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mrmaidstore/keyboard-gaming-and-mouse-8310-rgb-keyboard-and-mouse-gaming-for-laptop-komputer-pc-2-in-1-gaming-set-white-0fc1b?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mrmaidstore/keyboard-gaming-and-mouse-8310-rgb-keyboard-and-mouse-gaming-for-laptop-komputer-pc-2-in-1-gaming-set-white-0fc1b?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e55445b6e9a42439b246d1d5c9cc663~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=23FoR41BgorYJ6Lfiu2YSSR6LUY%3D&amp;x-signature-webp=Z7W6NIghcLu873DIuImZTeIRxU8%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e55445b6e9a42439b246d1d5c9cc663~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=uT0mKY0mKOn3gk9FsHdhB0H5%2BVs%3D&amp;x-signature-webp=CAxNZF67IoWjpi2ozpm7i62KHZs%3D</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e2dd930661a346f8813df1a0968a4693.jpeg</t>
+          <t>Lib\hardware\data\images\6cbe33bb93eb4b6397ff33e47994454a.jpeg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fantech-official-store/fantech-carbon-7-1-hg30-headset-gaming-usb-7-1-virtual-surround-sound-mic-noise-cancelling-driver-40-mm-pc-laptop-mac-ps4-ps5-switch-1731357616041067843?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fantech-official-store/fantech-carbon-7-1-hg30-headset-gaming-usb-7-1-virtual-surround-sound-mic-noise-cancelling-driver-40-mm-pc-laptop-mac-ps4-ps5-switch-1731357616041067843?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/67226b19-6b3d-41f1-b2f3-c0c0d81b1319.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=lkjFSpRtIfOf1ZSspkwzoSpcyg8%3D&amp;x-signature-webp=bO1%2BQuTvdJ84iUYw1Td%2Fnfc5FhU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/67226b19-6b3d-41f1-b2f3-c0c0d81b1319.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=GXWtzY8OPM7NH5%2BPh9HSaazjG2s%3D&amp;x-signature-webp=OSXGINEzh414dqUNu9usnwopZks%3D</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cdf47eda4a90435a8b16360a6b01b002.png</t>
+          <t>Lib\hardware\data\images\d1923b90585d40c7ae0d6a6d34292259.png</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-tv-home-theater-pc-monitor-gaming-laptop-hdmi-male-to-hdmi-male-2-1-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928891163543425?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-tv-home-theater-pc-monitor-gaming-laptop-hdmi-male-to-hdmi-male-2-1-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928891163543425?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -906,17 +906,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/9b61818c-7d6b-4657-b87b-cda3f5f9bcf3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=yZeoS72R3NEWyQir8XdL4SSeiNo%3D&amp;x-signature-webp=qvhKyY9fEkWUMk%2BSIC10D34901g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/9b61818c-7d6b-4657-b87b-cda3f5f9bcf3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=3W7IDr2p4VbXj4JbObimLbtzQ8U%3D&amp;x-signature-webp=95pz3lpmsaOZUI%2Fz9idELlhIF2s%3D</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\291c08b01dd34866a5fe04f953d15030.png</t>
+          <t>Lib\hardware\data\images\6f96e82564bd4b8ba20f5d85565df836.png</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-pc-monitor-gaming-laptop-displayport-dp-1-4-to-displayport-dp-1-4-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928629547304833?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-pc-monitor-gaming-laptop-displayport-dp-1-4-to-displayport-dp-1-4-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928629547304833?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/5d1519ada63b4e6d9117033d63f53c0a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=pU%2B3pCwsOJvLRmIjTB9%2F4BVfNo4%3D&amp;x-signature-webp=SclQqsj7hLvzpTb1BUcQwu8tzgc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/5d1519ada63b4e6d9117033d63f53c0a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=i4xbc7fzngmIK67VY%2FcplFZDdy0%3D&amp;x-signature-webp=rPgVXacG%2FunUpvRMjvF1Wk0fTjI%3D</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fb51b79448254c0db87f5b48cf7a85b9.jpeg</t>
+          <t>Lib\hardware\data\images\142b94d68e194714ba88967eabc1719b.jpeg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/himtech/hagibis-kabel-hdmi-to-hdmi-2-1-ultra-hd-2k-4k-8k-3d-hdr-earc-vrr-qms-allm-qft-displayhdr-tv-pc-gaming-monitor-laptop-video-audio-cable-1730928835618703202?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/himtech/hagibis-kabel-hdmi-to-hdmi-2-1-ultra-hd-2k-4k-8k-3d-hdr-earc-vrr-qms-allm-qft-displayhdr-tv-pc-gaming-monitor-laptop-video-audio-cable-1730928835618703202?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/de586d5ac89841249f0ded879ec5efcc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=LsOCMnk3sN%2FVIiWx5KllsXvz8JM%3D&amp;x-signature-webp=%2FDYE8QHbjmZn4B28gI4hdftwFDY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/de586d5ac89841249f0ded879ec5efcc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=hj6NpiL7xUqOLw4fuHhUJ4PxVuQ%3D&amp;x-signature-webp=P2xQ2TZzcOK2y4yMTS0BT50J46c%3D</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d3f4351f931e474a9485eba5f1b3c565.jpeg</t>
+          <t>Lib\hardware\data\images\77feb2349ff646c394d5a463feeda7b2.jpeg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fantech-official-store/fantech-cooling-pad-rgb-nc22-notebook-cooler-with-phone-holder-adjustable-fan-speed-up-to-14kg-19-inch-laptop-gaming-1731339017679177162?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fantech-official-store/fantech-cooling-pad-rgb-nc22-notebook-cooler-with-phone-holder-adjustable-fan-speed-up-to-14kg-19-inch-laptop-gaming-1731339017679177162?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c93407def7484a1da7ab81928956adc0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=8nURLixMTXKhEKsd8SNUEhJbGmk%3D&amp;x-signature-webp=CEjEnHz4FBWC%2BPoukh10tN2UqF4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c93407def7484a1da7ab81928956adc0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=u%2BkXTBsaGMputj6OaR%2Fz16QP2Eg%3D&amp;x-signature-webp=DDog%2FzG1ADgfzWgaNygTiF4igwA%3D</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ad2973de974d477bb3d56c2d71b9d727.jpeg</t>
+          <t>Lib\hardware\data\images\104bc527e1364bcfbdb19300d697fa37.jpeg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mousepad-gaming-premium-unitech-90cm-x-40cm-x-0-3cm-alas-mouse-pad-jumbo-anti-slip-untuk-laptop-pc-1731687141802083738?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/mousepad-gaming-premium-unitech-90cm-x-40cm-x-0-3cm-alas-mouse-pad-jumbo-anti-slip-untuk-laptop-pc-1731687141802083738?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/29/eeb6fab6-76fe-412e-a3af-dd3792478a70.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=ibBXYBfIuMGk5G41WsOMQgh6hu8%3D&amp;x-signature-webp=gWWQHh3aJY8Si10Iy8r6lyRH3q0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/29/eeb6fab6-76fe-412e-a3af-dd3792478a70.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=CXt7l51hl6hB31eJq%2Fi%2FQZGtHhs%3D&amp;x-signature-webp=PnjstDUsn9HjiNiYXw1CaneQZQc%3D</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fd8cf42fc6204bde8a8828a5f4cfdb72.jpeg</t>
+          <t>Lib\hardware\data\images\66382a9fdf7e4349b0dfe151044609fe.jpeg</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/blisatu/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-komputer-laptop-garansi-1-tahun-hitam-39941?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/blisatu/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-komputer-laptop-garansi-1-tahun-hitam-39941?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1163,17 +1163,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/11/f1a5e8dc-36e6-41b1-b297-0871c88cdc8d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=pAQgM9zYoVtf6UOR8MnoSvG4nnM%3D&amp;x-signature-webp=iL2xqu3toZwLuTKtvrP5e5WKFYs%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/11/f1a5e8dc-36e6-41b1-b297-0871c88cdc8d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=O7HTQajrepaQ%2BnxMSmQqn7i9GtQ%3D&amp;x-signature-webp=3ias0ItaGx79tRby9M9DbCAMWuE%3D</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fb7882d1d98341a09aff1a627e519bea.png</t>
+          <t>Lib\hardware\data\images\7796d996e6694acca6f149fd3a118b65.png</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/blisatu/speaker-robot-rs190-laptop-pc-gaming-soundbar-super-bass-portable-rgb?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/blisatu/speaker-robot-rs190-laptop-pc-gaming-soundbar-super-bass-portable-rgb?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/25/92ac9a5e-5d03-4584-82a7-00705b6f7bd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=zEY4QUhViSVC78uqdgjOE3GjY%2FE%3D&amp;x-signature-webp=bEWniAGu3krgnymUZApKJGjXQNA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/25/92ac9a5e-5d03-4584-82a7-00705b6f7bd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=zEMiussqkG2hkDdr8GtIVNZIJaw%3D&amp;x-signature-webp=kotVnorx067ClWH08Z4v33SbjRk%3D</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\97e16da2c66240ad8cda250d3f05fd2a.jpeg</t>
+          <t>Lib\hardware\data\images\f303705fa5cf4d74aefd503bc5365c6c.jpeg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/venusmobile/xiaomi-redmi-speaker-soundbar-komputer-bluetooth-aux-koneksi-desktop-laptop-gaming-rgb-computer?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/venusmobile/xiaomi-redmi-speaker-soundbar-komputer-bluetooth-aux-koneksi-desktop-laptop-gaming-rgb-computer?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=DyBkMUdM92zOdtKsgqra2J9WPbo%3D&amp;x-signature-webp=m8y%2BJEYuhZ3Z3WH%2BjiAXt%2FiKZ7g%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=x5SgoZLEXwfCikssyq0vOdMFGhk%3D&amp;x-signature-webp=q07x4vvjn6HGNa5p%2BIP8M5YOukw%3D</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1e032f247a8d4524af16aa677dec644c.jpeg</t>
+          <t>Lib\hardware\data\images\54d6c1756ae44aba86c73104de38e8c2.jpeg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2023/11/11/c6e5f1ac-a7ee-42d3-b7f4-87e11a768173.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=GY8UgTFEyEG1OFVM3sFZKBjaA4c%3D&amp;x-signature-webp=u3DZxCTHGKCqakOfgyJcNCF8Mnk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2023/11/11/c6e5f1ac-a7ee-42d3-b7f4-87e11a768173.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=kgDnt3JJ8yyo1fEexmi%2B%2BGV0ySc%3D&amp;x-signature-webp=%2FLOFSRShS2p8HZSJfCInbiiTy5c%3D</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f3f840069874418e8e61209968459733.jpeg</t>
+          <t>Lib\hardware\data\images\26a9fbe34f5a460da11d70a86f2a98d3.jpeg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/expocomp/charger-innergie-by-delta-240w-gaming-adaptor-laptop-universal-t24?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/expocomp/charger-innergie-by-delta-240w-gaming-adaptor-laptop-universal-t24?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fa2db5fb271245a99a2a7fdaad38723b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=pRJH7DQaE449sSEeeQeeNrRzd9E%3D&amp;x-signature-webp=Nqr8ICsiRPKRseRDL7urJDJW8Js%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fa2db5fb271245a99a2a7fdaad38723b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=IQztm31J1PS7zLB5l%2FMe1kWH%2BwU%3D&amp;x-signature-webp=1S7gzy34%2BABvtlyfrCi78V9IJxo%3D</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8cc217d0f56b4ae7b075b7c63980283b.jpeg</t>
+          <t>Lib\hardware\data\images\e5c740dea352402d9050d8e5f9a3bf5a.jpeg</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-kl332-kipas-pendingin-laptop-tornado-5-fan-tidak-licin-blue-1729729632344771388?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-kl332-kipas-pendingin-laptop-tornado-5-fan-tidak-licin-blue-1729729632344771388?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1420,17 +1420,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6ff3324cae5f46c3acb745a01c0de934~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=3HQDiuqc4pRJALM9McgM7QksjQ4%3D&amp;x-signature-webp=9W2gN0sJSOw%2FGhSnlGblt0KvKfQ%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6ff3324cae5f46c3acb745a01c0de934~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=kdf5Jr1p2lrODAzCUbdJkzLNjok%3D&amp;x-signature-webp=H1b42nH8AXkk0J0XmzbbiANzbGk%3D</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ebdcf91253784a06a1820ebb45bc5051.jpeg</t>
+          <t>Lib\hardware\data\images\6f82295df90c42a29fc74c3a32a7216d.jpeg</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokobaru-s/skyworth-monitor-gaming-24-inch-h24g30q-2k-180hz-fast-ips-panel-1440x2560-16-9-hdr10-99-srgb-untuk-laptop-1731695301096015656?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch%26whid%3D18717103</t>
+          <t>https://www.tokopedia.com/tokobaru-s/skyworth-monitor-gaming-24-inch-h24g30q-2k-180hz-fast-ips-panel-1440x2560-16-9-hdr10-99-srgb-untuk-laptop-1731695301096015656?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch%26whid%3D18717103</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1472,17 +1472,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/3/28/1a2e9b92-8bfd-42a2-b3fb-6050eb6867b5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=BIcYkda%2FVCbbr0zWL60Q6n1%2BFVs%3D&amp;x-signature-webp=t2seFFiRnWLchlO3RyZQcPuXTbM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/3/28/1a2e9b92-8bfd-42a2-b3fb-6050eb6867b5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=7RoEBPAE916Nh0r6Acr1D3H4zhs%3D&amp;x-signature-webp=EehsI5a557YABTHfARK9n%2FJZCws%3D</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1ab23523663746b3a2c782dba9a8ef29.jpeg</t>
+          <t>Lib\hardware\data\images\77732425040947d380d9953a323250b7.jpeg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/liemgroup/robot-m206s-wireless-mouse-optical-1600-dpi-silent-click-gaming-pc-laptop-new-m206-m206s-merah-muda-10503?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/liemgroup/robot-m206s-wireless-mouse-optical-1600-dpi-silent-click-gaming-pc-laptop-new-m206-m206s-merah-muda-10503?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/18/9b1c74c6-ffd2-45b1-bdd3-54758efb4bcf.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=U4t7ucOwmGktOklffBhUNYp%2B3rg%3D&amp;x-signature-webp=hXrv9WY3uRvHF3ywW2Zz0kIsjbQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/18/9b1c74c6-ffd2-45b1-bdd3-54758efb4bcf.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=f2hPR%2FBBcPk%2FFTkPqdh5UXlIbDU%3D&amp;x-signature-webp=XN7KwNchlqYvhlueOSsUgeEhXZQ%3D</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\82f44e2cc63d4a82bc10844514da91e3.jpeg</t>
+          <t>Lib\hardware\data\images\f5b9273bac514347b0e7a020de5a2d65.jpeg</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/hagibis-indonesia-store/hagibis-8k-displayport-cable-1-4-high-refresh-rate-dp-cable-8k-60hz-4k-240hz-2k-360hz-for-gaming-monitor-graphics-card-pc-tv-laptop-1730797185172539267?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/hagibis-indonesia-store/hagibis-8k-displayport-cable-1-4-high-refresh-rate-dp-cable-8k-60hz-4k-240hz-2k-360hz-for-gaming-monitor-graphics-card-pc-tv-laptop-1730797185172539267?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/fe3c30b0c1da4d0fa9741d40670b6485~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=u6gmGUTtH%2BGOLZdcxxxzVpszHH0%3D&amp;x-signature-webp=YNfU7MCgdhZqH4MQg365LeqsZEg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/fe3c30b0c1da4d0fa9741d40670b6485~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=e92hIWvmPa5JemLY4%2BvfcSrQKF4%3D&amp;x-signature-webp=KqM2XMfJZChlvgajrfgGXrusOjM%3D</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2b8ad0dc26d14a089f86b4db3cb12d4b.jpeg</t>
+          <t>Lib\hardware\data\images\5122f5a62eb54d6884ecd337ec83503d.jpeg</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/soruindonesia/soru-cooling-pad-stand-laptop-gaming-6-fan-kipas-pendingin-laptop-kipas-cooler-1729982466431355783?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/soruindonesia/soru-cooling-pad-stand-laptop-gaming-6-fan-kipas-pendingin-laptop-kipas-cooler-1729982466431355783?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1b714cec8f61478a99ddbdc25d4e5003~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=7qW28gKN9L%2B9eYL0sTSb0Gso21U%3D&amp;x-signature-webp=qLFR9AcS743LQdFRigl3iMnrgS0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1b714cec8f61478a99ddbdc25d4e5003~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=U6U2USfIP3yX4wQo8MrR1biFcj0%3D&amp;x-signature-webp=GcP3iMpceT6smtl8o%2BN%2B8a52EHM%3D</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d7a90553d9f54bd7b0df0d1c512c46ce.jpeg</t>
+          <t>Lib\hardware\data\images\cb7667c396414c73b73681be6c72ffce.jpeg</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/onikumaindonesia/onikuma-cw902-mouse-gaming-hitam-kabel-original-untuk-laptop-komputer-pc-dengan-6400-dpi-tombol-rgb-dan-sensor-optik-tingkat-definisi-tinggi-button-1730338257921934858?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/onikumaindonesia/onikuma-cw902-mouse-gaming-hitam-kabel-original-untuk-laptop-komputer-pc-dengan-6400-dpi-tombol-rgb-dan-sensor-optik-tingkat-definisi-tinggi-button-1730338257921934858?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/13/31a814f6-f0bb-4d89-b3d4-0dafe63f22d7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=QDyT7R%2BTsdKFW8MSMkJjkTusTJA%3D&amp;x-signature-webp=havojmRoB8qrZnztERVXLbWJNoY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/13/31a814f6-f0bb-4d89-b3d4-0dafe63f22d7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=ulGDpxbm6jCPtVmIz6cZZSpU5zI%3D&amp;x-signature-webp=1liFlQajDpajZfv6LOWN0EoPpao%3D</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6db493fa5d4e40deb9ed6c51e0004690.jpeg</t>
+          <t>Lib\hardware\data\images\40e15b029a944d0fbce7ebefcbcb27b2.jpeg</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lenovo-authorized-surabaya/charger-innergie-by-delta-180w-gaming-adaptor-laptop-universal-t18?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch%26whid%3D11569999</t>
+          <t>https://www.tokopedia.com/lenovo-authorized-surabaya/charger-innergie-by-delta-180w-gaming-adaptor-laptop-universal-t18?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch%26whid%3D11569999</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/70a5e998-ee7d-48c8-b0f6-c652f9a12d32.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=EWXHj8w%2BrjTIKC9HlftIjspnwsw%3D&amp;x-signature-webp=GtY1VK4p%2F7BVppLsFM2qoRSGJEc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/70a5e998-ee7d-48c8-b0f6-c652f9a12d32.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=Ctf9%2FnLGoXSmFmkOacS1BRQwd3g%3D&amp;x-signature-webp=yA3ZWHTrtNt6%2BmOjH3pCy%2F7VCGI%3D</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\152050fe452645d3821e41cd45df8626.jpeg</t>
+          <t>Lib\hardware\data\images\a2f1afeb7dc34df8b6053792daad871c.jpeg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-innergie-gaming-universal-original-180w-150w-130w-65w-45w-1731234857708193451?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-innergie-gaming-universal-original-180w-150w-130w-65w-45w-1731234857708193451?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/15/373a1aa1-4150-4341-9439-debc881a4fd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=YsXZi4MeFTH5yw80yguaNLNk%2FE4%3D&amp;x-signature-webp=sik8sRbYYyZqKgrQzVGjg5vIiOU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/15/373a1aa1-4150-4341-9439-debc881a4fd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=6P9MVImP3oNwFZ6tc0nKVH4hids%3D&amp;x-signature-webp=sOml%2BmK5qBQtz3NYGl0qlV7jn1M%3D</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6508dbae71104622aa59b32cb6abeed2.jpeg</t>
+          <t>Lib\hardware\data\images\ebb38dbfba854ca9b27523733c771345.jpeg</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-gaming-mechanical-87-keys-wired-keyboard-layout-rgb-light-universal-pc-laptop-1730787426880030393?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-gaming-mechanical-87-keys-wired-keyboard-layout-rgb-light-universal-pc-laptop-1730787426880030393?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1830,17 +1830,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/20/b4aa025b-29e1-44b1-b8e7-776a2899eef3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=hyjPL9eXU6f6tt0Ppa9qspiqEZY%3D&amp;x-signature-webp=m0TvRpUtDBqtuqPjwGj3ZB%2FqcGY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/20/b4aa025b-29e1-44b1-b8e7-776a2899eef3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=G1i3Uis%2FtnGRWTxsaYUtTrtdcZI%3D&amp;x-signature-webp=zoI79HlvI8Qv11Wk6%2Btsvz%2Bpa8w%3D</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\59e06bda1784433e835a24a1027095ed.png</t>
+          <t>Lib\hardware\data\images\fd992f9fa14e4135b835324cbb9a4be6.png</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-wireless-mouse-mechanical-gaming-bluetooth-5-0-dual-mode-silent-click-type-c-fast-charging-screen-display-3200dpi-untuk-pc-laptop-1730803778625832633?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-wireless-mouse-mechanical-gaming-bluetooth-5-0-dual-mode-silent-click-type-c-fast-charging-screen-display-3200dpi-untuk-pc-laptop-1730803778625832633?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5d662cb1-9633-4475-9bb5-82f645202a74.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=A1zTun5JdxMAIcCn2yyZcpfmAAs%3D&amp;x-signature-webp=cltuPjd9QSduOCGGc%2FepdhVdgmo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5d662cb1-9633-4475-9bb5-82f645202a74.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=3WJfsskRgIxCjeHn%2BUwvAKBh4pQ%3D&amp;x-signature-webp=iycKYwTqo70I23yk8%2BxkJDjzZxo%3D</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5f5f775b06c741e199045215631fed61.jpeg</t>
+          <t>Lib\hardware\data\images\e337d3caa69f4fdab820074c0e2f38d0.jpeg</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adapter-innergie-charger-laptop-gaming-acer-asus-dell-hp-lenovo-280w-200w-1731234851512288939?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adapter-innergie-charger-laptop-gaming-acer-asus-dell-hp-lenovo-280w-200w-1731234851512288939?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5087391e11d74a6cbbd2950bf01e6539~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=R%2FzuRrY%2BR6p3KwRZZWU8JdToa2c%3D&amp;x-signature-webp=X%2F8i5ZSQSPi9ZFMyi9r0wAtcQ6U%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5087391e11d74a6cbbd2950bf01e6539~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=4IYbakIaYspTFCmOcAMhiN7W3xM%3D&amp;x-signature-webp=OqioZPdxIy1m1ejt0HW9eIgZe%2F0%3D</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4549a76d78814eefb3fd567d4599fe4b.jpeg</t>
+          <t>Lib\hardware\data\images\3b4c42566a0a48839622d4f2830008dc.jpeg</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-pendingin-laptop-2-kipas-kl330-fan-1729636686228589372?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-pendingin-laptop-2-kipas-kl330-fan-1729636686228589372?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/1/26/4f9883a0-3d3f-4986-97f3-3f5751f7165c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=hj596LlEmAFjXGmY9cgl0s%2F%2B19o%3D&amp;x-signature-webp=eKiKEfkmkbF7cQU4nLUEx4PndpE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/1/26/4f9883a0-3d3f-4986-97f3-3f5751f7165c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=LcB1Td1JTabmW%2FLxnKH0QdOJW8s%3D&amp;x-signature-webp=sbew2%2FvqWEX%2FAKsunhPEIskdQqE%3D</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\238526f0df224071a831e6d19bb3fb51.jpeg</t>
+          <t>Lib\hardware\data\images\2b0523aa162d470baae0f8cb9e996e5b.jpeg</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/d-m-i/nyk-x1-wind-coaster-gaming-cooling-pad-laptop-with-3-fan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/d-m-i/nyk-x1-wind-coaster-gaming-cooling-pad-laptop-with-3-fan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/3/23/a52ecf75-8473-45e9-a91d-36c8da636f5e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=5mWsieA5k1IiXIBp%2FKhxVGopMtc%3D&amp;x-signature-webp=AllGpcLWDELMUFlv1T0ZcVVJXZk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/3/23/a52ecf75-8473-45e9-a91d-36c8da636f5e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=gbSfYG1X8PydKp6SeTdz7O7b7kc%3D&amp;x-signature-webp=IhdE7Em4PaGVoXtIMoAX8FyVDdw%3D</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6c1de166d813495d882daec7c232a310.png</t>
+          <t>Lib\hardware\data\images\25407f9fba3a4ddc9ee85ef7d827992d.png</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/andalassuryagemilang/fan-laptop-cooling-pad-notebook-gaming-nyk-x3-winterstorm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/andalassuryagemilang/fan-laptop-cooling-pad-notebook-gaming-nyk-x3-winterstorm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6b4457908324a2788e9a7da6815e258~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=9HXPeJPGHFrBUqWdJ047hVKebas%3D&amp;x-signature-webp=tURIWp4GYeVynmsC1omP0CaTWE8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6b4457908324a2788e9a7da6815e258~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=rA%2BasICYcnGCD1nT1MvBgcRtYvQ%3D&amp;x-signature-webp=v7SubtmHOFcoJmf8g6UnRbrLMUo%3D</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0158787531934b949d4554e615b53f7b.jpeg</t>
+          <t>Lib\hardware\data\images\abb91cdb732a4adc907b5ad7da7f8fed.jpeg</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mouse-gaming-kabel-unitech-s1-colorfull-rgb-light-3200-dpi-untuk-komputer-pc-laptop-1729643499823991194?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/mouse-gaming-kabel-unitech-s1-colorfull-rgb-light-3200-dpi-untuk-komputer-pc-laptop-1729643499823991194?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/25/98ce42ec-a8a6-4112-9380-10eadb2994f5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=xUzAn6xnI%2BW6WBrkNReHq1HGLlc%3D&amp;x-signature-webp=vbIwk854FYh8jz9m8giGCwQiJA8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/25/98ce42ec-a8a6-4112-9380-10eadb2994f5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=MpSZNGAFYoUx8r0uoG7z%2Bwc9d68%3D&amp;x-signature-webp=c0d1Ca5YHGbVru3NNBRQo89bN7Y%3D</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0803651e6d594e9c8c02c6b161b57df6.png</t>
+          <t>Lib\hardware\data\images\4d28be5afb79454d8d56d06c7aface27.png</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-gaming-kabel-usb-wired-rgb-light-optical-1200-1600dpi-ergonomic-untuk-pc-laptop-dengan-2-speed-dpi-adjustable-dan-tombol-6d-black-1731239865956402840?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-gaming-kabel-usb-wired-rgb-light-optical-1200-1600dpi-ergonomic-untuk-pc-laptop-dengan-2-speed-dpi-adjustable-dan-tombol-6d-black-1731239865956402840?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5c94cc2b-9899-4e95-ae52-c5f60a45630c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=B%2Fatxgfbxrs5qw1ZBWtJfiqwCMs%3D&amp;x-signature-webp=USWfsBwVQpEGFpWgirkCCkc08wQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5c94cc2b-9899-4e95-ae52-c5f60a45630c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=hA5oj%2BZzrU4DZuS0r3FKCohAzyM%3D&amp;x-signature-webp=ZSEcg8S%2FpORL9kx2KlE1JdvN8rw%3D</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1bc3b27408a549d4939131751b01f45d.jpeg</t>
+          <t>Lib\hardware\data\images\3327fc732d64433584071eb88516c222.jpeg</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-gaming-universal-innergie-240w-230w-200w-20v-12a-t24-1731234878706910891?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-gaming-universal-innergie-240w-230w-200w-20v-12a-t24-1731234878706910891?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0c39492bae8949e79deb61008e4da18c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=n3wEfe12%2Fq%2FWfB2G%2FDpP6JP6t7g%3D&amp;x-signature-webp=HoyA76b7%2BBHQKJLwvsGxI%2F0p3f4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0c39492bae8949e79deb61008e4da18c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=g120hQdB0l7VjybwkAQoiR0in4E%3D&amp;x-signature-webp=VUcDZaw2REI5ZkbqyNoAprHkD74%3D</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a069b6871b8346b6b68a8dc952dbaec7.jpeg</t>
+          <t>Lib\hardware\data\images\4be30067fcce463a8754bd30da0a40a0.jpeg</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bikepremiumstore/headset-headphone-gaming-power-full-bass-hs04su-mic-earphone-komputer-laptop-pc-3-5mm?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bikepremiumstore/headset-headphone-gaming-power-full-bass-hs04su-mic-earphone-komputer-laptop-pc-3-5mm?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2289,17 +2289,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e190eea8efac4e969fd89e79beb0140f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=wbERdVOiIj9ML0y8FxUn5oxeRSk%3D&amp;x-signature-webp=D9ByZSFaVOVF56xsWz8EIqeijT4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e190eea8efac4e969fd89e79beb0140f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=gdxw2vNAgyi3xC2XHYd4WNetrdY%3D&amp;x-signature-webp=5Oi%2BFbmv%2BulDb9YGNIkMuTNDeQA%3D</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f580025f28c042459dced04c56c6c81f.jpeg</t>
+          <t>Lib\hardware\data\images\22f77d0cec9341f7a6298a7e5c4ae581.jpeg</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/allitems-id/cabletime-mouse-pad-aluminium-metal-premium-gaming-dekstop-laptop-deskmat-smooth-1731201382108268433?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/allitems-id/cabletime-mouse-pad-aluminium-metal-premium-gaming-dekstop-laptop-deskmat-smooth-1731201382108268433?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6e153097f95486d892d9338928ef0fa~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=bVie2oKTxT0rErID1hGX4v1vynE%3D&amp;x-signature-webp=kmYKffy7hO%2F5VtRSHjwm26ADNYk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6e153097f95486d892d9338928ef0fa~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=ACy9vMznCMa5qs9tdJV6L2Gzk7s%3D&amp;x-signature-webp=GvzdDXUj9pyKQX0sw6OdPQhemI0%3D</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f0be6a46ffdd4f9dbe1acd92f09fdd16.jpeg</t>
+          <t>Lib\hardware\data\images\d8983ac07e1d4b66a8918ebf1e4ffd79.jpeg</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bestit/nemesis-coolingpad-gaming-turbo-air-compressed-up-to-21-inch-laptop-beiruz-ax3-cooling-pad-rgb-1732247682542044373?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bestit/nemesis-coolingpad-gaming-turbo-air-compressed-up-to-21-inch-laptop-beiruz-ax3-cooling-pad-rgb-1732247682542044373?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3b54f1bf88024c7482a8a32e8c98eaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=IKLLR4VB2YYY7zCtZXtGSBxTW3I%3D&amp;x-signature-webp=QbEh70Dnc3uQWOBMe89toIJ8enY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3b54f1bf88024c7482a8a32e8c98eaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=L4lNKUQYDlRMp0de4aN%2FsjHbZxE%3D&amp;x-signature-webp=BehZhLlWIOgU6HqIkkxq2HcKgAY%3D</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5ed4d9aed6dc4b0199551094d7774ad3.jpeg</t>
+          <t>Lib\hardware\data\images\1071107b056e48a8be72bca22ce5f7f6.jpeg</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bikepremiumstore/headset-gaming-headphone-mic-power-full-bass-hs-04su-earphone-komputer-laptop-pc-3-5mm-mobile-live-streaming?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bikepremiumstore/headset-gaming-headphone-mic-power-full-bass-hs-04su-earphone-komputer-laptop-pc-3-5mm-mobile-live-streaming?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/9/22/73b26064-75be-46de-b155-5535d7d164c0.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=xinNpBJPCGNS%2FlBRSTT7SbMdxu0%3D&amp;x-signature-webp=soKv1U9jkoTKaw1MeMm0SWBgFp8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/9/22/73b26064-75be-46de-b155-5535d7d164c0.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=WE%2FBKsfcR546fKb%2Bgf9HQXkERwI%3D&amp;x-signature-webp=qFX6I6gucfvBca6tn7lc%2FJPlj94%3D</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dee4460921734a2f992e4b1d581e6f2d.jpeg</t>
+          <t>Lib\hardware\data\images\b8fdaefa658a495ebc5ae7351e811dd9.jpeg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-laptop-cooler-gaming-cooling-pad-fan-cooler-turbo-silent-srq-019-32d50?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-laptop-cooler-gaming-cooling-pad-fan-cooler-turbo-silent-srq-019-32d50?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9863a40e2c6f4645a11e10bb72c0701c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=DOHX%2FUsI4dFFuixhAoxQNq59bZo%3D&amp;x-signature-webp=tJqifjLzO3Or%2Ftb3%2F34WnQozq8M%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9863a40e2c6f4645a11e10bb72c0701c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=gxuply1FwHco9KjhJNjOnEH7G6I%3D&amp;x-signature-webp=7aBBbmTQW7jBellczGi8zowzLfk%3D</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3e8a778f4ac84f3f90658549fa8d0bc2.jpeg</t>
+          <t>Lib\hardware\data\images\97f6084518474ea69c986a01e8d42a47.jpeg</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tasairbone/tas-ransel-laptop-gaming-polofelix-anti-air-waterproof-soft-case-pelindung-laptop-macbook-size-besar-1731153071094466207?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tasairbone/tas-ransel-laptop-gaming-polofelix-anti-air-waterproof-soft-case-pelindung-laptop-macbook-size-besar-1731153071094466207?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2540,17 +2540,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/22/99a529bd-4693-440e-90e1-cf2b813f8692.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=O2sCH%2F1L4ZoW8TgLrUt82eV0zW8%3D&amp;x-signature-webp=PpNvU48QBOJvRlDmNZR4WTrPkDg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/22/99a529bd-4693-440e-90e1-cf2b813f8692.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=lq%2BxkUaZFLGDUb94X%2BsaqxQj1sw%3D&amp;x-signature-webp=ebZBC0ff06PwRpFQyfTzqKsOOWs%3D</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4d2bea898ca04f8eb535d1e956fc4686.jpeg</t>
+          <t>Lib\hardware\data\images\f4837177250d4cf5bcc47750b12a16ad.jpeg</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/d-m-i/deepcool-n80-rgb-gaming-cooling-pad-for-laptop-cooler?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/d-m-i/deepcool-n80-rgb-gaming-cooling-pad-for-laptop-cooler?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/6/23/42a98edc-3f69-43a5-acb7-82cd258ba31a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=VY74vCwuCl812cUvoddNv14hTKk%3D&amp;x-signature-webp=ieuTYkQAZ%2Fd5Z37Bwl0Snk%2Fa93M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/6/23/42a98edc-3f69-43a5-acb7-82cd258ba31a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=YaTShuG2NC2SupE3QW7Lh%2F9SVIo%3D&amp;x-signature-webp=Z0kh3D%2BlS1X%2FnVTaKfwKvS7SKyc%3D</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\54c22ebdff8e48eb876f075d103231f8.jpeg</t>
+          <t>Lib\hardware\data\images\3a21ed8d31aa45368387cc64f7d2d866.jpeg</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/affselv-now/affselv-cooler-laptop-cooling-pad-5-fan-17-inch-adjustable-speed-2600-rpm-kipas-pendingin-laptop-gaming-dengan-6-level-kecepatan-dan-4-level-ketinggian-untuk-laptop-hingga-15-6-inch-1733156196976723940?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/affselv-now/affselv-cooler-laptop-cooling-pad-5-fan-17-inch-adjustable-speed-2600-rpm-kipas-pendingin-laptop-gaming-dengan-6-level-kecepatan-dan-4-level-ketinggian-untuk-laptop-hingga-15-6-inch-1733156196976723940?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2641,17 +2641,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4c66596fc2ce4ad29797c2e977512d7f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=vYAyvcJaWnf2okYm1hXH%2BMIEMgg%3D&amp;x-signature-webp=qC%2BUjDsQLOvwUJAol57ZNxTxMYw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4c66596fc2ce4ad29797c2e977512d7f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=JHBBMjokpZC0oLc966pdynfzS18%3D&amp;x-signature-webp=hZQFgbRa50UPkXcxBc%2BZhV7bsII%3D</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3a2f13886fd54627b539d9f80dd573f1.jpeg</t>
+          <t>Lib\hardware\data\images\cac3b0ebf4984475a6e49df78e0ae6f1.jpeg</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olike-official/new-product-olike-desktop-speaker-sc07-6w-subwoofer-rgb-light-gaming-full-bass-360-surround-sound-portable-wired-connection-for-laptop-pc-1733184933872698864?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olike-official/new-product-olike-desktop-speaker-sc07-6w-subwoofer-rgb-light-gaming-full-bass-360-surround-sound-portable-wired-connection-for-laptop-pc-1733184933872698864?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/10/11/7d1054d5-ebac-4558-a9f0-204c541144bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=D3tJUY7VHLarO5DeQBFFlLex3i4%3D&amp;x-signature-webp=GZC4IE6L1ese4jewpx70tWfwZmk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/10/11/7d1054d5-ebac-4558-a9f0-204c541144bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=D93ScIQID29PWapS4J6sFYPngXE%3D&amp;x-signature-webp=Oc9UULRf0HLzeO%2BsUfNozYwhBvs%3D</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fb6ed51f9e2d46e1b4c646faa95fe36f.png</t>
+          <t>Lib\hardware\data\images\6cb34da97b074575851937db528fdeda.png</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fashionselular/headset-gaming-led-onesos-sy830-headphone-bass-with-mic-hp-pc-laptop-led-blue?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fashionselular/headset-gaming-led-onesos-sy830-headphone-bass-with-mic-hp-pc-laptop-led-blue?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2739,17 +2739,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/152cf82999ae4c61845620b1616abb22~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=XoqD%2Fp5APgKse%2FvbdkHXIqds4G8%3D&amp;x-signature-webp=ZlEQi6v64w7r8radSDbQP8C9rC8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/152cf82999ae4c61845620b1616abb22~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=%2BEy%2BRcm1MalnlHYv7oSrzWPMTt8%3D&amp;x-signature-webp=UfCoVO5xtt2ec82MSbBLQ%2BJiJVU%3D</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\273aa7ceef304e4084cf913e7ec5b3d2.jpeg</t>
+          <t>Lib\hardware\data\images\d3a1f68cbeba497489e7f749c62aa6c1.jpeg</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dell-premium-official/dell-backpack-alienware-vindicator-17-3inch-armored-tas-gaming-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dell-premium-official/dell-backpack-alienware-vindicator-17-3inch-armored-tas-gaming-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/d1ef1c4a86a7447988bcbdce4d35fa2b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=M%2BEo7yx1k%2Fhw%2FfsicKF6gO50CGY%3D&amp;x-signature-webp=SqBFq0kIytLYBV8btnJgo4J%2BHWk%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/d1ef1c4a86a7447988bcbdce4d35fa2b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=ll%2F31fqvitYwMvtMz4nNXGQu8eI%3D&amp;x-signature-webp=G8B0vId5H0vxvpkJHHyvOovbnAU%3D</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dff7f7bd2411428ca4c104e59da83aa3.jpeg</t>
+          <t>Lib\hardware\data\images\f81bade762874b038f3fd9def47fa05b.jpeg</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-keyboard-gaming-k358-led-rgb-bachlight-support-all-komputer-laptop-hitam-7a474?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-keyboard-gaming-k358-led-rgb-bachlight-support-all-komputer-laptop-hitam-7a474?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/f9a4449e-bfff-4df1-b18f-c1e2af70c4b4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=eJQwL7tunkIZEdtVytaC%2FBn0eTA%3D&amp;x-signature-webp=qBGwImSYfBTHdLtp%2FgH53vBzMYU%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/f9a4449e-bfff-4df1-b18f-c1e2af70c4b4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=1C1%2Bq0lHm1u6scBkh77Ysl0Q0bM%3D&amp;x-signature-webp=8w7CiugRE2ulFG0ylp4EtFHrD%2FE%3D</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\77fe22155c5a4695933772e9159cb120.png</t>
+          <t>Lib\hardware\data\images\7b2e0e07717248b89a4824c38d1a757e.png</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/promodazzle/terlaris-ugreen-headset-kabel-mfi-iphone-android-type-c-lightning-3-5mm-original-100-garansi-resmi-24-bulan-official-store-mall-ori-murah-termurah-terbaik-tablet-samsung-xiaomi-macbook-laptop-pc-typec-earphone-handsfree-super-extra-full-bass-gaming-typec-60700-a7403?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/promodazzle/terlaris-ugreen-headset-kabel-mfi-iphone-android-type-c-lightning-3-5mm-original-100-garansi-resmi-24-bulan-official-store-mall-ori-murah-termurah-terbaik-tablet-samsung-xiaomi-macbook-laptop-pc-typec-earphone-handsfree-super-extra-full-bass-gaming-typec-60700-a7403?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2895,17 +2895,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/16/59db287d-8254-4933-b80e-ef38ff1ddbb7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=5wAHoxPSK%2BF6bk5KajIKudxOSDY%3D&amp;x-signature-webp=%2ByNXfzMugEFqO2unaZdy2wuuKko%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/16/59db287d-8254-4933-b80e-ef38ff1ddbb7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=bh5lA0QQylDABd5dKrDJ2sYhq%2FY%3D&amp;x-signature-webp=GAruuc9OJm%2F3sA2KVh84JuqySrA%3D</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4220c40bb1dc4cf291c97f431fba3e06.jpeg</t>
+          <t>Lib\hardware\data\images\3ab76c66c0d54f38bf84ed552c5f3861.jpeg</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-pc-komputer-laptop-garansi-1-tahun-bisa-cod-1731162798337328677?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-pc-komputer-laptop-garansi-1-tahun-bisa-cod-1731162798337328677?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9c456a2e30e64b50b899963631939be0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=CoqXOupCfqtocfIj0zjmAgx8Jbg%3D&amp;x-signature-webp=2iwDwEJWIRQfvptm1krEdaTiDXs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9c456a2e30e64b50b899963631939be0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=i6r2lLfsrhSGfkd8AMJhLYYvbyc%3D&amp;x-signature-webp=j%2FY6eXHTEHrXpr0qVLAbCLw7g3I%3D</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7676c558e6bd4e54bf71c81358577a64.jpeg</t>
+          <t>Lib\hardware\data\images\3d6386aa0a0d4c89a18e8b838ccbc170.jpeg</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/donatur/gamen-gs2-speaker-gaming-laptop-pc-rgb-surround-sound-powerfull-bass-1729873792547194354?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/donatur/gamen-gs2-speaker-gaming-laptop-pc-rgb-surround-sound-powerfull-bass-1729873792547194354?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -2999,17 +2999,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/3/16/62a45061-18e3-48fb-ba3f-42dd8d84b589.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=HqrLQ%2BoORCkmdlWXANnb5Kx6uqg%3D&amp;x-signature-webp=nXooR%2FDd4t%2BgHi2IqInoSNqUbgo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/3/16/62a45061-18e3-48fb-ba3f-42dd8d84b589.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997961&amp;x-signature=EkcOUaEwtFQB8pVmPz9ixNui7CE%3D&amp;x-signature-webp=W5z4K1PlWKA4HahlrfZX%2BdVttHs%3D</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b14c7183a82443c483fb0ebab229100e.png</t>
+          <t>Lib\hardware\data\images\80f115aece7c4839a9a3b8fda9931f8a.png</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/donatur/robot-rs200-speaker-e-sports-gaming-for-pc-laptop-smartphone-ori?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/donatur/robot-rs200-speaker-e-sports-gaming-for-pc-laptop-smartphone-ori?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112414260011B9842E0A271F3BD1ZP%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9060d5fb44cf4b2faa8e9864b1542c37~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=cpQ%2FSodBKkAEcgymQN3grUvJtoM%3D&amp;x-signature-webp=xizsTV7eXu4i4ZKFee9mr4uQRog%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9060d5fb44cf4b2faa8e9864b1542c37~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=34wE%2BlcicgZcotaYQsroYz1Pq88%3D&amp;x-signature-webp=pFMAM5jdCpqoHwk4yhAw6DRkiMg%3D</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b5d478f4e8674ce2a8480c55254da23b.jpeg</t>
+          <t>Lib\hardware\data\images\09bc2386cca04771aa3ea4028716f610.jpeg</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocofficialstore/tomtoc-t60-explorer-laptop-backpack-office-bag-size-22l-1732719801450137078?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocofficialstore/tomtoc-t60-explorer-laptop-backpack-office-bag-size-22l-1732719801450137078?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3100,17 +3100,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/11/28/265f544d-72eb-43c7-8a97-1756f4f7fcb6.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=JGRiD9LNVWElv%2BZnZGVlj0noiGg%3D&amp;x-signature-webp=AQEumYzkWCDefaUuSIFc1BPmj0Q%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/11/28/265f544d-72eb-43c7-8a97-1756f4f7fcb6.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=JJ9O95wY3nw2f9VALJyFtFI9FiY%3D&amp;x-signature-webp=a84C2xMR3kW1KNmSWn8ileRuJcE%3D</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3eda55e7e77c446397879aaacebb51ef.jpeg</t>
+          <t>Lib\hardware\data\images\f2d60db2a75040baa89db9933213b2e1.jpeg</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcompsolo/mikuso-kb-052u-wired-usb-keyboard-104-key-pc-laptop-office-ergonomic-hitam-6ac76?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D16130095</t>
+          <t>https://www.tokopedia.com/starcompsolo/mikuso-kb-052u-wired-usb-keyboard-104-key-pc-laptop-office-ergonomic-hitam-6ac76?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch%26whid%3D16130095</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3152,17 +3152,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/26f44dfba5404212ad862b746e42857a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=m1UKxz%2F0JVfhbkl%2BiJmyN5mglz8%3D&amp;x-signature-webp=Dq2Au2SxOYL2DV1PmbFdBtYFk7w%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/26f44dfba5404212ad862b746e42857a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=qTXsAgRhUGj%2FQLe4Xl5kNvgIBDY%3D&amp;x-signature-webp=CQPpRzWVMHvWx8NZAPqhdvuH33o%3D</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9222a534609f4d55b6764a9913acee78.jpeg</t>
+          <t>Lib\hardware\data\images\ba1df263367e4396b469de948d7f257a.jpeg</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitechone-keyboard-mouse-combo-set-office-master-keyboard-mouse-for-pc-laptop-gadget?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitechone-keyboard-mouse-combo-set-office-master-keyboard-mouse-for-pc-laptop-gadget?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e59a9d3733e44c89e422d639b080b4b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=m7qIx6aeKGy9z26H1vxdVSCMPgs%3D&amp;x-signature-webp=XTY9pbDanugPHEFI0%2BAcT%2B7yWjE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e59a9d3733e44c89e422d639b080b4b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=%2FcpxuQngJnzM3stvWRjOUgxwwJg%3D&amp;x-signature-webp=4hU8fuyhpk6xx%2B1SXNkxEAjOS3U%3D</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3f62a520a0da4c13aea399fbbe67fb97.jpeg</t>
+          <t>Lib\hardware\data\images\e7e046b3293a418c8de22c0f6b1ed04f.jpeg</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/gameridsurabaya/laptop-lenovo-legion-5-15-intel-core-i7-13650hx-rtx-5050-8-gb-ram-16-gb-ssd-512-gb-windows-11-office-home-student-15-3-wuxga-165hz-100srgb-1732195924137248723?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/gameridsurabaya/laptop-lenovo-legion-5-15-intel-core-i7-13650hx-rtx-5050-8-gb-ram-16-gb-ssd-512-gb-windows-11-office-home-student-15-3-wuxga-165hz-100srgb-1732195924137248723?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3256,17 +3256,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/9/4/92698dcd-813c-417b-a377-062feb24f1da.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=jrtoyk%2FmsUviWUpMgRCOLACfhWk%3D&amp;x-signature-webp=C1aP%2FHYDJmEMc1s5dtABMwBFGvs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/9/4/92698dcd-813c-417b-a377-062feb24f1da.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=3t6mOx%2F%2B%2BaXq%2FGYfI8jTR3%2B13o4%3D&amp;x-signature-webp=QV0va5JkrmNtWvauWDy3r49xwbs%3D</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\70434cf4f113445c92a7b13a6a0544c8.png</t>
+          <t>Lib\hardware\data\images\e5fce154d09a4d41bf0d4ee8a2007328.png</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-gradaz-office-bundle-tas-ransel-kerja-backpack-laptop-tas-selempang-ipad-organizer-charger-pouch-multifungsi-only-bag-black-0e00a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-gradaz-office-bundle-tas-ransel-kerja-backpack-laptop-tas-selempang-ipad-organizer-charger-pouch-multifungsi-only-bag-black-0e00a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=y1jTTY9R6db%2FvI5BerJTlKjR5PU%3D&amp;x-signature-webp=CnKZzleTN%2BD2pZZmozIJ7OflSJE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=3ffXMu0ytvXGe7IK4YmqcK5vqXY%3D&amp;x-signature-webp=wg14vIOiC%2FVk%2BMJGdCgfs67%2F41U%3D</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5de5b5e76e3d440c8b37a3faf318eb13.png</t>
+          <t>Lib\hardware\data\images\a857443a59b748f8b3285181240c1966.png</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/13/c3ad5491-fc3d-4b80-b80a-59b49374ce68.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=kih4zIV4oYWRN1rnq1NYxzBP0Us%3D&amp;x-signature-webp=TsUBXiiGzb5X6PGDiPNspzyorzs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/13/c3ad5491-fc3d-4b80-b80a-59b49374ce68.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=5GOrcx%2BuBNL1sGehN0f1JE6Z0qs%3D&amp;x-signature-webp=cbwrOyiscaTurtkr8pUfH0hdS1s%3D</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9231229570a8485aa037a751f961cd93.jpeg</t>
+          <t>Lib\hardware\data\images\e91f7c2133bd4b46856af2f83fd15e6d.jpeg</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/backpack-tas-ransel-office-punggung-sekolah-kuliah-kerja-laptop-15-inch-torch-loka-1730777953781646394?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/backpack-tas-ransel-office-punggung-sekolah-kuliah-kerja-laptop-15-inch-torch-loka-1730777953781646394?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3409,17 +3409,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/15/a0091498-b7ce-4323-9e2d-682fd5afcdde.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=UXEsiLrQbQAQpdLag0TBWIupTxI%3D&amp;x-signature-webp=FeaZAZhqrIF2Vk4LCMfOR9jIiGQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/15/a0091498-b7ce-4323-9e2d-682fd5afcdde.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=4SrcppsA6tF%2BLmyUS9M2W6%2FDJ6o%3D&amp;x-signature-webp=T8URgIS53iTfoLrXgH1W9hTnElU%3D</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7680fa5a5c11488ca63b47cc478187e3.png</t>
+          <t>Lib\hardware\data\images\9013197df50f4763a53d62f975e51e32.png</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-office-collection-tas-ransel-kerja-kantor-laptop-stylish-pria-wanita-hongcheon-black-eaee2?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-office-collection-tas-ransel-kerja-kantor-laptop-stylish-pria-wanita-hongcheon-black-eaee2?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/45db327a9c23430aa3e9f3da70e0d1af~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=MqNPAVJ8x2yBY%2BemRkwa0lHY8lY%3D&amp;x-signature-webp=JcALQybxEWfGQaHMiyPADRw5Sd0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/45db327a9c23430aa3e9f3da70e0d1af~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=fk0w1fS45xsxdTkSfnhijsPZweI%3D&amp;x-signature-webp=1QNEUYexE6Pi492KC9v4IlIgLyM%3D</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\88964ddaa2ce4976810394e0aca20b35.jpeg</t>
+          <t>Lib\hardware\data\images\fb3eda127f0e46f48fe0b31bb2e7d4ce.jpeg</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-g6-untuk-komputer-laptop-pc-1000-dpi-mouse-office-computer-1729590282578069914?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-g6-untuk-komputer-laptop-pc-1000-dpi-mouse-office-computer-1729590282578069914?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3513,17 +3513,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f1f4aa17bf5c43cc9eea095c93d0bf11~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=e5TNqFKirkGO7plpxvjfe9F%2FCbU%3D&amp;x-signature-webp=6ve2%2Ff5cvhkNgIqkfxQuaFt2opY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f1f4aa17bf5c43cc9eea095c93d0bf11~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=HXYZXY2jHSOdcZlZg6oGm4VnUOs%3D&amp;x-signature-webp=gqZyvpRfENbbVrMXv75jL8%2FouFU%3D</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\78db6ad5ed4340d88c429c6a1a2c5bf1.jpeg</t>
+          <t>Lib\hardware\data\images\327a723cb9e34168897e28a6ef3ce98f.jpeg</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/optical-mouse-office-kabel-usb-unitech-g5-1000-dpi-untuk-laptop-pc-computer-1729588341583546778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/optical-mouse-office-kabel-usb-unitech-g5-1000-dpi-untuk-laptop-pc-computer-1729588341583546778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3562,17 +3562,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3baef23e7214219af4e67c58e42992c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=FYUo05P%2FX0lO4d8jGSja6q1m8cU%3D&amp;x-signature-webp=HBXOtMNS%2FLyfDDOYAYR1q%2Ft6EC0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3baef23e7214219af4e67c58e42992c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=HpbKama3alQL9NquGx2QbXMv2No%3D&amp;x-signature-webp=3QJ3MQ8X%2FKvtyypdEF%2B5NmwN9dQ%3D</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\709b8caacf8f4298a1c74c64d9173671.jpeg</t>
+          <t>Lib\hardware\data\images\7c613da800874a328f0b728d51abe998.jpeg</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-wired-usb-portable-office-keyboard-for-pc-laptop-computer-hitam-keyboard-1731239918096844440?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-wired-usb-portable-office-keyboard-for-pc-laptop-computer-hitam-keyboard-1731239918096844440?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3614,17 +3614,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/4/5/a58e1a18-1f10-4a59-a55a-fd1832f3e691.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=2K7LxzjFpHLPxWNTzqw0bNYenXM%3D&amp;x-signature-webp=URHU40%2FAmR6fRBkyqnik3niCRfY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/4/5/a58e1a18-1f10-4a59-a55a-fd1832f3e691.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=UewSd9qXCppiiHPBLqFo0tjph6w%3D&amp;x-signature-webp=2Xvz0IDiSOWYHBv5FNTcM3ocO4o%3D</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\73aa3f140212429384d3381225daad39.png</t>
+          <t>Lib\hardware\data\images\ffc476e084474c52bbb6a316b1f41142.png</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-loka-backpack-office-tas-ransel-punggung-kuliah-kerja-laptop-15-inch-black-a2f1a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-loka-backpack-office-tas-ransel-punggung-kuliah-kerja-laptop-15-inch-black-a2f1a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3666,17 +3666,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/11/e53481e1-2aa7-4a54-b392-ca8165e0854d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=PZwBlVBxnXFqwxbviZfxuMkp5Jw%3D&amp;x-signature-webp=3LpSe0Irft8e%2B5iZ%2F1nlnIkLioY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/11/e53481e1-2aa7-4a54-b392-ca8165e0854d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=%2FQ%2Ff%2F9evZ%2BWBWKdPGle7rdsGK54%3D&amp;x-signature-webp=%2F5%2FYABanIfLc28raQUoogeRhndI%3D</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\121b6a75b177430bb4f173c7e39882d2.jpeg</t>
+          <t>Lib\hardware\data\images\c3152ae5fc9448e0838b06a981339465.jpeg</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/toko1973/brewyn-kremlin-mens-office-laptop-bag-tas-sekolah-kuliah-kerja-new-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/toko1973/brewyn-kremlin-mens-office-laptop-bag-tas-sekolah-kuliah-kerja-new-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3715,17 +3715,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfea1365d2224b02b0cd6e3066c04563~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=7y7zZP9Y8tCgGhu7eAPxzaFoqb8%3D&amp;x-signature-webp=CgWf%2FH4E84PvmqvKNAP4S96wKhM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfea1365d2224b02b0cd6e3066c04563~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=ANpjffGz%2B9hkdLPSLYQqkP8YvsQ%3D&amp;x-signature-webp=LiMyEOC%2B3emCqF%2FF7xp0UIMr5Fs%3D</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\de86a79b191a4f46a5f8196e9d948a92.jpeg</t>
+          <t>Lib\hardware\data\images\19df43d8c20c440faae5b4ad708adff2.jpeg</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fashionselular/onesos-mouse-bluetooth-wireless-office-silent-click-dual-mode-2-4ghz-receiver-usb-for-pc-laptop-black-97680?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fashionselular/onesos-mouse-bluetooth-wireless-office-silent-click-dual-mode-2-4ghz-receiver-usb-for-pc-laptop-black-97680?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/b431006e2c274740a5d254c732987c47~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=%2BtX4OY8wRWU5WGRgi%2BO6qdB85PY%3D&amp;x-signature-webp=Q17ZpksKHroqymGqyvRPXINrotQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/b431006e2c274740a5d254c732987c47~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=4ac2NsGOOYaH5Acn6D%2BIV%2FJL%2Bdk%3D&amp;x-signature-webp=W18SyeVYGDn8E9MZihOh%2Bu1oQ6M%3D</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dade424a262345a5ae4ace1c6e1f4f63.jpeg</t>
+          <t>Lib\hardware\data\images\092724db95c34c24be9eddc2cb38284d.jpeg</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/thekingdomshop/taffware-meja-laptop-42x26cm-portable-desk-table-besi-alumunium-bed-hospital-ranjang-tempat-tidur?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/thekingdomshop/taffware-meja-laptop-42x26cm-portable-desk-table-besi-alumunium-bed-hospital-ranjang-tempat-tidur?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -3813,17 +3813,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/25/e5d80580-d276-4193-95c2-467a317bbbce.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Kq8GPYHPY5dwkPMzyMThwU124LY%3D&amp;x-signature-webp=YMbSgh7I2pgNWWsXrlA%2B7%2BcztzE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/25/e5d80580-d276-4193-95c2-467a317bbbce.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=UKqu%2FkRLwXK8GzxuG0NJJ4Omo64%3D&amp;x-signature-webp=g9GEJ8O%2BlAGWEHR9LyZz7Eilgto%3D</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\174d7179ea8f489bbbc899d967956733.jpeg</t>
+          <t>Lib\hardware\data\images\10db7b943a5944ef8bb391267bce7d95.jpeg</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-malvern-tas-ransel-laptop-14-backpack-office-sekolah-hitam-bfe09?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-malvern-tas-ransel-laptop-14-backpack-office-sekolah-hitam-bfe09?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/6fde5fe1-e2aa-4dae-9a14-e22668d1df63.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=xPu3vDGvLDHk0tmfu8SDo%2FvPbus%3D&amp;x-signature-webp=8OHM%2Bg%2Bbf8mZBIB5dzzsAHbi6tk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/6fde5fe1-e2aa-4dae-9a14-e22668d1df63.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=6a3xHlTImLBDFZfe%2Bp%2BBua%2FSx04%3D&amp;x-signature-webp=gc%2FoXvrNDfX%2BnaloMJZpPPZ%2FPfM%3D</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a57c6d6316c3449598037bcf030473fd.jpeg</t>
+          <t>Lib\hardware\data\images\726897b7cf9a41a899ebac4e5c8e3f88.jpeg</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-malware-ransel-tas-backpack-laptop-14-inch-unisex-for-school-office-travel-hitam-e60e8?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-malware-ransel-tas-backpack-laptop-14-inch-unisex-for-school-office-travel-hitam-e60e8?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/a1b6a357-020a-40c2-82e1-1a04455a483d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=z57Jb4NULMPiie3XBDLuuXMRcZ8%3D&amp;x-signature-webp=l65Z7tnzwveHPBlYWLjd%2B4WIpGo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/a1b6a357-020a-40c2-82e1-1a04455a483d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=spmayy1V7eXAGFBHWCfCNDV%2Bmh4%3D&amp;x-signature-webp=hIe11R6qdO9SqFfilq2qtQKkz8I%3D</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7314b3c4c41747dda799e045b224ce33.jpeg</t>
+          <t>Lib\hardware\data\images\3c0c6e1a47b8456ca0c6f2b6859b047c.jpeg</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-munich-tas-ransel-laptop-outdoor-backpack-travel-22l-office?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-munich-tas-ransel-laptop-outdoor-backpack-travel-22l-office?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/10/80613ad1-822a-420c-b539-8982c04fd198.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=liZvAsQnLy2KmCU6dDXLR2xdgEs%3D&amp;x-signature-webp=dNNAJAbHrTKR7DqRKPeONJjQTOo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/10/80613ad1-822a-420c-b539-8982c04fd198.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=du7MjuCoWG430%2FeSmThGSoa5z98%3D&amp;x-signature-webp=iAahM4K9FqyhUVJv6FmhjhMeaAU%3D</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\98bacb8156464781a46bbe1a4bf84876.jpeg</t>
+          <t>Lib\hardware\data\images\a94a3363e2ae494494d413dde9e5d44c.jpeg</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/delioa/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-20619?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D8108753</t>
+          <t>https://www.tokopedia.com/delioa/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-20619?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch%26whid%3D8108753</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/31f0e7ca2307423d9af05931721c8709~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=eS5rbx4ztpIJnxizpearo0fEl0U%3D&amp;x-signature-webp=3%2FZZf0YOhMkiT%2BD0wO2e69jcCNo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/31f0e7ca2307423d9af05931721c8709~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=d1JMVUmuwAtX%2BoQreXtqJxSp7m0%3D&amp;x-signature-webp=Yba%2BLpHylwTGldzdrcvHK3YWc8A%3D</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\36aad53913bf422ea12d88613a6dee68.jpeg</t>
+          <t>Lib\hardware\data\images\a87cc44957b54a008a468c560bbb3973.jpeg</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-field-of-view-ransel-backpack-outdoor-travel-laptop-14inch-office-sekolah-22-24l-1729771080242594987?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-field-of-view-ransel-backpack-outdoor-travel-laptop-14inch-office-sekolah-22-24l-1729771080242594987?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/2/a4358b69-68cb-47b5-a840-f1b889e39e24.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=%2BvHGR9LAevR4oBip0SC2PO3A6oE%3D&amp;x-signature-webp=d8iQtL8CVJQ6ZE0qEELlr4gvtD8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/2/a4358b69-68cb-47b5-a840-f1b889e39e24.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=fFaIo%2F0xVUwMLicvEufWr2rq50A%3D&amp;x-signature-webp=z9DCUeeRZYFvX67KvAvWXfMEDgM%3D</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\61c1d1fba1114622ab38735386a81c84.jpeg</t>
+          <t>Lib\hardware\data\images\94fdf61e0e4047efaf55b61b05ec9b7c.jpeg</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-yerevan-tas-ransel-laptop-urban-14inch-sekolah-office-merah-b6b5a?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-yerevan-tas-ransel-laptop-urban-14inch-sekolah-office-merah-b6b5a?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4113,17 +4113,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1e1c78d14ba1493b9ddd5c8bded02385~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Ui87Q5NOm8t7roDFzaicplRQtN4%3D&amp;x-signature-webp=%2FAfY2K8w7S7gYH7iGzbcEnndTY4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1e1c78d14ba1493b9ddd5c8bded02385~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=0tMeTRNRowHHAqwZEuwE%2BPWMXP4%3D&amp;x-signature-webp=q%2FDVq2U9cFFNUtusjDcrcn7oRyE%3D</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bdf3584d9b174ab681f24726b1b14188.jpeg</t>
+          <t>Lib\hardware\data\images\5b3a403ce3d042cba73b95ec886a1545.jpeg</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-enrekang-ransel-tas-laptop-15-inch-backpack-travel-28l-office-sekolah-kampus-1731143360590087339?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-enrekang-ransel-tas-laptop-15-inch-backpack-travel-28l-office-sekolah-kampus-1731143360590087339?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4162,17 +4162,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/614ebd8bb1c04a7eb3fd1b4df55f7237~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=lRgqEW9%2BdH6DgkXvv3%2F3YoK3Ug8%3D&amp;x-signature-webp=Vlo5qaEkVEojZOmpAZ3IRZBqU1c%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/614ebd8bb1c04a7eb3fd1b4df55f7237~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=0QUvK2yA7lnDFFndJQRulCtmWx4%3D&amp;x-signature-webp=Z6Tc4SAMLJw6E4QZXQV%2Ff8qXvHY%3D</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a9c7a4d8fc8f4d96b65f9fb629c551fa.jpeg</t>
+          <t>Lib\hardware\data\images\cbc614e702474851a6edbaa8773171a1.jpeg</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/reformasicompute/mouse-wireless-rexus-office-q30-silent-mouse-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/reformasicompute/mouse-wireless-rexus-office-q30-silent-mouse-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5e73c1ebd62c4a558d22d17793191345~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=gNc%2FFA8sMGpsqxiAZ9%2FsjdPTP2A%3D&amp;x-signature-webp=VutbPHJLGa1TPouhbsed%2F7o0Fg0%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5e73c1ebd62c4a558d22d17793191345~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=cCEN2%2BylVlyy16%2FVZrIfdZ1rabw%3D&amp;x-signature-webp=Fxh3FtepInwW8toWFiblGwo8q5g%3D</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4acdcf3ee2c8410db133068793a9e98a.jpeg</t>
+          <t>Lib\hardware\data\images\895ce34bba7547808ac594e4b2f27037.jpeg</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/reformasicompute/rexus-q10-mouse-wireless-office-silent-click-biru-muda?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/reformasicompute/rexus-q10-mouse-wireless-office-silent-click-biru-muda?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/21/8bbc37d0-0a5e-4c6e-8b65-594ce61d6773.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=pIt3Eu8RmiASVIW8omr0TGWGwuY%3D&amp;x-signature-webp=yhCYlpXYfnkRRBFscjvp9e3uBlk%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/21/8bbc37d0-0a5e-4c6e-8b65-594ce61d6773.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=tpGAq5Rv3sWH35gc4LaETq6MQY4%3D&amp;x-signature-webp=%2F2fEtzMYSORQ213kdppiHSPjm7U%3D</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fd44d6d21ef6443795367e62d1f0bb8e.jpeg</t>
+          <t>Lib\hardware\data\images\f81b2013f5f5477a8588152423375ffd.jpeg</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dnd-olshop/baseus-smart-desk-mat-pad-with-wireless-charger-for-gaming-office-wrist-rest-laptop-phone-stand-holder-keyboard-mouse-pad-basic-edition-3ec7d?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dnd-olshop/baseus-smart-desk-mat-pad-with-wireless-charger-for-gaming-office-wrist-rest-laptop-phone-stand-holder-keyboard-mouse-pad-basic-edition-3ec7d?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=axElALC4Less5oxAOEXQYR0fJB8%3D&amp;x-signature-webp=dXSPxKEHAL%2B7IcIBQ5hPT7Y2HpY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=IbBkxfY3jPDNefz27lu%2FPfxp6CU%3D&amp;x-signature-webp=wtCpKGB6msvat4bdeO0F%2F7BSoGw%3D</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3c5a64a65dcd48798ca89f196edaafbb.jpeg</t>
+          <t>Lib\hardware\data\images\6cddad004fd54d4583e2f5542ded62f4.jpeg</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-x-aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1732911892490716709?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-x-aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1732911892490716709?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4367,17 +4367,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f4b1f90a2d4f48fc91d0262d2c72a43e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=uQjn%2FQazffjWzv4hiFJo2i7ojtc%3D&amp;x-signature-webp=dacmViHNSlnFpi26RX7Z1xPCynk%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f4b1f90a2d4f48fc91d0262d2c72a43e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=R5Jr3zIx7Kcje%2BfL7q4GERVOH28%3D&amp;x-signature-webp=DzFauM1pQ7YYbe8In7XEKThd7iA%3D</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fb3873d3d61640dab949bd76b19fdde5.jpeg</t>
+          <t>Lib\hardware\data\images\4df8150a8ad14a409a53fc0b8acf63c3.jpeg</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mouse-kabel-office-unitech-g8-wired-usb-1000-dpi-untuk-laptop-pc-computer-1729588315193248154?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/mouse-kabel-office-unitech-g8-wired-usb-1000-dpi-untuk-laptop-pc-computer-1729588315193248154?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4419,17 +4419,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/27/da8fc5bd-5e79-432a-9e9e-71dccf3a3137.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=O77X23lo5R0mpHlrNLLwe68wL7Q%3D&amp;x-signature-webp=y%2FlDqADQQV4NJNs9DRwBOfIzSII%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/27/da8fc5bd-5e79-432a-9e9e-71dccf3a3137.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=kKUIUfgoNMcO%2FpKlpU3JSYbbte0%3D&amp;x-signature-webp=NOC9MWYKrAbnXq0nJ7wXgOBM1HI%3D</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d2015acb9796418d89b8a8db831bae72.png</t>
+          <t>Lib\hardware\data\images\fa3b1a8e497a489fbf2f30f6370cce9e.png</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supermallori/office-desk-mat-alas-laptop-meja-kerja-mouse-pad-xl-anti-slip-hitam-87010?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supermallori/office-desk-mat-alas-laptop-meja-kerja-mouse-pad-xl-anti-slip-hitam-87010?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/dd1c7673e9244b86998b388fcfb3086e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=RwpvALnrNsyReYThbcN6H5%2Fowg8%3D&amp;x-signature-webp=l3%2BwVGSeePkI4kfc4AYAsksY7cw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/dd1c7673e9244b86998b388fcfb3086e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=M%2Bjh99DoUtcOAWIdgeZjCPK7pqg%3D&amp;x-signature-webp=G3gE8n0DznWqMEZh3ZCfusrRHWA%3D</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4d268887cf854de585254f0828256be2.jpeg</t>
+          <t>Lib\hardware\data\images\056dd6a6f5544df8a0fc9cf83c767afa.jpeg</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/suryatama/mouse-quinton-e100-hitam-kabel-usb-for-laptop-pc-computer-1730805992441873603?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/suryatama/mouse-quinton-e100-hitam-kabel-usb-for-laptop-pc-computer-1730805992441873603?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4520,17 +4520,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/3f12aef7d5d541d8a166d75fb1e151fd~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=cZFqqN19XckqfDHbQhHiY6GIJyg%3D&amp;x-signature-webp=164VDbTs2xhBKn53sZXfVSNoits%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/3f12aef7d5d541d8a166d75fb1e151fd~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=5yiHeTFRFa75sT1bzxRrVB0oZys%3D&amp;x-signature-webp=DzSE6KPElfzsqZPPH31QyFV10E0%3D</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\83dcbb7191fb44afa54a7bc215684af9.jpeg</t>
+          <t>Lib\hardware\data\images\ccd893258b9d4505b5728c0304c57699.jpeg</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-tongkonan-ransel-backpack-laptop-14inch-urban-traveling-22-24l-top-load-sekolah-office-corporate-1729641642932603051?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-tongkonan-ransel-backpack-laptop-14inch-urban-traveling-22-24l-top-load-sekolah-office-corporate-1729641642932603051?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/7/46bf75d3-fdb9-44d8-b4ac-0fc2de7f5648.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=mMwtaYlaXluGscZJXC0v1U%2BAiI4%3D&amp;x-signature-webp=ro3vVWq8ygY9EZP2lwYaaSmoW58%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/7/46bf75d3-fdb9-44d8-b4ac-0fc2de7f5648.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=qnj2FI50L1j8WepLFqrkeFpf1oc%3D&amp;x-signature-webp=n1mrDPqQz29EPdhcJkbbcm9GQ%2BI%3D</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2ae76e6d0c9d43deb2081beda1a1e4a0.jpeg</t>
+          <t>Lib\hardware\data\images\ad1e43d957834cbf9282b1e05774ac7d.jpeg</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-56342?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-56342?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/9/db166b0e-7561-45c4-8f94-c7e1fd6b5ca3.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=7YgNDa%2F3CoxkoaOgrD%2B7bnX%2BVRY%3D&amp;x-signature-webp=iIwbeRYknA6ezNyaEDg9SQaEkuw%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/9/db166b0e-7561-45c4-8f94-c7e1fd6b5ca3.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=a6wy1HyoIu85Yv2XTUFaPHppV90%3D&amp;x-signature-webp=GBr64irh92ErfduEErYaryQSsxk%3D</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f618f8f04cd9474598e6908c38900f24.jpeg</t>
+          <t>Lib\hardware\data\images\8acbdf0e1d4e410c80eed96807ebaa7f.jpeg</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-laptop-kerja-kantor-selempang-office-briefcase-14-bg106-abu-abu-f6cb7?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D4203398</t>
+          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-laptop-kerja-kantor-selempang-office-briefcase-14-bg106-abu-abu-f6cb7?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch%26whid%3D4203398</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4667,17 +4667,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d837c49cb2a5448a810541ddc84ee84c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=goVs1gi5ewZoZMjcwvAModtnWVw%3D&amp;x-signature-webp=vSgnxtb4losx%2F83sXNrDL767Z6Y%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d837c49cb2a5448a810541ddc84ee84c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=IFTfGBXQPOJre%2FcFOf30GxxSvrA%3D&amp;x-signature-webp=ZuPyPvB5I0QfokPt6sEMRhXeuB8%3D</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4464748ebbe84f5cbb9063191ae9cd0d.jpeg</t>
+          <t>Lib\hardware\data\images\52743e1ce0ba4c23b3588e79295633a9.jpeg</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laptopmurahid/laptop-murah-zyrex-lifebook-n4020-8gb-128gb-w11pro-14-0-gry-office-1731531184748463382?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laptopmurahid/laptop-murah-zyrex-lifebook-n4020-8gb-128gb-w11pro-14-0-gry-office-1731531184748463382?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4719,17 +4719,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6338aa902f724277b3c5004260b37911~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Zo2hp%2BbzSQpuUJj0lEmg5ByBSD0%3D&amp;x-signature-webp=uUwOlDrYtcF%2F6Fx54%2BOTC4tc3xg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6338aa902f724277b3c5004260b37911~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=64T5HwRAeb9kD9PSf9ZWNMoQ7RQ%3D&amp;x-signature-webp=0iCv5SgoyRhSUeQTzMdQae5xMRQ%3D</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\335b1e7c75274a7da1fc0d4ca4f58e8c.jpeg</t>
+          <t>Lib\hardware\data\images\9be0ef9836b6465caec0af159f198378.jpeg</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/philips-voicetracer-store/philips-mouse-meetion-kabel-usb-office-mouse-kabel-usb-1200dpi-kursor-halus-dan-presisi-untuk-pc-laptop-1732408374889449090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/philips-voicetracer-store/philips-mouse-meetion-kabel-usb-office-mouse-kabel-usb-1200dpi-kursor-halus-dan-presisi-untuk-pc-laptop-1732408374889449090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -4768,17 +4768,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/20/d54e8ffa-2df9-4c94-af64-9dfd3427faa1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=fQ0zhYAWiJs1rtOGu9vRmzUWr7I%3D&amp;x-signature-webp=fZVbQXTnBDdeCWWVxZ0pPLqgvDQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/20/d54e8ffa-2df9-4c94-af64-9dfd3427faa1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=MFOvl%2FpoAXZ5YXS7mQF8KBJzidI%3D&amp;x-signature-webp=lsYsud1gXlp8QQkLJF55W2HoEi8%3D</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\be86a1f6676d47faae3da183174b5807.png</t>
+          <t>Lib\hardware\data\images\08ceb8ec40d441aca6ec72196d6e9609.png</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/technosify/robot-m102-optical-mouse-wired-pc-laptop-office-1200-dpi-new-m100-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/technosify/robot-m102-optical-mouse-wired-pc-laptop-office-1200-dpi-new-m100-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -4820,17 +4820,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43a06819c1b648dc99f1a089d8642d3e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=TTtH%2FQCFguprg70lGWycRes8UFw%3D&amp;x-signature-webp=DMPb%2FzkYb3bTkDZ%2B%2BA%2Fv1RWqIpg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43a06819c1b648dc99f1a089d8642d3e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=rg3y5nOJD%2BhanVfNbDIz01w3wv4%3D&amp;x-signature-webp=TG0Zl%2B%2FkFeu7jnWUSesm2hOuv4Y%3D</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5b9e318565a340dba580608279811a26.jpeg</t>
+          <t>Lib\hardware\data\images\04d8b0f5c0be4403a57af4e710b0c7d5.jpeg</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/huaiwen-pc-store/hw-keyboard-mouse-set-kabel-usb-portable-104-key-full-size-office-wired-keyboard-for-pc-laptop-1731395301317248711?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/huaiwen-pc-store/hw-keyboard-mouse-set-kabel-usb-portable-104-key-full-size-office-wired-keyboard-for-pc-laptop-1731395301317248711?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -4872,17 +4872,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8e46ce56c02d46fabf7d0c8d97fe2c48~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=tskc7v8FhWvveAc8wB%2F%2BC4lshB0%3D&amp;x-signature-webp=PYwYDnRHQpL0cVvpTG1sM7ZCI2A%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8e46ce56c02d46fabf7d0c8d97fe2c48~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=OtdLiAc%2Fg4GzQAo%2BzMFH%2F9MWEeQ%3D&amp;x-signature-webp=itlj%2By%2Bm9tMhGp37qzUSZ3Ujg8M%3D</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2831e9d26d6e4b62ac308b168509da01.jpeg</t>
+          <t>Lib\hardware\data\images\cac8f9b844974192a3cd82336f8ce623.jpeg</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dap-indonesia-official-store/dap-keyboard-kabel-usb-2-0-portable-104-key-full-size-office-wired-keyboard-bass-button-for-pc-laptop-d-k02-garansi-1-tahun-1729677965436487996?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dap-indonesia-official-store/dap-keyboard-kabel-usb-2-0-portable-104-key-full-size-office-wired-keyboard-bass-button-for-pc-laptop-d-k02-garansi-1-tahun-1729677965436487996?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -4921,17 +4921,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a0501ec6bd9b4b99a2538ce910e8d7cf~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=VXrgN2inN5nlEjokjfoLQbl4npc%3D&amp;x-signature-webp=3Dzw0rz9oTm%2FAvNyz1G6IJyxHCw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a0501ec6bd9b4b99a2538ce910e8d7cf~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=D8%2Bs4qVlt9KI0rAjW99DdHQBWTY%3D&amp;x-signature-webp=X8GiLKWsMRfmbv5urQHA8L2sgdc%3D</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\308b0570e389451ca914a1fb6eba14e4.jpeg</t>
+          <t>Lib\hardware\data\images\6205e827f2eb470b8ebca1edb8005a91.jpeg</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-florin-ransel-tas-laptop-15-inch-backpack-travel-office-sekolah-kampus-1732937353765881003?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-florin-ransel-tas-laptop-15-inch-backpack-travel-office-sekolah-kampus-1732937353765881003?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1f52c929a7754ed4aacff0b2d2a0aaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=SJBg22OjSIRwPpl7uQa5rGBDI38%3D&amp;x-signature-webp=CFtbRqDOtISYuWf%2BuRijCG0bPN4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1f52c929a7754ed4aacff0b2d2a0aaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=r7jzNjNiLrFH2m8jne5VqdYwKEc%3D&amp;x-signature-webp=LBzGqtqmNHA96PlzECMDj0BHcxE%3D</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\260050896e2d489697e2daaee6bd34b0.jpeg</t>
+          <t>Lib\hardware\data\images\c3a419aa560a4709bb97138e09776a80.jpeg</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/royalltech/asus-vivobook-x1404va-intel-core-i7-1355-i5-1335-i5-1334-16gb-512gb-w11-office-14-0fhd-ips-laptop-ultrabook-laptop-tipis-nyaman-untuk-kerja-kuliah-1732832432834512375?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D4029903</t>
+          <t>https://www.tokopedia.com/royalltech/asus-vivobook-x1404va-intel-core-i7-1355-i5-1335-i5-1334-16gb-512gb-w11-office-14-0fhd-ips-laptop-ultrabook-laptop-tipis-nyaman-untuk-kerja-kuliah-1732832432834512375?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch%26whid%3D4029903</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5025,17 +5025,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/11/5/dbc78023-d6f5-4a1c-b574-362511ab85b9.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=kD8L%2FgMWfNXvg%2FKKkMrO3vqDZZY%3D&amp;x-signature-webp=nBc3ggMf2VBgQgQpswPemVEei5g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/11/5/dbc78023-d6f5-4a1c-b574-362511ab85b9.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=5hA3kfqnc3K8n3lb8sN%2BBDo4wnU%3D&amp;x-signature-webp=vREQHd47ClplG6qKIag02xdukE8%3D</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\70352064b1134ebd9262614847a0398a.png</t>
+          <t>Lib\hardware\data\images\0f6eeddb74ef492d8f1507d5bc29fb16.png</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/movioofficialstore/movio-desk-mat-leather-office-deskmate-mouse-pad-gaming-alas-laptop-1730814937146492460?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/movioofficialstore/movio-desk-mat-leather-office-deskmate-mouse-pad-gaming-alas-laptop-1730814937146492460?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5077,17 +5077,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=axElALC4Less5oxAOEXQYR0fJB8%3D&amp;x-signature-webp=dXSPxKEHAL%2B7IcIBQ5hPT7Y2HpY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=IbBkxfY3jPDNefz27lu%2FPfxp6CU%3D&amp;x-signature-webp=wtCpKGB6msvat4bdeO0F%2F7BSoGw%3D</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\34169ac11c7642ca9108653e7698688e.jpeg</t>
+          <t>Lib\hardware\data\images\ced1f76b031e4163a43ed84cbe63af4a.jpeg</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/aula-indonesia/aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1730707911523271760?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/aula-indonesia/aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1730707911523271760?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5129,17 +5129,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9574249e5aa14f9e9ff0ec25065ea773~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=kEIvKQDGiEvYA1BjJstbjJECL10%3D&amp;x-signature-webp=C%2B90qByLHqOlBWFQy5sim7whkGo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9574249e5aa14f9e9ff0ec25065ea773~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=cysxSAetnGv8OCqn%2BlyY7ZFh2no%3D&amp;x-signature-webp=ZBYIwI7SAFKSVY9%2FJavmX11zWHI%3D</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3f25efbc08254963b1b47f5cbee5245c.jpeg</t>
+          <t>Lib\hardware\data\images\4a5c8db8d0b34217b0a37b1538bf3246.jpeg</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-t23-women-tote-bag-for-laptop-macbook-ladies-shoulder-bag-office-bag-beg-perempuan-1732147400330019985?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-t23-women-tote-bag-for-laptop-macbook-ladies-shoulder-bag-office-bag-beg-perempuan-1732147400330019985?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5181,17 +5181,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/142ebd455039474c9b6a28130ac65ab9~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Khdc0Aty1eDW6Cc0PIkuLHa4DgE%3D&amp;x-signature-webp=E49LDKbCPRkAgBD96Ugl7MKY7pY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/142ebd455039474c9b6a28130ac65ab9~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=66uERpQtGOoMnEFtb%2Bgc6%2B1PNHk%3D&amp;x-signature-webp=3uaSHy2vsFQZyNwb%2BpxaGJ3ky1w%3D</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fad1341af6534c829b4ff38557653437.jpeg</t>
+          <t>Lib\hardware\data\images\f347e118a04346b2a7a0f63e48e190c5.jpeg</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-a40-defender-laptop-messenger-bag-14-16-inch-business-shoulder-bag-office-briefcase-beg-silang-lelaki-1732455130755335313?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-a40-defender-laptop-messenger-bag-14-16-inch-business-shoulder-bag-office-briefcase-beg-silang-lelaki-1732455130755335313?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5233,17 +5233,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8cb82b7c455e4e0fa79003e51a3c33c3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=%2B6oVi0%2Fem0a7%2FqXYf0UI4U%2F6HJ8%3D&amp;x-signature-webp=X7zWkb6whSd%2FxEqoOjci6QXGotI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8cb82b7c455e4e0fa79003e51a3c33c3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=RChXWvKpYojVCStxc9gz6tMxPAA%3D&amp;x-signature-webp=xJVfxAIfSGK3RpTSskXwjQUS460%3D</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7827b65da87f4d20bb532e1ea377e388.jpeg</t>
+          <t>Lib\hardware\data\images\06ce1a717cbd49dc8a8eae1a413bfe59.jpeg</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a30-defender-messenger-bag-14-16-inch-laptop-bag-business-briefcase-office-bag-for-macbook-beg-silang-lelaki-1732460964531569809?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a30-defender-messenger-bag-14-16-inch-laptop-bag-business-briefcase-office-bag-for-macbook-beg-silang-lelaki-1732460964531569809?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5285,17 +5285,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/697f15b91d5a4320a3484f2b65beb688~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Jmt9O8UlK%2FeAXtjY%2FCV2wHdOSOM%3D&amp;x-signature-webp=RYhdL2DW4PucPADa%2BfgEtO7jiAQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/697f15b91d5a4320a3484f2b65beb688~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=sNOuYrMKMtZB7FWuIivYUCrxaao%3D&amp;x-signature-webp=q7rIr9G%2FN2IOt9vIwwJ9hGb41HQ%3D</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4a46c6a13b8e414ebc33141d1471876a.jpeg</t>
+          <t>Lib\hardware\data\images\42122184fe884b4fbe1e23584b350e1a.jpeg</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-t71-premium-laptop-backpack-urban-fashion-bag-15-6-17-3-inch-macbook-bag-office-laptop-bag-beg-lelaki-1732140544120292497?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-t71-premium-laptop-backpack-urban-fashion-bag-15-6-17-3-inch-macbook-bag-office-laptop-bag-beg-lelaki-1732140544120292497?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e73d1e41c3be4c94b13dca55172a7763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=crH0CEbKGP%2FyiHJg2FDZW%2BQNklk%3D&amp;x-signature-webp=pC1oesJk1BJBVnckGPwl%2BKZVBKE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e73d1e41c3be4c94b13dca55172a7763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=aBvRnHhVSEJILrKh4kax3s2AJvc%3D&amp;x-signature-webp=VLsBc3gl9wZ%2Fig0kedKt%2BzEzHtk%3D</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1362cf78bb5244e098b9615d25a981ec.jpeg</t>
+          <t>Lib\hardware\data\images\e96a5001a0bc464eb586cb2b4823bacd.jpeg</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a33-navigator-messenger-bag-14-16-inch-laptop-bag-men-business-briefcase-office-bag-beg-silang-lelaki-1732460907579016337?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a33-navigator-messenger-bag-14-16-inch-laptop-bag-men-business-briefcase-office-bag-beg-silang-lelaki-1732460907579016337?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5389,17 +5389,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2860a24a9e3b43bc827afade643aa71a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=yofHWheBuFzFL2YxoRGPby3hKiw%3D&amp;x-signature-webp=MpLrjmYy82fi9KVDssMGtxETHIM%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2860a24a9e3b43bc827afade643aa71a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=RSwkGsOpaYyH1bLwsB8XwwtF3aQ%3D&amp;x-signature-webp=bbnk%2BuBYTg3wI3dstp%2B6x9TzcNE%3D</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\86790c4c9d334b3eba34f58df402c18f.jpeg</t>
+          <t>Lib\hardware\data\images\9b0803cd4d8c4185ac4e72f37b3400ad.jpeg</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/goojodoq/goojodoq-gm0001-office-use-usb-wired-mouse-for-pc-laptop-tablet-w-led-1731786143330567436?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/goojodoq/goojodoq-gm0001-office-use-usb-wired-mouse-for-pc-laptop-tablet-w-led-1731786143330567436?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6d81861615c94e9d9a2c35ef160645a6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=h%2B%2BtjXtF5sCjKw70yxs%2F42Q9HZY%3D&amp;x-signature-webp=HfXgovEjJLD7GuaAvz8931Bkp6I%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6d81861615c94e9d9a2c35ef160645a6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=8u33NUJBVx8UWFDUa8tpUpMC4Os%3D&amp;x-signature-webp=ae1TtNb6nje8s3G75lsElbyFo78%3D</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ed92e5ecd45949c1bbe37f22a83ae2c1.jpeg</t>
+          <t>Lib\hardware\data\images\460b3442abc64809b8615f216424ffec.jpeg</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-office-automation/deli-office-vusign-folding-table-meja-belajar-laptop-lipat-warna-warni-dengan-cup-holder-dan-phone-tab-holder-vs860-computer-1729434977497286678?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D18379622</t>
+          <t>https://www.tokopedia.com/deli-office-automation/deli-office-vusign-folding-table-meja-belajar-laptop-lipat-warna-warni-dengan-cup-holder-dan-phone-tab-holder-vs860-computer-1729434977497286678?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch%26whid%3D18379622</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -5493,17 +5493,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2a42027251e44e9ca4d6b1aa02296fd0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=2a9FbwHWDpM9Ddlr5OoHkhhNe6Q%3D&amp;x-signature-webp=AjiRuPm%2BX6OLWqJ78cpIuQppJaQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2a42027251e44e9ca4d6b1aa02296fd0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=V66EoWfyXTZcpnI5%2B6U6NkOB1GE%3D&amp;x-signature-webp=qg37ltC5PUsPrVkP0dxaNygd2zU%3D</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1e1e21e1999e432ead80acb64e4b8fcf.jpeg</t>
+          <t>Lib\hardware\data\images\5d4fb01964c947fcb7f5f6023b7c0cb5.jpeg</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/royalltech/lenovo-ideapad-5-2in1-14-touch-amd-ryzen-ai-7-350-16gb-1tb-w11-office-14-0fhd-ips-laptop-2in1-touch-screen-notebook-1733282836276479479?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/royalltech/lenovo-ideapad-5-2in1-14-touch-amd-ryzen-ai-7-350-16gb-1tb-w11-office-14-0fhd-ips-laptop-2in1-touch-screen-notebook-1733282836276479479?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -5542,17 +5542,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c9d8b76508d243b68d6b5ad417ae9f60~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=1Sgc0YBEYKw71zYi55YTe08I%2BG4%3D&amp;x-signature-webp=ZAUWPM%2BkXjcypdJoxipNCUdB%2Brc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c9d8b76508d243b68d6b5ad417ae9f60~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997977&amp;x-signature=WkmsOHTwOHrI2SJ%2BcKlpZL%2BP2Pc%3D&amp;x-signature-webp=fIM%2FiIX8dzB68kIRYgyR4dujWTc%3D</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6708e345681d48e09af4af8a79e140ec.jpeg</t>
+          <t>Lib\hardware\data\images\4ffa89c56a2b4e87a85ae1cc9e09a257.jpeg</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deliindonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-1729461164801230362?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D18553129</t>
+          <t>https://www.tokopedia.com/deliindonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-1729461164801230362?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251124142616EDDEA82AD2755B2B4C51%26src%3Dsearch%26whid%3D18553129</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5563,11 +5563,11 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>459067759</v>
+        <v>459067732</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sticker - Stiker Logo C Sharp Programming Language untuk PC Laptop HP</t>
+          <t>Sticker - Stiker Logo Go Golang Programming Language untuk PC Laptop</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -5577,7 +5577,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5591,17 +5591,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_d335da00-22f5-4912-8bef-32b3775be378.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=UPvNYRBJGlJFA4o13LXUV0rkdMc%3D&amp;x-signature-webp=4W4sBwGIAW%2B5hyoY56cNs19vHKg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_fb1a930f-e114-4bd2-8224-e722de4ed1ac.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=SRPyj744hxgMKm84g%2FCvuRh3MWI%3D&amp;x-signature-webp=HvA2qrZe%2B01yCdoZV%2Bvb7W91OSs%3D</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\395d86feb9d54045bb2907733204a2ae.jpeg</t>
+          <t>Lib\hardware\data\images\379c44920be844a08bea93168142b79a.jpeg</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-sharp-programming-language-untuk-pc-laptop-hp?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-go-golang-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5612,11 +5612,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>459067732</v>
+        <v>459067759</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sticker - Stiker Logo Go Golang Programming Language untuk PC Laptop</t>
+          <t>Sticker - Stiker Logo C Sharp Programming Language untuk PC Laptop HP</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -5626,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5640,17 +5640,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_fb1a930f-e114-4bd2-8224-e722de4ed1ac.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=AeAhOs%2BWPD4%2FEtplfBUlH20gk7c%3D&amp;x-signature-webp=q0gRXdhZOH%2BhXzgm7jmabpq1dkU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_d335da00-22f5-4912-8bef-32b3775be378.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=lP3YkLoEVvuf%2FxxMpbGPDrKAQoA%3D&amp;x-signature-webp=68s874dWMi1Zu2vIS%2BpC0JGIHlM%3D</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\25b9d50545234227a039d5d7d8b98b33.jpeg</t>
+          <t>Lib\hardware\data\images\16b2e672f5894a2e838e1d5c877ebd86.jpeg</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-go-golang-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-sharp-programming-language-untuk-pc-laptop-hp?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -5689,17 +5689,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_57fb509a-be23-471e-989e-1f4d6e8d6456.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=18iSyefE7FFcwvuOBFslnCofdVc%3D&amp;x-signature-webp=Dvwd8Ta3BJz8HQKzP95Cj81pb9M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_57fb509a-be23-471e-989e-1f4d6e8d6456.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=qP5m9ddCAmryvmw54DFLNSokhQ0%3D&amp;x-signature-webp=WmrAveBWzhGlibIYTiqurmXccdw%3D</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8b4ac423caef479ba66d50627f7115be.jpeg</t>
+          <t>Lib\hardware\data\images\8760593c44f745a7a1964b36fa9263f5.jpeg</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0cdf5c85ae0a40a69404e6a02408149c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=W%2F0AyOO%2Fuv1o9LHMwGRD9fy%2FvFk%3D&amp;x-signature-webp=9dcFKAqXDkeiWVM4nQt0IM82SmI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0cdf5c85ae0a40a69404e6a02408149c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=PNjMEHVCJB4aP9sEn8bFOAlRP58%3D&amp;x-signature-webp=q95PdY6UUqut1%2FNIXJ%2FMOTpUqWA%3D</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\95695fb95d694933a85b4ce6a1c90657.jpeg</t>
+          <t>Lib\hardware\data\images\66468cd871af45bb99850a736b0469f1.jpeg</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/inlinefoursticker/sticker-pack-premium-it-stiker-program-teknologi-tema-coding-programming-coder-programmer-waterproof-tumblr-laptop-case-hp-koper-helm-sepeda-motor-1729660102472074470?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/inlinefoursticker/sticker-pack-premium-it-stiker-program-teknologi-tema-coding-programming-coder-programmer-waterproof-tumblr-laptop-case-hp-koper-helm-sepeda-motor-1729660102472074470?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5790,17 +5790,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/2/a80e659e-9b9a-4c2a-b57a-50ed8cf2ff65.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=U4DjbOjaneTW3SR17YVaKOE67d0%3D&amp;x-signature-webp=GePlHRM5gPZIXJ%2FXe9okv2Ifah8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/2/a80e659e-9b9a-4c2a-b57a-50ed8cf2ff65.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=YWzz%2BbGiACTkL3ScG8fHDfHOJNw%3D&amp;x-signature-webp=uKJZNzNVxiI%2B93LS8NF6mDX0Ntw%3D</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cf685ab9666448218bce592e7923592b.png</t>
+          <t>Lib\hardware\data\images\30d823614d034a7481dab3907d440ba0.png</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/yeagerart/sticker-pack-programming-coding-sticker-koper-sticker-tumbler-sticker-laptop-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/yeagerart/sticker-pack-programming-coding-sticker-koper-sticker-tumbler-sticker-laptop-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -5839,17 +5839,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/21/3f892503-b128-4c98-81cb-00fb5661f466.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=E0Hd%2Fuk3ursNOpdCyXPz%2B%2FMWEFE%3D&amp;x-signature-webp=g0t97K0LE5Hu%2F0m21%2Bd9Qy4EIrA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/21/3f892503-b128-4c98-81cb-00fb5661f466.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=qDlLk7T2fVuBgYrhbiuNZ9MmgD0%3D&amp;x-signature-webp=3aKpGgWqVkyPGlk66iIb0w5PkBU%3D</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\96f726e5521546528ef73a0d7ab6b09f.jpeg</t>
+          <t>Lib\hardware\data\images\a735c49fa4304ab49ece3a2fc440b2d0.jpeg</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerplus/sticker-programming-2-sticker-laptop-sticker-pack-stiker-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerplus/sticker-programming-2-sticker-laptop-sticker-pack-stiker-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -5888,17 +5888,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_1e2c0c59-fda9-45b4-ae3a-ff69cf747612.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=3lU4k50SiWQoQ6hWxKT8sUxvw2I%3D&amp;x-signature-webp=ZQD2rG2XojNCvJ%2BSTbJqa6pMR9w%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_1e2c0c59-fda9-45b4-ae3a-ff69cf747612.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=bo3eNqXDHj871ue57QNbJaGJa1E%3D&amp;x-signature-webp=j1Xy5UUH7iZszh%2Bqt27OuzhFhsU%3D</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\682e09f76d1a46e79cb7f61c16406529.jpeg</t>
+          <t>Lib\hardware\data\images\d691fca99da94ec9b43d74ddff037ba3.jpeg</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-plus-plus-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-plus-plus-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_e96fd7ec-b826-46fb-9e12-bf86a0adc00a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=PVyfP%2BdYyAboT4OyRHQnibItZGs%3D&amp;x-signature-webp=JCRCfmx38jdTLCHmqIbNTNPRWjw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_e96fd7ec-b826-46fb-9e12-bf86a0adc00a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=8i7iUmQM1qcBVw5vBhae92LYsq0%3D&amp;x-signature-webp=MniWzZNPMvx%2Frb7%2BlFgpjQ1Nq6c%3D</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f5a6feaa0c6f4a5c90aec7e3cc2ed44a.jpeg</t>
+          <t>Lib\hardware\data\images\122e59a9b3c24c3e942335bdd7516530.jpeg</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-r-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-r-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -5958,11 +5958,11 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>15035337971</v>
+        <v>15190731793</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bootstrap - Sticker Laptop Programming Vinyl Waterproof</t>
+          <t>Cutting Sticker IT Programming Programmer Coding Stiker Laptop - Vue JS</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -5986,17 +5986,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/77ae15f3-c056-41f7-94f4-c008303a79f3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=UMy4Cm0xlOPvfU3pdPWw61PpxFw%3D&amp;x-signature-webp=IacLZEH79jHm5bDVRniw3S2%2FJrA%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/2c485272-3bc8-4c64-a8f0-baf8415b97e1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=R%2FQ8zPCqiUaI%2F%2F%2BAVnH9jMsFiPk%3D&amp;x-signature-webp=YaVPZFGvO3w50ABc8CuWLsCmRlk%3D</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5a5f119846a34551969bd9b9b2c19c5b.png</t>
+          <t>Lib\hardware\data\images\5f08775ed0254bf38a9078c85f9ff65f.png</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/bootstrap-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/cutting-sticker-it-programming-programmer-coding-stiker-laptop-vue-js?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6007,11 +6007,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>15190731793</v>
+        <v>15035337971</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cutting Sticker IT Programming Programmer Coding Stiker Laptop - Vue JS</t>
+          <t>Bootstrap - Sticker Laptop Programming Vinyl Waterproof</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -6035,17 +6035,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/2c485272-3bc8-4c64-a8f0-baf8415b97e1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=Sb7aLIAbz%2FvbtUvEkpNd3nvk6yM%3D&amp;x-signature-webp=fUDt12F9BVdc9UJceajuzZLmtIA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/77ae15f3-c056-41f7-94f4-c008303a79f3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=I3%2F0RvX6l6QqG15jQGzM3xxByIY%3D&amp;x-signature-webp=YzIZxFr3SYt%2FTT%2Bz8MRtbkEeArc%3D</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c8c48e3e3a124b15bbc64407e9099e99.png</t>
+          <t>Lib\hardware\data\images\a74cce55918f4cc2befb690d64e7f9ef.png</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/cutting-sticker-it-programming-programmer-coding-stiker-laptop-vue-js?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/bootstrap-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6084,17 +6084,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/674d0478-bc6d-4c09-b6b9-88af31fea1d1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=c7dBDE9EiL0hwel%2FM1ql8Z33cmw%3D&amp;x-signature-webp=k9SW%2F1MMcqsDyfKsGtQYG07ne4I%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/674d0478-bc6d-4c09-b6b9-88af31fea1d1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=E%2FR0dlJPG8ZKZYlDMxeK8YWsmyM%3D&amp;x-signature-webp=DrQPGDdiBEYtPzKGZpflKP66vwk%3D</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1f7b6162cd8c465a9e887ea8036afc27.png</t>
+          <t>Lib\hardware\data\images\6f197f0b1e8f4188aa739deeaaff7b6b.png</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/linux-mint-cutting-sticker-it-programming-stiker-satuan-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/linux-mint-cutting-sticker-it-programming-stiker-satuan-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6133,17 +6133,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/22/d6a5263e-e87f-4f56-b43e-3b9544f68e28.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=MWS1qP7cd9TvCQrr%2FzhagBiRGDY%3D&amp;x-signature-webp=8iXhSpYO3MoiTuXTozfeuT44VwI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/22/d6a5263e-e87f-4f56-b43e-3b9544f68e28.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=AtDD1sM5dRxNm94sxjbe5oL5E3Y%3D&amp;x-signature-webp=L5AKQ1so0g2M6AjIKdgu8CmbnoE%3D</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\49e71e0f4e1740ae9bd0b136e13a09d4.png</t>
+          <t>Lib\hardware\data\images\59da7659e4944adfba3e8c367b5698a7.png</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-stiker-tumbler-laptop-stiker-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-stiker-tumbler-laptop-stiker-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6182,17 +6182,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/356b601d-1120-43ac-bc8d-f91265fff9b2.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=XWTL7wVFDBlQPRbYdz2MKWJxR9Q%3D&amp;x-signature-webp=jg%2FKfE5TcD%2B4rQVfUeu68%2B1a1HY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/356b601d-1120-43ac-bc8d-f91265fff9b2.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=P8ha%2BkLaLXq58jXxhn%2FqfccJdHc%3D&amp;x-signature-webp=pRJ6guBOowdES2cV2kxs4cJeQyY%3D</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a4ed2058d19e4de2ab19447627ebdeb8.png</t>
+          <t>Lib\hardware\data\images\5f8a2d97841f48499be396fb54f49af6.png</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/java-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/java-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6231,17 +6231,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/28/82978a46-7432-4e38-9f63-c39dee0f3ba4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=YR1slLCZ4jJ1CrrIyqg10UwMDvw%3D&amp;x-signature-webp=RIfj1n1zbvgQqnajTBZLPqD3Kv0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/28/82978a46-7432-4e38-9f63-c39dee0f3ba4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=zz5Frc1szenb6g4OjVW0Rv7Iqyo%3D&amp;x-signature-webp=erQk5%2BM%2BeY1vW52WF8Wjp82uu2c%3D</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c56f7a3072334defa123e4c620be3849.png</t>
+          <t>Lib\hardware\data\images\be8cac5696764cd2b8c8de2ffab065b1.png</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6252,11 +6252,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>15608613564</v>
+        <v>15614737477</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IntelliJ Idea - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>Spring Boot - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -6266,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6280,17 +6280,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/3b45f322-32f5-4b0c-858f-59219a51c153.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=KQcz6dpHoxoBop3BnFK%2BquEwVHQ%3D&amp;x-signature-webp=xXRZOXrUmYJWY%2B8Du1dlQFuktwE%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/148d053d-e670-4ddd-bd5b-c5489f84c28f.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=KUBBJIfjxtntDLcwsD5Xp0nXwf4%3D&amp;x-signature-webp=D1kmVe5oJq8pLt%2B7h%2B7f2OlxPxs%3D</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d32f2dde20f544aeab74c31d72dd9c3a.png</t>
+          <t>Lib\hardware\data\images\1fdda03e6ec24f6a91a00a7f1f4e5380.png</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/intellij-idea-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/spring-boot-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6301,11 +6301,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>15614737477</v>
+        <v>15608613564</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Spring Boot - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>IntelliJ Idea - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -6315,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6329,17 +6329,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/148d053d-e670-4ddd-bd5b-c5489f84c28f.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=GKk2eUxqn9MkEjO2UU4DO%2BHj1EM%3D&amp;x-signature-webp=03Ih%2F6HlH3RauyGBevoeoFGlMjY%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/3b45f322-32f5-4b0c-858f-59219a51c153.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=SecreFR38MvY3dBIdCOuA1nV6JQ%3D&amp;x-signature-webp=gbOysv6AKw3I7AYhm7XClbf8sqY%3D</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\748467be2e254005b47eb62ff30c6671.png</t>
+          <t>Lib\hardware\data\images\fcb8e203ec274d10b749f12254afaf6a.png</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/spring-boot-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/intellij-idea-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6378,17 +6378,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/bd6bf479-e882-4ed2-a264-28c75b168c29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=JnJxAtqQG1bFHAIMIc7QCcff1PU%3D&amp;x-signature-webp=vmr8Bqx85qDsvNs1ia61kIIzEKg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/bd6bf479-e882-4ed2-a264-28c75b168c29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=%2Fyse8d9LQSlGOGT3bwGiXDOqHrc%3D&amp;x-signature-webp=5EvaT1VvQ64YBDpA8Q0mW4mYq1U%3D</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3a31217a0600452d9d65d674cce3fcbc.png</t>
+          <t>Lib\hardware\data\images\a35424397e764d73a21a2d7656e14fa0.png</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/css-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/css-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -6399,11 +6399,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>15029253978</v>
+        <v>15614711766</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Meta - Sticker Laptop Programming Vinyl Waterproof</t>
+          <t>PHP - Cutting Sticker IT Programming Stiker Programmer Coding Laptop</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6427,17 +6427,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/722bc896-e581-4919-9192-737948477d10.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=t2kqHwouH2O7pzO8PrjBsyPVaR8%3D&amp;x-signature-webp=oLZFBT4uOdoOWJShKQhXwroUGug%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/32a21bef-6229-4a57-8094-a707c4210ac4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=gplaQ6Cqbrwuf3FcsXDsS1crFV0%3D&amp;x-signature-webp=cR47IrMDDffgYFx83rVDV3uMHCI%3D</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\56f65d5e8d2f4d81bd709efed8760a01.png</t>
+          <t>Lib\hardware\data\images\3c69b89371104e00bbb3b2ae5dd7dc80.png</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/meta-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/php-cutting-sticker-it-programming-stiker-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -6448,11 +6448,11 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>15614711766</v>
+        <v>15029253978</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PHP - Cutting Sticker IT Programming Stiker Programmer Coding Laptop</t>
+          <t>Meta - Sticker Laptop Programming Vinyl Waterproof</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -6462,7 +6462,7 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6476,17 +6476,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/32a21bef-6229-4a57-8094-a707c4210ac4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=vR6w9%2F%2BxaWoS0h8q%2BFGgHmrnpM8%3D&amp;x-signature-webp=gxWOwgBgNRSFwKeqG4EZQPvFgPk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/722bc896-e581-4919-9192-737948477d10.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=94q7pDn3UQ4RzbYL402pWyRjtoQ%3D&amp;x-signature-webp=zLCuAiyByJ8N8cTnNZiWNz1YuRM%3D</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dfee2a3211c54e97b904f9574c846fea.png</t>
+          <t>Lib\hardware\data\images\9c574538f35f49059246a3d167d5fcfe.png</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/php-cutting-sticker-it-programming-stiker-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/meta-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/247f6d04-d1b7-4b0a-b69d-44df83a98403.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=jqFXDKygtnZSXiWxCqGgpoCu9JE%3D&amp;x-signature-webp=4oi7w%2BKLw2ejRUHXU9nUOZwrdI0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/247f6d04-d1b7-4b0a-b69d-44df83a98403.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=5pfbD3Em0HPHqbnbnc6uAuWizVU%3D&amp;x-signature-webp=1Uk7iPVgDku4Lpp%2FhjkMd5hnNMA%3D</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c66341e0599f49918fde5e6ae05b045d.png</t>
+          <t>Lib\hardware\data\images\e5dbf9341f4a4338bd113de6be235585.png</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/ubuntu-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/ubuntu-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -6574,17 +6574,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/fd492c8b-c24d-42f6-9532-4ec429fe91c5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=DJi9JyM1yGy%2FFc3THok06fCpwIk%3D&amp;x-signature-webp=igaL4Y5wEpWZxm34wlHa8E7aJ6M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/fd492c8b-c24d-42f6-9532-4ec429fe91c5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=o84GXLLMwZGrb7TIKMkl2HLv5y8%3D&amp;x-signature-webp=D15zDHsH6RvM57mDwmUmh%2FOwnCY%3D</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2e26e14ca84443c08a337a16f30561ea.png</t>
+          <t>Lib\hardware\data\images\415dbb5fcb3f4161b50e487727c09434.png</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/kali-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/kali-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -6626,17 +6626,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e016ed68c334c7cbc4f8e994d90718b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=zOeB%2Btz27dJfVueSihnBW7PPOwQ%3D&amp;x-signature-webp=y9f55FiDh2bRy1rbJw0EQS3lsTY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e016ed68c334c7cbc4f8e994d90718b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=nCIC%2FFDlbxLKxRY2%2BqJhHBT1YxI%3D&amp;x-signature-webp=awJ1%2FRql3FMUSiZa4Ielr0ZPPcs%3D</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\44b7259ad0d94baf9184cf5fc266ba40.jpeg</t>
+          <t>Lib\hardware\data\images\9c82be9d67ea4ca692808c78a47b78a7.jpeg</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/indoluxdigiprint/programmer-sticker-pack-50-pcs-stiker-code-komputer-anti-air-sticker-coding-computer-it-programming-laptop-hp-paper-1729751165829088355?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/indoluxdigiprint/programmer-sticker-pack-50-pcs-stiker-code-komputer-anti-air-sticker-coding-computer-it-programming-laptop-hp-paper-1729751165829088355?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -6675,17 +6675,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/6dc31a5b-13dc-461c-affd-cb836b3d7649.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=hZ%2F2qCshaDOVnhnpMpWrUOVnF%2B4%3D&amp;x-signature-webp=YoUFuKjGoZQI0TX55BebTOGCFz8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/6dc31a5b-13dc-461c-affd-cb836b3d7649.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=o9H3UUEifLQ1urwD7D%2FXjvB%2BpLM%3D&amp;x-signature-webp=2MKqRVc0gR26K1S2y359yT2rTKw%3D</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8d11d91894f748e19c70711147963af7.png</t>
+          <t>Lib\hardware\data\images\af246473395f46edab92a4905dec0499.png</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/html-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/html-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -6724,17 +6724,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9e56cad1-941e-4da1-b48a-271cbe36ab77.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=8waJ7VeeaQEmkJUsZL1RrvhW508%3D&amp;x-signature-webp=YfGubPqxHrTKvy4SRFjn%2FoUvBPw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9e56cad1-941e-4da1-b48a-271cbe36ab77.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=YdT5YcBurybz%2BdaO9uQeDD7zDZw%3D&amp;x-signature-webp=4HWct1ITnHiMfVu5mx7Cl1t38CE%3D</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7ade71aca3134ec08760a5c3998457f1.png</t>
+          <t>Lib\hardware\data\images\34282f33e54c4d7f84a19fbc383f3971.png</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/debian-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/debian-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -6773,17 +6773,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a26ba20e-d4b0-45e2-8d41-247e37e6a478.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=LZE%2B8dS5C6eImLlURH6kQc4QKNo%3D&amp;x-signature-webp=JF8UTmLlAp4gTRo54uUgivpVR6Y%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a26ba20e-d4b0-45e2-8d41-247e37e6a478.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=a1Wcla0zL6ejXKxIvJL2%2FdWCgxA%3D&amp;x-signature-webp=P4t%2FL%2BzhvqLP5eeApRfLAJ2TifQ%3D</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a5c79d0d9f98469cbe9a8c679f23053b.png</t>
+          <t>Lib\hardware\data\images\5f6701d3e53c432187e78b371ce3ce8e.png</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/cpanel-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/cpanel-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -6822,17 +6822,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4aa5f4f-ae42-4541-81f3-1421c0a92ee8.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=D%2Fb2CUdoxM5gw6jrw4Vch5kEtwM%3D&amp;x-signature-webp=QNFgu0Cg3nPQOKhPd6bFmvCQbvc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4aa5f4f-ae42-4541-81f3-1421c0a92ee8.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=Aywlws%2BbNIgnVaFPKHI0v5yP4H4%3D&amp;x-signature-webp=qfDTp10Z2TjE4Ky3rVPpoShU%2Bl0%3D</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e440ef669ad44185b5f0ea455b276648.png</t>
+          <t>Lib\hardware\data\images\507dc4a8914543f4a9b5ec30ceb7a569.png</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/js-javascript-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/js-javascript-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9441c648-abf5-4189-bda6-523c5625881e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=6SAEIPnTmgF3o9LBDRhsJwwHi6s%3D&amp;x-signature-webp=vxi9AkkeaFBt2Poy2pP%2Bk8WydPE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9441c648-abf5-4189-bda6-523c5625881e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=8VMJRFPXsTRIuYZJd26SgJt0W84%3D&amp;x-signature-webp=yLterYEj2A9%2B0JpnFrjRbdOT7%2Bs%3D</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b96f85b33da24d63a6b2f6c938c73fb9.png</t>
+          <t>Lib\hardware\data\images\d759aa2f214b468d88626787027d66ff.png</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/jetbrains-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/jetbrains-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -6920,17 +6920,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/487fec30-5abd-485d-90e1-97aa59e4dc8e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=61lDn8JAE9aJQY4XWmYWfon%2FIgM%3D&amp;x-signature-webp=7nRlJqF%2FMcrmv2jfuiUiupB8trc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/487fec30-5abd-485d-90e1-97aa59e4dc8e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=z9E5HlCXoKQyaOGkW8x87AMH2Yw%3D&amp;x-signature-webp=1jp%2BCf3xuzzhL03TSGeCT6Qb9HQ%3D</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cb7c822bc4314233991ba82f8e86215a.png</t>
+          <t>Lib\hardware\data\images\c66101029750467ea6c329e7a4a87d6b.png</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/android-developer-cutting-sticker-it-programming-coding-programmer-laptop-1730925852202665522?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/android-developer-cutting-sticker-it-programming-coding-programmer-laptop-1730925852202665522?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -6969,17 +6969,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/52e270bf-8f13-4743-989a-135d563c7c13.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=Vf38crBS7My%2BfMk1UCvCjxk4Q6o%3D&amp;x-signature-webp=ovjUJriV%2BtMPhlq7DtMMq5GKbl0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/52e270bf-8f13-4743-989a-135d563c7c13.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=Pwmt%2B4L2j%2BUjO6lpLkP5aFhtt%2BQ%3D&amp;x-signature-webp=GMjd7w%2BWahMuYTCJKNifH%2F97ACg%3D</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9adc5f69d85b4b76bd37cb0bb2135ce7.png</t>
+          <t>Lib\hardware\data\images\1aca647e1f814c1cb34275b42e4a2dfc.png</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/c-plus-plus-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/c-plus-plus-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -7018,17 +7018,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4f53049-4d44-4b49-ae9e-b4a06d7aa864.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=WrTuLfC3REe2HbSil7oImLnW%2B6o%3D&amp;x-signature-webp=ogxi7nihXIoK0mxBQfxTE8RGhhE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4f53049-4d44-4b49-ae9e-b4a06d7aa864.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=ZD0j8XlkiMjcssOILsqXI04Nh7M%3D&amp;x-signature-webp=IVobrc642B9ZkronV%2FHCNa7UUhw%3D</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c3504150c14441cbab3df8e1c13a84b8.png</t>
+          <t>Lib\hardware\data\images\245d6ab421c04a3a8fe46832757cf9c4.png</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/python-language-sticker-laptop-programming-vinyl-waterproof-1730910518060090930?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/python-language-sticker-laptop-programming-vinyl-waterproof-1730910518060090930?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -7067,17 +7067,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/5e031a76-a3f2-4fc1-940b-4150386d8618.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=W8lBp8jE92DacisOq0YKl1aQxc0%3D&amp;x-signature-webp=g9yskzOP02dEf4QGIje0Y0YqiDk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/5e031a76-a3f2-4fc1-940b-4150386d8618.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=y%2BgglMzkZxzwIU383POmp0cfCzw%3D&amp;x-signature-webp=WZtYkgkHPfah6YJq8SCW0YheaIk%3D</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\14b2c5d1ef534d21b1e265fa1a894211.png</t>
+          <t>Lib\hardware\data\images\801de78ae20a4d818993f6117baf0061.png</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/tux-linux-penguin-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/tux-linux-penguin-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -7116,17 +7116,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9f70aa88-0b3e-4f1a-b1e2-ff8c1f724f83.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=bKwDaz%2BlKzXlAbHM%2FkBui0p8BEE%3D&amp;x-signature-webp=IvLCpEqGOvMT9ZBK5QiwgjZ4s5U%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9f70aa88-0b3e-4f1a-b1e2-ff8c1f724f83.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=U0Yw9FPsn7Mr1Rob5RI786qPuik%3D&amp;x-signature-webp=HysHBDnsppR7qz4YmSss6F%2FELwo%3D</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b840de28ee6844f68ae823c54458fd43.png</t>
+          <t>Lib\hardware\data\images\9ccd91f5faec4842872e6bff4acabe83.png</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/google-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/google-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -7165,17 +7165,17 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/05097cce-f0d3-41a1-9a3e-dc787f21a1bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=mBF2lO0JqC3T38lZRJ5fgaCVjkg%3D&amp;x-signature-webp=ulb5D6Ze4B20JJKVuMhCiQCsztk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/05097cce-f0d3-41a1-9a3e-dc787f21a1bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=L%2BYZyBQTf%2Bugj3oAiOnSOqvnqDA%3D&amp;x-signature-webp=kgiS3NvMubCmftF9lGmFUoINQkg%3D</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\19758cd4135547c0b28436997d75dddb.png</t>
+          <t>Lib\hardware\data\images\49b7f0fe6dbf45bcbc08f1991aa0356f.png</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/arch-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan-1730778695673939506?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/arch-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan-1730778695673939506?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -7214,17 +7214,17 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/d2e910e6-71e1-493a-9ad0-7e644045fa68.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=lAX52r8fo6aCpzSY0tFXNdH%2B5q8%3D&amp;x-signature-webp=hkKwprYz7onrmq2FYwa0vIM07cI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/d2e910e6-71e1-493a-9ad0-7e644045fa68.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=fW%2BWCc6ZNt6sDlno1eQdd1vutgs%3D&amp;x-signature-webp=9xCfbIiy1BPgI5A8RiNqABz01Ek%3D</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\568089f26a7342baa4201f979e265969.png</t>
+          <t>Lib\hardware\data\images\8d3ae036a1e64739b2169f783bfbe54e.png</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/fedora-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/fedora-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -7263,17 +7263,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/9/29/f8d3eab6-1d0d-4a33-8e74-ee48be7014e1.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=KeK%2FnSwFCUaGkBxdZnhmWiklYsQ%3D&amp;x-signature-webp=RWa5xuuEWSK6B0gZ1a5F%2BiCS9tA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/9/29/f8d3eab6-1d0d-4a33-8e74-ee48be7014e1.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=YDUFQn%2FRqpxEeAVQ8y25Zd%2BdO9c%3D&amp;x-signature-webp=Zl1Us9AAs6gspu2Lfhc%2FbcDNorU%3D</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4dcb32ad34a040fe986fca13d2edb51a.jpeg</t>
+          <t>Lib\hardware\data\images\91195bcf00ce4399b95cfa3a0d7f33dd.jpeg</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/archive-zhanghua-1630738705/stiker-programming-java-php-linux-bitcoin-ubuntu-geek-untuk-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/archive-zhanghua-1630738705/stiker-programming-java-php-linux-bitcoin-ubuntu-geek-untuk-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -7312,17 +7312,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/d7dbbf07-cde0-4b81-a809-7c268bac8704.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=x4NcaVcmTol6p9dQ7q5D8u1s27g%3D&amp;x-signature-webp=B8YjGLLWBmWX5aOJ10l%2B4SaC%2Bwk%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/d7dbbf07-cde0-4b81-a809-7c268bac8704.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=wWsnwllNMshXdFrKPHRtP6HHxo8%3D&amp;x-signature-webp=PvP%2B6PggasEBsB6scPHhV7Oh%2BU4%3D</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\de21e7a2f1b041a38af5628eeb7be66d.jpeg</t>
+          <t>Lib\hardware\data\images\b72476c599b2442286a77d585d1153e1.jpeg</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/coffee-sleep-coding-game-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/coffee-sleep-coding-game-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/3c9c2511-b651-4389-846a-da1c078d510d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=PFmz%2FkwBuYCpX6a7HrunCAymktE%3D&amp;x-signature-webp=ayzyjgBRitvZS911layvXp%2BrKgk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/3c9c2511-b651-4389-846a-da1c078d510d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=JNNvN7wZZ9yxLEUYxitgYrLl22w%3D&amp;x-signature-webp=2AY9lyAj0JlcBNyJgoo%2BpVW65L0%3D</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\90e3d63bef0644eab3fd20b9ee607aa5.png</t>
+          <t>Lib\hardware\data\images\dd70d1396f0f494ab46a6f0f88d9996b.png</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/sticker-sheet-a6-vinyl-waterproof-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/sticker-sheet-a6-vinyl-waterproof-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -7410,17 +7410,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/c6cbe66b-30fb-4b15-9a7b-cdba7bdb6344.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=SMQPHQK7xd1oCz9hRuM0HWRkBkI%3D&amp;x-signature-webp=4YMlUQhjYhsVQGebY7uypCWZCaU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/c6cbe66b-30fb-4b15-9a7b-cdba7bdb6344.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=bvnuJTNa%2Fh36Mj9KGn7BuFveFbs%3D&amp;x-signature-webp=z1pVCFR9eCHmvvXkLCIkAF2gJ%2B8%3D</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f691f479daee4f0e9261d313ef89be4e.png</t>
+          <t>Lib\hardware\data\images\85924979ad544822b1db9f1d882369d9.png</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/full-stack-developer-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/full-stack-developer-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -7462,17 +7462,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e83fe7fc87c4ce6ad067de5078f19f5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=HySjm2Dw45rs6KJVT2VtCGKdOHY%3D&amp;x-signature-webp=2gez%2BPdI67l%2FYpt30tp0DTXoUwc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e83fe7fc87c4ce6ad067de5078f19f5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=x931%2BhdX31i1krNuN8Pa8PH96OM%3D&amp;x-signature-webp=Qx1zza75YoJwyhZUgEEF04S0Bzg%3D</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c4b217517f0b48bb9ca776931bf5c86c.jpeg</t>
+          <t>Lib\hardware\data\images\dba7234fcdfb4c929133071c7ef6fdd7.jpeg</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-untuk-scrapbook-tumbler-hp-laptop-motor-helm-koper-1730766186130146514?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-untuk-scrapbook-tumbler-hp-laptop-motor-helm-koper-1730766186130146514?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -7514,17 +7514,17 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/364156f76e624431b6c3dc72dd64ecdc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=DPeUUJBOY0MU8HuOoVZmPP%2BVJ%2Fs%3D&amp;x-signature-webp=QIR8ZozEfVYILDJwkuXLLY%2BOTx4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/364156f76e624431b6c3dc72dd64ecdc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=ViTSIwaNIZApNWg2V4h4XyZ5zjY%3D&amp;x-signature-webp=F9XJUYdVSa6XYXUboDVLRr8pNQk%3D</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\25de462eb4a1419da6f6236a90389960.jpeg</t>
+          <t>Lib\hardware\data\images\e53fbe3cb463458d9b02e5e548743a97.jpeg</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-meme-plesetan-untuk-scrapbook-tumbler-hp-laptop-koper-motor-1730770027949688018?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-meme-plesetan-untuk-scrapbook-tumbler-hp-laptop-koper-motor-1730770027949688018?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -7563,17 +7563,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/265be12a-181a-4c2e-85ad-c6544f36203e.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=QyEFn2ZPY6DwJaVTqOVFBy53rq4%3D&amp;x-signature-webp=E2Pe72LSne%2FvebRsLg8kAYj50%2Bs%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/265be12a-181a-4c2e-85ad-c6544f36203e.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=jfUUPon2pXvhyGsoo1LrExAGqyQ%3D&amp;x-signature-webp=2d5suGEnpUrEN%2FxknX%2FXn7c7YdM%3D</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\937b715199564274884e984bb5f812fc.jpeg</t>
+          <t>Lib\hardware\data\images\6403a35351cb4ca4b1ef1b20377be643.jpeg</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/vnylarc/saas-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/vnylarc/saas-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -7612,17 +7612,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/4020a1f4-6c92-4356-8439-3db0af377f5f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=78zT6VkjndBWdHr9kcGeKd7dLL4%3D&amp;x-signature-webp=6GkBroIXMvFTgmNdqpdvDHUiLm0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/4020a1f4-6c92-4356-8439-3db0af377f5f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=d%2FgjlJgSMQO6zw48YvMzp4QHdSU%3D&amp;x-signature-webp=ML4UTFk8fvXXabqb2WVkVxVAsyA%3D</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\051a15b5f160447ab97723931e5a2e1d.jpeg</t>
+          <t>Lib\hardware\data\images\8b3cf0c764884574aace0a40adeff6ed.jpeg</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/vnylarc/golang-icon-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/vnylarc/golang-icon-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -7661,17 +7661,17 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/4/4d205830-0c3f-4681-a668-c1d10845afb5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=W4h%2FdstG5oUt9uJ7KEJTRgRZWaw%3D&amp;x-signature-webp=aj6XoQaqcGBhXaCssDeQhisPC1o%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/4/4d205830-0c3f-4681-a668-c1d10845afb5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=NNlduyAHCGjAho98%2B0x%2BawNOh%2Fg%3D&amp;x-signature-webp=Hmo2F%2B7b5L%2FBCWGY66xr7Vmj7i4%3D</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\76f76c48c4e349089ea2d41c861ece81.jpeg</t>
+          <t>Lib\hardware\data\images\1e2086fc3eb645c59d6ace75b198efaf.jpeg</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokopedia-tokolaris/sticker-pack-20-pcs-teknologi-programming-untuk-laptop-tumblr-helm-first-edition?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokopedia-tokolaris/sticker-pack-20-pcs-teknologi-programming-untuk-laptop-tumblr-helm-first-edition?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -7710,17 +7710,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/0bd6c17c643c4ba8875360f0f7dedf05~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=YS5nJzPeEA0PCjWlDLt5U6R7YRU%3D&amp;x-signature-webp=4NtwapGV0z2rdZZ6DlAbWL7wqO0%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/0bd6c17c643c4ba8875360f0f7dedf05~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=og6GJ00zViLGCYowlonDydglHXk%3D&amp;x-signature-webp=mwKx6d7bkOfckpp1Ed%2FkJpFfFnQ%3D</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b9df8e11400b45178e1901d0a5d9cc9e.jpeg</t>
+          <t>Lib\hardware\data\images\bee38281c4a24214897ad3f7d976f1ca.jpeg</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -7759,17 +7759,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fe66c8e873de4883aa66c310f1cb065a~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=BHVOmtnfuo7RTR0KPd8UPChv3lQ%3D&amp;x-signature-webp=9EEwUemQikwo7IFydIH5RfQWS%2B8%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fe66c8e873de4883aa66c310f1cb065a~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=ow7PWOVmzHboDpDRYKDDsaLLjzk%3D&amp;x-signature-webp=s6BZF5oCKF3V3vof6pzhl3zPVQU%3D</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7361efd0ca064ecaa1738d12cf472efc.jpeg</t>
+          <t>Lib\hardware\data\images\708e1394be4f4154b9d8538a475b1b78.jpeg</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programmer-coding-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programmer-coding-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -7808,17 +7808,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d1f458121310473e8394b993711abd3b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=9bgLMo0cdUyNCryAMtdhfdOTp6k%3D&amp;x-signature-webp=lAb9G8YInimO9vynn9Its2qkayU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d1f458121310473e8394b993711abd3b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=x5ogPBgSjf7o%2F8YQhtquOxxLStc%3D&amp;x-signature-webp=Lyx8yc%2FFto%2BgKIWbNiajSiKAGiQ%3D</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\df34c40844a34f5fad9ce78ee5d65d49.jpeg</t>
+          <t>Lib\hardware\data\images\66337bb8e5ab467ba5d552b5fb41c0a9.jpeg</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/auto-diagnostic-programming-tool-expert-mode-for-icom-next-software-v2023-09-1tb-mini-ssd-windows10-laptop-cf-ax2-8g-d-4-43-1732688398569998202?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/auto-diagnostic-programming-tool-expert-mode-for-icom-next-software-v2023-09-1tb-mini-ssd-windows10-laptop-cf-ax2-8g-d-4-43-1732688398569998202?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -7857,17 +7857,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/10d441e1e3db48d184effed1bc09575b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=bokgYZm1iSyd71w19wsi4j8c0o0%3D&amp;x-signature-webp=hIkudiCY%2FVDJzybkTWvmsvkjgNE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/10d441e1e3db48d184effed1bc09575b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=p83y7VKXv65c6Yw4OIWgqtmbdrc%3D&amp;x-signature-webp=%2BbxZNnNzTYWGFuC%2F%2BLI5SgJyHAg%3D</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c745c4a6106f47d1a8eb8940a724e698.jpeg</t>
+          <t>Lib\hardware\data\images\09418ba2a5604db7bdbaa88e28193d93.jpeg</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/new-for-icom-next-a-b-c-with-v2023-09-software-expert-mode-installed-d630-4g-laptop-for-icom-next-programming-tool-1732688989206054778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/new-for-icom-next-a-b-c-with-v2023-09-software-expert-mode-installed-d630-4g-laptop-for-icom-next-programming-tool-1732688989206054778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -7906,17 +7906,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e5f3a470390d4bcc88c465e59babd2ea~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=dCfw0%2FSUDORzOnHU5dzWAs6PEmA%3D&amp;x-signature-webp=YCF815aGCjGm%2Frztp9ZRCgNqGc0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e5f3a470390d4bcc88c465e59babd2ea~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=G3p5Da473r6GsddPCVWyP2RNfDU%3D&amp;x-signature-webp=DJLCi%2B5%2FKbcqHrWgle0yBaa7SLQ%3D</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6a2aa1a9483c4285bb5b611987300c36.jpeg</t>
+          <t>Lib\hardware\data\images\6b55f646be0d4557b4201f670358ca48.jpeg</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/cfc2-laptop-for-jlr-doip-wifi-car-diagnostic-tool-support-new-car-profesional-auto-programming-tool-1732690386628020090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/cfc2-laptop-for-jlr-doip-wifi-car-diagnostic-tool-support-new-car-profesional-auto-programming-tool-1732690386628020090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -7955,17 +7955,17 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43b554c10baa4e20a7f9e75f23312185~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=SrlPlZ%2BvbDtqchjj33XfCrarGqU%3D&amp;x-signature-webp=VhCcdnS8NJIustGljsNxm6LNzhQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43b554c10baa4e20a7f9e75f23312185~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=5ja6enzFZxwJWpfXnw1s5sVwME4%3D&amp;x-signature-webp=ui5okeKtKhpX6C0Y77xgurh10dQ%3D</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cd73e76b3c0a408996c4ae16b782de6a.jpeg</t>
+          <t>Lib\hardware\data\images\ed18b45e48ed48bd8f7e18aeae7d82d9.jpeg</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/car-diagnostic-tool-for-jlr-doip-v-ci-wifi-with-cf19-laptop-support-new-car-profesional-auto-programming-tool-1732690368491587450?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/car-diagnostic-tool-for-jlr-doip-v-ci-wifi-with-cf19-laptop-support-new-car-profesional-auto-programming-tool-1732690368491587450?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8004,17 +8004,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c27b24e4e8a149f8afdec0aef9a21471~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=SjUkIKzoMfuaiJGtsby5%2Ftqrr18%3D&amp;x-signature-webp=WXmzl7g1rA79Rt2kpDCTJi2N2UE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c27b24e4e8a149f8afdec0aef9a21471~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763997991&amp;x-signature=%2BDLUGaUEHFM%2FtGBya2gCyj3t9w8%3D&amp;x-signature-webp=%2B4Ur7ns29rDDXoEQZI3YkLstSYA%3D</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\47ae3596b2bc4f43a41ef7fd1fd23723.jpeg</t>
+          <t>Lib\hardware\data\images\90ce634fc1374c6db6ef742d04cb9d1f.jpeg</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/for-icom-a2-with-full-cables-professional-for-diagnostic-programming-tool-with-software-720gb-ssd-win10-in-x220t-laptop-1732688342876587898?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/for-icom-a2-with-full-cables-professional-for-diagnostic-programming-tool-with-software-720gb-ssd-win10-in-x220t-laptop-1732688342876587898?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511241426316DA37DD3139AA4254CQ8%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -8056,17 +8056,17 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/0e0094f8-4e21-4aab-b63e-25e6f39a9a2d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=DsuviELMq9mN0O685eDHZtUjdXU%3D&amp;x-signature-webp=VSzrOYji2Oegk6NdrwHhwGXxWaE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/0e0094f8-4e21-4aab-b63e-25e6f39a9a2d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=fLpH8Uesny2BmScoPFCQzduLQ%2F0%3D&amp;x-signature-webp=qn4yfobSFWt1uPYXHqnX734AlXM%3D</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\61ac58e30fea4c599e223329123f350c.jpeg</t>
+          <t>Lib\hardware\data\images\6e22ce2525bc4fa9947243a15d4d4d19.jpeg</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/housesparepart/jakemy-jm-8183-145in1-obeng-set-hp-torx-laptop-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/housesparepart/jakemy-jm-8183-145in1-obeng-set-hp-torx-laptop-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -8105,17 +8105,17 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/18/2e15fe28-10bf-41e9-868d-6cb423cd4c8c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=M4TaZka2R52dlsPdpQuuBl6CdWk%3D&amp;x-signature-webp=KeKozfaaK22X2yVpe5d3pL5DBcg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/18/2e15fe28-10bf-41e9-868d-6cb423cd4c8c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=wv0YKb2KqgjVPv9bFLe2WkXscEg%3D&amp;x-signature-webp=0Ge38rnFU0atNgOEs3XdieKF3Es%3D</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8331a354bbf24b609cc3b4a2115a8dda.jpeg</t>
+          <t>Lib\hardware\data\images\da24bee6106d484dbd7a658e644c3101.jpeg</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/ezren/jakemy-jm-8183-screwdriver-set-hp-torx-laptop-computer-new-design-145in1-1730880897306690560?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/ezren/jakemy-jm-8183-screwdriver-set-hp-torx-laptop-computer-new-design-145in1-1730880897306690560?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -8157,17 +8157,17 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/660a3068-b7f9-418c-8ac3-25c629b1e0c7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2FPzQw7Ziqa%2BeH6Cv361OK6rTKKM%3D&amp;x-signature-webp=GEeMGB5WAPLKajxKBAKQ8%2FouCek%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/660a3068-b7f9-418c-8ac3-25c629b1e0c7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=TAxaXDd6ZLvuj4jIRKFoe7PdU2Q%3D&amp;x-signature-webp=T9L4UbUtMu1TChTGh%2F8c6nQoC0k%3D</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f7099ee1fa5b42ba9112d0a85134a46c.jpeg</t>
+          <t>Lib\hardware\data\images\b0b209c7aa294ab18b904097f79675f6.jpeg</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jakemy-official-store/jakemy-jm-8183-145in1-obeng-set-hp-laptop-macbook-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jakemy-official-store/jakemy-jm-8183-145in1-obeng-set-hp-laptop-macbook-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8209,17 +8209,17 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=j3Q%2F9Pw1Svs%2B28cAfYI13btKX%2BU%3D&amp;x-signature-webp=tjahuipkB2I0RpXyF6DYu2lJbdo%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=tNoB9LDX9mc4bL2LIwgJ5r9dxL0%3D&amp;x-signature-webp=xADxVfIw3JoEVNrU3BqqbsLPQik%3D</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5e8b6796230345f3a2b6036fe9bf4fe8.jpeg</t>
+          <t>Lib\hardware\data\images\af1aa90cee3642cbb02a4bd8c04b1e0d.jpeg</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8258,17 +8258,17 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f261db1a485a484fb269a53c633ed896~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=XVItsvOX0TIcvub4bR18jVMgwAk%3D&amp;x-signature-webp=LhYziQm1F8Aj5bxPlCufiWZNV4c%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f261db1a485a484fb269a53c633ed896~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=mS0o%2FVot1f2Ttuv8pd3OC%2BhFM4Y%3D&amp;x-signature-webp=yCaFjRF0BIrcas7b6R5MA%2BDrnxU%3D</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\323ebd874f1844f3b832449822ecfdd5.jpeg</t>
+          <t>Lib\hardware\data\images\aa54661409b6426380ed57fd4b16a5ab.jpeg</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/bobby-soft-daypack-water-repellant-backpack-by-xd-design-tas-ransel-laptop-original-unisex-black-bfd8e?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/bobby-soft-daypack-water-repellant-backpack-by-xd-design-tas-ransel-laptop-original-unisex-black-bfd8e?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -8307,17 +8307,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/8b7fcd6f-843a-4f43-9ed7-23b395be8bf8.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=GidEWHHKpo1vcWDhI78L%2B2CyYXo%3D&amp;x-signature-webp=xni7WdZxPtPhpr1417dpGyr1r70%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/8b7fcd6f-843a-4f43-9ed7-23b395be8bf8.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=PWZ3eU9RGFGaSLV6VpPRSiwts7Q%3D&amp;x-signature-webp=6EPt%2BdDv3spsr79%2BYU6RFBTeBV0%3D</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\688fe650744048c0b6b91e68480e6bcd.jpeg</t>
+          <t>Lib\hardware\data\images\6e2dee2e0e42432399cc5c56562c3789.jpeg</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-bag-black-1731594664039319238?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-bag-black-1731594664039319238?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -8356,17 +8356,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/32274fe1-96e5-4c4b-b9a1-8a54ed3cd196.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=L%2Bav3h9od2y90hSbFc9vaEKjYuQ%3D&amp;x-signature-webp=zokYByCIt%2Fe9bIQ5T8OFyds97aU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/32274fe1-96e5-4c4b-b9a1-8a54ed3cd196.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=DKxLSwb2WM8k8wpfc%2FPryezUQno%3D&amp;x-signature-webp=CkY%2FlOcy2477EE1CJOJ6LFB0hl0%3D</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\90528e9d11f9451ea46e571a0ec4a8d5.jpeg</t>
+          <t>Lib\hardware\data\images\6bf79fbfefc649c68a449ec82e018683.jpeg</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-sleeve-1731594608912926406?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-sleeve-1731594608912926406?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/20/d1423af4-f39b-45ce-a5e1-4e98654a57a9.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=nH3SPrTYcUEZpoWvzUtkelyWsis%3D&amp;x-signature-webp=nPYzpHfg795ifZx%2BYOfix5Py8rU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/20/d1423af4-f39b-45ce-a5e1-4e98654a57a9.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=ADqv6qGQawhWlJEwYtFBiezoPaI%3D&amp;x-signature-webp=gu1%2F946ejbgTrlC7N9s5WU6q18I%3D</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f2c4e491f7834c548ad2af469457aa1a.jpeg</t>
+          <t>Lib\hardware\data\images\185a2ac42015402aab644e50f2a7da67.jpeg</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-laptop-original-off-white-987cc?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-laptop-original-off-white-987cc?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -8454,17 +8454,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/74672521-d63c-4345-8d7c-1a4c6d44107d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=MdgFRX7cnrUUVfXrTdLJX%2FbifI8%3D&amp;x-signature-webp=klw%2FQqkavhksfp3Izk51n1pRdT8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/74672521-d63c-4345-8d7c-1a4c6d44107d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=yBVh1OU%2BhIHlPe%2FyD949keltBQE%3D&amp;x-signature-webp=tHWvDah3bq7TD8ezUnIRElQ4r1E%3D</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9fb965837d174fdcbd4f8443944badf3.jpeg</t>
+          <t>Lib\hardware\data\images\fda72c6610df450ea5177e6aad9c6349.jpeg</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-14-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-14-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -8503,17 +8503,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/0cb9f188-7016-4eff-b964-b13b4f39e7be.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=ww0GRAi6rPabDa%2FUHkWJ9hzDab0%3D&amp;x-signature-webp=pM2Ywci1F7pLi%2BQL5x0HQjEKJYg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/0cb9f188-7016-4eff-b964-b13b4f39e7be.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=cMUnvKF3Kz4bYy6yEFH2G9tC1x8%3D&amp;x-signature-webp=DpntvAu9mOtXqoEiXUqQf5VTzv4%3D</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3075d85ebac64eda80f6e8882e9504b6.jpeg</t>
+          <t>Lib\hardware\data\images\11dcd4bf32214de2a98e08ce8fd5ab7d.jpeg</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-15-6-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-15-6-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -8552,17 +8552,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=lHbDDfn0Sydy4Zjr4KQequrk2xc%3D&amp;x-signature-webp=AUbDGTC6s9ZGglGKENZHjmeWPDk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=z7BILhfc2JiWsmRxYbHrC27u8Nw%3D&amp;x-signature-webp=venMnVnHCAtriH3z8AQ%2BRPUKLPs%3D</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\447bed187bd04e3e9c578bbe79317d9a.png</t>
+          <t>Lib\hardware\data\images\59ee9236d8794fc2ad41660af0d1cc05.png</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -8601,17 +8601,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/4/211ca921-7a59-4d54-b8a4-b0a866a8a1fc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2BoKGKFn8JWOW6UYuL8PweT3UWcg%3D&amp;x-signature-webp=kuncdp3Bcjyu9htEb7u0mgVlJgk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/4/211ca921-7a59-4d54-b8a4-b0a866a8a1fc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=J%2FAOpmVIpY62S%2BRx6SLncCgtI18%3D&amp;x-signature-webp=ua8BSlnDFuR21GZNY%2FbQU5OhwWg%3D</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\91cdd2eefbf641e28669a15dd6522aeb.jpeg</t>
+          <t>Lib\hardware\data\images\ac0319ff1d774e97950a43d23de755e4.jpeg</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-2-4g-wireless-optical-mous-1600dpi-ergonomic-design-for-pc-laptop-portable-usb-receiver-connection-mou19-blue-549c3?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-2-4g-wireless-optical-mous-1600dpi-ergonomic-design-for-pc-laptop-portable-usb-receiver-connection-mou19-blue-549c3?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -8653,17 +8653,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3f70bf285cdd4ba78101ac0ce308ca29~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=Mh0vNbZlqtOyC%2BHKXcCf%2FXhXtkg%3D&amp;x-signature-webp=Htve3rxG1twjit%2B1XL8SGcVKVBQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3f70bf285cdd4ba78101ac0ce308ca29~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=KIBJkELenSMrW23ELEly13ZBC4E%3D&amp;x-signature-webp=XXhkfKGJbgzyFECnuOhGF1lYbLw%3D</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\62d25cea090d4400a48b88da888a667a.jpeg</t>
+          <t>Lib\hardware\data\images\8dfeeee0c000423cb7794be11b070edd.jpeg</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/poloalvisofficial/polo-alvis-urban-stanford-tas-ransel-waterproof-laptop-15-inch-sma-kampus-cowok-23-l-minimalis-design-1732445419512170430?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/poloalvisofficial/polo-alvis-urban-stanford-tas-ransel-waterproof-laptop-15-inch-sma-kampus-cowok-23-l-minimalis-design-1732445419512170430?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -8702,17 +8702,17 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/66c11c4fd34d4d6882e98ed086d9b763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=UB0tV7cJLwh7g4FLAzNuA6JcHw4%3D&amp;x-signature-webp=r6FHj%2BNh2T3vVJ1GWYa326rwSJA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/66c11c4fd34d4d6882e98ed086d9b763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=wcwEh33IJ%2Flhd%2FBOHysRSuM7okY%3D&amp;x-signature-webp=bWKt8MVtKTpskDlhB5jYdGczG5w%3D</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cb2dbc48c7a94c2b8ed689cc0a771223.jpeg</t>
+          <t>Lib\hardware\data\images\d3eed8ef35d7480a9328c073c68a0113.jpeg</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/asterosofficial/ugreen-mouse-wireless-2-4gh-dongle-slim-design-silent-click-4-level-dpi-for-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/asterosofficial/ugreen-mouse-wireless-2-4gh-dongle-slim-design-silent-click-4-level-dpi-for-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -8754,17 +8754,17 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4cebea9086a44f65b64de3af3ab65a97~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=f7Us2ps2sg3Eb5cmCZka12wgtWQ%3D&amp;x-signature-webp=aCZIn%2F27X1iCvWi5VG2WC7bwkm0%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4cebea9086a44f65b64de3af3ab65a97~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=Z3HkmbeXKLPvxivi92oRm9Br9BA%3D&amp;x-signature-webp=EBW%2BsWB2ncFVcrSTAo2t9QSP%2F%2BY%3D</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3e7ff28ed6ef4e189b55c6a552a86ad2.jpeg</t>
+          <t>Lib\hardware\data\images\e433a72d77b54bcb8e080d221c8f3a1b.jpeg</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-koper-2-in-1-mini-14-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charge-1731259158583739685?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-koper-2-in-1-mini-14-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charge-1731259158583739685?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -8803,17 +8803,17 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/2/12/79679dee-c94c-4311-bcd5-4f2eff9ffde0.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=OMjb7dRz8LvJZzhPHr7q7o%2FThXo%3D&amp;x-signature-webp=iR2JTs0UloK9uShya2PvuJ%2FJkVA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/2/12/79679dee-c94c-4311-bcd5-4f2eff9ffde0.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=C4pAy4JHOcAS5f4cgqSrvvc5IRE%3D&amp;x-signature-webp=hF7oHBs8RB76ycBm3%2FFBvhuGQ7M%3D</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\06f9088cc8d24263a91222d6fac8a67c.png</t>
+          <t>Lib\hardware\data\images\9fd62584089044d89b8ffb5a3edd0bff.png</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mitra-visual-store/magnus-computer-hand-elbow-bracket-ergonomic-design-untuk-laptop-dengan-kapasitas-beban-50kg-instalasi-tanpa-lubang-dan-desain-penyimpanan-aman-dan-terpercaya-1730001110731359391?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mitra-visual-store/magnus-computer-hand-elbow-bracket-ergonomic-design-untuk-laptop-dengan-kapasitas-beban-50kg-instalasi-tanpa-lubang-dan-desain-penyimpanan-aman-dan-terpercaya-1730001110731359391?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -8855,17 +8855,17 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/619af75ea7304f43b85045a7eb5d04d6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=Gq2ijVQJg0UIn6eqZfRS6vXaAUs%3D&amp;x-signature-webp=xDIRU0hTGstb31l2QZsHXPJiJz0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/619af75ea7304f43b85045a7eb5d04d6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=dNZyo7jVWJbgsTfbGBCstJzOcj4%3D&amp;x-signature-webp=xrnqKYiEbgmKIM3f%2BtnP7ONSX08%3D</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\82a68e92c42848728c59ffb0a5b6bacc.jpeg</t>
+          <t>Lib\hardware\data\images\6ba7f3da6cdc4a58abf3f1140dff0cd6.jpeg</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732093254842418725?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732093254842418725?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -8907,17 +8907,17 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/551a82aed56c47eb9e3ee0fba57f90b2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=L46DEK2JCT8LeRYDf6zXqcvWbfY%3D&amp;x-signature-webp=TOM4ugi8yC76Fv3kjIv8MDcc6hY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/551a82aed56c47eb9e3ee0fba57f90b2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=rDG76Ka6Po3WWFo6YRFpfuumJ08%3D&amp;x-signature-webp=dmYGxmDPAcfZsPDKe%2BTQ8lCuPXQ%3D</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3e7b431b36d04f63bb3e560ca02c852a.jpeg</t>
+          <t>Lib\hardware\data\images\d10b45cd24604a58ac0e17d3580a4f1c.jpeg</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/freeknight/freeknight-tas-ransel-pria-jumbo-tas-backpack-rain-cover-scalable-design-tas-laptop-anti-air-kokoh-expandable-usb-anti-maling-for-working-traveling-kulit-sekolah-hitam-tr748-1731255717575886209?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/freeknight/freeknight-tas-ransel-pria-jumbo-tas-backpack-rain-cover-scalable-design-tas-laptop-anti-air-kokoh-expandable-usb-anti-maling-for-working-traveling-kulit-sekolah-hitam-tr748-1731255717575886209?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -8959,17 +8959,17 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4fcd798501a442ba8d7d822ab4ca3653~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=NJ%2BiiMS4PyiOSX0Tkexn%2BUsBKCA%3D&amp;x-signature-webp=z8FVGz37976YjrkhhIqN%2BUEyQF0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4fcd798501a442ba8d7d822ab4ca3653~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=4ioOGatGi%2FTGgvHv4h8qsOJuMKI%3D&amp;x-signature-webp=39lSaCl0VtSc59OMB%2BDaBui1%2FVg%3D</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\58272aff58c5497181803dcf7afb753e.jpeg</t>
+          <t>Lib\hardware\data\images\784085efee49479c951392aea8c5ba01.jpeg</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1731286329775916501?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1731286329775916501?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4a7f13da9aad455ab9fdba3f50b1c198~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=1FU6F1tvOeSd2R%2Bk8UWzJtJsCx4%3D&amp;x-signature-webp=RqodWbyfoaN78S1W%2FaRFdBX5c4o%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4a7f13da9aad455ab9fdba3f50b1c198~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=4FQzXPqtju7PV%2B4oz28O2GeFMBs%3D&amp;x-signature-webp=TkLlg%2FDbrxiAYb%2BXCrQ%2FLYwQxeU%3D</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e69efcb4df034734ac87234c73251338.jpeg</t>
+          <t>Lib\hardware\data\images\e3c92042129246c58f2b872e70440567.jpeg</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-koper-2-in-1mini-14-inch-1730797361031578784?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-koper-2-in-1mini-14-inch-1730797361031578784?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -9063,17 +9063,17 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3252748fff24ac1b364458644770abc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=wrDb3y5FVEO6agbbDi6Nl4TneNs%3D&amp;x-signature-webp=WKoKSdTFcuYKW5bXVbjWATEAx6Y%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3252748fff24ac1b364458644770abc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=9eU6qoMrb7kZG%2FP%2F0O0Md85qLbY%3D&amp;x-signature-webp=ZLBNrCfVkYPH2hDbs94A7JL9o%2FU%3D</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b10106e8cea94847bb40384ae10dcc1d.jpeg</t>
+          <t>Lib\hardware\data\images\ffb9ab48c51f4c4597c00a31cfd838ea.jpeg</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-laptop-komputer-a909-design-ergonomic-with-volume-control-pc-spiker-speker-bass-1729384758482863585?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-laptop-komputer-a909-design-ergonomic-with-volume-control-pc-spiker-speker-bass-1729384758482863585?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -9115,17 +9115,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfeae6c1c6224919b5aa8184f6d941d3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=8Wz7bt2OSS0hyxIvnC8vcbMuwjQ%3D&amp;x-signature-webp=OYVlvPFPREqupxoqsZPZeRjY6MI%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfeae6c1c6224919b5aa8184f6d941d3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=IhKOkf7ncTGZykLHARBvidRRMiQ%3D&amp;x-signature-webp=Uar183SLnCwSKoWoCmitoR0xSfM%3D</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c01fb1cb66f140499d6577edc71ae27d.jpeg</t>
+          <t>Lib\hardware\data\images\c417e6d4ddfa4de481547d28db8b805c.jpeg</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robot-powerbank-indonesia/robot-m315-mouse-pc-laptop-computer-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-bergaransi-resmi-1-tahun-1732091684148970925?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robot-powerbank-indonesia/robot-m315-mouse-pc-laptop-computer-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-bergaransi-resmi-1-tahun-1732091684148970925?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -9167,17 +9167,17 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/761cf6e500cc429b8864a69dc5572e5c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=XRQTW8vI1Qkwg%2F5pdcetGyVSSSw%3D&amp;x-signature-webp=zuepJ2slgiw2FMxbsn0NC5MHNL8%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/761cf6e500cc429b8864a69dc5572e5c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=PaPdI1EmQ7roFw83VaY76okbKL4%3D&amp;x-signature-webp=qYWtBTRHktzSPfBENJAzmYAAVt8%3D</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\11526bb366054edba0d3f8ece3b840c3.jpeg</t>
+          <t>Lib\hardware\data\images\bf7aae395b92407c8fc389a3475e1aa6.jpeg</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotsmartpower/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732092778590929924?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch%26whid%3D18553152</t>
+          <t>https://www.tokopedia.com/robotsmartpower/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732092778590929924?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch%26whid%3D18553152</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -9219,17 +9219,17 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1cfc199626c74270b7f2df4afa4837df~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2FaaVfaMipOuLSD8psJc9sbtmsDY%3D&amp;x-signature-webp=La5KGNeeASmorA71uIhBrF5sByA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1cfc199626c74270b7f2df4afa4837df~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=BY5MVH3dxscKkayDX5RQR2s5i8I%3D&amp;x-signature-webp=zSa2f4mO8M7ftRPA7J6rNIQsWfk%3D</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b291b9180ac848d4af1b54b79b467372.jpeg</t>
+          <t>Lib\hardware\data\images\f056c557473e461db0a386a394e33288.jpeg</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robot-official-surabaya/robot-mouse-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-robot-m315-mouse-nirkabel-kompatibel-pc-computer-laptop-original-bergaransi-resmi-1-tahun-1732189678655407803?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch%26whid%3D20644317</t>
+          <t>https://www.tokopedia.com/robot-official-surabaya/robot-mouse-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-robot-m315-mouse-nirkabel-kompatibel-pc-computer-laptop-original-bergaransi-resmi-1-tahun-1732189678655407803?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch%26whid%3D20644317</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -9271,17 +9271,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cdba5499d0c541eabd966bd3251dd080~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=XtaRzs5IQKt4J9qkENGLpqW%2BzWA%3D&amp;x-signature-webp=OnBPc%2Bj8Gwzw%2FZBFj8laLMPbKWk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cdba5499d0c541eabd966bd3251dd080~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=veQllJGgSCaMTL8Wo62lB5q0ccU%3D&amp;x-signature-webp=Bp6Wsp7dq3ovU7Tnzqr5UBDoqas%3D</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d8273bd498fc4fd68a39c29a37afdf80.jpeg</t>
+          <t>Lib\hardware\data\images\02be5ccac6ab44b7a8739e19029044b4.jpeg</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731285332222182869?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731285332222182869?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -9323,17 +9323,17 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/736c25698fe647b7b3a2740fc3a0941d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=VwhtlM9qLKK3x4Aj%2Bbwdd903GkU%3D&amp;x-signature-webp=lybt0g3D9XgBaLBrTChqvhY4xqQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/736c25698fe647b7b3a2740fc3a0941d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=WQydouo0D%2F8lt07CtoTUmPKBqlo%3D&amp;x-signature-webp=w2EVyKJFS%2FnzyPfu1iDcxNzZQdE%3D</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f25de0805e7c45e5bbea400c14d2d714.jpeg</t>
+          <t>Lib\hardware\data\images\eee4e68686b240ac99d8314748ac64ec.jpeg</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730915957094909397?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730915957094909397?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -9375,17 +9375,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/38dcad3fe4a041af8676ce38b7af63c5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=CzVemc65Ifxb3W19%2FOJdnoExkxs%3D&amp;x-signature-webp=MJPlCHStathJmA2GQZYW7I5rnSk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/38dcad3fe4a041af8676ce38b7af63c5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=mbItfR6bwM0Li1oooVMLlhJ%2F8n4%3D&amp;x-signature-webp=dIKMM9PzcD2Rir1qB90UWVPAr7k%3D</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f1df19a5958c4628b93a65ad20a7ed55.jpeg</t>
+          <t>Lib\hardware\data\images\5bf0b9a162fe4ddc8f51ad204993b554.jpeg</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1730932169696708053?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1730932169696708053?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -9427,17 +9427,17 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0765aa228c7e4eb98f5cddffb3cd161e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=p5JqoUz7TBQm4D91uE3TpycDg9w%3D&amp;x-signature-webp=8eE1Yatosm6p9pqchGenr9%2F2SQs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0765aa228c7e4eb98f5cddffb3cd161e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=MOzIrsrMRPRTfmWBYEfIAWZ2G%2FE%3D&amp;x-signature-webp=Sh6bu6iL9b%2BXevEjQ%2BvYDDOP0hE%3D</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bf9d0a5197854442a366f4879dae46ee.jpeg</t>
+          <t>Lib\hardware\data\images\201e3401671843a79a1bfda62fe5190e.jpeg</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730797091346285728?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730797091346285728?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -9448,24 +9448,24 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2435707299</v>
+        <v>100000200273</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KISONLI - Speaker Design Long Strip for Laptop / Komputer / PC - I600</t>
+          <t>KISONLI - Speaker Design Long Strip LED for Laptop / Komputer / PC / CPU - I560</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>113751</v>
+        <v>123651</v>
       </c>
       <c r="D180" t="n">
-        <v>169000</v>
+        <v>225000</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>493</v>
+        <v>2421</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -9479,17 +9479,17 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/6/559a865b-d5dc-46a6-b4cc-1cbcaac99452.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=rdRSWzooWxzJUSJCAXOBEZVGqnE%3D&amp;x-signature-webp=FsEs%2Fc5ZcK9aRot9sRvhCE00cxA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/15dbf2c96f3e48028a7d92838124dd06~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=meOSFFUQyKErkZaazlqnvPjgNTM%3D&amp;x-signature-webp=kVK33LNDOkVKShBuSIGYoruOXhQ%3D</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cb106b2698974e8c9584e1da1be4d1a9.jpeg</t>
+          <t>Lib\hardware\data\images\aef47fd403c842bca3442f405f8aa8c7.jpeg</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-for-laptop-komputer-pc-i600-1730809914258851297?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-led-for-laptop-komputer-pc-cpu-i560-1729692448934234593?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -9500,24 +9500,24 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>100000211116</v>
+        <v>2435707299</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>KISONLI Gaming Speaker Soundbar Laptop Pc /Komputer i520 Design Long Strip With Volume Control</t>
+          <t>KISONLI - Speaker Design Long Strip for Laptop / Komputer / PC - I600</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>102861</v>
+        <v>113751</v>
       </c>
       <c r="D181" t="n">
-        <v>209000</v>
+        <v>169000</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>128</v>
+        <v>493</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -9531,17 +9531,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9b778382d9e042acbbf6fc51f0b4b3cc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=58S06LgLipNgPp%2Fm7K1rSxvVgLM%3D&amp;x-signature-webp=FV%2BWQAoeR02rie%2FwYRegaJuDkqM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/6/559a865b-d5dc-46a6-b4cc-1cbcaac99452.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=AH96Xq9mCFRlcebuKJP5el1%2BIg4%3D&amp;x-signature-webp=%2F0%2B3fEP9T2%2BVZsgVVIYdCxX69eI%3D</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3329f81bbbe44e01a38ba687f9695605.jpeg</t>
+          <t>Lib\hardware\data\images\1e4f76a92425451590ae80143cf838d9.jpeg</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-soundbar-laptop-pc-komputer-i520-design-long-strip-with-volume-control-1729384483568911841?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-for-laptop-komputer-pc-i600-1730809914258851297?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -9552,48 +9552,48 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>100556558048</v>
+        <v>100000211116</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Love bird kapasitas besar Koper 24 Inch 20 / 22 inch travel kabin &amp; bagasi laptop new design bagasi stand cup / charger</t>
+          <t>KISONLI Gaming Speaker Soundbar Laptop Pc /Komputer i520 Design Long Strip With Volume Control</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>388133</v>
+        <v>102861</v>
       </c>
       <c r="D182" t="n">
-        <v>750000</v>
+        <v>209000</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Love.bird</t>
+          <t>Kisonli</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Jakarta Utara</t>
+          <t>Kab. Tangerang</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/08a5710421f849f0ba33f538d160f9fb~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=wTeU32Y1XJSJVcHUlqUPUeaTNVc%3D&amp;x-signature-webp=V%2FdCXHjA%2BP7Z32rGc%2BylubcDSIc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9b778382d9e042acbbf6fc51f0b4b3cc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=ZeE6hD41ceJwN5LRXM4eIJBIP9s%3D&amp;x-signature-webp=YA4ARIoZuJ%2BI7ibydIiDn6Hne2s%3D</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3cf071584c4e4b78a7a5a15d1a39d63f.jpeg</t>
+          <t>Lib\hardware\data\images\35cf319ffc314c1a995e3dd2acf37019.jpeg</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-1730797282857354400?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-soundbar-laptop-pc-komputer-i520-design-long-strip-with-volume-control-1729384483568911841?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -9604,28 +9604,28 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>100267166259</v>
+        <v>100556558048</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LAOSHIDAISHU KAPASITAS BESAR Koper 24 Inch 20''22 inch TRAVEL KABIN &amp; BAGASI LAPTOP NEW DESIGN STAND CUP / CHARGER Koper 2 in 1Mini 14 Inch</t>
+          <t>Love bird kapasitas besar Koper 24 Inch 20 / 22 inch travel kabin &amp; bagasi laptop new design bagasi stand cup / charger</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>367320</v>
+        <v>388133</v>
       </c>
       <c r="D183" t="n">
-        <v>760000</v>
+        <v>750000</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Laoshidaishu Toko koper</t>
+          <t>Love.bird</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9635,17 +9635,17 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3a7b9972f596402094058c182b8ba340~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=B87S%2BIuxcg%2BKFmAPGumt%2FRTiLFU%3D&amp;x-signature-webp=7OKUhNipapGXZYrNxaznFDTEMCg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/08a5710421f849f0ba33f538d160f9fb~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=kb3ZLJ1LQcWkDHUOWEK%2BDCOAqKQ%3D&amp;x-signature-webp=%2Bd2CSJjf7x3p9kgDiY%2F%2F5guu2aI%3D</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fcc2ade4621b4fdcb0e1775e1ebee354.jpeg</t>
+          <t>Lib\hardware\data\images\b09234fbbe494fc88499f960bf4b49fe.jpeg</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730755375298348501?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-1730797282857354400?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -9656,25 +9656,28 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>102392526345</v>
+        <v>100267166259</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Orashare A01 Decorative Assorted Cartoon Stickers for Power Bank Wall Charger Laptop Tablet Aquaflask and so on Decoration Long Lasting Waterproof Aesthetic Cute Cartoon Design Magic Paper Stickers((Random 1PC Sticker) )</t>
+          <t>LAOSHIDAISHU KAPASITAS BESAR Koper 24 Inch 20''22 inch TRAVEL KABIN &amp; BAGASI LAPTOP NEW DESIGN STAND CUP / CHARGER Koper 2 in 1Mini 14 Inch</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>9999</v>
+        <v>367320</v>
+      </c>
+      <c r="D184" t="n">
+        <v>760000</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Orashare Indonesia Shop</t>
+          <t>Laoshidaishu Toko koper</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9684,17 +9687,17 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/92ffb7bcb5ba4243bf5aa5c96cd90e61~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=RmBuAPYWbvjPao29j3dL7gMQ16I%3D&amp;x-signature-webp=sPY%2F15f%2BEdLmMyEQv6x3SG9CKBU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3a7b9972f596402094058c182b8ba340~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=w5OMzQjeKUzIcsMD9k3AgNrrAps%3D&amp;x-signature-webp=lp8lK8gQq4gwxxW2pq%2FPw2H%2FIXA%3D</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bf0184b554cd428aa85e753a611780fb.jpeg</t>
+          <t>Lib\hardware\data\images\d0af6cff007e434c905716399ea766e6.jpeg</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/orashare/orashare-a01-decorative-assorted-cartoon-stickers-for-power-bank-wall-charger-laptop-tablet-aquaflask-and-so-on-decoration-long-lasting-waterproof-aesthetic-cute-cartoon-design-magic-paper-stickers-random-1pc-sticker-1732799857834428193?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730755375298348501?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -9705,45 +9708,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>6149737245</v>
+        <v>102392526345</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TAS BOBBY EXPLORE BACKPACK BY XD DESIGN FOR LAPTOP 17 INCH RANSEL ORIGINAL</t>
+          <t>Orashare A01 Decorative Assorted Cartoon Stickers for Power Bank Wall Charger Laptop Tablet Aquaflask and so on Decoration Long Lasting Waterproof Aesthetic Cute Cartoon Design Magic Paper Stickers((Random 1PC Sticker) )</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2280000</v>
+        <v>9999</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Luxer</t>
+          <t>Orashare Indonesia Shop</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/9/14/e90d0ad0-232f-4503-9d30-433258dedbd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=7nmNTuUXlnE2D8XEkPq9eU5tPmU%3D&amp;x-signature-webp=gpcFdAti5y8TjLDwXZKLatQS%2B5U%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/92ffb7bcb5ba4243bf5aa5c96cd90e61~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=Kz%2FWPS18oyg45Asn1RHVHh3RVlI%3D&amp;x-signature-webp=bCsK70eafm8NNx%2F%2BTGCiWLKINFw%3D</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8469366da1e64db0b0b55a0cf20eec2c.jpeg</t>
+          <t>Lib\hardware\data\images\b9df4b83e6d1466582efdd8b4557acbe.jpeg</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-bobby-explore-backpack-by-xd-design-for-laptop-17-inch-ransel-original-1731176351546115751?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/orashare/orashare-a01-decorative-assorted-cartoon-stickers-for-power-bank-wall-charger-laptop-tablet-aquaflask-and-so-on-decoration-long-lasting-waterproof-aesthetic-cute-cartoon-design-magic-paper-stickers-random-1pc-sticker-1732799857834428193?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -9754,21 +9757,21 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>15564984049</v>
+        <v>6149737245</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tas Ransel  Eco Flex Bag FOR Laptop Untuk Kerja Sekolah Original Water Resistant Original XD Design</t>
+          <t>TAS BOBBY EXPLORE BACKPACK BY XD DESIGN FOR LAPTOP 17 INCH RANSEL ORIGINAL</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>900000</v>
+        <v>2280000</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -9782,17 +9785,17 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/19/3048426c-97a8-4891-ad6a-9d3335136017.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=8lUpGeYYrOHOW0yzv5lr4USUc1Q%3D&amp;x-signature-webp=BcqZ9lCSA4z4lEDcXrb5QPOFQII%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/9/14/e90d0ad0-232f-4503-9d30-433258dedbd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=vso4Ueru1H5B1esuZDF%2BRq3NXu4%3D&amp;x-signature-webp=u%2BzIqMxHFg6Fek67waps42uQBqM%3D</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b12a7f4f0d894a28b2dcbe2f03cf7d53.jpeg</t>
+          <t>Lib\hardware\data\images\d6987a9530d641f391252e55dddd080f.jpeg</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-ransel-eco-flex-bag-for-laptop-untuk-kerja-sekolah-original-water-resistant-original-xd-design-1731176336923592359?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-bobby-explore-backpack-by-xd-design-for-laptop-17-inch-ransel-original-1731176351546115751?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -9803,21 +9806,21 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>10689379736</v>
+        <v>15564984049</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Original XD-Design Bobby Bizz 2.0 Anti theft Backpack Briefcase FOR Laptop</t>
+          <t>Tas Ransel  Eco Flex Bag FOR Laptop Untuk Kerja Sekolah Original Water Resistant Original XD Design</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2280000</v>
+        <v>900000</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -9831,17 +9834,17 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/7/15/2a8e3008-0cc1-456c-a1eb-8712b4e3afef.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=gRkxXC%2BuvaH4EIVAcy8%2FbFfNvTM%3D&amp;x-signature-webp=AGcB3CKPyUuBBojNgYZF1yuPasA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/19/3048426c-97a8-4891-ad6a-9d3335136017.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=v12QXB2zmCBZBKpb1f1scJIPgwI%3D&amp;x-signature-webp=hufUWriCvT1TWuMh3uqeT37Jp64%3D</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\209563a2d8da40e6b64f0dba83b08641.jpeg</t>
+          <t>Lib\hardware\data\images\c731f662e8114599ba2c9e2732e41dab.jpeg</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-2-0-anti-theft-backpack-briefcase-for-laptop-1731176367656371879?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-ransel-eco-flex-bag-for-laptop-untuk-kerja-sekolah-original-water-resistant-original-xd-design-1731176336923592359?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -9852,21 +9855,21 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>14960666592</v>
+        <v>10689379736</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bobby Edge Anti-Theft Backpack by XD Design Tas Ransel Backpack FOR Laptop Original</t>
+          <t>Original XD-Design Bobby Bizz 2.0 Anti theft Backpack Briefcase FOR Laptop</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1900000</v>
+        <v>2280000</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -9880,17 +9883,17 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/26/3934712d-a1d2-4f48-af1b-0b1037ea9e26.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2Bm5%2FXJTARw1xASeAjqb9tB1gCPs%3D&amp;x-signature-webp=A99AeSETYgp28v2xANHa%2BeXmMhg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/7/15/2a8e3008-0cc1-456c-a1eb-8712b4e3afef.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=KtDSV5XwrFKuMkpYbQvUzxqkbIU%3D&amp;x-signature-webp=ZCczMd4ODrtzzZ%2BVDiXKmZL%2Bu5I%3D</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5cfb592e6e92415b89a059049e1c6d50.jpeg</t>
+          <t>Lib\hardware\data\images\bf1dc2578fbc463a9946afc836be60ed.jpeg</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-backpack-for-laptop-original-1731176301652117159?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-2-0-anti-theft-backpack-briefcase-for-laptop-1731176367656371879?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -9901,48 +9904,45 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>100289507999</v>
+        <v>14960666592</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Pro Design Patron PATSLT 50 Meja Samping / Nakas / Meja Laptop</t>
+          <t>Bobby Edge Anti-Theft Backpack by XD Design Tas Ransel Backpack FOR Laptop Original</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>399000</v>
-      </c>
-      <c r="D189" t="n">
-        <v>643000</v>
+        <v>1900000</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pro Design Furniture</t>
+          <t>Luxer</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Kab. Gresik</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e0cb31b7859943a7818f516b7a76c398~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=zVft9RcgCN%2FdcW87RDllKTBrq%2BY%3D&amp;x-signature-webp=POELeab8%2F00SAuKmPvmLgIJO%2BOI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/26/3934712d-a1d2-4f48-af1b-0b1037ea9e26.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=ZhXxrasFpS9NT79uxYyiEkPXXbY%3D&amp;x-signature-webp=JXQ08S0P8p%2FMYCaB%2Bt3wHrLLH3U%3D</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d8ba75e20d5c440cb9c527c1f49e0176.jpeg</t>
+          <t>Lib\hardware\data\images\a98ecd1ecffb44c68011b43161fc19e4.jpeg</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/prodesign/pro-design-patron-patslt-50-meja-samping-nakas-meja-laptop-1729384439739745584?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-backpack-for-laptop-original-1731176301652117159?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -9953,48 +9953,48 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>100295676877</v>
+        <v>100289507999</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sleeve Nillkin Versatile for Laptop / Notebook / MacBook (Horizontal Design)</t>
+          <t>Pro Design Patron PATSLT 50 Meja Samping / Nakas / Meja Laptop</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>430000</v>
+        <v>399000</v>
       </c>
       <c r="D190" t="n">
-        <v>740000</v>
+        <v>643000</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>unomax</t>
+          <t>Pro Design Furniture</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Kab. Gresik</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e100902e37f5405f95ab14ceca042fbe~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=hYWP1%2BchK%2BAV%2BIQPyePETkjUREQ%3D&amp;x-signature-webp=QA%2FVUBQ%2BKbc9EJwNq1UzGgBnUvg%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e0cb31b7859943a7818f516b7a76c398~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=fqPghNGcVHWziRd1h%2FgyeGiBdiA%3D&amp;x-signature-webp=33PiFl2pQhc3%2F1ARu4ZcEjqOGnw%3D</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\146463122f4d4bc4874e19e808bd945d.jpeg</t>
+          <t>Lib\hardware\data\images\75051e8f23b44cc2a44541748c192cfc.jpeg</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/unomax/sleeve-nillkin-versatile-for-laptop-notebook-macbook-horizontal-design-1729542909144501215?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/prodesign/pro-design-patron-patslt-50-meja-samping-nakas-meja-laptop-1729384439739745584?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -10005,45 +10005,48 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2166270847</v>
+        <v>100295676877</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Original XD-Design Bobby Bizz Anti theft Backpack Briefcase FOR Laptop 15"</t>
+          <t>Sleeve Nillkin Versatile for Laptop / Notebook / MacBook (Horizontal Design)</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1700000</v>
+        <v>430000</v>
+      </c>
+      <c r="D191" t="n">
+        <v>740000</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Luxer</t>
+          <t>unomax</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/4/12/4a196eba-99a6-4d86-ba5d-42198ae0ae47.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=6xke75Z0lL3UiionZTeB8D9cU5Q%3D&amp;x-signature-webp=d%2FLKiZhVNWCTJq3rtoPnEAlh1QM%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e100902e37f5405f95ab14ceca042fbe~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=Tv75eKBhu%2Bn5somIOWH4crlWTOo%3D&amp;x-signature-webp=t5OMaVv3%2F83b4OPdpOHx7paMjqs%3D</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0b811dc8eb4c4b2484dbf4bed3ab5cb5.jpeg</t>
+          <t>Lib\hardware\data\images\1cc55961b50a40d9b6736966a1001843.jpeg</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-anti-theft-backpack-briefcase-for-laptop-15-1731176360280164007?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/unomax/sleeve-nillkin-versatile-for-laptop-notebook-macbook-horizontal-design-1729542909144501215?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -10054,45 +10057,45 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>14639380063</v>
+        <v>2166270847</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>WIA XD Design Bobby Edge Anti-Theft Backpack Tas Ransel Laptop Unisex Original</t>
+          <t>Original XD-Design Bobby Bizz Anti theft Backpack Briefcase FOR Laptop 15"</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1900000</v>
+        <v>1700000</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>WIA OFFICIAL</t>
+          <t>Luxer</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Kab. Tangerang</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/65b3b9f2049f476ba5c95f176912c01f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=Pdd6WB75NH8t3nQ2g3Y7myJBwjU%3D&amp;x-signature-webp=ix0dvqJdrxmkUCgBeWeT5ylAH%2BQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/4/12/4a196eba-99a6-4d86-ba5d-42198ae0ae47.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=CN2jmkFULLYAKFqVEcq33GJ74gA%3D&amp;x-signature-webp=nScMnaNtEOH9pmZYh0HWukr2Kuw%3D</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e43fc3b1ab924a68a04a3fec0fd151ee.jpeg</t>
+          <t>Lib\hardware\data\images\2b9b654ed0b54e65a20d3fa2e1785c05.jpeg</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/wia-official/wia-xd-design-bobby-edge-anti-theft-backpack-tas-ransel-laptop-unisex-original-1729752607370544988?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-anti-theft-backpack-briefcase-for-laptop-15-1731176360280164007?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -10103,45 +10106,45 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>12557319829</v>
+        <v>14639380063</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>VRS DESIGN Ark BackpacK Organize Laptop Carry Bag Multi-use Up To 15.6</t>
+          <t>WIA XD Design Bobby Edge Anti-Theft Backpack Tas Ransel Laptop Unisex Original</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1499000</v>
+        <v>1900000</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Primary Cares Official</t>
+          <t>WIA OFFICIAL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Kab. Tangerang</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/1/16/61242af3-3630-4531-8d25-e625e9e80dea.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=aA98fWD%2BoJCe6hUYO%2FPM6HScXho%3D&amp;x-signature-webp=%2Fpf1eF1hIAEWhjr2nN1bFMWJqYk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/65b3b9f2049f476ba5c95f176912c01f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=PvewWzCeaq0QsstJT2TASkntvaU%3D&amp;x-signature-webp=Za%2BGgqonBY1i7xlP9CUU4zMwDFE%3D</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\01ebf442faba43f2b0e6703405daf068.jpeg</t>
+          <t>Lib\hardware\data\images\4ff47734615e4c6db61e261014cfcef4.jpeg</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/primarycaresofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black-80565?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/wia-official/wia-xd-design-bobby-edge-anti-theft-backpack-tas-ransel-laptop-unisex-original-1729752607370544988?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -10152,28 +10155,25 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>15596117902</v>
+        <v>12557319829</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>POLO GODEN 62194-2B - Tas Ransel / Backpack / Tas Punggung / Tas Laptop / Tas Kantor / Tas Kerja - Premium Material, Sleek Design,  Multi Compartment, Banyak Tempat Penyimpanan, Hitam</t>
+          <t>VRS DESIGN Ark BackpacK Organize Laptop Carry Bag Multi-use Up To 15.6</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>598500</v>
-      </c>
-      <c r="D194" t="n">
-        <v>1197000</v>
+        <v>1499000</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sempana Bags</t>
+          <t>Primary Cares Official</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -10183,17 +10183,17 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/1d2dc8699f1a427e82b9077ea324a552~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=kfDaX4qmUrtCaub7dwNsZvE6TJM%3D&amp;x-signature-webp=ipDSanEmK%2FEf%2Fkfjfv4wy2vxqjE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/1/16/61242af3-3630-4531-8d25-e625e9e80dea.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=rS8wrQ1J8NJhhuq6r7Tyo88MTco%3D&amp;x-signature-webp=AZgQV7F%2BiBJrd%2Be63bL%2Br%2BkRyrM%3D</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7b27a0094a7047198af3ff29955b2b87.jpeg</t>
+          <t>Lib\hardware\data\images\c3158ccc064d4c08826818a0a76a751b.jpeg</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/sempanabags/polo-goden-62194-2b-tas-ransel-backpack-tas-punggung-tas-laptop-tas-kantor-tas-kerja-premium-material-sleek-design-multi-compartment-banyak-tempat-penyimpanan-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/primarycaresofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black-80565?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -10204,48 +10204,48 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>100553472793</v>
+        <v>15596117902</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Advan Laptop WorkPlus Heritage/AMD Ryzen 5-7535HS/8GB DDR4 (Upgrade)/512GB SSD (Upgrade)/AMD Radeon 660M/WIN 11/14" WUXGA (16:10)/Megamendung Batik Design</t>
+          <t>POLO GODEN 62194-2B - Tas Ransel / Backpack / Tas Punggung / Tas Laptop / Tas Kantor / Tas Kerja - Premium Material, Sleek Design,  Multi Compartment, Banyak Tempat Penyimpanan, Hitam</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>7399000</v>
+        <v>598500</v>
       </c>
       <c r="D195" t="n">
-        <v>7999000</v>
+        <v>1197000</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>ADVAN BY URBANLIFE</t>
+          <t>Sempana Bags</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a04b8b3b3b064a0fa6aaf3e379856c92~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=86gTLgzpfzWTdehoNN%2Fki9LXlfc%3D&amp;x-signature-webp=W3dyae%2F1iW6jbP1rdUzYDDZjz%2BA%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/1d2dc8699f1a427e82b9077ea324a552~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=Y9%2BEx7YjFKQtftdkNYWctsfbXmU%3D&amp;x-signature-webp=vwLfnaBxISPaNSXNiOQ7TiYONVU%3D</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b9525a11605b4b14b080c735f8f78b13.jpeg</t>
+          <t>Lib\hardware\data\images\b0dfa22c083d40a99efe1a3d07a298be.jpeg</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/advan-by-urbanlife/advan-laptop-workplus-heritage-amd-ryzen-5-7535hs-8gb-ddr4-upgrade-512gb-ssd-upgrade-amd-radeon-660m-win-11-14-wuxga-16-10-megamendung-batik-design-1731557661886154575?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/sempanabags/polo-goden-62194-2b-tas-ransel-backpack-tas-punggung-tas-laptop-tas-kantor-tas-kerja-premium-material-sleek-design-multi-compartment-banyak-tempat-penyimpanan-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -10256,45 +10256,48 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>14786168852</v>
+        <v>100553472793</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>UGREEN Ergonomic Premium Mouse Pad With Arm Rest Design Bantal Tangan Anti Slip Mousepad Untuk Kerja Kantor Meja Komputer PC Laptop</t>
+          <t>Advan Laptop WorkPlus Heritage/AMD Ryzen 5-7535HS/8GB DDR4 (Upgrade)/512GB SSD (Upgrade)/AMD Radeon 660M/WIN 11/14" WUXGA (16:10)/Megamendung Batik Design</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>80000</v>
+        <v>7399000</v>
+      </c>
+      <c r="D196" t="n">
+        <v>7999000</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DERUMA TECHNOLOGY OFFICIAL</t>
+          <t>ADVAN BY URBANLIFE</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/12/ffd6e4db-90b2-4e80-b558-4833df06bfc3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=8wh19F9cNEND8mMIPjQPxou3TOQ%3D&amp;x-signature-webp=wKHE1BWZmRV03uRMz3TVWlz6pzE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a04b8b3b3b064a0fa6aaf3e379856c92~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=zftuGCs4knnzfPyKW%2FheSgcYS4A%3D&amp;x-signature-webp=wMtEESuAe4S7yEuar1L69HYZ0FI%3D</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7bf295760d5e4f7eb6e117c1d402bfb3.png</t>
+          <t>Lib\hardware\data\images\da83c5f48f5e4285b7f27f7f1b773a7e.jpeg</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deermatech/ugreen-ergonomic-premium-mouse-pad-with-arm-rest-design-bantal-tangan-anti-slip-mousepad-untuk-kerja-kantor-meja-komputer-pc-laptop-black-faf99?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/advan-by-urbanlife/advan-laptop-workplus-heritage-amd-ryzen-5-7535hs-8gb-ddr4-upgrade-512gb-ssd-upgrade-amd-radeon-660m-win-11-14-wuxga-16-10-megamendung-batik-design-1731557661886154575?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -10305,28 +10308,25 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>100593801369</v>
+        <v>14786168852</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TaffHOME Meja Lipat Serbaguna Laptop Portable Desk Minimalist Design - I042767</t>
+          <t>UGREEN Ergonomic Premium Mouse Pad With Arm Rest Design Bantal Tangan Anti Slip Mousepad Untuk Kerja Kantor Meja Komputer PC Laptop</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>159000</v>
-      </c>
-      <c r="D197" t="n">
-        <v>295000</v>
+        <v>80000</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Usea Official Store</t>
+          <t>DERUMA TECHNOLOGY OFFICIAL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -10336,17 +10336,17 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/af145de2fcdb4ec3a9dc41740a920a72~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=mh%2FYwKETGFY4bQyWaacQqKFjWfk%3D&amp;x-signature-webp=anJCJNC7JGxMMkpVl2xhdzYqNbU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/12/ffd6e4db-90b2-4e80-b558-4833df06bfc3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=K60p7iQzMETFZLSeKtDixs9HIxc%3D&amp;x-signature-webp=ghC247SE1VjiakhHjlhRbmVRbuA%3D</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b2df4381c96d4aa09ffafd1af700af97.jpeg</t>
+          <t>Lib\hardware\data\images\0694d467b4634a1fbec2e4a12931a248.png</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/usea/taffhome-meja-lipat-serbaguna-laptop-portable-desk-minimalist-design-i042767-1731655641388386299?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/deermatech/ugreen-ergonomic-premium-mouse-pad-with-arm-rest-design-bantal-tangan-anti-slip-mousepad-untuk-kerja-kantor-meja-komputer-pc-laptop-black-faf99?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -10357,45 +10357,48 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>100000060946</v>
+        <v>100593801369</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>WIA XD Design 14" / 16" Laptop Sleeve Black Tas Pelindung Laptop Original</t>
+          <t>TaffHOME Meja Lipat Serbaguna Laptop Portable Desk Minimalist Design - I042767</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>300000</v>
+        <v>159000</v>
+      </c>
+      <c r="D198" t="n">
+        <v>295000</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>WIA OFFICIAL</t>
+          <t>Usea Official Store</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Kab. Tangerang</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9d59757d49a84775a35c06bdeb14cede~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=0n6%2B5077gNAuCAfgV8dS7DgtVxM%3D&amp;x-signature-webp=hIumIcqnTR7EwczBs%2B92T00i0Mk%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/af145de2fcdb4ec3a9dc41740a920a72~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=Jk9BP3U6WL2%2Bf5WafcFfyxqYgFw%3D&amp;x-signature-webp=8uSxJ%2BBRA4%2FYPHeyhZS39YzfHrQ%3D</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b29e2bd1e15b4481a6331bae25fc780f.jpeg</t>
+          <t>Lib\hardware\data\images\8cc33fcfabf84be09542ec76de4f70b1.jpeg</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/wia-official/wia-xd-design-14-16-laptop-sleeve-black-tas-pelindung-laptop-original-1729909128724056924?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/usea/taffhome-meja-lipat-serbaguna-laptop-portable-desk-minimalist-design-i042767-1731655641388386299?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -10406,45 +10409,45 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>7074049017</v>
+        <v>100000060946</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Tas Bobby Hero Anti Theft Backpack XL 17 inch Bag FOR Laptop XD Design Ori</t>
+          <t>WIA XD Design 14" / 16" Laptop Sleeve Black Tas Pelindung Laptop Original</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1780000</v>
+        <v>300000</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Luxer</t>
+          <t>WIA OFFICIAL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Kab. Tangerang</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/8/dd821518-9132-4894-82f2-34caf0bb2acc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=wBI%2Bkh%2FiIw5h7NIsAYJm7G3YzcE%3D&amp;x-signature-webp=c1ITsUSp58%2BLaFztJ30HMgacDhM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9d59757d49a84775a35c06bdeb14cede~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=62jk%2FNDy2B4e8vMyCy%2FpJ77WYlU%3D&amp;x-signature-webp=rN73UcesjkMbwsaXY75Ce7KAMCk%3D</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6026c715af5a40b39d1adf1c8390b8d3.jpeg</t>
+          <t>Lib\hardware\data\images\87a2b11cedb249b0b8056d9122b6fcd1.jpeg</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-bobby-hero-anti-theft-backpack-xl-17-inch-bag-for-laptop-xd-design-ori-1731176367509243559?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/wia-official/wia-xd-design-14-16-laptop-sleeve-black-tas-pelindung-laptop-original-1729909128724056924?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -10455,25 +10458,25 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>7177223938</v>
+        <v>7074049017</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>VRS DESIGN Ark BackpacK Organize Laptop Carry Bag Multi-use Up To 15.6</t>
+          <t>Tas Bobby Hero Anti Theft Backpack XL 17 inch Bag FOR Laptop XD Design Ori</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1499000</v>
+        <v>1780000</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Supcase Official ID</t>
+          <t>Luxer</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10483,17 +10486,17 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/12/9/54c88793-1151-49b3-ae07-078a15223f01.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=BaHH7GpiKO6VkfiXWWUv0v1JhtA%3D&amp;x-signature-webp=XSd1Z%2BVsEjWoroubc57pv%2FVW87g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/8/dd821518-9132-4894-82f2-34caf0bb2acc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=JwDLJZZgeAZc7o7Z3sKlKCLgjdo%3D&amp;x-signature-webp=JHKy141v26Fc7qNNeX6L3gsuh3s%3D</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\af20c72585e2469db46954246ac47954.jpeg</t>
+          <t>Lib\hardware\data\images\fdc45c17b5c3468d8cfc9397e85ffd0f.jpeg</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supcaseofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-bobby-hero-anti-theft-backpack-xl-17-inch-bag-for-laptop-xd-design-ori-1731176367509243559?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -10504,48 +10507,45 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>100556535366</v>
+        <v>7177223938</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Forgui kapasitas besar Koper 24 Inch 20''22 inch travel kabin &amp; bagasi laptop new design stand CUP / charger</t>
+          <t>VRS DESIGN Ark BackpacK Organize Laptop Carry Bag Multi-use Up To 15.6</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>349490</v>
-      </c>
-      <c r="D201" t="n">
-        <v>760000</v>
+        <v>1499000</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Forgui</t>
+          <t>Supcase Official ID</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Jakarta Utara</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/def128a136764f57b050b851ac499649~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2FyuftHRSOCK5yxkEf8j%2BwgbhZA4%3D&amp;x-signature-webp=pqVYGNIh%2Fbl3PJtYb2U2Zm9kMXM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/12/9/54c88793-1151-49b3-ae07-078a15223f01.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763998027&amp;x-signature=oENe5vntONjUD%2FqaxZKv7Wd8B2g%3D&amp;x-signature-webp=Co9UPHtjDTCkIUb3c4xU244c3I0%3D</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\037e39b4c144419a9864ee348f4921e2.jpeg</t>
+          <t>Lib\hardware\data\images\44bd3cadea5c4ee2a869c066bb44ff32.jpeg</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731259837866738981?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supcaseofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112414270711B9842E0A271F0335D1%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">

--- a/Lib/hardware/data/tokopedia_products_latest.xlsx
+++ b/Lib/hardware/data/tokopedia_products_latest.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/1/7aeb95bc-e841-4938-b4bc-170c843ec092.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=JJ%2BopeCN5yYlw2aaZmmCeCBbHRg%3D&amp;x-signature-webp=5GwQt1OXgQksK0igZrUdD4ClkpA%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/1/7aeb95bc-e841-4938-b4bc-170c843ec092.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=KRU%2FfpbJVFMEmC8dlzfEA7dNIbM%3D&amp;x-signature-webp=ChH%2FDAUQnTzAJKsgzT1AxDFoEyM%3D</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d1c57722b70e4b7a864178ab8d5b07aa.jpeg</t>
+          <t>Lib\hardware\data\images\81c882f3b26143538ce3cc9111e66a02.jpeg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomppurwokerto/speaker-gaming-pc-dan-laptop-nyk-sp-n02?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomppurwokerto/speaker-gaming-pc-dan-laptop-nyk-sp-n02?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/df0f4a61aed14dcb8da81f3c4f338f43~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=FcKejrNkp6i%2F5AB%2F%2FexbrYlvMxU%3D&amp;x-signature-webp=qFt76k2g5WJnwrVE3Ymkarwd9oE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/df0f4a61aed14dcb8da81f3c4f338f43~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=QWz7DcbxaXMndw1tSl6Qr7NDTiE%3D&amp;x-signature-webp=I%2FrWeO%2F0P3vpid%2BwUdlnYVXFnLc%3D</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\18c5efcd853d49babb393f5d3a5ea1fe.jpeg</t>
+          <t>Lib\hardware\data\images\9fa14261524b4bd3b45204fd78c19ed0.jpeg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomppurwokerto/coolingpad-nyk-x6-thunderstorm-gaming-cooling-pad-laptop-2-fan-x-6-x-6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomppurwokerto/coolingpad-nyk-x6-thunderstorm-gaming-cooling-pad-laptop-2-fan-x-6-x-6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -606,17 +606,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/22/cc4b9584-80b6-44d6-87d5-f4611d98002d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=6%2BFL9zT0SKV%2B%2BSJ2ggsiZyB3bnU%3D&amp;x-signature-webp=VM7M%2B4nUm30ThkP5b9OYW0dvgQY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/22/cc4b9584-80b6-44d6-87d5-f4611d98002d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=QGv4XZdo%2B41nl2CItDYcKuXcubc%3D&amp;x-signature-webp=Xrvj7MU65ws0AsL%2FG3Hg9ohp67Y%3D</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f596ad0108c84ea78b861c7c24f0ce0a.png</t>
+          <t>Lib\hardware\data\images\948f632c443e43ce93b56556938b39d4.png</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomp-semarang/rexus-gladius-gx2-gaming-pro-gamepad-joystick-laptop-pc-hitam-95b39?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomp-semarang/rexus-gladius-gx2-gaming-pro-gamepad-joystick-laptop-pc-hitam-95b39?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -655,17 +655,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/3/c0410e6b-f108-42d2-9b67-ea029ba1ab29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=zFzNd7lOXyLXeCemc2i3mtpFDpc%3D&amp;x-signature-webp=M8IvDM1vHpxQ6LE%2FBefkHur2DNs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/3/c0410e6b-f108-42d2-9b67-ea029ba1ab29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=LMKg6b0%2FyfVPYoTPTmzEFIcTp9k%3D&amp;x-signature-webp=2EhV%2B%2Fmp3cbqcXXqS4HD7JYzXgA%3D</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5695550a96db40ac9b0dec97a73af966.png</t>
+          <t>Lib\hardware\data\images\06d8c4837175412ba7f47d247acff939.png</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomp-semarang/nyk-x6-thunderstorm-gaming-coolingpad-laptop-2-fan-x-6-x6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomp-semarang/nyk-x6-thunderstorm-gaming-coolingpad-laptop-2-fan-x-6-x6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/13/35945633-babb-4760-81cb-d4986d80ec0f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=dPorr1xZVc2Rzs3EHBqgmityAIM%3D&amp;x-signature-webp=QdOjQDGjZqWYYViWFzUIsmUvlk4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/13/35945633-babb-4760-81cb-d4986d80ec0f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=zhiUL9adOiqAIkjXQ0SaP1zzilA%3D&amp;x-signature-webp=hKNZfAgDbajsgsMyeQBYQwIKa1s%3D</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7e1c837bacb042869942b7b2be0dd3e5.jpeg</t>
+          <t>Lib\hardware\data\images\cbc86a78b4404b598383fd186e5b3ec4.jpeg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/oceanbike/headset-headphone-gaming-power-full-bass-hs04su-mic-3-5mm-earphone-komputer-laptop-pc?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/oceanbike/headset-headphone-gaming-power-full-bass-hs04su-mic-3-5mm-earphone-komputer-laptop-pc?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/16/f7f0720b-7ffd-4402-9d19-9a8e519ea683.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=rA6wK8n0xpmAGAKeCYu0RMSvr7s%3D&amp;x-signature-webp=AHGGoVi1Grp3v4JhQ%2F3csMrp4c8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/16/f7f0720b-7ffd-4402-9d19-9a8e519ea683.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=hQeztLSdPSLS5oak%2BrJrjPZHY1I%3D&amp;x-signature-webp=bwGE%2Berw3dz61zSpApjfJu%2BlHCg%3D</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f55c8098a41b468485dace1e542be45a.png</t>
+          <t>Lib\hardware\data\images\85e4e4fd83e4493597116e76b53c85d2.png</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mrmaidstore/keyboard-gaming-and-mouse-8310-rgb-keyboard-and-mouse-gaming-for-laptop-komputer-pc-2-in-1-gaming-set-white-0fc1b?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mrmaidstore/keyboard-gaming-and-mouse-8310-rgb-keyboard-and-mouse-gaming-for-laptop-komputer-pc-2-in-1-gaming-set-white-0fc1b?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e55445b6e9a42439b246d1d5c9cc663~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=23FoR41BgorYJ6Lfiu2YSSR6LUY%3D&amp;x-signature-webp=Z7W6NIghcLu873DIuImZTeIRxU8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e55445b6e9a42439b246d1d5c9cc663~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=rIeSkJkdvP%2FKUx2rn%2BYZ77Uw%2FRQ%3D&amp;x-signature-webp=au%2F2bK%2Fy0%2FNgJ%2B1PtgV%2Bby9%2F0PA%3D</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e2dd930661a346f8813df1a0968a4693.jpeg</t>
+          <t>Lib\hardware\data\images\792ac80f837d45c6bddf239072962e78.jpeg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fantech-official-store/fantech-carbon-7-1-hg30-headset-gaming-usb-7-1-virtual-surround-sound-mic-noise-cancelling-driver-40-mm-pc-laptop-mac-ps4-ps5-switch-1731357616041067843?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fantech-official-store/fantech-carbon-7-1-hg30-headset-gaming-usb-7-1-virtual-surround-sound-mic-noise-cancelling-driver-40-mm-pc-laptop-mac-ps4-ps5-switch-1731357616041067843?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/67226b19-6b3d-41f1-b2f3-c0c0d81b1319.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=lkjFSpRtIfOf1ZSspkwzoSpcyg8%3D&amp;x-signature-webp=bO1%2BQuTvdJ84iUYw1Td%2Fnfc5FhU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/67226b19-6b3d-41f1-b2f3-c0c0d81b1319.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=yRNUEaLGphr0zM4%2BS1u%2Bik01aF4%3D&amp;x-signature-webp=rifDJTbQizJTDHl%2FHh99hc4gPlc%3D</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cdf47eda4a90435a8b16360a6b01b002.png</t>
+          <t>Lib\hardware\data\images\4486392290d84c1daae41e1491050ada.png</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-tv-home-theater-pc-monitor-gaming-laptop-hdmi-male-to-hdmi-male-2-1-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928891163543425?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-tv-home-theater-pc-monitor-gaming-laptop-hdmi-male-to-hdmi-male-2-1-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928891163543425?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -906,17 +906,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/9b61818c-7d6b-4657-b87b-cda3f5f9bcf3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=yZeoS72R3NEWyQir8XdL4SSeiNo%3D&amp;x-signature-webp=qvhKyY9fEkWUMk%2BSIC10D34901g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/9b61818c-7d6b-4657-b87b-cda3f5f9bcf3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=jk9bmmklbURDh0MRGPdbHGx0X3g%3D&amp;x-signature-webp=CYjT9%2Fq72pLP8YwjKBlbJdHCNFE%3D</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\291c08b01dd34866a5fe04f953d15030.png</t>
+          <t>Lib\hardware\data\images\c31a066837324731817608b79b1afecf.png</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-pc-monitor-gaming-laptop-displayport-dp-1-4-to-displayport-dp-1-4-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928629547304833?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-pc-monitor-gaming-laptop-displayport-dp-1-4-to-displayport-dp-1-4-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928629547304833?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/5d1519ada63b4e6d9117033d63f53c0a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=pU%2B3pCwsOJvLRmIjTB9%2F4BVfNo4%3D&amp;x-signature-webp=SclQqsj7hLvzpTb1BUcQwu8tzgc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/5d1519ada63b4e6d9117033d63f53c0a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=5UKxXVjBMp4P7pEzFP%2FvDeKgMo0%3D&amp;x-signature-webp=0oaaF7QKRv3zp%2BSaOGn84u98FoA%3D</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fb51b79448254c0db87f5b48cf7a85b9.jpeg</t>
+          <t>Lib\hardware\data\images\a1a3e90c3e164cb08cbabf9c165bb064.jpeg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/himtech/hagibis-kabel-hdmi-to-hdmi-2-1-ultra-hd-2k-4k-8k-3d-hdr-earc-vrr-qms-allm-qft-displayhdr-tv-pc-gaming-monitor-laptop-video-audio-cable-1730928835618703202?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/himtech/hagibis-kabel-hdmi-to-hdmi-2-1-ultra-hd-2k-4k-8k-3d-hdr-earc-vrr-qms-allm-qft-displayhdr-tv-pc-gaming-monitor-laptop-video-audio-cable-1730928835618703202?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/de586d5ac89841249f0ded879ec5efcc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=LsOCMnk3sN%2FVIiWx5KllsXvz8JM%3D&amp;x-signature-webp=%2FDYE8QHbjmZn4B28gI4hdftwFDY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/de586d5ac89841249f0ded879ec5efcc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=G7qaZ2DHE8AjqqHbJZjEHGEie08%3D&amp;x-signature-webp=x23Ew4ayAgi%2BrgExB8Ha92rcK2E%3D</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d3f4351f931e474a9485eba5f1b3c565.jpeg</t>
+          <t>Lib\hardware\data\images\442006420e2445c39350f56ecbf51932.jpeg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fantech-official-store/fantech-cooling-pad-rgb-nc22-notebook-cooler-with-phone-holder-adjustable-fan-speed-up-to-14kg-19-inch-laptop-gaming-1731339017679177162?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fantech-official-store/fantech-cooling-pad-rgb-nc22-notebook-cooler-with-phone-holder-adjustable-fan-speed-up-to-14kg-19-inch-laptop-gaming-1731339017679177162?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c93407def7484a1da7ab81928956adc0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=8nURLixMTXKhEKsd8SNUEhJbGmk%3D&amp;x-signature-webp=CEjEnHz4FBWC%2BPoukh10tN2UqF4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c93407def7484a1da7ab81928956adc0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=AED7b1oewe0dHbIxXXgmO7hy7Nk%3D&amp;x-signature-webp=6bzh5%2Fwd33dqNr2Vh2hmk2aL6p8%3D</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ad2973de974d477bb3d56c2d71b9d727.jpeg</t>
+          <t>Lib\hardware\data\images\6568a713ccbf4dc3bd402c9cc642471b.jpeg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mousepad-gaming-premium-unitech-90cm-x-40cm-x-0-3cm-alas-mouse-pad-jumbo-anti-slip-untuk-laptop-pc-1731687141802083738?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/mousepad-gaming-premium-unitech-90cm-x-40cm-x-0-3cm-alas-mouse-pad-jumbo-anti-slip-untuk-laptop-pc-1731687141802083738?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/29/eeb6fab6-76fe-412e-a3af-dd3792478a70.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=ibBXYBfIuMGk5G41WsOMQgh6hu8%3D&amp;x-signature-webp=gWWQHh3aJY8Si10Iy8r6lyRH3q0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/29/eeb6fab6-76fe-412e-a3af-dd3792478a70.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=juM%2BLOmhRKDu7YcIVoOfkTbOipo%3D&amp;x-signature-webp=S21fDWnJCQ5K8Sy07F9TcYu6p%2Bs%3D</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fd8cf42fc6204bde8a8828a5f4cfdb72.jpeg</t>
+          <t>Lib\hardware\data\images\de562a68a895415d90f13e5101632f6c.jpeg</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/blisatu/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-komputer-laptop-garansi-1-tahun-hitam-39941?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/blisatu/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-komputer-laptop-garansi-1-tahun-hitam-39941?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1163,17 +1163,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/11/f1a5e8dc-36e6-41b1-b297-0871c88cdc8d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=pAQgM9zYoVtf6UOR8MnoSvG4nnM%3D&amp;x-signature-webp=iL2xqu3toZwLuTKtvrP5e5WKFYs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/11/f1a5e8dc-36e6-41b1-b297-0871c88cdc8d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=DrFRLM0%2BOIzjMNJ99mmoFJNSYoU%3D&amp;x-signature-webp=Nq38tZZfZmAjG3ElHYmriRfrjaQ%3D</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fb7882d1d98341a09aff1a627e519bea.png</t>
+          <t>Lib\hardware\data\images\251db54fd1fe4952a683cea771e842f2.png</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/blisatu/speaker-robot-rs190-laptop-pc-gaming-soundbar-super-bass-portable-rgb?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/blisatu/speaker-robot-rs190-laptop-pc-gaming-soundbar-super-bass-portable-rgb?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/25/92ac9a5e-5d03-4584-82a7-00705b6f7bd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=zEY4QUhViSVC78uqdgjOE3GjY%2FE%3D&amp;x-signature-webp=bEWniAGu3krgnymUZApKJGjXQNA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/25/92ac9a5e-5d03-4584-82a7-00705b6f7bd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=KVGX%2BEOkqgXlGG0wLLQL8Y%2FQzN4%3D&amp;x-signature-webp=EAEATxqEf0NxExkHNSYeFVxLGNk%3D</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\97e16da2c66240ad8cda250d3f05fd2a.jpeg</t>
+          <t>Lib\hardware\data\images\880d5d6579b948c9b705bf6cb800bb27.jpeg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/venusmobile/xiaomi-redmi-speaker-soundbar-komputer-bluetooth-aux-koneksi-desktop-laptop-gaming-rgb-computer?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/venusmobile/xiaomi-redmi-speaker-soundbar-komputer-bluetooth-aux-koneksi-desktop-laptop-gaming-rgb-computer?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=DyBkMUdM92zOdtKsgqra2J9WPbo%3D&amp;x-signature-webp=m8y%2BJEYuhZ3Z3WH%2BjiAXt%2FiKZ7g%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=z3si6t1gUZe5kw1gL5kvjEp3s2s%3D&amp;x-signature-webp=CQ%2Fu1NAeoRaW9Vw0JdwjBh2keBU%3D</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1e032f247a8d4524af16aa677dec644c.jpeg</t>
+          <t>Lib\hardware\data\images\9c759fc297ae4733bb5cee7f270e258e.jpeg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2023/11/11/c6e5f1ac-a7ee-42d3-b7f4-87e11a768173.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=GY8UgTFEyEG1OFVM3sFZKBjaA4c%3D&amp;x-signature-webp=u3DZxCTHGKCqakOfgyJcNCF8Mnk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2023/11/11/c6e5f1ac-a7ee-42d3-b7f4-87e11a768173.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=DpbNqVulnByrf3jWpJcYijGRyrY%3D&amp;x-signature-webp=3i%2BLAmWtzracLeKZ0aNjMR4to88%3D</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f3f840069874418e8e61209968459733.jpeg</t>
+          <t>Lib\hardware\data\images\b9689d4a71924e319b7c72d723318c9d.jpeg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/expocomp/charger-innergie-by-delta-240w-gaming-adaptor-laptop-universal-t24?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/expocomp/charger-innergie-by-delta-240w-gaming-adaptor-laptop-universal-t24?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>177210</v>
+        <v>179000</v>
       </c>
       <c r="D19" t="n">
         <v>399000</v>
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fa2db5fb271245a99a2a7fdaad38723b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=pRJH7DQaE449sSEeeQeeNrRzd9E%3D&amp;x-signature-webp=Nqr8ICsiRPKRseRDL7urJDJW8Js%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fa2db5fb271245a99a2a7fdaad38723b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=L8LLSU%2BGUkJGw77AcQlxP%2B8M6ZQ%3D&amp;x-signature-webp=Sw80SHZvweomAvzl9SWd8dYATNE%3D</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8cc217d0f56b4ae7b075b7c63980283b.jpeg</t>
+          <t>Lib\hardware\data\images\54b8ec46125e48e18b9fc0be1609ad91.jpeg</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-kl332-kipas-pendingin-laptop-tornado-5-fan-tidak-licin-blue-1729729632344771388?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-kl332-kipas-pendingin-laptop-tornado-5-fan-tidak-licin-blue-1729729632344771388?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1420,17 +1420,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6ff3324cae5f46c3acb745a01c0de934~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=3HQDiuqc4pRJALM9McgM7QksjQ4%3D&amp;x-signature-webp=9W2gN0sJSOw%2FGhSnlGblt0KvKfQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6ff3324cae5f46c3acb745a01c0de934~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=dGMwwKBFIAt0Yl8l7MMHnoQg034%3D&amp;x-signature-webp=z7tFr8IJh8Oq9GeFhDo1p0lpzdk%3D</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ebdcf91253784a06a1820ebb45bc5051.jpeg</t>
+          <t>Lib\hardware\data\images\f750e46a04b74e1a8490f75066b51ec5.jpeg</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokobaru-s/skyworth-monitor-gaming-24-inch-h24g30q-2k-180hz-fast-ips-panel-1440x2560-16-9-hdr10-99-srgb-untuk-laptop-1731695301096015656?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch%26whid%3D18717103</t>
+          <t>https://www.tokopedia.com/tokobaru-s/skyworth-monitor-gaming-24-inch-h24g30q-2k-180hz-fast-ips-panel-1440x2560-16-9-hdr10-99-srgb-untuk-laptop-1731695301096015656?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch%26whid%3D18717103</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1472,17 +1472,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/3/28/1a2e9b92-8bfd-42a2-b3fb-6050eb6867b5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=BIcYkda%2FVCbbr0zWL60Q6n1%2BFVs%3D&amp;x-signature-webp=t2seFFiRnWLchlO3RyZQcPuXTbM%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/3/28/1a2e9b92-8bfd-42a2-b3fb-6050eb6867b5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=2QwBstm6F%2FTE2VhmT9xNVzzVcOM%3D&amp;x-signature-webp=q51vUddtqapbUXHTDUg13KkwyiE%3D</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1ab23523663746b3a2c782dba9a8ef29.jpeg</t>
+          <t>Lib\hardware\data\images\b4218190bdb24780bcd349c19090c7b3.jpeg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/liemgroup/robot-m206s-wireless-mouse-optical-1600-dpi-silent-click-gaming-pc-laptop-new-m206-m206s-merah-muda-10503?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/liemgroup/robot-m206s-wireless-mouse-optical-1600-dpi-silent-click-gaming-pc-laptop-new-m206-m206s-merah-muda-10503?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/18/9b1c74c6-ffd2-45b1-bdd3-54758efb4bcf.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=U4t7ucOwmGktOklffBhUNYp%2B3rg%3D&amp;x-signature-webp=hXrv9WY3uRvHF3ywW2Zz0kIsjbQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/18/9b1c74c6-ffd2-45b1-bdd3-54758efb4bcf.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=xGKw5AIuZD1CB5c5QDfiI37eUyM%3D&amp;x-signature-webp=y5EtIA0FN4%2FbBJOh1VqLOMip2rQ%3D</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\82f44e2cc63d4a82bc10844514da91e3.jpeg</t>
+          <t>Lib\hardware\data\images\a211ea7d9221472a843b7c7f23e42105.jpeg</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/hagibis-indonesia-store/hagibis-8k-displayport-cable-1-4-high-refresh-rate-dp-cable-8k-60hz-4k-240hz-2k-360hz-for-gaming-monitor-graphics-card-pc-tv-laptop-1730797185172539267?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/hagibis-indonesia-store/hagibis-8k-displayport-cable-1-4-high-refresh-rate-dp-cable-8k-60hz-4k-240hz-2k-360hz-for-gaming-monitor-graphics-card-pc-tv-laptop-1730797185172539267?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/fe3c30b0c1da4d0fa9741d40670b6485~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=u6gmGUTtH%2BGOLZdcxxxzVpszHH0%3D&amp;x-signature-webp=YNfU7MCgdhZqH4MQg365LeqsZEg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/fe3c30b0c1da4d0fa9741d40670b6485~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=r5oEsc9UHYGMWn5vnyVmVHrQ%2BYU%3D&amp;x-signature-webp=7Bjc%2BkQ0Qf%2BqxMUAUG2%2FrU9HwVo%3D</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2b8ad0dc26d14a089f86b4db3cb12d4b.jpeg</t>
+          <t>Lib\hardware\data\images\150fa24d465748118d06c6846ff2b3f7.jpeg</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/soruindonesia/soru-cooling-pad-stand-laptop-gaming-6-fan-kipas-pendingin-laptop-kipas-cooler-1729982466431355783?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/soruindonesia/soru-cooling-pad-stand-laptop-gaming-6-fan-kipas-pendingin-laptop-kipas-cooler-1729982466431355783?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1b714cec8f61478a99ddbdc25d4e5003~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=7qW28gKN9L%2B9eYL0sTSb0Gso21U%3D&amp;x-signature-webp=qLFR9AcS743LQdFRigl3iMnrgS0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1b714cec8f61478a99ddbdc25d4e5003~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=5vgco26ONLW5yy2fAi8TcwTWo5I%3D&amp;x-signature-webp=jmORWF2vXus8pxpvsl40kreqbww%3D</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d7a90553d9f54bd7b0df0d1c512c46ce.jpeg</t>
+          <t>Lib\hardware\data\images\8948b52ff0d5406385dfffc126f13575.jpeg</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/onikumaindonesia/onikuma-cw902-mouse-gaming-hitam-kabel-original-untuk-laptop-komputer-pc-dengan-6400-dpi-tombol-rgb-dan-sensor-optik-tingkat-definisi-tinggi-button-1730338257921934858?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/onikumaindonesia/onikuma-cw902-mouse-gaming-hitam-kabel-original-untuk-laptop-komputer-pc-dengan-6400-dpi-tombol-rgb-dan-sensor-optik-tingkat-definisi-tinggi-button-1730338257921934858?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/13/31a814f6-f0bb-4d89-b3d4-0dafe63f22d7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=QDyT7R%2BTsdKFW8MSMkJjkTusTJA%3D&amp;x-signature-webp=havojmRoB8qrZnztERVXLbWJNoY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/13/31a814f6-f0bb-4d89-b3d4-0dafe63f22d7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=wt8juubHJa%2F5vXudCMD1RC879lo%3D&amp;x-signature-webp=QuxHB28jW04O3yNodgNr3hmWV4U%3D</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6db493fa5d4e40deb9ed6c51e0004690.jpeg</t>
+          <t>Lib\hardware\data\images\ba68760bce184c56b3b830fe53982182.jpeg</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lenovo-authorized-surabaya/charger-innergie-by-delta-180w-gaming-adaptor-laptop-universal-t18?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch%26whid%3D11569999</t>
+          <t>https://www.tokopedia.com/lenovo-authorized-surabaya/charger-innergie-by-delta-180w-gaming-adaptor-laptop-universal-t18?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch%26whid%3D11569999</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/70a5e998-ee7d-48c8-b0f6-c652f9a12d32.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=EWXHj8w%2BrjTIKC9HlftIjspnwsw%3D&amp;x-signature-webp=GtY1VK4p%2F7BVppLsFM2qoRSGJEc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/70a5e998-ee7d-48c8-b0f6-c652f9a12d32.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=b%2BRgS8Ore65%2B0pscSMOQDkPMGJY%3D&amp;x-signature-webp=WK5QX3qvF4q48eBe84x5iqJ%2FUVc%3D</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\152050fe452645d3821e41cd45df8626.jpeg</t>
+          <t>Lib\hardware\data\images\b895f00d19b34c6a8cbdc63b7bc5f8ea.jpeg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-innergie-gaming-universal-original-180w-150w-130w-65w-45w-1731234857708193451?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-innergie-gaming-universal-original-180w-150w-130w-65w-45w-1731234857708193451?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/15/373a1aa1-4150-4341-9439-debc881a4fd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=YsXZi4MeFTH5yw80yguaNLNk%2FE4%3D&amp;x-signature-webp=sik8sRbYYyZqKgrQzVGjg5vIiOU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/15/373a1aa1-4150-4341-9439-debc881a4fd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=VC2F3ZYQN6vtFy0Yz1XDB84r7MQ%3D&amp;x-signature-webp=wx1%2F2SFX2jHRIcvul5ZtWUwVk4M%3D</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6508dbae71104622aa59b32cb6abeed2.jpeg</t>
+          <t>Lib\hardware\data\images\e2cc4acd7d25425c8191cb836045c754.jpeg</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-gaming-mechanical-87-keys-wired-keyboard-layout-rgb-light-universal-pc-laptop-1730787426880030393?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-gaming-mechanical-87-keys-wired-keyboard-layout-rgb-light-universal-pc-laptop-1730787426880030393?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1799,48 +1799,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16086886525</v>
+        <v>12595828509</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OLYPS Wireless Mouse Mechanical Gaming Bluetooth 5.0 Dual Mode Silent Click Type-C Fast Charging Screen Display 3200DPI Untuk PC Laptop</t>
+          <t>Power Adapter Innergie Charger Laptop Gaming ACER ASUS DELL HP LENOVO 280W 200W</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>308618</v>
-      </c>
-      <c r="D28" t="n">
-        <v>514363</v>
+        <v>2345000</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Olyps Official</t>
+          <t>LINDY INDONESIA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Jakarta Utara</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/20/b4aa025b-29e1-44b1-b8e7-776a2899eef3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=hyjPL9eXU6f6tt0Ppa9qspiqEZY%3D&amp;x-signature-webp=m0TvRpUtDBqtuqPjwGj3ZB%2FqcGY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5d662cb1-9633-4475-9bb5-82f645202a74.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=lvMFSZ1AUJ5KDjbQZgR%2FLDcMN0o%3D&amp;x-signature-webp=kHirZ%2B7gerTVGmjNGtsqcdD9twc%3D</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\59e06bda1784433e835a24a1027095ed.png</t>
+          <t>Lib\hardware\data\images\b140c4236b424ef283362f2d0741e593.jpeg</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-wireless-mouse-mechanical-gaming-bluetooth-5-0-dual-mode-silent-click-type-c-fast-charging-screen-display-3200dpi-untuk-pc-laptop-1730803778625832633?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adapter-innergie-charger-laptop-gaming-acer-asus-dell-hp-lenovo-280w-200w-1731234851512288939?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1851,45 +1848,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12595828509</v>
+        <v>16086886525</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Power Adapter Innergie Charger Laptop Gaming ACER ASUS DELL HP LENOVO 280W 200W</t>
+          <t>OLYPS Wireless Mouse Mechanical Gaming Bluetooth 5.0 Dual Mode Silent Click Type-C Fast Charging Screen Display 3200DPI Untuk PC Laptop</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2345000</v>
+        <v>308618</v>
+      </c>
+      <c r="D29" t="n">
+        <v>514363</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LINDY INDONESIA</t>
+          <t>Olyps Official</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5d662cb1-9633-4475-9bb5-82f645202a74.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=A1zTun5JdxMAIcCn2yyZcpfmAAs%3D&amp;x-signature-webp=cltuPjd9QSduOCGGc%2FepdhVdgmo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/20/b4aa025b-29e1-44b1-b8e7-776a2899eef3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=CApA%2BtrN%2B4LdC%2FGKYQGxeLSUCfY%3D&amp;x-signature-webp=RB9yxUyi5xcwaSUQgZjYgkSm8JA%3D</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5f5f775b06c741e199045215631fed61.jpeg</t>
+          <t>Lib\hardware\data\images\d388ea1220fa49f6b2227003f51f33ea.png</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adapter-innergie-charger-laptop-gaming-acer-asus-dell-hp-lenovo-280w-200w-1731234851512288939?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-wireless-mouse-mechanical-gaming-bluetooth-5-0-dual-mode-silent-click-type-c-fast-charging-screen-display-3200dpi-untuk-pc-laptop-1730803778625832633?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5087391e11d74a6cbbd2950bf01e6539~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=R%2FzuRrY%2BR6p3KwRZZWU8JdToa2c%3D&amp;x-signature-webp=X%2F8i5ZSQSPi9ZFMyi9r0wAtcQ6U%3D</t>
+          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5087391e11d74a6cbbd2950bf01e6539~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=eWommA%2FqcIeLaQlmre0G5XPAsbk%3D&amp;x-signature-webp=gtMvmabBYWdLiM9YQCe6z1%2Btb0A%3D</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4549a76d78814eefb3fd567d4599fe4b.jpeg</t>
+          <t>Lib\hardware\data\images\7559742216e1499080727dc80ea2981b.jpeg</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-pendingin-laptop-2-kipas-kl330-fan-1729636686228589372?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-pendingin-laptop-2-kipas-kl330-fan-1729636686228589372?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/1/26/4f9883a0-3d3f-4986-97f3-3f5751f7165c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=hj596LlEmAFjXGmY9cgl0s%2F%2B19o%3D&amp;x-signature-webp=eKiKEfkmkbF7cQU4nLUEx4PndpE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/1/26/4f9883a0-3d3f-4986-97f3-3f5751f7165c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=parm2WyIvvz8pCuidOXERQ33rek%3D&amp;x-signature-webp=6ufEIPIQv8ocPPsydAdtIjNar%2Fk%3D</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\238526f0df224071a831e6d19bb3fb51.jpeg</t>
+          <t>Lib\hardware\data\images\4605611cd3a54af686a6e0441ba5c89d.jpeg</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/d-m-i/nyk-x1-wind-coaster-gaming-cooling-pad-laptop-with-3-fan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/d-m-i/nyk-x1-wind-coaster-gaming-cooling-pad-laptop-with-3-fan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/3/23/a52ecf75-8473-45e9-a91d-36c8da636f5e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=5mWsieA5k1IiXIBp%2FKhxVGopMtc%3D&amp;x-signature-webp=AllGpcLWDELMUFlv1T0ZcVVJXZk%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/3/23/a52ecf75-8473-45e9-a91d-36c8da636f5e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=J2utVlde9XRDqGU6nZz1TWEm8Rk%3D&amp;x-signature-webp=jLW8P7zYOC0eeP8eabT2piLKl2M%3D</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6c1de166d813495d882daec7c232a310.png</t>
+          <t>Lib\hardware\data\images\bb8d5ad20465405d931e2ff3a7cac6ee.png</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/andalassuryagemilang/fan-laptop-cooling-pad-notebook-gaming-nyk-x3-winterstorm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/andalassuryagemilang/fan-laptop-cooling-pad-notebook-gaming-nyk-x3-winterstorm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6b4457908324a2788e9a7da6815e258~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=9HXPeJPGHFrBUqWdJ047hVKebas%3D&amp;x-signature-webp=tURIWp4GYeVynmsC1omP0CaTWE8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6b4457908324a2788e9a7da6815e258~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=1vluCvuzyD2sX%2BszqSO1HnvlgMA%3D&amp;x-signature-webp=bo4Ob5rjBm7aher2QihEYc5Hwh0%3D</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0158787531934b949d4554e615b53f7b.jpeg</t>
+          <t>Lib\hardware\data\images\39b636e5b64c45e0a2f472ddcdda8bfb.jpeg</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mouse-gaming-kabel-unitech-s1-colorfull-rgb-light-3200-dpi-untuk-komputer-pc-laptop-1729643499823991194?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/mouse-gaming-kabel-unitech-s1-colorfull-rgb-light-3200-dpi-untuk-komputer-pc-laptop-1729643499823991194?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/25/98ce42ec-a8a6-4112-9380-10eadb2994f5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=xUzAn6xnI%2BW6WBrkNReHq1HGLlc%3D&amp;x-signature-webp=vbIwk854FYh8jz9m8giGCwQiJA8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/25/98ce42ec-a8a6-4112-9380-10eadb2994f5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=vO6lOaeTQq4NtBruBn6Re1d8Uhg%3D&amp;x-signature-webp=3vWOH9dbEilCe4XZ05Jzp%2FQqGWQ%3D</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0803651e6d594e9c8c02c6b161b57df6.png</t>
+          <t>Lib\hardware\data\images\652b6207570641718ecf2615d887f124.png</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-gaming-kabel-usb-wired-rgb-light-optical-1200-1600dpi-ergonomic-untuk-pc-laptop-dengan-2-speed-dpi-adjustable-dan-tombol-6d-black-1731239865956402840?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-gaming-kabel-usb-wired-rgb-light-optical-1200-1600dpi-ergonomic-untuk-pc-laptop-dengan-2-speed-dpi-adjustable-dan-tombol-6d-black-1731239865956402840?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5c94cc2b-9899-4e95-ae52-c5f60a45630c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=B%2Fatxgfbxrs5qw1ZBWtJfiqwCMs%3D&amp;x-signature-webp=USWfsBwVQpEGFpWgirkCCkc08wQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5c94cc2b-9899-4e95-ae52-c5f60a45630c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=kJhBXm%2BpZXtCTlpPm1OqLXBOuJ4%3D&amp;x-signature-webp=ImTvTwlF%2BZEmhtdBJN%2BJcie5Vmo%3D</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1bc3b27408a549d4939131751b01f45d.jpeg</t>
+          <t>Lib\hardware\data\images\f85ef1d578e84caaaa45d81c0f93196a.jpeg</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-gaming-universal-innergie-240w-230w-200w-20v-12a-t24-1731234878706910891?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-gaming-universal-innergie-240w-230w-200w-20v-12a-t24-1731234878706910891?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0c39492bae8949e79deb61008e4da18c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=n3wEfe12%2Fq%2FWfB2G%2FDpP6JP6t7g%3D&amp;x-signature-webp=HoyA76b7%2BBHQKJLwvsGxI%2F0p3f4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0c39492bae8949e79deb61008e4da18c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=nmEjkd5Cs4RCKp419wnbAyakt1M%3D&amp;x-signature-webp=neD9Kfk48Fw%2FjsAoswCnKcQyHO0%3D</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a069b6871b8346b6b68a8dc952dbaec7.jpeg</t>
+          <t>Lib\hardware\data\images\110439d5ce0a4aec98d66491fbd171bd.jpeg</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bikepremiumstore/headset-headphone-gaming-power-full-bass-hs04su-mic-earphone-komputer-laptop-pc-3-5mm?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bikepremiumstore/headset-headphone-gaming-power-full-bass-hs04su-mic-earphone-komputer-laptop-pc-3-5mm?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2258,48 +2258,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>11689876861</v>
+        <v>102118726768</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CABLETIME Mouse Pad Aluminium Metal Premium Gaming Dekstop Laptop DeskMat Smooth</t>
+          <t>Nemesis Coolingpad Gaming Turbo Air Compressed Up To 21 Inch Laptop BEIRUZ AX3 COOLING PAD RGB</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>136900</v>
+        <v>539000</v>
       </c>
       <c r="D37" t="n">
-        <v>150250</v>
+        <v>700000</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CABLETIME Jakarta</t>
+          <t>Best Elektronik IT</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Jakarta Pusat</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e190eea8efac4e969fd89e79beb0140f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=wbERdVOiIj9ML0y8FxUn5oxeRSk%3D&amp;x-signature-webp=D9ByZSFaVOVF56xsWz8EIqeijT4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6e153097f95486d892d9338928ef0fa~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=izZ0vzBMWu5Usm%2BwA%2BYimwVmT5M%3D&amp;x-signature-webp=Ts6PVQ968NsTXBQbrMsYZwlXNIk%3D</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f580025f28c042459dced04c56c6c81f.jpeg</t>
+          <t>Lib\hardware\data\images\8a86036d8f294c3a9ef2477d44ad9391.jpeg</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/allitems-id/cabletime-mouse-pad-aluminium-metal-premium-gaming-dekstop-laptop-deskmat-smooth-1731201382108268433?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bestit/nemesis-coolingpad-gaming-turbo-air-compressed-up-to-21-inch-laptop-beiruz-ax3-cooling-pad-rgb-1732247682542044373?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2310,48 +2310,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>102118726768</v>
+        <v>11689876861</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nemesis Coolingpad Gaming Turbo Air Compressed Up To 21 Inch Laptop BEIRUZ AX3 COOLING PAD RGB</t>
+          <t>CABLETIME Mouse Pad Aluminium Metal Premium Gaming Dekstop Laptop DeskMat Smooth</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>539000</v>
+        <v>136900</v>
       </c>
       <c r="D38" t="n">
-        <v>700000</v>
+        <v>150250</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Best Elektronik IT</t>
+          <t>CABLETIME Jakarta</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jakarta Pusat</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6e153097f95486d892d9338928ef0fa~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=bVie2oKTxT0rErID1hGX4v1vynE%3D&amp;x-signature-webp=kmYKffy7hO%2F5VtRSHjwm26ADNYk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e190eea8efac4e969fd89e79beb0140f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=VGG%2F5ZcB%2BfcT9lq4yW0WLk0NgRA%3D&amp;x-signature-webp=zsf9Qcntl2DhTL6KQy4101rwNrQ%3D</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f0be6a46ffdd4f9dbe1acd92f09fdd16.jpeg</t>
+          <t>Lib\hardware\data\images\0dbbed8d24c74437a3258db767489b85.jpeg</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bestit/nemesis-coolingpad-gaming-turbo-air-compressed-up-to-21-inch-laptop-beiruz-ax3-cooling-pad-rgb-1732247682542044373?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/allitems-id/cabletime-mouse-pad-aluminium-metal-premium-gaming-dekstop-laptop-deskmat-smooth-1731201382108268433?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3b54f1bf88024c7482a8a32e8c98eaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=IKLLR4VB2YYY7zCtZXtGSBxTW3I%3D&amp;x-signature-webp=QbEh70Dnc3uQWOBMe89toIJ8enY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3b54f1bf88024c7482a8a32e8c98eaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=%2BjSVu%2FasZWpDD365ZHNIHRc1vU8%3D&amp;x-signature-webp=CVB60jxmjgpPJz80jGMITjtarVU%3D</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5ed4d9aed6dc4b0199551094d7774ad3.jpeg</t>
+          <t>Lib\hardware\data\images\991e6bca3ad440449a9b07d0ab767186.jpeg</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bikepremiumstore/headset-gaming-headphone-mic-power-full-bass-hs-04su-earphone-komputer-laptop-pc-3-5mm-mobile-live-streaming?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bikepremiumstore/headset-gaming-headphone-mic-power-full-bass-hs-04su-earphone-komputer-laptop-pc-3-5mm-mobile-live-streaming?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/9/22/73b26064-75be-46de-b155-5535d7d164c0.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=xinNpBJPCGNS%2FlBRSTT7SbMdxu0%3D&amp;x-signature-webp=soKv1U9jkoTKaw1MeMm0SWBgFp8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/9/22/73b26064-75be-46de-b155-5535d7d164c0.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=WBelytEHJP6fIUFFBfRt%2Fs69jLc%3D&amp;x-signature-webp=N5vXTbKIVrO3AWgz3q2ywbDgqx4%3D</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dee4460921734a2f992e4b1d581e6f2d.jpeg</t>
+          <t>Lib\hardware\data\images\86177208348f4642b66b97b195e6b344.jpeg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-laptop-cooler-gaming-cooling-pad-fan-cooler-turbo-silent-srq-019-32d50?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-laptop-cooler-gaming-cooling-pad-fan-cooler-turbo-silent-srq-019-32d50?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9863a40e2c6f4645a11e10bb72c0701c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=DOHX%2FUsI4dFFuixhAoxQNq59bZo%3D&amp;x-signature-webp=tJqifjLzO3Or%2Ftb3%2F34WnQozq8M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9863a40e2c6f4645a11e10bb72c0701c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=VIgZAUtu655r4eb8DVr%2BOHpHeA8%3D&amp;x-signature-webp=J2CRda1zcHdm4ZuAT88OYHSuQn8%3D</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3e8a778f4ac84f3f90658549fa8d0bc2.jpeg</t>
+          <t>Lib\hardware\data\images\7ddc97312861442ab57b7fbca3fd2f3e.jpeg</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tasairbone/tas-ransel-laptop-gaming-polofelix-anti-air-waterproof-soft-case-pelindung-laptop-macbook-size-besar-1731153071094466207?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tasairbone/tas-ransel-laptop-gaming-polofelix-anti-air-waterproof-soft-case-pelindung-laptop-macbook-size-besar-1731153071094466207?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2540,17 +2540,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/22/99a529bd-4693-440e-90e1-cf2b813f8692.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=O2sCH%2F1L4ZoW8TgLrUt82eV0zW8%3D&amp;x-signature-webp=PpNvU48QBOJvRlDmNZR4WTrPkDg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/22/99a529bd-4693-440e-90e1-cf2b813f8692.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=6o5GckgMaexuS7hXlszYKQPia5U%3D&amp;x-signature-webp=dg809nuqYvyaMGz%2F3Dx9xcyIhB4%3D</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4d2bea898ca04f8eb535d1e956fc4686.jpeg</t>
+          <t>Lib\hardware\data\images\52c5d6b608bc4aef92b4705143421d42.jpeg</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/d-m-i/deepcool-n80-rgb-gaming-cooling-pad-for-laptop-cooler?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/d-m-i/deepcool-n80-rgb-gaming-cooling-pad-for-laptop-cooler?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/6/23/42a98edc-3f69-43a5-acb7-82cd258ba31a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=VY74vCwuCl812cUvoddNv14hTKk%3D&amp;x-signature-webp=ieuTYkQAZ%2Fd5Z37Bwl0Snk%2Fa93M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/6/23/42a98edc-3f69-43a5-acb7-82cd258ba31a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=oCyDvC37OmjJSNCYuD5XbBmIwns%3D&amp;x-signature-webp=We8ufK1TKsIHtgJisQNtyAOopZY%3D</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\54c22ebdff8e48eb876f075d103231f8.jpeg</t>
+          <t>Lib\hardware\data\images\18a9847b3bfc469bb113da447f9072ac.jpeg</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/affselv-now/affselv-cooler-laptop-cooling-pad-5-fan-17-inch-adjustable-speed-2600-rpm-kipas-pendingin-laptop-gaming-dengan-6-level-kecepatan-dan-4-level-ketinggian-untuk-laptop-hingga-15-6-inch-1733156196976723940?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/affselv-now/affselv-cooler-laptop-cooling-pad-5-fan-17-inch-adjustable-speed-2600-rpm-kipas-pendingin-laptop-gaming-dengan-6-level-kecepatan-dan-4-level-ketinggian-untuk-laptop-hingga-15-6-inch-1733156196976723940?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2641,17 +2641,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4c66596fc2ce4ad29797c2e977512d7f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=vYAyvcJaWnf2okYm1hXH%2BMIEMgg%3D&amp;x-signature-webp=qC%2BUjDsQLOvwUJAol57ZNxTxMYw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4c66596fc2ce4ad29797c2e977512d7f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=jGRaWuwj0HowZf7GPcriBZYWQ6Y%3D&amp;x-signature-webp=wz5lSKkJg9oqXGR4lJK3GkCbjVY%3D</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3a2f13886fd54627b539d9f80dd573f1.jpeg</t>
+          <t>Lib\hardware\data\images\bdcde03b6936497e91449ca03343bcc4.jpeg</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olike-official/new-product-olike-desktop-speaker-sc07-6w-subwoofer-rgb-light-gaming-full-bass-360-surround-sound-portable-wired-connection-for-laptop-pc-1733184933872698864?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olike-official/new-product-olike-desktop-speaker-sc07-6w-subwoofer-rgb-light-gaming-full-bass-360-surround-sound-portable-wired-connection-for-laptop-pc-1733184933872698864?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/10/11/7d1054d5-ebac-4558-a9f0-204c541144bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=D3tJUY7VHLarO5DeQBFFlLex3i4%3D&amp;x-signature-webp=GZC4IE6L1ese4jewpx70tWfwZmk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/10/11/7d1054d5-ebac-4558-a9f0-204c541144bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=rwtNB8zsdzjJwuRb0pWDahKh6o8%3D&amp;x-signature-webp=EvhZGJNQx6RB7HMZkpuegpaTXN0%3D</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fb6ed51f9e2d46e1b4c646faa95fe36f.png</t>
+          <t>Lib\hardware\data\images\ee57a1ae0480425b89394a7ca70fd1a7.png</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fashionselular/headset-gaming-led-onesos-sy830-headphone-bass-with-mic-hp-pc-laptop-led-blue?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fashionselular/headset-gaming-led-onesos-sy830-headphone-bass-with-mic-hp-pc-laptop-led-blue?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2739,17 +2739,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/152cf82999ae4c61845620b1616abb22~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=XoqD%2Fp5APgKse%2FvbdkHXIqds4G8%3D&amp;x-signature-webp=ZlEQi6v64w7r8radSDbQP8C9rC8%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/152cf82999ae4c61845620b1616abb22~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=6OP9ETg55WveHtayI%2BHcuTMwAUA%3D&amp;x-signature-webp=B6%2BRTJhoYOfWGNOJSMSjY%2BxG1rU%3D</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\273aa7ceef304e4084cf913e7ec5b3d2.jpeg</t>
+          <t>Lib\hardware\data\images\a2558b3f03814856a334fd2bf99bd384.jpeg</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dell-premium-official/dell-backpack-alienware-vindicator-17-3inch-armored-tas-gaming-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dell-premium-official/dell-backpack-alienware-vindicator-17-3inch-armored-tas-gaming-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/d1ef1c4a86a7447988bcbdce4d35fa2b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=M%2BEo7yx1k%2Fhw%2FfsicKF6gO50CGY%3D&amp;x-signature-webp=SqBFq0kIytLYBV8btnJgo4J%2BHWk%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/d1ef1c4a86a7447988bcbdce4d35fa2b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=0ov9Vb9Cmpvm9ROfThlMh%2B7iHvw%3D&amp;x-signature-webp=r1N78QHfQaeAJwhO1JzRtlttS5c%3D</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dff7f7bd2411428ca4c104e59da83aa3.jpeg</t>
+          <t>Lib\hardware\data\images\c4bb3a9232774618968d0b7951391467.jpeg</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-keyboard-gaming-k358-led-rgb-bachlight-support-all-komputer-laptop-hitam-7a474?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-keyboard-gaming-k358-led-rgb-bachlight-support-all-komputer-laptop-hitam-7a474?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/f9a4449e-bfff-4df1-b18f-c1e2af70c4b4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=eJQwL7tunkIZEdtVytaC%2FBn0eTA%3D&amp;x-signature-webp=qBGwImSYfBTHdLtp%2FgH53vBzMYU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/f9a4449e-bfff-4df1-b18f-c1e2af70c4b4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=ao6x8BB0HW%2Bzd3pbXyGgmUAw8HU%3D&amp;x-signature-webp=zGvM6bBwS4l1BK1F%2FDxXR9WJiuY%3D</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\77fe22155c5a4695933772e9159cb120.png</t>
+          <t>Lib\hardware\data\images\83b25822e8024ca5b72e9e61f9b17567.png</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/promodazzle/terlaris-ugreen-headset-kabel-mfi-iphone-android-type-c-lightning-3-5mm-original-100-garansi-resmi-24-bulan-official-store-mall-ori-murah-termurah-terbaik-tablet-samsung-xiaomi-macbook-laptop-pc-typec-earphone-handsfree-super-extra-full-bass-gaming-typec-60700-a7403?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/promodazzle/terlaris-ugreen-headset-kabel-mfi-iphone-android-type-c-lightning-3-5mm-original-100-garansi-resmi-24-bulan-official-store-mall-ori-murah-termurah-terbaik-tablet-samsung-xiaomi-macbook-laptop-pc-typec-earphone-handsfree-super-extra-full-bass-gaming-typec-60700-a7403?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2895,17 +2895,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/16/59db287d-8254-4933-b80e-ef38ff1ddbb7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=5wAHoxPSK%2BF6bk5KajIKudxOSDY%3D&amp;x-signature-webp=%2ByNXfzMugEFqO2unaZdy2wuuKko%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/16/59db287d-8254-4933-b80e-ef38ff1ddbb7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=HxbMUdficcq79UTBb8LAVbPil9g%3D&amp;x-signature-webp=SHdem%2FN9DNZsr%2BN556%2Bi5e7gj30%3D</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4220c40bb1dc4cf291c97f431fba3e06.jpeg</t>
+          <t>Lib\hardware\data\images\887caf6424514d229d119f52b2cccbb5.jpeg</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-pc-komputer-laptop-garansi-1-tahun-bisa-cod-1731162798337328677?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-pc-komputer-laptop-garansi-1-tahun-bisa-cod-1731162798337328677?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2916,24 +2916,24 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>13118188848</v>
+        <v>8555888796</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GAMEN GS2 Speaker Gaming Laptop / Pc Rgb Surround Sound Powerfull Bass</t>
+          <t>Robot RS200 speaker E-Sports Gaming for PC laptop &amp; smartphone ori</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>89000</v>
+        <v>109000</v>
       </c>
       <c r="D50" t="n">
-        <v>89964</v>
+        <v>140760</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2947,17 +2947,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9c456a2e30e64b50b899963631939be0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=CoqXOupCfqtocfIj0zjmAgx8Jbg%3D&amp;x-signature-webp=2iwDwEJWIRQfvptm1krEdaTiDXs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/3/16/62a45061-18e3-48fb-ba3f-42dd8d84b589.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=%2FQU7U3CKCKyicxBYUWCA8MVbTMo%3D&amp;x-signature-webp=L6upgV8P02%2FH3SP%2Bhzk9V%2B2i8Qo%3D</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7676c558e6bd4e54bf71c81358577a64.jpeg</t>
+          <t>Lib\hardware\data\images\cbeaeb2a372c4b8f844809ce96ad6892.png</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/donatur/gamen-gs2-speaker-gaming-laptop-pc-rgb-surround-sound-powerfull-bass-1729873792547194354?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/donatur/robot-rs200-speaker-e-sports-gaming-for-pc-laptop-smartphone-ori?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -2968,48 +2968,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>8555888796</v>
+        <v>4183889004</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Robot RS200 speaker E-Sports Gaming for PC laptop &amp; smartphone ori</t>
+          <t>SUPERMALL Mouse Pad Gaming - Mousepad Alas Laptop XL - 900 x 400mm</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>109000</v>
-      </c>
-      <c r="D51" t="n">
-        <v>140760</v>
+        <v>59000</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Donatur official store</t>
+          <t>Supermall Nusantara</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/3/16/62a45061-18e3-48fb-ba3f-42dd8d84b589.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992021&amp;x-signature=HqrLQ%2BoORCkmdlWXANnb5Kx6uqg%3D&amp;x-signature-webp=nXooR%2FDd4t%2BgHi2IqInoSNqUbgo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/6/9/09ab3d23-47ae-4005-ab4a-cfbc36d7fa4d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=NYJwXL%2F0eEbbA8STd63fbJuAEF4%3D&amp;x-signature-webp=LZR39mh5Y%2BLCmHDBJ7EOufYxHeU%3D</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b14c7183a82443c483fb0ebab229100e.png</t>
+          <t>Lib\hardware\data\images\cd869595b1824c6fb7c7f2c167bfd26c.png</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/donatur/robot-rs200-speaker-e-sports-gaming-for-pc-laptop-smartphone-ori?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D20251124124700496E05E1AEA0A9376MJ4%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supermallori/supermall-mouse-pad-gaming-mousepad-alas-laptop-xl-900-x-400mm-blue-dora?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3051,17 +3048,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9060d5fb44cf4b2faa8e9864b1542c37~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=cpQ%2FSodBKkAEcgymQN3grUvJtoM%3D&amp;x-signature-webp=xizsTV7eXu4i4ZKFee9mr4uQRog%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9060d5fb44cf4b2faa8e9864b1542c37~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=Bjj7rr2AcAfQEfbPJzmJaUUs35k%3D&amp;x-signature-webp=05kPhjPtmCl6W%2BpMLJPRkCPXLiI%3D</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b5d478f4e8674ce2a8480c55254da23b.jpeg</t>
+          <t>Lib\hardware\data\images\a74e6761c08944f89c79a0db7c7f44cf.jpeg</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocofficialstore/tomtoc-t60-explorer-laptop-backpack-office-bag-size-22l-1732719801450137078?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocofficialstore/tomtoc-t60-explorer-laptop-backpack-office-bag-size-22l-1732719801450137078?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3100,17 +3097,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/11/28/265f544d-72eb-43c7-8a97-1756f4f7fcb6.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=JGRiD9LNVWElv%2BZnZGVlj0noiGg%3D&amp;x-signature-webp=AQEumYzkWCDefaUuSIFc1BPmj0Q%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/11/28/265f544d-72eb-43c7-8a97-1756f4f7fcb6.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=flRqNG4WgquBf4E3pSOBg7xySJ4%3D&amp;x-signature-webp=kBlKUA%2BaX0ylnvLtj7A4Esfvmc4%3D</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3eda55e7e77c446397879aaacebb51ef.jpeg</t>
+          <t>Lib\hardware\data\images\c5fe51c9cfb249659a3db62f8ec6410f.jpeg</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcompsolo/mikuso-kb-052u-wired-usb-keyboard-104-key-pc-laptop-office-ergonomic-hitam-6ac76?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D16130095</t>
+          <t>https://www.tokopedia.com/starcompsolo/mikuso-kb-052u-wired-usb-keyboard-104-key-pc-laptop-office-ergonomic-hitam-6ac76?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D16130095</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3152,17 +3149,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/26f44dfba5404212ad862b746e42857a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=m1UKxz%2F0JVfhbkl%2BiJmyN5mglz8%3D&amp;x-signature-webp=Dq2Au2SxOYL2DV1PmbFdBtYFk7w%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/26f44dfba5404212ad862b746e42857a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=UPK7tBCmLcuAkXn3iTaVE%2BVLRkg%3D&amp;x-signature-webp=c6sio%2FRgTFQZ0AsQD53EiuKJMlM%3D</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9222a534609f4d55b6764a9913acee78.jpeg</t>
+          <t>Lib\hardware\data\images\f8061192e69543aa8bb774c7d9947c90.jpeg</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitechone-keyboard-mouse-combo-set-office-master-keyboard-mouse-for-pc-laptop-gadget?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitechone-keyboard-mouse-combo-set-office-master-keyboard-mouse-for-pc-laptop-gadget?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3204,17 +3201,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e59a9d3733e44c89e422d639b080b4b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=m7qIx6aeKGy9z26H1vxdVSCMPgs%3D&amp;x-signature-webp=XTY9pbDanugPHEFI0%2BAcT%2B7yWjE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e59a9d3733e44c89e422d639b080b4b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=B77OM70uMhuny0lkGinqaftVywk%3D&amp;x-signature-webp=1uFD%2Fw%2Baf5h3OuydKxqpF8iVAOA%3D</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3f62a520a0da4c13aea399fbbe67fb97.jpeg</t>
+          <t>Lib\hardware\data\images\a4fd4da530e54c778711d45a886251fe.jpeg</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/gameridsurabaya/laptop-lenovo-legion-5-15-intel-core-i7-13650hx-rtx-5050-8-gb-ram-16-gb-ssd-512-gb-windows-11-office-home-student-15-3-wuxga-165hz-100srgb-1732195924137248723?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/gameridsurabaya/laptop-lenovo-legion-5-15-intel-core-i7-13650hx-rtx-5050-8-gb-ram-16-gb-ssd-512-gb-windows-11-office-home-student-15-3-wuxga-165hz-100srgb-1732195924137248723?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3256,17 +3253,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/9/4/92698dcd-813c-417b-a377-062feb24f1da.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=jrtoyk%2FmsUviWUpMgRCOLACfhWk%3D&amp;x-signature-webp=C1aP%2FHYDJmEMc1s5dtABMwBFGvs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/9/4/92698dcd-813c-417b-a377-062feb24f1da.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=xKOcJr5q9cqLu2ixCp1WT%2F0cHLE%3D&amp;x-signature-webp=9V2UGnSJ1BON%2FUdq7nXnl%2BWI%2FzI%3D</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\70434cf4f113445c92a7b13a6a0544c8.png</t>
+          <t>Lib\hardware\data\images\bfaf9e148d8745eca88f14ade228aad6.png</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-gradaz-office-bundle-tas-ransel-kerja-backpack-laptop-tas-selempang-ipad-organizer-charger-pouch-multifungsi-only-bag-black-0e00a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-gradaz-office-bundle-tas-ransel-kerja-backpack-laptop-tas-selempang-ipad-organizer-charger-pouch-multifungsi-only-bag-black-0e00a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3305,17 +3302,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=y1jTTY9R6db%2FvI5BerJTlKjR5PU%3D&amp;x-signature-webp=CnKZzleTN%2BD2pZZmozIJ7OflSJE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=f%2FQXafuG7Qx25tMmPnh93NIYdX8%3D&amp;x-signature-webp=i3ik5DjSX3XQySejU5fe2I2Qq3o%3D</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5de5b5e76e3d440c8b37a3faf318eb13.png</t>
+          <t>Lib\hardware\data\images\5d60a166211e44ec9da3dd77163a37e8.png</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3357,17 +3354,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/13/c3ad5491-fc3d-4b80-b80a-59b49374ce68.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=kih4zIV4oYWRN1rnq1NYxzBP0Us%3D&amp;x-signature-webp=TsUBXiiGzb5X6PGDiPNspzyorzs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/13/c3ad5491-fc3d-4b80-b80a-59b49374ce68.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=YMBiEnoNJCmPARmpyCxCmV6Uzmo%3D&amp;x-signature-webp=uJ84FBok0zKdZUnhlUOMiXSlzA0%3D</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9231229570a8485aa037a751f961cd93.jpeg</t>
+          <t>Lib\hardware\data\images\d41eecbb7279491f9c5190ebd557802d.jpeg</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/backpack-tas-ransel-office-punggung-sekolah-kuliah-kerja-laptop-15-inch-torch-loka-1730777953781646394?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/backpack-tas-ransel-office-punggung-sekolah-kuliah-kerja-laptop-15-inch-torch-loka-1730777953781646394?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3409,17 +3406,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/15/a0091498-b7ce-4323-9e2d-682fd5afcdde.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=UXEsiLrQbQAQpdLag0TBWIupTxI%3D&amp;x-signature-webp=FeaZAZhqrIF2Vk4LCMfOR9jIiGQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/15/a0091498-b7ce-4323-9e2d-682fd5afcdde.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=tpD0WqZke8OzouMO9vWEzGRc4GY%3D&amp;x-signature-webp=kmz46w68MsHaisng%2FCvRMp7Ks6E%3D</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7680fa5a5c11488ca63b47cc478187e3.png</t>
+          <t>Lib\hardware\data\images\bc1279a69ac64e18afd1f8af129b150d.png</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-office-collection-tas-ransel-kerja-kantor-laptop-stylish-pria-wanita-hongcheon-black-eaee2?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-office-collection-tas-ransel-kerja-kantor-laptop-stylish-pria-wanita-hongcheon-black-eaee2?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3461,17 +3458,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/45db327a9c23430aa3e9f3da70e0d1af~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=MqNPAVJ8x2yBY%2BemRkwa0lHY8lY%3D&amp;x-signature-webp=JcALQybxEWfGQaHMiyPADRw5Sd0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/45db327a9c23430aa3e9f3da70e0d1af~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=hzjrIfNKBO3pTrN6HmmluwdtEYQ%3D&amp;x-signature-webp=2XUzn6SYH30HFm8k%2FxJWcZQeJmI%3D</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\88964ddaa2ce4976810394e0aca20b35.jpeg</t>
+          <t>Lib\hardware\data\images\f1c7e6e378aa4377859db3a17422d211.jpeg</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-g6-untuk-komputer-laptop-pc-1000-dpi-mouse-office-computer-1729590282578069914?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-g6-untuk-komputer-laptop-pc-1000-dpi-mouse-office-computer-1729590282578069914?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3513,17 +3510,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f1f4aa17bf5c43cc9eea095c93d0bf11~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=e5TNqFKirkGO7plpxvjfe9F%2FCbU%3D&amp;x-signature-webp=6ve2%2Ff5cvhkNgIqkfxQuaFt2opY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f1f4aa17bf5c43cc9eea095c93d0bf11~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=PcfdUTWWORYWoPTZwqjGMbwLuSE%3D&amp;x-signature-webp=sTkj5tW2o33VF9ufVxFlFEUcaio%3D</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\78db6ad5ed4340d88c429c6a1a2c5bf1.jpeg</t>
+          <t>Lib\hardware\data\images\e4ef8823fbd34e8ba838b806b4e80c85.jpeg</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/optical-mouse-office-kabel-usb-unitech-g5-1000-dpi-untuk-laptop-pc-computer-1729588341583546778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/optical-mouse-office-kabel-usb-unitech-g5-1000-dpi-untuk-laptop-pc-computer-1729588341583546778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3562,17 +3559,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3baef23e7214219af4e67c58e42992c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=FYUo05P%2FX0lO4d8jGSja6q1m8cU%3D&amp;x-signature-webp=HBXOtMNS%2FLyfDDOYAYR1q%2Ft6EC0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3baef23e7214219af4e67c58e42992c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=G1K2EyZ0nC2m4q%2FLdwZpeQB01FE%3D&amp;x-signature-webp=o5umcjNdhDUiEEYzvfOey1%2BXJdM%3D</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\709b8caacf8f4298a1c74c64d9173671.jpeg</t>
+          <t>Lib\hardware\data\images\947761a14e93474d9bd62bdaba5be1d9.jpeg</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-wired-usb-portable-office-keyboard-for-pc-laptop-computer-hitam-keyboard-1731239918096844440?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-wired-usb-portable-office-keyboard-for-pc-laptop-computer-hitam-keyboard-1731239918096844440?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3614,17 +3611,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/4/5/a58e1a18-1f10-4a59-a55a-fd1832f3e691.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=2K7LxzjFpHLPxWNTzqw0bNYenXM%3D&amp;x-signature-webp=URHU40%2FAmR6fRBkyqnik3niCRfY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/4/5/a58e1a18-1f10-4a59-a55a-fd1832f3e691.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=U6%2F2os3bwEpmyA9cp58NYQEsVcw%3D&amp;x-signature-webp=Jj%2B9YbkyOlLzk33emnaQ1ZrpakY%3D</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\73aa3f140212429384d3381225daad39.png</t>
+          <t>Lib\hardware\data\images\7afdd8435eec4b9183fefb421bac4c64.png</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-loka-backpack-office-tas-ransel-punggung-kuliah-kerja-laptop-15-inch-black-a2f1a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-loka-backpack-office-tas-ransel-punggung-kuliah-kerja-laptop-15-inch-black-a2f1a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3666,17 +3663,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/11/e53481e1-2aa7-4a54-b392-ca8165e0854d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=PZwBlVBxnXFqwxbviZfxuMkp5Jw%3D&amp;x-signature-webp=3LpSe0Irft8e%2B5iZ%2F1nlnIkLioY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/11/e53481e1-2aa7-4a54-b392-ca8165e0854d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=FOGpqt%2BBokdxtuieKVdLxDt1qZA%3D&amp;x-signature-webp=T8OWyZaR%2BiAdUkAcqh36ySVwcKo%3D</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\121b6a75b177430bb4f173c7e39882d2.jpeg</t>
+          <t>Lib\hardware\data\images\0ebdf0706bf1469faaf5f6d4159b0d5a.jpeg</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/toko1973/brewyn-kremlin-mens-office-laptop-bag-tas-sekolah-kuliah-kerja-new-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/toko1973/brewyn-kremlin-mens-office-laptop-bag-tas-sekolah-kuliah-kerja-new-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3715,17 +3712,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfea1365d2224b02b0cd6e3066c04563~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=7y7zZP9Y8tCgGhu7eAPxzaFoqb8%3D&amp;x-signature-webp=CgWf%2FH4E84PvmqvKNAP4S96wKhM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfea1365d2224b02b0cd6e3066c04563~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=n%2FGTy9yj%2F8x3F1gyuDO%2BGp5qvy4%3D&amp;x-signature-webp=AKlnEJwKrDPHcEAgEqaAo8G24Go%3D</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\de86a79b191a4f46a5f8196e9d948a92.jpeg</t>
+          <t>Lib\hardware\data\images\49bdcd4f9a8a46f0baecdf38a657b5d4.jpeg</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fashionselular/onesos-mouse-bluetooth-wireless-office-silent-click-dual-mode-2-4ghz-receiver-usb-for-pc-laptop-black-97680?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fashionselular/onesos-mouse-bluetooth-wireless-office-silent-click-dual-mode-2-4ghz-receiver-usb-for-pc-laptop-black-97680?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3764,17 +3761,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/b431006e2c274740a5d254c732987c47~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=%2BtX4OY8wRWU5WGRgi%2BO6qdB85PY%3D&amp;x-signature-webp=Q17ZpksKHroqymGqyvRPXINrotQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/b431006e2c274740a5d254c732987c47~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=fNPBPpITb5GPufpa2PKTHxBfzXg%3D&amp;x-signature-webp=CUlZaA0VMXeX0%2BRIfNubpb%2BIn78%3D</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dade424a262345a5ae4ace1c6e1f4f63.jpeg</t>
+          <t>Lib\hardware\data\images\017c3cb00cf04ac69fa7d939e7681231.jpeg</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/thekingdomshop/taffware-meja-laptop-42x26cm-portable-desk-table-besi-alumunium-bed-hospital-ranjang-tempat-tidur?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/thekingdomshop/taffware-meja-laptop-42x26cm-portable-desk-table-besi-alumunium-bed-hospital-ranjang-tempat-tidur?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -3813,17 +3810,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/25/e5d80580-d276-4193-95c2-467a317bbbce.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Kq8GPYHPY5dwkPMzyMThwU124LY%3D&amp;x-signature-webp=YMbSgh7I2pgNWWsXrlA%2B7%2BcztzE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/25/e5d80580-d276-4193-95c2-467a317bbbce.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=BqqonlJzsqE%2BcCTcZQsowisXb7g%3D&amp;x-signature-webp=oSQ0KKnlZM39hRsx9b50fhvLPjE%3D</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\174d7179ea8f489bbbc899d967956733.jpeg</t>
+          <t>Lib\hardware\data\images\a40bab678cfc4b62b7ad03f68e7d0ee1.jpeg</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-malvern-tas-ransel-laptop-14-backpack-office-sekolah-hitam-bfe09?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-malvern-tas-ransel-laptop-14-backpack-office-sekolah-hitam-bfe09?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -3862,17 +3859,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/6fde5fe1-e2aa-4dae-9a14-e22668d1df63.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=xPu3vDGvLDHk0tmfu8SDo%2FvPbus%3D&amp;x-signature-webp=8OHM%2Bg%2Bbf8mZBIB5dzzsAHbi6tk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/6fde5fe1-e2aa-4dae-9a14-e22668d1df63.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=dKc9n%2BtwFB7lSLAaFL5tUXOHVxU%3D&amp;x-signature-webp=B%2Fz299%2BD7JbWqMIx9TWTq2bPmDo%3D</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a57c6d6316c3449598037bcf030473fd.jpeg</t>
+          <t>Lib\hardware\data\images\0a2b9737d9fd49868894442501ad746f.jpeg</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-malware-ransel-tas-backpack-laptop-14-inch-unisex-for-school-office-travel-hitam-e60e8?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-malware-ransel-tas-backpack-laptop-14-inch-unisex-for-school-office-travel-hitam-e60e8?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -3911,17 +3908,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/a1b6a357-020a-40c2-82e1-1a04455a483d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=z57Jb4NULMPiie3XBDLuuXMRcZ8%3D&amp;x-signature-webp=l65Z7tnzwveHPBlYWLjd%2B4WIpGo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/a1b6a357-020a-40c2-82e1-1a04455a483d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=ICbldsdIBTTCc8xbMmHhHewv1pk%3D&amp;x-signature-webp=X1djDHPqqwiDxhv0ZvBon6syMLU%3D</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7314b3c4c41747dda799e045b224ce33.jpeg</t>
+          <t>Lib\hardware\data\images\742896bbad814ef29fe93191cbaa2229.jpeg</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-munich-tas-ransel-laptop-outdoor-backpack-travel-22l-office?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-munich-tas-ransel-laptop-outdoor-backpack-travel-22l-office?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3963,17 +3960,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/10/80613ad1-822a-420c-b539-8982c04fd198.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=liZvAsQnLy2KmCU6dDXLR2xdgEs%3D&amp;x-signature-webp=dNNAJAbHrTKR7DqRKPeONJjQTOo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/10/80613ad1-822a-420c-b539-8982c04fd198.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=e%2FV%2BfQkA%2BXAIBed23YV009PFjQU%3D&amp;x-signature-webp=N24TW16dq81YzYIxNbs0Bhp1EDA%3D</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\98bacb8156464781a46bbe1a4bf84876.jpeg</t>
+          <t>Lib\hardware\data\images\3b3f95c25f994d3ab62b9c284b2eb07c.jpeg</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/delioa/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-20619?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D8108753</t>
+          <t>https://www.tokopedia.com/delioa/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-20619?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D8108753</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4012,17 +4009,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/31f0e7ca2307423d9af05931721c8709~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=eS5rbx4ztpIJnxizpearo0fEl0U%3D&amp;x-signature-webp=3%2FZZf0YOhMkiT%2BD0wO2e69jcCNo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/31f0e7ca2307423d9af05931721c8709~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=EH3G7GXdnoF2qXQQPjHYcRUQQ2U%3D&amp;x-signature-webp=0Cbklfqe6QfO1hQNJZIjSJRFdCg%3D</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\36aad53913bf422ea12d88613a6dee68.jpeg</t>
+          <t>Lib\hardware\data\images\72454860b3df490eb8201db2f84a7253.jpeg</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-field-of-view-ransel-backpack-outdoor-travel-laptop-14inch-office-sekolah-22-24l-1729771080242594987?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-field-of-view-ransel-backpack-outdoor-travel-laptop-14inch-office-sekolah-22-24l-1729771080242594987?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4061,17 +4058,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/2/a4358b69-68cb-47b5-a840-f1b889e39e24.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=%2BvHGR9LAevR4oBip0SC2PO3A6oE%3D&amp;x-signature-webp=d8iQtL8CVJQ6ZE0qEELlr4gvtD8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/2/a4358b69-68cb-47b5-a840-f1b889e39e24.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=%2BBgrBmNKof8COZwkwJc2CS0cJz4%3D&amp;x-signature-webp=hETIAwwJeMaG2wa2%2B8by%2BHBckbo%3D</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\61c1d1fba1114622ab38735386a81c84.jpeg</t>
+          <t>Lib\hardware\data\images\c4ccb8f484874529a7c60420646c373e.jpeg</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-yerevan-tas-ransel-laptop-urban-14inch-sekolah-office-merah-b6b5a?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-yerevan-tas-ransel-laptop-urban-14inch-sekolah-office-merah-b6b5a?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4113,17 +4110,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1e1c78d14ba1493b9ddd5c8bded02385~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Ui87Q5NOm8t7roDFzaicplRQtN4%3D&amp;x-signature-webp=%2FAfY2K8w7S7gYH7iGzbcEnndTY4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1e1c78d14ba1493b9ddd5c8bded02385~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=Z6XQBgEu4hGjK9MBLoF%2BxN2sBRA%3D&amp;x-signature-webp=4sZCBnfp2Z0F9ua%2FiNNeGhXFyQ8%3D</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bdf3584d9b174ab681f24726b1b14188.jpeg</t>
+          <t>Lib\hardware\data\images\a306f85053864b3584bf62aec35a8202.jpeg</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-enrekang-ransel-tas-laptop-15-inch-backpack-travel-28l-office-sekolah-kampus-1731143360590087339?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-enrekang-ransel-tas-laptop-15-inch-backpack-travel-28l-office-sekolah-kampus-1731143360590087339?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4162,17 +4159,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/614ebd8bb1c04a7eb3fd1b4df55f7237~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=lRgqEW9%2BdH6DgkXvv3%2F3YoK3Ug8%3D&amp;x-signature-webp=Vlo5qaEkVEojZOmpAZ3IRZBqU1c%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/614ebd8bb1c04a7eb3fd1b4df55f7237~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=oEH%2FOGDHnrACKdxCnbhGY50WqYY%3D&amp;x-signature-webp=zorKx0i16puo1ZE1gnmI55FfZN0%3D</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a9c7a4d8fc8f4d96b65f9fb629c551fa.jpeg</t>
+          <t>Lib\hardware\data\images\21e4679056344fa78011e2119b91cf38.jpeg</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/reformasicompute/mouse-wireless-rexus-office-q30-silent-mouse-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/reformasicompute/mouse-wireless-rexus-office-q30-silent-mouse-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4211,17 +4208,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5e73c1ebd62c4a558d22d17793191345~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=gNc%2FFA8sMGpsqxiAZ9%2FsjdPTP2A%3D&amp;x-signature-webp=VutbPHJLGa1TPouhbsed%2F7o0Fg0%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5e73c1ebd62c4a558d22d17793191345~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=j8uYKQh9t8im5SqrO5wYfJagpgo%3D&amp;x-signature-webp=01QhHIRMaAC0Qd4e04bUXlZwPo0%3D</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4acdcf3ee2c8410db133068793a9e98a.jpeg</t>
+          <t>Lib\hardware\data\images\95052edbfa6b492597fb99fcadfcfc6f.jpeg</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/reformasicompute/rexus-q10-mouse-wireless-office-silent-click-biru-muda?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/reformasicompute/rexus-q10-mouse-wireless-office-silent-click-biru-muda?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4263,17 +4260,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/21/8bbc37d0-0a5e-4c6e-8b65-594ce61d6773.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=pIt3Eu8RmiASVIW8omr0TGWGwuY%3D&amp;x-signature-webp=yhCYlpXYfnkRRBFscjvp9e3uBlk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/21/8bbc37d0-0a5e-4c6e-8b65-594ce61d6773.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=3cKpa0xM1w6QGzlgDF%2BbxuobrEE%3D&amp;x-signature-webp=itBZAKq3Nl1aMdzcmEN14U5iAJs%3D</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fd44d6d21ef6443795367e62d1f0bb8e.jpeg</t>
+          <t>Lib\hardware\data\images\5d9db68df7a94639a1deb96902384ecd.jpeg</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dnd-olshop/baseus-smart-desk-mat-pad-with-wireless-charger-for-gaming-office-wrist-rest-laptop-phone-stand-holder-keyboard-mouse-pad-basic-edition-3ec7d?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dnd-olshop/baseus-smart-desk-mat-pad-with-wireless-charger-for-gaming-office-wrist-rest-laptop-phone-stand-holder-keyboard-mouse-pad-basic-edition-3ec7d?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4315,17 +4312,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=axElALC4Less5oxAOEXQYR0fJB8%3D&amp;x-signature-webp=dXSPxKEHAL%2B7IcIBQ5hPT7Y2HpY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=aR2fz1a3Ti%2Fz7OFS%2Bs2YoREZB1U%3D&amp;x-signature-webp=vEmNmQtQnPTn397Zpqk7gQkH5L8%3D</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3c5a64a65dcd48798ca89f196edaafbb.jpeg</t>
+          <t>Lib\hardware\data\images\a72efae45e474a65b8e0ddc13817a2cc.jpeg</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-x-aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1732911892490716709?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-x-aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1732911892490716709?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4336,7 +4333,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102021317880</v>
+        <v>102021317884</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -4344,10 +4341,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>18900</v>
-      </c>
-      <c r="D78" t="n">
-        <v>60000</v>
+        <v>39000</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -4367,17 +4361,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f4b1f90a2d4f48fc91d0262d2c72a43e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=uQjn%2FQazffjWzv4hiFJo2i7ojtc%3D&amp;x-signature-webp=dacmViHNSlnFpi26RX7Z1xPCynk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f4b1f90a2d4f48fc91d0262d2c72a43e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=DV9JafyQ%2F%2BQsJg9pppbVgPvzGwM%3D&amp;x-signature-webp=Aj9bxQHB4spPWGoSgE49%2B4MsFiw%3D</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fb3873d3d61640dab949bd76b19fdde5.jpeg</t>
+          <t>Lib\hardware\data\images\232e173b81914bbb84a9877770fb6771.jpeg</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mouse-kabel-office-unitech-g8-wired-usb-1000-dpi-untuk-laptop-pc-computer-1729588315193248154?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-optical-g8-wired-kabel-usb-1000dpi-for-laptop-pc-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4419,17 +4413,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/27/da8fc5bd-5e79-432a-9e9e-71dccf3a3137.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=O77X23lo5R0mpHlrNLLwe68wL7Q%3D&amp;x-signature-webp=y%2FlDqADQQV4NJNs9DRwBOfIzSII%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/27/da8fc5bd-5e79-432a-9e9e-71dccf3a3137.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=6pHL0ZcGGhVbDshpg6IHDpiRFHg%3D&amp;x-signature-webp=MnLzdPkxvpgwC6lOhyhV9pCwbCQ%3D</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d2015acb9796418d89b8a8db831bae72.png</t>
+          <t>Lib\hardware\data\images\275c63368c3a42eaa6a0a896c66a4859.png</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supermallori/office-desk-mat-alas-laptop-meja-kerja-mouse-pad-xl-anti-slip-hitam-87010?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supermallori/office-desk-mat-alas-laptop-meja-kerja-mouse-pad-xl-anti-slip-hitam-87010?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4471,17 +4465,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/dd1c7673e9244b86998b388fcfb3086e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=RwpvALnrNsyReYThbcN6H5%2Fowg8%3D&amp;x-signature-webp=l3%2BwVGSeePkI4kfc4AYAsksY7cw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/dd1c7673e9244b86998b388fcfb3086e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=xd%2F86WtjsmjG9xv8LZd%2B5mnd0Jo%3D&amp;x-signature-webp=vH6XYnQmnpD1qzUlUxjZzl47pvs%3D</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4d268887cf854de585254f0828256be2.jpeg</t>
+          <t>Lib\hardware\data\images\cdf5033ac8174d508419a071a9ff7e6b.jpeg</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/suryatama/mouse-quinton-e100-hitam-kabel-usb-for-laptop-pc-computer-1730805992441873603?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/suryatama/mouse-quinton-e100-hitam-kabel-usb-for-laptop-pc-computer-1730805992441873603?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4520,17 +4514,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/3f12aef7d5d541d8a166d75fb1e151fd~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=cZFqqN19XckqfDHbQhHiY6GIJyg%3D&amp;x-signature-webp=164VDbTs2xhBKn53sZXfVSNoits%3D</t>
+          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/3f12aef7d5d541d8a166d75fb1e151fd~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=D5tyFLDj%2FQu2Z7KNy8P8awVSnd0%3D&amp;x-signature-webp=fjRS%2BUIz%2BqL2aCCYmwHrx8ICOVU%3D</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\83dcbb7191fb44afa54a7bc215684af9.jpeg</t>
+          <t>Lib\hardware\data\images\187e2f3886dc4b54980fabb5ad7bd585.jpeg</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-tongkonan-ransel-backpack-laptop-14inch-urban-traveling-22-24l-top-load-sekolah-office-corporate-1729641642932603051?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-tongkonan-ransel-backpack-laptop-14inch-urban-traveling-22-24l-top-load-sekolah-office-corporate-1729641642932603051?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -4569,17 +4563,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/7/46bf75d3-fdb9-44d8-b4ac-0fc2de7f5648.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=mMwtaYlaXluGscZJXC0v1U%2BAiI4%3D&amp;x-signature-webp=ro3vVWq8ygY9EZP2lwYaaSmoW58%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/7/46bf75d3-fdb9-44d8-b4ac-0fc2de7f5648.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=JHKBGdOuk6vWMLlu6agiIHHdfGE%3D&amp;x-signature-webp=Zp7DUZV95xPHWLEuYk7FLNvXQrw%3D</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2ae76e6d0c9d43deb2081beda1a1e4a0.jpeg</t>
+          <t>Lib\hardware\data\images\1dd56810ae2c4756b0c418c9ad4d6c36.jpeg</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-56342?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-56342?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -4618,17 +4612,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/9/db166b0e-7561-45c4-8f94-c7e1fd6b5ca3.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=7YgNDa%2F3CoxkoaOgrD%2B7bnX%2BVRY%3D&amp;x-signature-webp=iIwbeRYknA6ezNyaEDg9SQaEkuw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/9/db166b0e-7561-45c4-8f94-c7e1fd6b5ca3.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=g9ehUeu81hWRnfDha5lIZVMuBVg%3D&amp;x-signature-webp=cIfWX6%2BLCO0RXDFYrxD9ID5fPPg%3D</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f618f8f04cd9474598e6908c38900f24.jpeg</t>
+          <t>Lib\hardware\data\images\836a8c4f4dc847e28e688510b649c32d.jpeg</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-laptop-kerja-kantor-selempang-office-briefcase-14-bg106-abu-abu-f6cb7?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D4203398</t>
+          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-laptop-kerja-kantor-selempang-office-briefcase-14-bg106-abu-abu-f6cb7?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D4203398</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4667,17 +4661,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d837c49cb2a5448a810541ddc84ee84c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=goVs1gi5ewZoZMjcwvAModtnWVw%3D&amp;x-signature-webp=vSgnxtb4losx%2F83sXNrDL767Z6Y%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d837c49cb2a5448a810541ddc84ee84c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=8UWk2hbXaBi8RBaR0NmGcxYs5pU%3D&amp;x-signature-webp=ygWJH9fLJm%2BBQjJ3aHs5Xaflbko%3D</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4464748ebbe84f5cbb9063191ae9cd0d.jpeg</t>
+          <t>Lib\hardware\data\images\f15a5141fae54c389e3987cd1dc832d7.jpeg</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laptopmurahid/laptop-murah-zyrex-lifebook-n4020-8gb-128gb-w11pro-14-0-gry-office-1731531184748463382?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laptopmurahid/laptop-murah-zyrex-lifebook-n4020-8gb-128gb-w11pro-14-0-gry-office-1731531184748463382?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4719,17 +4713,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6338aa902f724277b3c5004260b37911~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Zo2hp%2BbzSQpuUJj0lEmg5ByBSD0%3D&amp;x-signature-webp=uUwOlDrYtcF%2F6Fx54%2BOTC4tc3xg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6338aa902f724277b3c5004260b37911~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=J49WoBjoty8qt4rdf8CO%2Bcadyaw%3D&amp;x-signature-webp=PRh6FIQzpI3lNX80NBdX%2FXFhXM4%3D</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\335b1e7c75274a7da1fc0d4ca4f58e8c.jpeg</t>
+          <t>Lib\hardware\data\images\0ca7c26307e944a09fdb7e9c47a388b5.jpeg</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/philips-voicetracer-store/philips-mouse-meetion-kabel-usb-office-mouse-kabel-usb-1200dpi-kursor-halus-dan-presisi-untuk-pc-laptop-1732408374889449090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/philips-voicetracer-store/philips-mouse-meetion-kabel-usb-office-mouse-kabel-usb-1200dpi-kursor-halus-dan-presisi-untuk-pc-laptop-1732408374889449090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -4768,17 +4762,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/20/d54e8ffa-2df9-4c94-af64-9dfd3427faa1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=fQ0zhYAWiJs1rtOGu9vRmzUWr7I%3D&amp;x-signature-webp=fZVbQXTnBDdeCWWVxZ0pPLqgvDQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/20/d54e8ffa-2df9-4c94-af64-9dfd3427faa1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=A5iXq0uloBhaFugarKgR3tfPISQ%3D&amp;x-signature-webp=OEXBgGwml3PVGxSWTQ8mkJy40UQ%3D</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\be86a1f6676d47faae3da183174b5807.png</t>
+          <t>Lib\hardware\data\images\43c5247008264bac9642c50cb787a307.png</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/technosify/robot-m102-optical-mouse-wired-pc-laptop-office-1200-dpi-new-m100-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/technosify/robot-m102-optical-mouse-wired-pc-laptop-office-1200-dpi-new-m100-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -4820,17 +4814,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43a06819c1b648dc99f1a089d8642d3e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=TTtH%2FQCFguprg70lGWycRes8UFw%3D&amp;x-signature-webp=DMPb%2FzkYb3bTkDZ%2B%2BA%2Fv1RWqIpg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43a06819c1b648dc99f1a089d8642d3e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=mD9EroDwODT%2FXaMTROHEgRFnMLU%3D&amp;x-signature-webp=LH9fqUslwPd6kSKxj03a4thrccY%3D</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5b9e318565a340dba580608279811a26.jpeg</t>
+          <t>Lib\hardware\data\images\f18cf2579caa480b9f854a802119b204.jpeg</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/huaiwen-pc-store/hw-keyboard-mouse-set-kabel-usb-portable-104-key-full-size-office-wired-keyboard-for-pc-laptop-1731395301317248711?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/huaiwen-pc-store/hw-keyboard-mouse-set-kabel-usb-portable-104-key-full-size-office-wired-keyboard-for-pc-laptop-1731395301317248711?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -4872,17 +4866,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8e46ce56c02d46fabf7d0c8d97fe2c48~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=tskc7v8FhWvveAc8wB%2F%2BC4lshB0%3D&amp;x-signature-webp=PYwYDnRHQpL0cVvpTG1sM7ZCI2A%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8e46ce56c02d46fabf7d0c8d97fe2c48~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=nLUKsguBqp1XXEZZi95FMgnrYGA%3D&amp;x-signature-webp=S7iNiOlf0XpFME3y1pTy5lTgQB8%3D</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2831e9d26d6e4b62ac308b168509da01.jpeg</t>
+          <t>Lib\hardware\data\images\6e6a3e2b571a4659afbc3e0aebf0493f.jpeg</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dap-indonesia-official-store/dap-keyboard-kabel-usb-2-0-portable-104-key-full-size-office-wired-keyboard-bass-button-for-pc-laptop-d-k02-garansi-1-tahun-1729677965436487996?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dap-indonesia-official-store/dap-keyboard-kabel-usb-2-0-portable-104-key-full-size-office-wired-keyboard-bass-button-for-pc-laptop-d-k02-garansi-1-tahun-1729677965436487996?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -4921,17 +4915,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a0501ec6bd9b4b99a2538ce910e8d7cf~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=VXrgN2inN5nlEjokjfoLQbl4npc%3D&amp;x-signature-webp=3Dzw0rz9oTm%2FAvNyz1G6IJyxHCw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a0501ec6bd9b4b99a2538ce910e8d7cf~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=FpX3ND%2BCxi2dMy8tpW5IjRkbYNs%3D&amp;x-signature-webp=higA5ahpCih3nLEMij1hZhtjZd4%3D</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\308b0570e389451ca914a1fb6eba14e4.jpeg</t>
+          <t>Lib\hardware\data\images\bbcc2f3b4bb64c0d97b6ce2ab269a945.jpeg</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-florin-ransel-tas-laptop-15-inch-backpack-travel-office-sekolah-kampus-1732937353765881003?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-florin-ransel-tas-laptop-15-inch-backpack-travel-office-sekolah-kampus-1732937353765881003?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -4973,17 +4967,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1f52c929a7754ed4aacff0b2d2a0aaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=SJBg22OjSIRwPpl7uQa5rGBDI38%3D&amp;x-signature-webp=CFtbRqDOtISYuWf%2BuRijCG0bPN4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1f52c929a7754ed4aacff0b2d2a0aaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=Hs3FWxsmamBngxsiDA%2BqbpkQD9Q%3D&amp;x-signature-webp=4OMR4W3PAkg%2BxkUXDsDWBab0SQc%3D</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\260050896e2d489697e2daaee6bd34b0.jpeg</t>
+          <t>Lib\hardware\data\images\badbc581c7a3467d8cda2581f83de6d2.jpeg</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/royalltech/asus-vivobook-x1404va-intel-core-i7-1355-i5-1335-i5-1334-16gb-512gb-w11-office-14-0fhd-ips-laptop-ultrabook-laptop-tipis-nyaman-untuk-kerja-kuliah-1732832432834512375?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D4029903</t>
+          <t>https://www.tokopedia.com/royalltech/asus-vivobook-x1404va-intel-core-i7-1355-i5-1335-i5-1334-16gb-512gb-w11-office-14-0fhd-ips-laptop-ultrabook-laptop-tipis-nyaman-untuk-kerja-kuliah-1732832432834512375?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D4029903</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5025,17 +5019,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/11/5/dbc78023-d6f5-4a1c-b574-362511ab85b9.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=kD8L%2FgMWfNXvg%2FKKkMrO3vqDZZY%3D&amp;x-signature-webp=nBc3ggMf2VBgQgQpswPemVEei5g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/11/5/dbc78023-d6f5-4a1c-b574-362511ab85b9.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=67A54E%2F%2BIn1A5AT1V5ZL7qY7CtU%3D&amp;x-signature-webp=e%2F9sD4jv%2B9O4r6dfiN5ij%2BRrbSI%3D</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\70352064b1134ebd9262614847a0398a.png</t>
+          <t>Lib\hardware\data\images\ff8f12814ad14b519ab979ffa4149877.png</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/movioofficialstore/movio-desk-mat-leather-office-deskmate-mouse-pad-gaming-alas-laptop-1730814937146492460?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/movioofficialstore/movio-desk-mat-leather-office-deskmate-mouse-pad-gaming-alas-laptop-1730814937146492460?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5077,17 +5071,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=axElALC4Less5oxAOEXQYR0fJB8%3D&amp;x-signature-webp=dXSPxKEHAL%2B7IcIBQ5hPT7Y2HpY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=aR2fz1a3Ti%2Fz7OFS%2Bs2YoREZB1U%3D&amp;x-signature-webp=vEmNmQtQnPTn397Zpqk7gQkH5L8%3D</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\34169ac11c7642ca9108653e7698688e.jpeg</t>
+          <t>Lib\hardware\data\images\b0f0e9ae4ad348c18703bee1489ca327.jpeg</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/aula-indonesia/aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1730707911523271760?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/aula-indonesia/aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1730707911523271760?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5129,17 +5123,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9574249e5aa14f9e9ff0ec25065ea773~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=kEIvKQDGiEvYA1BjJstbjJECL10%3D&amp;x-signature-webp=C%2B90qByLHqOlBWFQy5sim7whkGo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9574249e5aa14f9e9ff0ec25065ea773~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=m4Gg16xC6mtpWRUT7zQXn1dtZAI%3D&amp;x-signature-webp=eVP1oGu5K3L57S3jH1FJYbvtlSs%3D</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3f25efbc08254963b1b47f5cbee5245c.jpeg</t>
+          <t>Lib\hardware\data\images\07655a03c0b84a13a9313916a3baca0f.jpeg</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-t23-women-tote-bag-for-laptop-macbook-ladies-shoulder-bag-office-bag-beg-perempuan-1732147400330019985?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-t23-women-tote-bag-for-laptop-macbook-ladies-shoulder-bag-office-bag-beg-perempuan-1732147400330019985?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5158,9 +5152,6 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>710000</v>
-      </c>
-      <c r="D94" t="n">
         <v>790000</v>
       </c>
       <c r="E94" t="n">
@@ -5181,17 +5172,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/142ebd455039474c9b6a28130ac65ab9~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Khdc0Aty1eDW6Cc0PIkuLHa4DgE%3D&amp;x-signature-webp=E49LDKbCPRkAgBD96Ugl7MKY7pY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/142ebd455039474c9b6a28130ac65ab9~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=lCCh%2FadrTd9WlMBUbRP04IYiQbY%3D&amp;x-signature-webp=WsV%2Bca6vjKhLmAj%2B1SgbfBKegAk%3D</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fad1341af6534c829b4ff38557653437.jpeg</t>
+          <t>Lib\hardware\data\images\e1f8a6c39cec406e8e0e46d3ae8f198f.jpeg</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-a40-defender-laptop-messenger-bag-14-16-inch-business-shoulder-bag-office-briefcase-beg-silang-lelaki-1732455130755335313?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-a40-defender-laptop-messenger-bag-14-16-inch-business-shoulder-bag-office-briefcase-beg-silang-lelaki-1732455130755335313?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5233,17 +5224,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8cb82b7c455e4e0fa79003e51a3c33c3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=%2B6oVi0%2Fem0a7%2FqXYf0UI4U%2F6HJ8%3D&amp;x-signature-webp=X7zWkb6whSd%2FxEqoOjci6QXGotI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8cb82b7c455e4e0fa79003e51a3c33c3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=LHcYvVAaWC1QfMbyQj0gk9gEPV4%3D&amp;x-signature-webp=U0R4%2Bl4aVY0JvNLVP6%2FBNXK6a3w%3D</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7827b65da87f4d20bb532e1ea377e388.jpeg</t>
+          <t>Lib\hardware\data\images\f191f8ec3592409598989c058a0788ca.jpeg</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a30-defender-messenger-bag-14-16-inch-laptop-bag-business-briefcase-office-bag-for-macbook-beg-silang-lelaki-1732460964531569809?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a30-defender-messenger-bag-14-16-inch-laptop-bag-business-briefcase-office-bag-for-macbook-beg-silang-lelaki-1732460964531569809?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5285,17 +5276,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/697f15b91d5a4320a3484f2b65beb688~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=Jmt9O8UlK%2FeAXtjY%2FCV2wHdOSOM%3D&amp;x-signature-webp=RYhdL2DW4PucPADa%2BfgEtO7jiAQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/697f15b91d5a4320a3484f2b65beb688~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=cJRb8yXD3y32uWUjb6SNMcVLraw%3D&amp;x-signature-webp=uAo4NViddGih%2B%2Flh%2BiU831c%2BJVE%3D</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4a46c6a13b8e414ebc33141d1471876a.jpeg</t>
+          <t>Lib\hardware\data\images\ec0677bb7aff4cbdb0bee5ac2d0d4f84.jpeg</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-t71-premium-laptop-backpack-urban-fashion-bag-15-6-17-3-inch-macbook-bag-office-laptop-bag-beg-lelaki-1732140544120292497?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-t71-premium-laptop-backpack-urban-fashion-bag-15-6-17-3-inch-macbook-bag-office-laptop-bag-beg-lelaki-1732140544120292497?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5337,17 +5328,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e73d1e41c3be4c94b13dca55172a7763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=crH0CEbKGP%2FyiHJg2FDZW%2BQNklk%3D&amp;x-signature-webp=pC1oesJk1BJBVnckGPwl%2BKZVBKE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e73d1e41c3be4c94b13dca55172a7763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=6f%2B0pnGvs767wDGoGOazX19ndYk%3D&amp;x-signature-webp=BYwjS7PJHO0srQ5v73jEE57NaYc%3D</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1362cf78bb5244e098b9615d25a981ec.jpeg</t>
+          <t>Lib\hardware\data\images\3597a5a30c8747439938b4277f665612.jpeg</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a33-navigator-messenger-bag-14-16-inch-laptop-bag-men-business-briefcase-office-bag-beg-silang-lelaki-1732460907579016337?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a33-navigator-messenger-bag-14-16-inch-laptop-bag-men-business-briefcase-office-bag-beg-silang-lelaki-1732460907579016337?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5389,17 +5380,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2860a24a9e3b43bc827afade643aa71a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=yofHWheBuFzFL2YxoRGPby3hKiw%3D&amp;x-signature-webp=MpLrjmYy82fi9KVDssMGtxETHIM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2860a24a9e3b43bc827afade643aa71a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=uLhPlV2%2FswAILb4sZIuOFyve9LY%3D&amp;x-signature-webp=VWUgcHzZFSmettE64i%2B7u0h1NSw%3D</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\86790c4c9d334b3eba34f58df402c18f.jpeg</t>
+          <t>Lib\hardware\data\images\ed5690f7038941f3b0ba6f035f68714c.jpeg</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/goojodoq/goojodoq-gm0001-office-use-usb-wired-mouse-for-pc-laptop-tablet-w-led-1731786143330567436?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/goojodoq/goojodoq-gm0001-office-use-usb-wired-mouse-for-pc-laptop-tablet-w-led-1731786143330567436?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5441,17 +5432,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6d81861615c94e9d9a2c35ef160645a6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=h%2B%2BtjXtF5sCjKw70yxs%2F42Q9HZY%3D&amp;x-signature-webp=HfXgovEjJLD7GuaAvz8931Bkp6I%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6d81861615c94e9d9a2c35ef160645a6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=A%2FdJtBvWo1fKs1q5O%2BSsXNKnEK4%3D&amp;x-signature-webp=KvUhSxLbw20rARWXh2ChWnUPFl0%3D</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ed92e5ecd45949c1bbe37f22a83ae2c1.jpeg</t>
+          <t>Lib\hardware\data\images\fe401c2092e54a4a8387aa8180fd0be4.jpeg</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-office-automation/deli-office-vusign-folding-table-meja-belajar-laptop-lipat-warna-warni-dengan-cup-holder-dan-phone-tab-holder-vs860-computer-1729434977497286678?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D18379622</t>
+          <t>https://www.tokopedia.com/deli-office-automation/deli-office-vusign-folding-table-meja-belajar-laptop-lipat-warna-warni-dengan-cup-holder-dan-phone-tab-holder-vs860-computer-1729434977497286678?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D18379622</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -5493,17 +5484,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2a42027251e44e9ca4d6b1aa02296fd0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=2a9FbwHWDpM9Ddlr5OoHkhhNe6Q%3D&amp;x-signature-webp=AjiRuPm%2BX6OLWqJ78cpIuQppJaQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2a42027251e44e9ca4d6b1aa02296fd0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=iSSvwpYX9AVPAQ5yoRJq%2BegKnog%3D&amp;x-signature-webp=fRTKlKWHS0LL5uHwveRCutRTj%2FQ%3D</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1e1e21e1999e432ead80acb64e4b8fcf.jpeg</t>
+          <t>Lib\hardware\data\images\360771de16ef4b449d3215a7352f8c26.jpeg</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/royalltech/lenovo-ideapad-5-2in1-14-touch-amd-ryzen-ai-7-350-16gb-1tb-w11-office-14-0fhd-ips-laptop-2in1-touch-screen-notebook-1733282836276479479?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/royalltech/lenovo-ideapad-5-2in1-14-touch-amd-ryzen-ai-7-350-16gb-1tb-w11-office-14-0fhd-ips-laptop-2in1-touch-screen-notebook-1733282836276479479?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -5542,17 +5533,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c9d8b76508d243b68d6b5ad417ae9f60~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992041&amp;x-signature=1Sgc0YBEYKw71zYi55YTe08I%2BG4%3D&amp;x-signature-webp=ZAUWPM%2BkXjcypdJoxipNCUdB%2Brc%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c9d8b76508d243b68d6b5ad417ae9f60~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=hTnWad9%2Bv7w9GfTV4GlgYF%2FP2tg%3D&amp;x-signature-webp=%2FdsAVB5yVTCrNq2fqO5kSYhI4tk%3D</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6708e345681d48e09af4af8a79e140ec.jpeg</t>
+          <t>Lib\hardware\data\images\9c3e8ae6dc3b42c8b5e3d432e0a31bab.jpeg</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deliindonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-1729461164801230362?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D2025112412472111B9842E0A271F1FF14A%26src%3Dsearch%26whid%3D18553129</t>
+          <t>https://www.tokopedia.com/deliindonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-1729461164801230362?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D18553129</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5591,17 +5582,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_d335da00-22f5-4912-8bef-32b3775be378.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=UPvNYRBJGlJFA4o13LXUV0rkdMc%3D&amp;x-signature-webp=4W4sBwGIAW%2B5hyoY56cNs19vHKg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_d335da00-22f5-4912-8bef-32b3775be378.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=OKbilnldnH7LxF3V2zhkVGOR%2FeM%3D&amp;x-signature-webp=Y%2BLkmMZpcbXwcjWRlYESwEaqcLQ%3D</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\395d86feb9d54045bb2907733204a2ae.jpeg</t>
+          <t>Lib\hardware\data\images\f7912089da88486eb09bc8ad24117ab5.jpeg</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-sharp-programming-language-untuk-pc-laptop-hp?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-sharp-programming-language-untuk-pc-laptop-hp?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5640,17 +5631,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_fb1a930f-e114-4bd2-8224-e722de4ed1ac.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=AeAhOs%2BWPD4%2FEtplfBUlH20gk7c%3D&amp;x-signature-webp=q0gRXdhZOH%2BhXzgm7jmabpq1dkU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_fb1a930f-e114-4bd2-8224-e722de4ed1ac.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=QIQ1hGuWb0DLgSPRwNxFUbIyhi4%3D&amp;x-signature-webp=cB0N3S%2FCD%2FmSA%2BP7oGqdNnXjOoM%3D</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\25b9d50545234227a039d5d7d8b98b33.jpeg</t>
+          <t>Lib\hardware\data\images\cd7a4174b9774592835ed5fd3eb72d60.jpeg</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-go-golang-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-go-golang-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -5689,17 +5680,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_57fb509a-be23-471e-989e-1f4d6e8d6456.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=18iSyefE7FFcwvuOBFslnCofdVc%3D&amp;x-signature-webp=Dvwd8Ta3BJz8HQKzP95Cj81pb9M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_57fb509a-be23-471e-989e-1f4d6e8d6456.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=4t9UwJCwauq%2BpUEuIDbzSHECVXA%3D&amp;x-signature-webp=mU2XBVBDQmYx7P60HFzAz3HX2%2FU%3D</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8b4ac423caef479ba66d50627f7115be.jpeg</t>
+          <t>Lib\hardware\data\images\a4afa4fcb22e4cf09f0e97d715e70adb.jpeg</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -5738,17 +5729,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0cdf5c85ae0a40a69404e6a02408149c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=W%2F0AyOO%2Fuv1o9LHMwGRD9fy%2FvFk%3D&amp;x-signature-webp=9dcFKAqXDkeiWVM4nQt0IM82SmI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0cdf5c85ae0a40a69404e6a02408149c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=NXN%2B9P5rVPEsmQwvbwACCbyp87s%3D&amp;x-signature-webp=SB2faH587wKZI99%2B9Rg40BvSwcQ%3D</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\95695fb95d694933a85b4ce6a1c90657.jpeg</t>
+          <t>Lib\hardware\data\images\cae1e965ff6f440195c81d1fb7f16045.jpeg</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/inlinefoursticker/sticker-pack-premium-it-stiker-program-teknologi-tema-coding-programming-coder-programmer-waterproof-tumblr-laptop-case-hp-koper-helm-sepeda-motor-1729660102472074470?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/inlinefoursticker/sticker-pack-premium-it-stiker-program-teknologi-tema-coding-programming-coder-programmer-waterproof-tumblr-laptop-case-hp-koper-helm-sepeda-motor-1729660102472074470?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5790,17 +5781,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/2/a80e659e-9b9a-4c2a-b57a-50ed8cf2ff65.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=U4DjbOjaneTW3SR17YVaKOE67d0%3D&amp;x-signature-webp=GePlHRM5gPZIXJ%2FXe9okv2Ifah8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/2/a80e659e-9b9a-4c2a-b57a-50ed8cf2ff65.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=m6sO%2B2iyd4x6z6RuLeq%2Fcq6k6a8%3D&amp;x-signature-webp=x8pY%2B%2BmC%2Bm412xw5yJiPuB5WKr8%3D</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cf685ab9666448218bce592e7923592b.png</t>
+          <t>Lib\hardware\data\images\ebff40b4e23d44659df1a60f00a44380.png</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/yeagerart/sticker-pack-programming-coding-sticker-koper-sticker-tumbler-sticker-laptop-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/yeagerart/sticker-pack-programming-coding-sticker-koper-sticker-tumbler-sticker-laptop-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -5839,17 +5830,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/21/3f892503-b128-4c98-81cb-00fb5661f466.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=E0Hd%2Fuk3ursNOpdCyXPz%2B%2FMWEFE%3D&amp;x-signature-webp=g0t97K0LE5Hu%2F0m21%2Bd9Qy4EIrA%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/21/3f892503-b128-4c98-81cb-00fb5661f466.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=WE2ltecM7O%2FcFBxnGcC6r1DEQWg%3D&amp;x-signature-webp=IHnh9aXI745siQ91IojA1wNoj3g%3D</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\96f726e5521546528ef73a0d7ab6b09f.jpeg</t>
+          <t>Lib\hardware\data\images\cccbe2b351b54c5ba5af30b6603323bb.jpeg</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerplus/sticker-programming-2-sticker-laptop-sticker-pack-stiker-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerplus/sticker-programming-2-sticker-laptop-sticker-pack-stiker-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -5888,17 +5879,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_1e2c0c59-fda9-45b4-ae3a-ff69cf747612.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=3lU4k50SiWQoQ6hWxKT8sUxvw2I%3D&amp;x-signature-webp=ZQD2rG2XojNCvJ%2BSTbJqa6pMR9w%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_1e2c0c59-fda9-45b4-ae3a-ff69cf747612.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=0d55mQKF8wuf3ueuEuwCBiBC%2FJU%3D&amp;x-signature-webp=Z1FqQkCkCHaGxIeQaWVx7%2FkBm0E%3D</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\682e09f76d1a46e79cb7f61c16406529.jpeg</t>
+          <t>Lib\hardware\data\images\31a419806cab4f88b82989a740a1f799.jpeg</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-plus-plus-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-plus-plus-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -5937,17 +5928,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_e96fd7ec-b826-46fb-9e12-bf86a0adc00a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=PVyfP%2BdYyAboT4OyRHQnibItZGs%3D&amp;x-signature-webp=JCRCfmx38jdTLCHmqIbNTNPRWjw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_e96fd7ec-b826-46fb-9e12-bf86a0adc00a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=Dr54KpKnYzSXHE%2BHalZcKP%2FPAjg%3D&amp;x-signature-webp=7ESjhNM0R2ov%2FZYJFmElvihEzzk%3D</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f5a6feaa0c6f4a5c90aec7e3cc2ed44a.jpeg</t>
+          <t>Lib\hardware\data\images\41d9e45d9a0e493c84450d8db46c497e.jpeg</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-r-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-r-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -5958,11 +5949,11 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>15035337971</v>
+        <v>15190731793</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bootstrap - Sticker Laptop Programming Vinyl Waterproof</t>
+          <t>Cutting Sticker IT Programming Programmer Coding Stiker Laptop - Vue JS</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -5986,17 +5977,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/77ae15f3-c056-41f7-94f4-c008303a79f3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=UMy4Cm0xlOPvfU3pdPWw61PpxFw%3D&amp;x-signature-webp=IacLZEH79jHm5bDVRniw3S2%2FJrA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/2c485272-3bc8-4c64-a8f0-baf8415b97e1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=OVt%2B62Y3D%2F9DOidY%2FLkSNFapioo%3D&amp;x-signature-webp=7ETSHH50cFbv1jkiPMlvcMI%2BOHY%3D</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5a5f119846a34551969bd9b9b2c19c5b.png</t>
+          <t>Lib\hardware\data\images\158fc34c28d74095b70dccd6bd4a2530.png</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/bootstrap-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/cutting-sticker-it-programming-programmer-coding-stiker-laptop-vue-js?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6007,11 +5998,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>15190731793</v>
+        <v>15035337971</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cutting Sticker IT Programming Programmer Coding Stiker Laptop - Vue JS</t>
+          <t>Bootstrap - Sticker Laptop Programming Vinyl Waterproof</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -6035,17 +6026,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/2c485272-3bc8-4c64-a8f0-baf8415b97e1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=Sb7aLIAbz%2FvbtUvEkpNd3nvk6yM%3D&amp;x-signature-webp=fUDt12F9BVdc9UJceajuzZLmtIA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/77ae15f3-c056-41f7-94f4-c008303a79f3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=ddfOEjrbneVwOR7BngysGsNWkIc%3D&amp;x-signature-webp=eRpjif2wryUkoUUHLRBoCz9%2FWao%3D</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c8c48e3e3a124b15bbc64407e9099e99.png</t>
+          <t>Lib\hardware\data\images\d53a74b3166a4d69ac29cc048271390b.png</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/cutting-sticker-it-programming-programmer-coding-stiker-laptop-vue-js?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/bootstrap-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6084,17 +6075,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/674d0478-bc6d-4c09-b6b9-88af31fea1d1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=c7dBDE9EiL0hwel%2FM1ql8Z33cmw%3D&amp;x-signature-webp=k9SW%2F1MMcqsDyfKsGtQYG07ne4I%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/674d0478-bc6d-4c09-b6b9-88af31fea1d1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=DydUmmkXMk%2FkplJC9iLveBBg%2BKA%3D&amp;x-signature-webp=A5wr0TZLC1FjpwHTGwFOWFFDfyo%3D</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1f7b6162cd8c465a9e887ea8036afc27.png</t>
+          <t>Lib\hardware\data\images\1c3d543714bc46109557358baf055024.png</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/linux-mint-cutting-sticker-it-programming-stiker-satuan-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/linux-mint-cutting-sticker-it-programming-stiker-satuan-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6133,17 +6124,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/22/d6a5263e-e87f-4f56-b43e-3b9544f68e28.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=MWS1qP7cd9TvCQrr%2FzhagBiRGDY%3D&amp;x-signature-webp=8iXhSpYO3MoiTuXTozfeuT44VwI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/22/d6a5263e-e87f-4f56-b43e-3b9544f68e28.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=7OGZTpL8BHh%2FuHt2vTWgZJZr%2FXk%3D&amp;x-signature-webp=h4ejyiUSMOoZM72qVGAc5hh6sQI%3D</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\49e71e0f4e1740ae9bd0b136e13a09d4.png</t>
+          <t>Lib\hardware\data\images\b104a28d68d04a6aa9e9d20e2d135e59.png</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-stiker-tumbler-laptop-stiker-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-stiker-tumbler-laptop-stiker-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6182,17 +6173,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/356b601d-1120-43ac-bc8d-f91265fff9b2.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=XWTL7wVFDBlQPRbYdz2MKWJxR9Q%3D&amp;x-signature-webp=jg%2FKfE5TcD%2B4rQVfUeu68%2B1a1HY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/356b601d-1120-43ac-bc8d-f91265fff9b2.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=npjVYYojjqfN7g69T1CIkCpq3mg%3D&amp;x-signature-webp=gX%2FiPbWxF0ZywsUCmYfByFT3YaE%3D</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a4ed2058d19e4de2ab19447627ebdeb8.png</t>
+          <t>Lib\hardware\data\images\6851c97a6ceb40a78cad32d74d014635.png</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/java-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/java-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6231,17 +6222,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/28/82978a46-7432-4e38-9f63-c39dee0f3ba4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=YR1slLCZ4jJ1CrrIyqg10UwMDvw%3D&amp;x-signature-webp=RIfj1n1zbvgQqnajTBZLPqD3Kv0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/28/82978a46-7432-4e38-9f63-c39dee0f3ba4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=nfJUFTNBhfpzv9FsJaIHdiikFZI%3D&amp;x-signature-webp=jGPdP9UtNW%2FgVe%2BcUhXFXnenXbg%3D</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c56f7a3072334defa123e4c620be3849.png</t>
+          <t>Lib\hardware\data\images\ae9c99a40f7f4eecbc5d20e90d361d43.png</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6252,11 +6243,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>15608613564</v>
+        <v>15614737477</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IntelliJ Idea - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>Spring Boot - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -6266,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6280,17 +6271,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/3b45f322-32f5-4b0c-858f-59219a51c153.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=KQcz6dpHoxoBop3BnFK%2BquEwVHQ%3D&amp;x-signature-webp=xXRZOXrUmYJWY%2B8Du1dlQFuktwE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/148d053d-e670-4ddd-bd5b-c5489f84c28f.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=Te9fBAncdDcYmRzTn0W8M7VvrfQ%3D&amp;x-signature-webp=0nvHFkZ4RXUJi0E5yQqMrXcIBd0%3D</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d32f2dde20f544aeab74c31d72dd9c3a.png</t>
+          <t>Lib\hardware\data\images\d648cfb0bb4c480db4a07c3cae2d7387.png</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/intellij-idea-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/spring-boot-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6301,11 +6292,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>15614737477</v>
+        <v>15608613564</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Spring Boot - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>IntelliJ Idea - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -6315,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6329,17 +6320,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/148d053d-e670-4ddd-bd5b-c5489f84c28f.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=GKk2eUxqn9MkEjO2UU4DO%2BHj1EM%3D&amp;x-signature-webp=03Ih%2F6HlH3RauyGBevoeoFGlMjY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/3b45f322-32f5-4b0c-858f-59219a51c153.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=%2FeiCcByGsvZSQcYZ%2BckkE1sUOYs%3D&amp;x-signature-webp=HMkMF%2FyXVmHq87a3KncEEl0d2zM%3D</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\748467be2e254005b47eb62ff30c6671.png</t>
+          <t>Lib\hardware\data\images\9043348431574da8a5940bc4c5ba3971.png</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/spring-boot-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/intellij-idea-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6378,17 +6369,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/bd6bf479-e882-4ed2-a264-28c75b168c29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=JnJxAtqQG1bFHAIMIc7QCcff1PU%3D&amp;x-signature-webp=vmr8Bqx85qDsvNs1ia61kIIzEKg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/bd6bf479-e882-4ed2-a264-28c75b168c29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=n%2BySOa%2B8CkVf%2BM%2BHqYJqNfnMx38%3D&amp;x-signature-webp=yb8hizbZn35QOWxrUaMbzK3O3RY%3D</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3a31217a0600452d9d65d674cce3fcbc.png</t>
+          <t>Lib\hardware\data\images\e8a3296c27ca451b9ffe2e0747e9b346.png</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/css-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/css-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -6427,17 +6418,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/722bc896-e581-4919-9192-737948477d10.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=t2kqHwouH2O7pzO8PrjBsyPVaR8%3D&amp;x-signature-webp=oLZFBT4uOdoOWJShKQhXwroUGug%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/722bc896-e581-4919-9192-737948477d10.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=BoOyR3lAGPF%2FicM%2BJ87qtm5iheE%3D&amp;x-signature-webp=T6pq1ZWq3L7lO4QcaSJmXBtg4hU%3D</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\56f65d5e8d2f4d81bd709efed8760a01.png</t>
+          <t>Lib\hardware\data\images\ec04dcf2d96a46c3af8402146351e3c4.png</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/meta-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/meta-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -6476,17 +6467,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/32a21bef-6229-4a57-8094-a707c4210ac4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=vR6w9%2F%2BxaWoS0h8q%2BFGgHmrnpM8%3D&amp;x-signature-webp=gxWOwgBgNRSFwKeqG4EZQPvFgPk%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/32a21bef-6229-4a57-8094-a707c4210ac4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=nGEne89u6sQztNQYCIkw0FDyNRg%3D&amp;x-signature-webp=4GDprLUP0MSfa1JtN4aEwz39tkw%3D</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dfee2a3211c54e97b904f9574c846fea.png</t>
+          <t>Lib\hardware\data\images\ac6734bb540045f68457a6825d155ee4.png</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/php-cutting-sticker-it-programming-stiker-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/php-cutting-sticker-it-programming-stiker-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -6525,17 +6516,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/247f6d04-d1b7-4b0a-b69d-44df83a98403.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=jqFXDKygtnZSXiWxCqGgpoCu9JE%3D&amp;x-signature-webp=4oi7w%2BKLw2ejRUHXU9nUOZwrdI0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/247f6d04-d1b7-4b0a-b69d-44df83a98403.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=pOUOofBL%2F0Bc6b2y65kjJgJ4SsE%3D&amp;x-signature-webp=712b7%2BdCKat3JCXqhW8RHVIdR4I%3D</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c66341e0599f49918fde5e6ae05b045d.png</t>
+          <t>Lib\hardware\data\images\b16a0fb83d8f4749ba4cea0c7ba638fa.png</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/ubuntu-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/ubuntu-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -6574,17 +6565,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/fd492c8b-c24d-42f6-9532-4ec429fe91c5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=DJi9JyM1yGy%2FFc3THok06fCpwIk%3D&amp;x-signature-webp=igaL4Y5wEpWZxm34wlHa8E7aJ6M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/fd492c8b-c24d-42f6-9532-4ec429fe91c5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=248LWiRCs1SlzHUJswd3BDRPycY%3D&amp;x-signature-webp=HioBfj%2B2cIo6CzqaXwU8G5oE9bc%3D</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2e26e14ca84443c08a337a16f30561ea.png</t>
+          <t>Lib\hardware\data\images\aa80faeba01e4e0b9f982af440d1117a.png</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/kali-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/kali-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -6626,17 +6617,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e016ed68c334c7cbc4f8e994d90718b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=zOeB%2Btz27dJfVueSihnBW7PPOwQ%3D&amp;x-signature-webp=y9f55FiDh2bRy1rbJw0EQS3lsTY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e016ed68c334c7cbc4f8e994d90718b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=vvYqP2yuXkDDT6BA0I4HF8BFm6A%3D&amp;x-signature-webp=Q41PdTSl1REtd9PAbOhvpeg3rBM%3D</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\44b7259ad0d94baf9184cf5fc266ba40.jpeg</t>
+          <t>Lib\hardware\data\images\5ccdac0d295548f99ce75ae2c756fd3d.jpeg</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/indoluxdigiprint/programmer-sticker-pack-50-pcs-stiker-code-komputer-anti-air-sticker-coding-computer-it-programming-laptop-hp-paper-1729751165829088355?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/indoluxdigiprint/programmer-sticker-pack-50-pcs-stiker-code-komputer-anti-air-sticker-coding-computer-it-programming-laptop-hp-paper-1729751165829088355?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -6675,17 +6666,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/6dc31a5b-13dc-461c-affd-cb836b3d7649.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=hZ%2F2qCshaDOVnhnpMpWrUOVnF%2B4%3D&amp;x-signature-webp=YoUFuKjGoZQI0TX55BebTOGCFz8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/6dc31a5b-13dc-461c-affd-cb836b3d7649.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=bV6JWckb8%2BQtdh3WxropwKY6bCo%3D&amp;x-signature-webp=LA4t3KjyUh7x0126lxssNbLj2uo%3D</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8d11d91894f748e19c70711147963af7.png</t>
+          <t>Lib\hardware\data\images\018e3c5c23174d78abf5d9210abe7dc2.png</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/html-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/html-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -6724,17 +6715,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9e56cad1-941e-4da1-b48a-271cbe36ab77.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=8waJ7VeeaQEmkJUsZL1RrvhW508%3D&amp;x-signature-webp=YfGubPqxHrTKvy4SRFjn%2FoUvBPw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9e56cad1-941e-4da1-b48a-271cbe36ab77.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=LroUuXoGhAerwItPaWnLYzEwIOY%3D&amp;x-signature-webp=nfkGv6Y3OXFZQdMF5NXlkRbjWPA%3D</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7ade71aca3134ec08760a5c3998457f1.png</t>
+          <t>Lib\hardware\data\images\f7b194db1bb948fdb9cb69bb0ae1b11d.png</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/debian-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/debian-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -6773,17 +6764,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a26ba20e-d4b0-45e2-8d41-247e37e6a478.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=LZE%2B8dS5C6eImLlURH6kQc4QKNo%3D&amp;x-signature-webp=JF8UTmLlAp4gTRo54uUgivpVR6Y%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a26ba20e-d4b0-45e2-8d41-247e37e6a478.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=cLif2IJZSGap%2FKas1DfL%2FYiktjo%3D&amp;x-signature-webp=ZDlk61ABpHF3%2FsOdzbTiRfvDGFs%3D</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a5c79d0d9f98469cbe9a8c679f23053b.png</t>
+          <t>Lib\hardware\data\images\f282e53bb6e64a388fb6db5c8f435b19.png</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/cpanel-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/cpanel-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -6822,17 +6813,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4aa5f4f-ae42-4541-81f3-1421c0a92ee8.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=D%2Fb2CUdoxM5gw6jrw4Vch5kEtwM%3D&amp;x-signature-webp=QNFgu0Cg3nPQOKhPd6bFmvCQbvc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4aa5f4f-ae42-4541-81f3-1421c0a92ee8.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=bHXzHCAzigygjrnRMH0caeCG8i0%3D&amp;x-signature-webp=ht%2FglEMGoUJ845yH9aNG97b%2BttQ%3D</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e440ef669ad44185b5f0ea455b276648.png</t>
+          <t>Lib\hardware\data\images\55fd024974dd4b1a86100b764898c3ee.png</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/js-javascript-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/js-javascript-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -6843,11 +6834,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>15608655266</v>
+        <v>16316426699</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JetBrains - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>Python Language - Sticker Laptop Programming Vinyl Waterproof</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -6857,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6871,17 +6862,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9441c648-abf5-4189-bda6-523c5625881e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=6SAEIPnTmgF3o9LBDRhsJwwHi6s%3D&amp;x-signature-webp=vxi9AkkeaFBt2Poy2pP%2Bk8WydPE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4f53049-4d44-4b49-ae9e-b4a06d7aa864.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=%2BSidVcVk7zFWM5TRi3H0OQwIPm4%3D&amp;x-signature-webp=fUzgF%2BGkU9KVWCJxadrzbuZjbgI%3D</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b96f85b33da24d63a6b2f6c938c73fb9.png</t>
+          <t>Lib\hardware\data\images\849f8ea03d74492e8e4812fa9aa31386.png</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/jetbrains-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/python-language-sticker-laptop-programming-vinyl-waterproof-1730910518060090930?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -6892,21 +6883,21 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>16334892715</v>
+        <v>15029163749</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Android Developer - Cutting Sticker IT Programming Coding Programmer Laptop</t>
+          <t>C++ (Plus Plus) Language - Sticker Laptop Programming Vinyl Waterproof</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6920,17 +6911,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/487fec30-5abd-485d-90e1-97aa59e4dc8e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=61lDn8JAE9aJQY4XWmYWfon%2FIgM%3D&amp;x-signature-webp=7nRlJqF%2FMcrmv2jfuiUiupB8trc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/52e270bf-8f13-4743-989a-135d563c7c13.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=YWsjuC2tj4hMi3cyOQHEGhNE3Y0%3D&amp;x-signature-webp=D%2FVI9EMooxyDDpr5BB0azyAnlgE%3D</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cb7c822bc4314233991ba82f8e86215a.png</t>
+          <t>Lib\hardware\data\images\d24860ceb5ea40e1956f638e0114bbcc.png</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/android-developer-cutting-sticker-it-programming-coding-programmer-laptop-1730925852202665522?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/c-plus-plus-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -6941,11 +6932,11 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>15029163749</v>
+        <v>15608655266</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>C++ (Plus Plus) Language - Sticker Laptop Programming Vinyl Waterproof</t>
+          <t>JetBrains - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -6955,7 +6946,7 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6969,17 +6960,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/52e270bf-8f13-4743-989a-135d563c7c13.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=Vf38crBS7My%2BfMk1UCvCjxk4Q6o%3D&amp;x-signature-webp=ovjUJriV%2BtMPhlq7DtMMq5GKbl0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9441c648-abf5-4189-bda6-523c5625881e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=6g8jSS0p7V2%2FgALUYHsjVvbAFzc%3D&amp;x-signature-webp=B0ASe53DEccE%2Bv00XOfQWprek6o%3D</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9adc5f69d85b4b76bd37cb0bb2135ce7.png</t>
+          <t>Lib\hardware\data\images\342714d1a24749f787a6509a490bfc46.png</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/c-plus-plus-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/jetbrains-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -6990,21 +6981,21 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>16316426699</v>
+        <v>16334892715</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Python Language - Sticker Laptop Programming Vinyl Waterproof</t>
+          <t>Android Developer - Cutting Sticker IT Programming Coding Programmer Laptop</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -7018,17 +7009,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4f53049-4d44-4b49-ae9e-b4a06d7aa864.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=WrTuLfC3REe2HbSil7oImLnW%2B6o%3D&amp;x-signature-webp=ogxi7nihXIoK0mxBQfxTE8RGhhE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/487fec30-5abd-485d-90e1-97aa59e4dc8e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=9llais5eSC8rzcFuZ1YzoI7rJ9o%3D&amp;x-signature-webp=l2n61o2mhoMKrMlpVFvAac2dIwc%3D</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c3504150c14441cbab3df8e1c13a84b8.png</t>
+          <t>Lib\hardware\data\images\61bad602417f4103bc533f81698d1db5.png</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/python-language-sticker-laptop-programming-vinyl-waterproof-1730910518060090930?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/android-developer-cutting-sticker-it-programming-coding-programmer-laptop-1730925852202665522?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -7067,17 +7058,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/5e031a76-a3f2-4fc1-940b-4150386d8618.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=W8lBp8jE92DacisOq0YKl1aQxc0%3D&amp;x-signature-webp=g9yskzOP02dEf4QGIje0Y0YqiDk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/5e031a76-a3f2-4fc1-940b-4150386d8618.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=RzfAIhMQ24r%2BAdWkULcPryqhJLQ%3D&amp;x-signature-webp=%2F7BDE4Jr924yd2tO%2FYvpgLBoe9c%3D</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\14b2c5d1ef534d21b1e265fa1a894211.png</t>
+          <t>Lib\hardware\data\images\ade8c1988d8647069f910ee5b28f5905.png</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/tux-linux-penguin-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/tux-linux-penguin-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -7116,17 +7107,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9f70aa88-0b3e-4f1a-b1e2-ff8c1f724f83.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=bKwDaz%2BlKzXlAbHM%2FkBui0p8BEE%3D&amp;x-signature-webp=IvLCpEqGOvMT9ZBK5QiwgjZ4s5U%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9f70aa88-0b3e-4f1a-b1e2-ff8c1f724f83.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=KbZR51mLXTiCkWi%2BqEIexk7GZcQ%3D&amp;x-signature-webp=yEJX5WQ2KO%2FPnknZuBX4tTD%2Frtg%3D</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b840de28ee6844f68ae823c54458fd43.png</t>
+          <t>Lib\hardware\data\images\ea9f2aeb60d644ee83358c91b5eb96a2.png</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/google-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/google-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -7165,17 +7156,17 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/05097cce-f0d3-41a1-9a3e-dc787f21a1bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=mBF2lO0JqC3T38lZRJ5fgaCVjkg%3D&amp;x-signature-webp=ulb5D6Ze4B20JJKVuMhCiQCsztk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/05097cce-f0d3-41a1-9a3e-dc787f21a1bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=2Bxh35LVOUYGNqroHdNxNT1ETn8%3D&amp;x-signature-webp=%2FGAzPOwZIS60z8prEooZu68M7vk%3D</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\19758cd4135547c0b28436997d75dddb.png</t>
+          <t>Lib\hardware\data\images\541468fa04a74b65bdaf108f0afb4962.png</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/arch-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan-1730778695673939506?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/arch-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan-1730778695673939506?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -7214,17 +7205,17 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/d2e910e6-71e1-493a-9ad0-7e644045fa68.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=lAX52r8fo6aCpzSY0tFXNdH%2B5q8%3D&amp;x-signature-webp=hkKwprYz7onrmq2FYwa0vIM07cI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/d2e910e6-71e1-493a-9ad0-7e644045fa68.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=zK%2BVrXVq0J6jqGaI1NOY2w6arjo%3D&amp;x-signature-webp=ojtkPW0VmSS8Y3kthURtwJEQ01M%3D</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\568089f26a7342baa4201f979e265969.png</t>
+          <t>Lib\hardware\data\images\9c609fd41d054e7e9b6644dcf42ab989.png</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/fedora-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/fedora-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -7263,17 +7254,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/9/29/f8d3eab6-1d0d-4a33-8e74-ee48be7014e1.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=KeK%2FnSwFCUaGkBxdZnhmWiklYsQ%3D&amp;x-signature-webp=RWa5xuuEWSK6B0gZ1a5F%2BiCS9tA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/9/29/f8d3eab6-1d0d-4a33-8e74-ee48be7014e1.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=UbggHrLguGU1qV9LXtdWVIS12MU%3D&amp;x-signature-webp=3kB5yzBR2t4OL504R7PLOxFrULc%3D</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4dcb32ad34a040fe986fca13d2edb51a.jpeg</t>
+          <t>Lib\hardware\data\images\d502dbcd494e4779832ba220aca068c6.jpeg</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/archive-zhanghua-1630738705/stiker-programming-java-php-linux-bitcoin-ubuntu-geek-untuk-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/archive-zhanghua-1630738705/stiker-programming-java-php-linux-bitcoin-ubuntu-geek-untuk-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -7312,17 +7303,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/d7dbbf07-cde0-4b81-a809-7c268bac8704.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=x4NcaVcmTol6p9dQ7q5D8u1s27g%3D&amp;x-signature-webp=B8YjGLLWBmWX5aOJ10l%2B4SaC%2Bwk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/d7dbbf07-cde0-4b81-a809-7c268bac8704.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=KVuZwgblPIqvoJck4G1m%2FmrZwgc%3D&amp;x-signature-webp=QaqcMFOTBvK%2F8Yd%2F4a7l9J%2FldH0%3D</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\de21e7a2f1b041a38af5628eeb7be66d.jpeg</t>
+          <t>Lib\hardware\data\images\6f0855c7518946349d3865ba0f492767.jpeg</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/coffee-sleep-coding-game-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/coffee-sleep-coding-game-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -7361,17 +7352,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/3c9c2511-b651-4389-846a-da1c078d510d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=PFmz%2FkwBuYCpX6a7HrunCAymktE%3D&amp;x-signature-webp=ayzyjgBRitvZS911layvXp%2BrKgk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/3c9c2511-b651-4389-846a-da1c078d510d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=Hjx5xXtEV702tWghN4dcRAwREzM%3D&amp;x-signature-webp=Gv%2F9YUaET7XMyLDLYkxSGBa7K%2FQ%3D</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\90e3d63bef0644eab3fd20b9ee607aa5.png</t>
+          <t>Lib\hardware\data\images\a0b1892d9579477f89e3dce966fb2f78.png</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/sticker-sheet-a6-vinyl-waterproof-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/sticker-sheet-a6-vinyl-waterproof-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -7410,17 +7401,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/c6cbe66b-30fb-4b15-9a7b-cdba7bdb6344.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=SMQPHQK7xd1oCz9hRuM0HWRkBkI%3D&amp;x-signature-webp=4YMlUQhjYhsVQGebY7uypCWZCaU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/c6cbe66b-30fb-4b15-9a7b-cdba7bdb6344.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=8mt6Q0tcaWB6ZGpwu4hL%2B%2Fs%2Bu0Q%3D&amp;x-signature-webp=9n9mB40sF3TaSjoueFxGl32gdwI%3D</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f691f479daee4f0e9261d313ef89be4e.png</t>
+          <t>Lib\hardware\data\images\230fd8d8122c45f9bc4fae2fbb2ac66b.png</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/full-stack-developer-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/full-stack-developer-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -7462,17 +7453,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e83fe7fc87c4ce6ad067de5078f19f5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=HySjm2Dw45rs6KJVT2VtCGKdOHY%3D&amp;x-signature-webp=2gez%2BPdI67l%2FYpt30tp0DTXoUwc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e83fe7fc87c4ce6ad067de5078f19f5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=dawYfT%2FNkEW3lrWfWoy7KJCDd2w%3D&amp;x-signature-webp=2GNpzxDQZqn6%2FaDILEb%2BQU%2F0DxM%3D</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c4b217517f0b48bb9ca776931bf5c86c.jpeg</t>
+          <t>Lib\hardware\data\images\c9cdf5c835f7433b8adce0a0b0158e7a.jpeg</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-untuk-scrapbook-tumbler-hp-laptop-motor-helm-koper-1730766186130146514?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-untuk-scrapbook-tumbler-hp-laptop-motor-helm-koper-1730766186130146514?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -7514,17 +7505,17 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/364156f76e624431b6c3dc72dd64ecdc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=DPeUUJBOY0MU8HuOoVZmPP%2BVJ%2Fs%3D&amp;x-signature-webp=QIR8ZozEfVYILDJwkuXLLY%2BOTx4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/364156f76e624431b6c3dc72dd64ecdc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=4gIjG5a7A1aA25U46aDU8Hyu3Tg%3D&amp;x-signature-webp=lwrLQKq3vjulkIynpfd37O5Nzi4%3D</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\25de462eb4a1419da6f6236a90389960.jpeg</t>
+          <t>Lib\hardware\data\images\d6ec1290f97d4c26ab4fa1b7e67aaf52.jpeg</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-meme-plesetan-untuk-scrapbook-tumbler-hp-laptop-koper-motor-1730770027949688018?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-meme-plesetan-untuk-scrapbook-tumbler-hp-laptop-koper-motor-1730770027949688018?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -7563,17 +7554,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/265be12a-181a-4c2e-85ad-c6544f36203e.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=QyEFn2ZPY6DwJaVTqOVFBy53rq4%3D&amp;x-signature-webp=E2Pe72LSne%2FvebRsLg8kAYj50%2Bs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/265be12a-181a-4c2e-85ad-c6544f36203e.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=vTb6oDywaW56oWyFTzDaZOWWuCg%3D&amp;x-signature-webp=x%2BGoWwvG4MwDtfDNM8Urv%2Bc5sjw%3D</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\937b715199564274884e984bb5f812fc.jpeg</t>
+          <t>Lib\hardware\data\images\44d5074ffd154f718a495318e0bbd574.jpeg</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/vnylarc/saas-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/vnylarc/saas-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -7612,17 +7603,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/4020a1f4-6c92-4356-8439-3db0af377f5f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=78zT6VkjndBWdHr9kcGeKd7dLL4%3D&amp;x-signature-webp=6GkBroIXMvFTgmNdqpdvDHUiLm0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/4020a1f4-6c92-4356-8439-3db0af377f5f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=7cRebCkXSd0DRhrlcWMdoVh6hJE%3D&amp;x-signature-webp=1VoupfHHuqDi7%2BdnjUncrnaJ%2BP4%3D</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\051a15b5f160447ab97723931e5a2e1d.jpeg</t>
+          <t>Lib\hardware\data\images\7f371efec9de418aa5b0b4020f21ecb8.jpeg</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/vnylarc/golang-icon-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/vnylarc/golang-icon-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -7661,17 +7652,17 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/4/4d205830-0c3f-4681-a668-c1d10845afb5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=W4h%2FdstG5oUt9uJ7KEJTRgRZWaw%3D&amp;x-signature-webp=aj6XoQaqcGBhXaCssDeQhisPC1o%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/4/4d205830-0c3f-4681-a668-c1d10845afb5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=voiVC%2FUGYzIM2PV7%2FE9SOwcuKr8%3D&amp;x-signature-webp=O1KVkmod1EUHm5RaPZZkpluA6X8%3D</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\76f76c48c4e349089ea2d41c861ece81.jpeg</t>
+          <t>Lib\hardware\data\images\2198932893b944e0b6d25d61b83eadd3.jpeg</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokopedia-tokolaris/sticker-pack-20-pcs-teknologi-programming-untuk-laptop-tumblr-helm-first-edition?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokopedia-tokolaris/sticker-pack-20-pcs-teknologi-programming-untuk-laptop-tumblr-helm-first-edition?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -7710,17 +7701,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/0bd6c17c643c4ba8875360f0f7dedf05~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=YS5nJzPeEA0PCjWlDLt5U6R7YRU%3D&amp;x-signature-webp=4NtwapGV0z2rdZZ6DlAbWL7wqO0%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/0bd6c17c643c4ba8875360f0f7dedf05~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=zeW3pqrWS3I%2Bbbee5fAI4cve9PQ%3D&amp;x-signature-webp=IqqJaQlnB4xD7YMle%2FcBYTd9S6w%3D</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b9df8e11400b45178e1901d0a5d9cc9e.jpeg</t>
+          <t>Lib\hardware\data\images\2fd5a55ce893450bbf82f3dfba22da93.jpeg</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -7759,17 +7750,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fe66c8e873de4883aa66c310f1cb065a~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=BHVOmtnfuo7RTR0KPd8UPChv3lQ%3D&amp;x-signature-webp=9EEwUemQikwo7IFydIH5RfQWS%2B8%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fe66c8e873de4883aa66c310f1cb065a~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=Fmoiq1SwZFu157oV%2BgDaocXYDg0%3D&amp;x-signature-webp=7sdf2fHpoCvsRxtvotfOCET8eJE%3D</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7361efd0ca064ecaa1738d12cf472efc.jpeg</t>
+          <t>Lib\hardware\data\images\4ca037f34377469dbbf50eaeddca01eb.jpeg</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programmer-coding-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programmer-coding-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -7808,17 +7799,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d1f458121310473e8394b993711abd3b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=9bgLMo0cdUyNCryAMtdhfdOTp6k%3D&amp;x-signature-webp=lAb9G8YInimO9vynn9Its2qkayU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d1f458121310473e8394b993711abd3b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=sRkYAPtuktITZ%2Fz4XxmPSv%2FHWQM%3D&amp;x-signature-webp=XBHjAlUj3YIlp8Ip2T%2BeuNktZ98%3D</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\df34c40844a34f5fad9ce78ee5d65d49.jpeg</t>
+          <t>Lib\hardware\data\images\1e166743dc4f4d3ca04bbc5516744d7d.jpeg</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/auto-diagnostic-programming-tool-expert-mode-for-icom-next-software-v2023-09-1tb-mini-ssd-windows10-laptop-cf-ax2-8g-d-4-43-1732688398569998202?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/auto-diagnostic-programming-tool-expert-mode-for-icom-next-software-v2023-09-1tb-mini-ssd-windows10-laptop-cf-ax2-8g-d-4-43-1732688398569998202?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -7857,17 +7848,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/10d441e1e3db48d184effed1bc09575b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=bokgYZm1iSyd71w19wsi4j8c0o0%3D&amp;x-signature-webp=hIkudiCY%2FVDJzybkTWvmsvkjgNE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/10d441e1e3db48d184effed1bc09575b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=kNGiGm6RnzOTcd3%2BmDqOf1OtukU%3D&amp;x-signature-webp=olFtVEoGYEYUnw3AAnoO7ZHb6do%3D</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c745c4a6106f47d1a8eb8940a724e698.jpeg</t>
+          <t>Lib\hardware\data\images\93b07a07077f4845aa082a163847a1fb.jpeg</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/new-for-icom-next-a-b-c-with-v2023-09-software-expert-mode-installed-d630-4g-laptop-for-icom-next-programming-tool-1732688989206054778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/new-for-icom-next-a-b-c-with-v2023-09-software-expert-mode-installed-d630-4g-laptop-for-icom-next-programming-tool-1732688989206054778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -7906,17 +7897,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e5f3a470390d4bcc88c465e59babd2ea~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=dCfw0%2FSUDORzOnHU5dzWAs6PEmA%3D&amp;x-signature-webp=YCF815aGCjGm%2Frztp9ZRCgNqGc0%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e5f3a470390d4bcc88c465e59babd2ea~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=wgxi%2Bo0Om97%2FEQHJmEuA5ecSUN4%3D&amp;x-signature-webp=vvPw727qksx6k6k7xOcKEA8Ad0Q%3D</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6a2aa1a9483c4285bb5b611987300c36.jpeg</t>
+          <t>Lib\hardware\data\images\657a84720dc84ba68e6dae686958d736.jpeg</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/cfc2-laptop-for-jlr-doip-wifi-car-diagnostic-tool-support-new-car-profesional-auto-programming-tool-1732690386628020090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/cfc2-laptop-for-jlr-doip-wifi-car-diagnostic-tool-support-new-car-profesional-auto-programming-tool-1732690386628020090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -7955,17 +7946,17 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43b554c10baa4e20a7f9e75f23312185~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=SrlPlZ%2BvbDtqchjj33XfCrarGqU%3D&amp;x-signature-webp=VhCcdnS8NJIustGljsNxm6LNzhQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43b554c10baa4e20a7f9e75f23312185~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=ECyEztQUr6uylrgA9ZD0qbqz0W0%3D&amp;x-signature-webp=Br6RuE23mxndt%2BVvBJLjwKhmSWM%3D</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cd73e76b3c0a408996c4ae16b782de6a.jpeg</t>
+          <t>Lib\hardware\data\images\e9781ee4e4824b9c8d4d2e0033faf2e1.jpeg</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/car-diagnostic-tool-for-jlr-doip-v-ci-wifi-with-cf19-laptop-support-new-car-profesional-auto-programming-tool-1732690368491587450?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/car-diagnostic-tool-for-jlr-doip-v-ci-wifi-with-cf19-laptop-support-new-car-profesional-auto-programming-tool-1732690368491587450?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -8004,17 +7995,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c27b24e4e8a149f8afdec0aef9a21471~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992065&amp;x-signature=SjUkIKzoMfuaiJGtsby5%2Ftqrr18%3D&amp;x-signature-webp=WXmzl7g1rA79Rt2kpDCTJi2N2UE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c27b24e4e8a149f8afdec0aef9a21471~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=l%2FAygdCJ%2FE86rSD%2B790TR7ergpg%3D&amp;x-signature-webp=h0fBfmKIIBMk2rb4HuLHBXcI7tc%3D</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\47ae3596b2bc4f43a41ef7fd1fd23723.jpeg</t>
+          <t>Lib\hardware\data\images\36c70f92f2454a3582272119ef84ca15.jpeg</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/for-icom-a2-with-full-cables-professional-for-diagnostic-programming-tool-with-software-720gb-ssd-win10-in-x220t-laptop-1732688342876587898?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251124124745B3967A0E938DC2141ICF%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/for-icom-a2-with-full-cables-professional-for-diagnostic-programming-tool-with-software-720gb-ssd-win10-in-x220t-laptop-1732688342876587898?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -8042,7 +8033,7 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -8056,17 +8047,17 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/0e0094f8-4e21-4aab-b63e-25e6f39a9a2d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=DsuviELMq9mN0O685eDHZtUjdXU%3D&amp;x-signature-webp=VSzrOYji2Oegk6NdrwHhwGXxWaE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/0e0094f8-4e21-4aab-b63e-25e6f39a9a2d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=bolxUY%2FMBXtIR%2F7oZtbBG9w0eEU%3D&amp;x-signature-webp=X8teRCQEIelW%2BZ8%2Fdjzr%2FWmA4jU%3D</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\61ac58e30fea4c599e223329123f350c.jpeg</t>
+          <t>Lib\hardware\data\images\0fcb688670b04e7099c2ee717cfb57e7.jpeg</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/housesparepart/jakemy-jm-8183-145in1-obeng-set-hp-torx-laptop-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/housesparepart/jakemy-jm-8183-145in1-obeng-set-hp-torx-laptop-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -8105,17 +8096,17 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/18/2e15fe28-10bf-41e9-868d-6cb423cd4c8c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=M4TaZka2R52dlsPdpQuuBl6CdWk%3D&amp;x-signature-webp=KeKozfaaK22X2yVpe5d3pL5DBcg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/18/2e15fe28-10bf-41e9-868d-6cb423cd4c8c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=qgKshWK20I%2ByKeCRimNfxvHRTX8%3D&amp;x-signature-webp=SzAMBXjIl82DOzVManiqYCDBxSY%3D</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8331a354bbf24b609cc3b4a2115a8dda.jpeg</t>
+          <t>Lib\hardware\data\images\7bae09a49cab4d0ea393f1b7b06f85a8.jpeg</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/ezren/jakemy-jm-8183-screwdriver-set-hp-torx-laptop-computer-new-design-145in1-1730880897306690560?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/ezren/jakemy-jm-8183-screwdriver-set-hp-torx-laptop-computer-new-design-145in1-1730880897306690560?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -8157,17 +8148,17 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/660a3068-b7f9-418c-8ac3-25c629b1e0c7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2FPzQw7Ziqa%2BeH6Cv361OK6rTKKM%3D&amp;x-signature-webp=GEeMGB5WAPLKajxKBAKQ8%2FouCek%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/660a3068-b7f9-418c-8ac3-25c629b1e0c7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=Uab5sskUDosc1kS70xPT7oS5wvs%3D&amp;x-signature-webp=n4ZZg6Le1nnSvZ0%2Bw5NelX4Z5Ws%3D</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f7099ee1fa5b42ba9112d0a85134a46c.jpeg</t>
+          <t>Lib\hardware\data\images\f6f8992d3bac4e02b18170d4daf2d4fd.jpeg</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jakemy-official-store/jakemy-jm-8183-145in1-obeng-set-hp-laptop-macbook-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jakemy-official-store/jakemy-jm-8183-145in1-obeng-set-hp-laptop-macbook-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8209,17 +8200,17 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=j3Q%2F9Pw1Svs%2B28cAfYI13btKX%2BU%3D&amp;x-signature-webp=tjahuipkB2I0RpXyF6DYu2lJbdo%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=mE17jNqUeNsts5SpGaXD75817bE%3D&amp;x-signature-webp=Rhx7x9kQ5b%2FGkTPRPBJZC3ES2oc%3D</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5e8b6796230345f3a2b6036fe9bf4fe8.jpeg</t>
+          <t>Lib\hardware\data\images\4d061f45531348afa5a07d014e5b7b61.jpeg</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8258,17 +8249,17 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f261db1a485a484fb269a53c633ed896~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=XVItsvOX0TIcvub4bR18jVMgwAk%3D&amp;x-signature-webp=LhYziQm1F8Aj5bxPlCufiWZNV4c%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f261db1a485a484fb269a53c633ed896~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=WRYQfRSaAWTobriDKGh7xNJWOb8%3D&amp;x-signature-webp=ELOGKTKwBkfLlKbz9yLDt9rz2eo%3D</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\323ebd874f1844f3b832449822ecfdd5.jpeg</t>
+          <t>Lib\hardware\data\images\b1d66123cb1d48b68ba888306905b7c3.jpeg</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/bobby-soft-daypack-water-repellant-backpack-by-xd-design-tas-ransel-laptop-original-unisex-black-bfd8e?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/bobby-soft-daypack-water-repellant-backpack-by-xd-design-tas-ransel-laptop-original-unisex-black-bfd8e?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -8307,17 +8298,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/8b7fcd6f-843a-4f43-9ed7-23b395be8bf8.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=GidEWHHKpo1vcWDhI78L%2B2CyYXo%3D&amp;x-signature-webp=xni7WdZxPtPhpr1417dpGyr1r70%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/8b7fcd6f-843a-4f43-9ed7-23b395be8bf8.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=h%2FZInJU%2BuhupqwmzHTPbzZjTr%2FA%3D&amp;x-signature-webp=ma35NsC7Hl817PU0NXhTkgEYrcE%3D</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\688fe650744048c0b6b91e68480e6bcd.jpeg</t>
+          <t>Lib\hardware\data\images\cf840eb2cef84d5287abbc238d8bba2a.jpeg</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-bag-black-1731594664039319238?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-bag-black-1731594664039319238?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -8356,17 +8347,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/32274fe1-96e5-4c4b-b9a1-8a54ed3cd196.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=L%2Bav3h9od2y90hSbFc9vaEKjYuQ%3D&amp;x-signature-webp=zokYByCIt%2Fe9bIQ5T8OFyds97aU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/32274fe1-96e5-4c4b-b9a1-8a54ed3cd196.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=IOnk2vg47P%2BjaZ6p5g5mE%2F6jeBE%3D&amp;x-signature-webp=T6ORs0VZA%2FZhO%2Fb5wF9c29vBEQw%3D</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\90528e9d11f9451ea46e571a0ec4a8d5.jpeg</t>
+          <t>Lib\hardware\data\images\35e51725059a4909aaeebe20c428c3ed.jpeg</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-sleeve-1731594608912926406?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-sleeve-1731594608912926406?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -8405,17 +8396,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/20/d1423af4-f39b-45ce-a5e1-4e98654a57a9.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=nH3SPrTYcUEZpoWvzUtkelyWsis%3D&amp;x-signature-webp=nPYzpHfg795ifZx%2BYOfix5Py8rU%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/20/d1423af4-f39b-45ce-a5e1-4e98654a57a9.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=rbXb7tIrdorRzmmySfq5v0MRWmM%3D&amp;x-signature-webp=pKiRr%2B9fWlfFjv4Eu4o4uRLiYW8%3D</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f2c4e491f7834c548ad2af469457aa1a.jpeg</t>
+          <t>Lib\hardware\data\images\6e8916eb5bb246eea5179a592b305d13.jpeg</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-laptop-original-off-white-987cc?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-laptop-original-off-white-987cc?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -8454,17 +8445,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/74672521-d63c-4345-8d7c-1a4c6d44107d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=MdgFRX7cnrUUVfXrTdLJX%2FbifI8%3D&amp;x-signature-webp=klw%2FQqkavhksfp3Izk51n1pRdT8%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/74672521-d63c-4345-8d7c-1a4c6d44107d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=QKgC3WhaiI%2BX3k6CISW3d216eNA%3D&amp;x-signature-webp=sANKFb5hF9eUnkLZPOxYSRvhjVI%3D</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9fb965837d174fdcbd4f8443944badf3.jpeg</t>
+          <t>Lib\hardware\data\images\e488bd4b22594145a19782a0f8034831.jpeg</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-14-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-14-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -8503,17 +8494,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/0cb9f188-7016-4eff-b964-b13b4f39e7be.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=ww0GRAi6rPabDa%2FUHkWJ9hzDab0%3D&amp;x-signature-webp=pM2Ywci1F7pLi%2BQL5x0HQjEKJYg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/0cb9f188-7016-4eff-b964-b13b4f39e7be.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=uijPizvB9%2F65IkgLEy0f%2Fd9l1EY%3D&amp;x-signature-webp=wEVpFnjo5urq0d6nX2PkkhMIG%2F0%3D</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3075d85ebac64eda80f6e8882e9504b6.jpeg</t>
+          <t>Lib\hardware\data\images\161924ed571442c6aa91d8f03592bb79.jpeg</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-15-6-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-15-6-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -8552,17 +8543,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=lHbDDfn0Sydy4Zjr4KQequrk2xc%3D&amp;x-signature-webp=AUbDGTC6s9ZGglGKENZHjmeWPDk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=q35wBCJwwUAV5l2njQtoP0XW5VI%3D&amp;x-signature-webp=NdIQq1k3oyk9%2FaYaTnvuD6yFCDM%3D</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\447bed187bd04e3e9c578bbe79317d9a.png</t>
+          <t>Lib\hardware\data\images\211a2cf57432441f9c830c3209b1354e.png</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -8601,17 +8592,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/4/211ca921-7a59-4d54-b8a4-b0a866a8a1fc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2BoKGKFn8JWOW6UYuL8PweT3UWcg%3D&amp;x-signature-webp=kuncdp3Bcjyu9htEb7u0mgVlJgk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/4/211ca921-7a59-4d54-b8a4-b0a866a8a1fc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=%2BZY63JjNzdhlrFitt%2FXa%2FLh6jjo%3D&amp;x-signature-webp=EEWu5H28Z7SFjArzEm7gNjpZXeg%3D</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\91cdd2eefbf641e28669a15dd6522aeb.jpeg</t>
+          <t>Lib\hardware\data\images\2e89feef37f34125aa88b562722d07e6.jpeg</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-2-4g-wireless-optical-mous-1600dpi-ergonomic-design-for-pc-laptop-portable-usb-receiver-connection-mou19-blue-549c3?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-2-4g-wireless-optical-mous-1600dpi-ergonomic-design-for-pc-laptop-portable-usb-receiver-connection-mou19-blue-549c3?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -8653,17 +8644,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3f70bf285cdd4ba78101ac0ce308ca29~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=Mh0vNbZlqtOyC%2BHKXcCf%2FXhXtkg%3D&amp;x-signature-webp=Htve3rxG1twjit%2B1XL8SGcVKVBQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3f70bf285cdd4ba78101ac0ce308ca29~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=SXUjP5f6P%2F%2BOJnq9KlhFJ1IqeaA%3D&amp;x-signature-webp=P%2FO2sHA9RbPdxcPKH7GqAnXM76k%3D</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\62d25cea090d4400a48b88da888a667a.jpeg</t>
+          <t>Lib\hardware\data\images\18f20f9faf55441e993dd930f311046b.jpeg</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/poloalvisofficial/polo-alvis-urban-stanford-tas-ransel-waterproof-laptop-15-inch-sma-kampus-cowok-23-l-minimalis-design-1732445419512170430?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/poloalvisofficial/polo-alvis-urban-stanford-tas-ransel-waterproof-laptop-15-inch-sma-kampus-cowok-23-l-minimalis-design-1732445419512170430?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -8702,17 +8693,17 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/66c11c4fd34d4d6882e98ed086d9b763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=UB0tV7cJLwh7g4FLAzNuA6JcHw4%3D&amp;x-signature-webp=r6FHj%2BNh2T3vVJ1GWYa326rwSJA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/66c11c4fd34d4d6882e98ed086d9b763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=pFPI%2BGQ7xpOPyJBSx8SDZ5qUWlY%3D&amp;x-signature-webp=7EyZguq%2F94koymHnnHZPATBEpoo%3D</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cb2dbc48c7a94c2b8ed689cc0a771223.jpeg</t>
+          <t>Lib\hardware\data\images\bc84643d09524aed8e1984d8fd29aae2.jpeg</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/asterosofficial/ugreen-mouse-wireless-2-4gh-dongle-slim-design-silent-click-4-level-dpi-for-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/asterosofficial/ugreen-mouse-wireless-2-4gh-dongle-slim-design-silent-click-4-level-dpi-for-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -8754,17 +8745,17 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4cebea9086a44f65b64de3af3ab65a97~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=f7Us2ps2sg3Eb5cmCZka12wgtWQ%3D&amp;x-signature-webp=aCZIn%2F27X1iCvWi5VG2WC7bwkm0%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4cebea9086a44f65b64de3af3ab65a97~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=WxgpKMvIodqY1B3ATIqF9jXxTsA%3D&amp;x-signature-webp=MQbrzcZkug09aw4%2BmmHoywPEhXs%3D</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3e7ff28ed6ef4e189b55c6a552a86ad2.jpeg</t>
+          <t>Lib\hardware\data\images\d6631dde14c04d9c803896335e709836.jpeg</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-koper-2-in-1-mini-14-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charge-1731259158583739685?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-koper-2-in-1-mini-14-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charge-1731259158583739685?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -8803,17 +8794,17 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/2/12/79679dee-c94c-4311-bcd5-4f2eff9ffde0.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=OMjb7dRz8LvJZzhPHr7q7o%2FThXo%3D&amp;x-signature-webp=iR2JTs0UloK9uShya2PvuJ%2FJkVA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/2/12/79679dee-c94c-4311-bcd5-4f2eff9ffde0.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=hBwK2Vg0SWL4LBSp2mgvCX08n18%3D&amp;x-signature-webp=%2Bn2nZnMWirb%2FQ6QPFElubQWrOIM%3D</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\06f9088cc8d24263a91222d6fac8a67c.png</t>
+          <t>Lib\hardware\data\images\96769d24c3424535ac6e45d9adfb190a.png</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mitra-visual-store/magnus-computer-hand-elbow-bracket-ergonomic-design-untuk-laptop-dengan-kapasitas-beban-50kg-instalasi-tanpa-lubang-dan-desain-penyimpanan-aman-dan-terpercaya-1730001110731359391?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mitra-visual-store/magnus-computer-hand-elbow-bracket-ergonomic-design-untuk-laptop-dengan-kapasitas-beban-50kg-instalasi-tanpa-lubang-dan-desain-penyimpanan-aman-dan-terpercaya-1730001110731359391?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -8855,17 +8846,17 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/619af75ea7304f43b85045a7eb5d04d6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=Gq2ijVQJg0UIn6eqZfRS6vXaAUs%3D&amp;x-signature-webp=xDIRU0hTGstb31l2QZsHXPJiJz0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/619af75ea7304f43b85045a7eb5d04d6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=OylnSfczUUpwLnM3hQJAx6hA3Mo%3D&amp;x-signature-webp=LqVRF5PDa%2B7rbT8T3E0DbMvmKYc%3D</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\82a68e92c42848728c59ffb0a5b6bacc.jpeg</t>
+          <t>Lib\hardware\data\images\135e2b444ee54a88a79482b9f0b8190d.jpeg</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732093254842418725?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732093254842418725?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -8893,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -8907,17 +8898,17 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/551a82aed56c47eb9e3ee0fba57f90b2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=L46DEK2JCT8LeRYDf6zXqcvWbfY%3D&amp;x-signature-webp=TOM4ugi8yC76Fv3kjIv8MDcc6hY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/551a82aed56c47eb9e3ee0fba57f90b2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=iE9T1poJyO33nETLZ%2F9xvvCVu9g%3D&amp;x-signature-webp=AtLFZuFdDMNeI2%2ByJdDdquyvI7Q%3D</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3e7b431b36d04f63bb3e560ca02c852a.jpeg</t>
+          <t>Lib\hardware\data\images\d575f3b77f934e1f9bd32e87718aa921.jpeg</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/freeknight/freeknight-tas-ransel-pria-jumbo-tas-backpack-rain-cover-scalable-design-tas-laptop-anti-air-kokoh-expandable-usb-anti-maling-for-working-traveling-kulit-sekolah-hitam-tr748-1731255717575886209?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/freeknight/freeknight-tas-ransel-pria-jumbo-tas-backpack-rain-cover-scalable-design-tas-laptop-anti-air-kokoh-expandable-usb-anti-maling-for-working-traveling-kulit-sekolah-hitam-tr748-1731255717575886209?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -8959,17 +8950,17 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4fcd798501a442ba8d7d822ab4ca3653~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=NJ%2BiiMS4PyiOSX0Tkexn%2BUsBKCA%3D&amp;x-signature-webp=z8FVGz37976YjrkhhIqN%2BUEyQF0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4fcd798501a442ba8d7d822ab4ca3653~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=kZEaSWhFHCVgIKAAFGMdJMloH4E%3D&amp;x-signature-webp=1uE74nW4SY9QINdETH37%2FPhBFFM%3D</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\58272aff58c5497181803dcf7afb753e.jpeg</t>
+          <t>Lib\hardware\data\images\704df4e70b9648d797fb6df0f1a05060.jpeg</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1731286329775916501?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1731286329775916501?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9011,17 +9002,17 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4a7f13da9aad455ab9fdba3f50b1c198~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=1FU6F1tvOeSd2R%2Bk8UWzJtJsCx4%3D&amp;x-signature-webp=RqodWbyfoaN78S1W%2FaRFdBX5c4o%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4a7f13da9aad455ab9fdba3f50b1c198~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=x2CqTAyWdZMOWWmIOX02a6lK3B8%3D&amp;x-signature-webp=JHSRKP2byi3o%2BpZEYmSGEXitofM%3D</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e69efcb4df034734ac87234c73251338.jpeg</t>
+          <t>Lib\hardware\data\images\7765959d33c048d7a5d3538193d7b0a1.jpeg</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-koper-2-in-1mini-14-inch-1730797361031578784?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-koper-2-in-1mini-14-inch-1730797361031578784?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -9063,17 +9054,17 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3252748fff24ac1b364458644770abc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=wrDb3y5FVEO6agbbDi6Nl4TneNs%3D&amp;x-signature-webp=WKoKSdTFcuYKW5bXVbjWATEAx6Y%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3252748fff24ac1b364458644770abc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=HqIuAQppCBNNgezLyzRjaYypaUs%3D&amp;x-signature-webp=vdrEwn%2BGBZfyjoDljNP8UY%2BhmVs%3D</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b10106e8cea94847bb40384ae10dcc1d.jpeg</t>
+          <t>Lib\hardware\data\images\32f6d60b61e9400f8eaccbd028f498c7.jpeg</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-laptop-komputer-a909-design-ergonomic-with-volume-control-pc-spiker-speker-bass-1729384758482863585?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-laptop-komputer-a909-design-ergonomic-with-volume-control-pc-spiker-speker-bass-1729384758482863585?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -9115,17 +9106,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfeae6c1c6224919b5aa8184f6d941d3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=8Wz7bt2OSS0hyxIvnC8vcbMuwjQ%3D&amp;x-signature-webp=OYVlvPFPREqupxoqsZPZeRjY6MI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfeae6c1c6224919b5aa8184f6d941d3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=caC0fHzk8driHavrFKj42SIpVEA%3D&amp;x-signature-webp=KuJtmZm6vD05Biyn9nn%2FmSlu%2FhM%3D</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c01fb1cb66f140499d6577edc71ae27d.jpeg</t>
+          <t>Lib\hardware\data\images\bb9419066376419a97efeb001e33ef32.jpeg</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robot-powerbank-indonesia/robot-m315-mouse-pc-laptop-computer-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-bergaransi-resmi-1-tahun-1732091684148970925?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robot-powerbank-indonesia/robot-m315-mouse-pc-laptop-computer-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-bergaransi-resmi-1-tahun-1732091684148970925?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -9153,7 +9144,7 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -9167,17 +9158,17 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/761cf6e500cc429b8864a69dc5572e5c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=XRQTW8vI1Qkwg%2F5pdcetGyVSSSw%3D&amp;x-signature-webp=zuepJ2slgiw2FMxbsn0NC5MHNL8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/761cf6e500cc429b8864a69dc5572e5c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=CWyvAJ2C%2FiZdVB56qJnF6Rj56zs%3D&amp;x-signature-webp=jWbAK%2BIA2C8ZRfiP7%2F01VXZXWpk%3D</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\11526bb366054edba0d3f8ece3b840c3.jpeg</t>
+          <t>Lib\hardware\data\images\4e47f908f9be4233b2080f5b7353ae57.jpeg</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotsmartpower/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732092778590929924?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch%26whid%3D18553152</t>
+          <t>https://www.tokopedia.com/robotsmartpower/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732092778590929924?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch%26whid%3D18553152</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -9219,17 +9210,17 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1cfc199626c74270b7f2df4afa4837df~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2FaaVfaMipOuLSD8psJc9sbtmsDY%3D&amp;x-signature-webp=La5KGNeeASmorA71uIhBrF5sByA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1cfc199626c74270b7f2df4afa4837df~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=0Enc2oyvNHZOt1REM0aWzN6YZLY%3D&amp;x-signature-webp=32t3om9EErg%2B484ZBQ%2FSQP2nyn4%3D</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b291b9180ac848d4af1b54b79b467372.jpeg</t>
+          <t>Lib\hardware\data\images\712ba8788f5f4a25bdca84144036e49e.jpeg</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robot-official-surabaya/robot-mouse-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-robot-m315-mouse-nirkabel-kompatibel-pc-computer-laptop-original-bergaransi-resmi-1-tahun-1732189678655407803?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch%26whid%3D20644317</t>
+          <t>https://www.tokopedia.com/robot-official-surabaya/robot-mouse-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-robot-m315-mouse-nirkabel-kompatibel-pc-computer-laptop-original-bergaransi-resmi-1-tahun-1732189678655407803?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch%26whid%3D20644317</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -9271,17 +9262,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cdba5499d0c541eabd966bd3251dd080~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=XtaRzs5IQKt4J9qkENGLpqW%2BzWA%3D&amp;x-signature-webp=OnBPc%2Bj8Gwzw%2FZBFj8laLMPbKWk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cdba5499d0c541eabd966bd3251dd080~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=bEUKYO92LxY2A44qTrCsoqs%2BtO8%3D&amp;x-signature-webp=Hvp1fnUdeWfOR4XUpzrfhPRSS30%3D</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d8273bd498fc4fd68a39c29a37afdf80.jpeg</t>
+          <t>Lib\hardware\data\images\e94e10488e0a4e5586768d516b30de68.jpeg</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731285332222182869?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731285332222182869?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -9323,17 +9314,17 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/736c25698fe647b7b3a2740fc3a0941d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=VwhtlM9qLKK3x4Aj%2Bbwdd903GkU%3D&amp;x-signature-webp=lybt0g3D9XgBaLBrTChqvhY4xqQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/736c25698fe647b7b3a2740fc3a0941d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=apj37RrAoompMX%2FRw1r7LBo3lJE%3D&amp;x-signature-webp=DoA0f6DdHP8iIVomReolzDrsFLw%3D</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f25de0805e7c45e5bbea400c14d2d714.jpeg</t>
+          <t>Lib\hardware\data\images\da018455ba094f1e9f8fb63a402e518e.jpeg</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730915957094909397?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730915957094909397?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -9375,17 +9366,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/38dcad3fe4a041af8676ce38b7af63c5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=CzVemc65Ifxb3W19%2FOJdnoExkxs%3D&amp;x-signature-webp=MJPlCHStathJmA2GQZYW7I5rnSk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/38dcad3fe4a041af8676ce38b7af63c5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=jDYEBidCJrOMG%2Ffs%2Bjp3YkatNDI%3D&amp;x-signature-webp=A%2FXGhdTFu5Uqe%2FV3%2FoJKQvm5EX8%3D</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f1df19a5958c4628b93a65ad20a7ed55.jpeg</t>
+          <t>Lib\hardware\data\images\7629727146cc4554b6f94ff0e59a8237.jpeg</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1730932169696708053?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1730932169696708053?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -9427,17 +9418,17 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0765aa228c7e4eb98f5cddffb3cd161e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=p5JqoUz7TBQm4D91uE3TpycDg9w%3D&amp;x-signature-webp=8eE1Yatosm6p9pqchGenr9%2F2SQs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0765aa228c7e4eb98f5cddffb3cd161e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=mV2a8R6AmiLILaFiowaWy3zh4DU%3D&amp;x-signature-webp=OGiF6wjYBIg5JXcAAycoP71H8vg%3D</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bf9d0a5197854442a366f4879dae46ee.jpeg</t>
+          <t>Lib\hardware\data\images\586744b0aae14546bbd4a9232960cf27.jpeg</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730797091346285728?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730797091346285728?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -9448,24 +9439,24 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2435707299</v>
+        <v>100000200273</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KISONLI - Speaker Design Long Strip for Laptop / Komputer / PC - I600</t>
+          <t>KISONLI - Speaker Design Long Strip LED for Laptop / Komputer / PC / CPU - I560</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>113751</v>
+        <v>123651</v>
       </c>
       <c r="D180" t="n">
-        <v>169000</v>
+        <v>225000</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>493</v>
+        <v>2422</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -9479,17 +9470,17 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/6/559a865b-d5dc-46a6-b4cc-1cbcaac99452.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=rdRSWzooWxzJUSJCAXOBEZVGqnE%3D&amp;x-signature-webp=FsEs%2Fc5ZcK9aRot9sRvhCE00cxA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/15dbf2c96f3e48028a7d92838124dd06~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=fiaVEqY3HgHo%2Bl11pcQL7SO46rs%3D&amp;x-signature-webp=z4DF4%2FGchbd%2B46Vn%2BMzSTMkPysI%3D</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cb106b2698974e8c9584e1da1be4d1a9.jpeg</t>
+          <t>Lib\hardware\data\images\23cd0e4dfb364d039adc03a8bf74fb51.jpeg</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-for-laptop-komputer-pc-i600-1730809914258851297?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-led-for-laptop-komputer-pc-cpu-i560-1729692448934234593?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -9500,24 +9491,24 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>100000211116</v>
+        <v>2435707299</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>KISONLI Gaming Speaker Soundbar Laptop Pc /Komputer i520 Design Long Strip With Volume Control</t>
+          <t>KISONLI - Speaker Design Long Strip for Laptop / Komputer / PC - I600</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>102861</v>
+        <v>113751</v>
       </c>
       <c r="D181" t="n">
-        <v>209000</v>
+        <v>169000</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>128</v>
+        <v>493</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -9531,17 +9522,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9b778382d9e042acbbf6fc51f0b4b3cc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=58S06LgLipNgPp%2Fm7K1rSxvVgLM%3D&amp;x-signature-webp=FV%2BWQAoeR02rie%2FwYRegaJuDkqM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/6/559a865b-d5dc-46a6-b4cc-1cbcaac99452.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=%2FNWnyw44jqsBOX%2BRpq4GQdYZjHM%3D&amp;x-signature-webp=iK0HOmX%2FnfthmZ438kSUvVPpoOE%3D</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3329f81bbbe44e01a38ba687f9695605.jpeg</t>
+          <t>Lib\hardware\data\images\4a2b639003434be2838a79ca3dae5ef4.jpeg</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-soundbar-laptop-pc-komputer-i520-design-long-strip-with-volume-control-1729384483568911841?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-for-laptop-komputer-pc-i600-1730809914258851297?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -9552,48 +9543,48 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>100556558048</v>
+        <v>100000211116</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Love bird kapasitas besar Koper 24 Inch 20 / 22 inch travel kabin &amp; bagasi laptop new design bagasi stand cup / charger</t>
+          <t>KISONLI Gaming Speaker Soundbar Laptop Pc /Komputer i520 Design Long Strip With Volume Control</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>388133</v>
+        <v>102861</v>
       </c>
       <c r="D182" t="n">
-        <v>750000</v>
+        <v>209000</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Love.bird</t>
+          <t>Kisonli</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Jakarta Utara</t>
+          <t>Kab. Tangerang</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/08a5710421f849f0ba33f538d160f9fb~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=wTeU32Y1XJSJVcHUlqUPUeaTNVc%3D&amp;x-signature-webp=V%2FdCXHjA%2BP7Z32rGc%2BylubcDSIc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9b778382d9e042acbbf6fc51f0b4b3cc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=OuLm3AGIg2rV66eGsx8YFfeuJj8%3D&amp;x-signature-webp=AVbP87ZBIAAyW5TMSIX6PgNirxY%3D</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3cf071584c4e4b78a7a5a15d1a39d63f.jpeg</t>
+          <t>Lib\hardware\data\images\ec227ed725224434ad7413e71403cd77.jpeg</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-1730797282857354400?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-soundbar-laptop-pc-komputer-i520-design-long-strip-with-volume-control-1729384483568911841?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -9604,28 +9595,28 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>100267166259</v>
+        <v>100556558048</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LAOSHIDAISHU KAPASITAS BESAR Koper 24 Inch 20''22 inch TRAVEL KABIN &amp; BAGASI LAPTOP NEW DESIGN STAND CUP / CHARGER Koper 2 in 1Mini 14 Inch</t>
+          <t>Love bird kapasitas besar Koper 24 Inch 20 / 22 inch travel kabin &amp; bagasi laptop new design bagasi stand cup / charger</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>367320</v>
+        <v>388133</v>
       </c>
       <c r="D183" t="n">
-        <v>760000</v>
+        <v>750000</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Laoshidaishu Toko koper</t>
+          <t>Love.bird</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9635,17 +9626,17 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3a7b9972f596402094058c182b8ba340~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=B87S%2BIuxcg%2BKFmAPGumt%2FRTiLFU%3D&amp;x-signature-webp=7OKUhNipapGXZYrNxaznFDTEMCg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/08a5710421f849f0ba33f538d160f9fb~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=XQzRHMIeo4MhYZOaLdxrBw2gP70%3D&amp;x-signature-webp=16SVPvgnfvbEle%2FS2FKjEYkjOYc%3D</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fcc2ade4621b4fdcb0e1775e1ebee354.jpeg</t>
+          <t>Lib\hardware\data\images\a456246c013748dab66c957873e6ef17.jpeg</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730755375298348501?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-1730797282857354400?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -9656,25 +9647,28 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>102392526345</v>
+        <v>100267166259</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Orashare A01 Decorative Assorted Cartoon Stickers for Power Bank Wall Charger Laptop Tablet Aquaflask and so on Decoration Long Lasting Waterproof Aesthetic Cute Cartoon Design Magic Paper Stickers((Random 1PC Sticker) )</t>
+          <t>LAOSHIDAISHU KAPASITAS BESAR Koper 24 Inch 20''22 inch TRAVEL KABIN &amp; BAGASI LAPTOP NEW DESIGN STAND CUP / CHARGER Koper 2 in 1Mini 14 Inch</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>9999</v>
+        <v>367320</v>
+      </c>
+      <c r="D184" t="n">
+        <v>760000</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Orashare Indonesia Shop</t>
+          <t>Laoshidaishu Toko koper</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9684,17 +9678,17 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/92ffb7bcb5ba4243bf5aa5c96cd90e61~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=RmBuAPYWbvjPao29j3dL7gMQ16I%3D&amp;x-signature-webp=sPY%2F15f%2BEdLmMyEQv6x3SG9CKBU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3a7b9972f596402094058c182b8ba340~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=LCQm4hz5FfFrjeLof7qrMuXmSEQ%3D&amp;x-signature-webp=0d%2BpBKy16jZ7Kqd2vg%2FOQlJKYoU%3D</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bf0184b554cd428aa85e753a611780fb.jpeg</t>
+          <t>Lib\hardware\data\images\46c28ce64c384eefb823ef9f9230e5c9.jpeg</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/orashare/orashare-a01-decorative-assorted-cartoon-stickers-for-power-bank-wall-charger-laptop-tablet-aquaflask-and-so-on-decoration-long-lasting-waterproof-aesthetic-cute-cartoon-design-magic-paper-stickers-random-1pc-sticker-1732799857834428193?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730755375298348501?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -9705,45 +9699,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>6149737245</v>
+        <v>102392526345</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TAS BOBBY EXPLORE BACKPACK BY XD DESIGN FOR LAPTOP 17 INCH RANSEL ORIGINAL</t>
+          <t>Orashare A01 Decorative Assorted Cartoon Stickers for Power Bank Wall Charger Laptop Tablet Aquaflask and so on Decoration Long Lasting Waterproof Aesthetic Cute Cartoon Design Magic Paper Stickers((Random 1PC Sticker) )</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2280000</v>
+        <v>9999</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Luxer</t>
+          <t>Orashare Indonesia Shop</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Jakarta Utara</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/9/14/e90d0ad0-232f-4503-9d30-433258dedbd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=7nmNTuUXlnE2D8XEkPq9eU5tPmU%3D&amp;x-signature-webp=gpcFdAti5y8TjLDwXZKLatQS%2B5U%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/92ffb7bcb5ba4243bf5aa5c96cd90e61~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=zfhI%2FYQdltvkYxwifzTTYkQiUeg%3D&amp;x-signature-webp=GObyPc8C6A%2BSCTKsETgVQyBwVoI%3D</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8469366da1e64db0b0b55a0cf20eec2c.jpeg</t>
+          <t>Lib\hardware\data\images\c882f954b66b43d3a13e53f85cf0ba9b.jpeg</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-bobby-explore-backpack-by-xd-design-for-laptop-17-inch-ransel-original-1731176351546115751?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/orashare/orashare-a01-decorative-assorted-cartoon-stickers-for-power-bank-wall-charger-laptop-tablet-aquaflask-and-so-on-decoration-long-lasting-waterproof-aesthetic-cute-cartoon-design-magic-paper-stickers-random-1pc-sticker-1732799857834428193?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -9754,21 +9748,21 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>15564984049</v>
+        <v>6149737245</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tas Ransel  Eco Flex Bag FOR Laptop Untuk Kerja Sekolah Original Water Resistant Original XD Design</t>
+          <t>TAS BOBBY EXPLORE BACKPACK BY XD DESIGN FOR LAPTOP 17 INCH RANSEL ORIGINAL</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>900000</v>
+        <v>2280000</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -9782,17 +9776,17 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/19/3048426c-97a8-4891-ad6a-9d3335136017.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=8lUpGeYYrOHOW0yzv5lr4USUc1Q%3D&amp;x-signature-webp=BcqZ9lCSA4z4lEDcXrb5QPOFQII%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/9/14/e90d0ad0-232f-4503-9d30-433258dedbd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=06OMgs0CAHa5TSbO7XLgIRtb2%2B0%3D&amp;x-signature-webp=VIVFokt%2BGy2yTqZhiANXlsw2KDM%3D</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b12a7f4f0d894a28b2dcbe2f03cf7d53.jpeg</t>
+          <t>Lib\hardware\data\images\09af97b68ba748498115c57af66e5f15.jpeg</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-ransel-eco-flex-bag-for-laptop-untuk-kerja-sekolah-original-water-resistant-original-xd-design-1731176336923592359?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-bobby-explore-backpack-by-xd-design-for-laptop-17-inch-ransel-original-1731176351546115751?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -9803,21 +9797,21 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>10689379736</v>
+        <v>15564984049</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Original XD-Design Bobby Bizz 2.0 Anti theft Backpack Briefcase FOR Laptop</t>
+          <t>Tas Ransel  Eco Flex Bag FOR Laptop Untuk Kerja Sekolah Original Water Resistant Original XD Design</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2280000</v>
+        <v>900000</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -9831,17 +9825,17 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/7/15/2a8e3008-0cc1-456c-a1eb-8712b4e3afef.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=gRkxXC%2BuvaH4EIVAcy8%2FbFfNvTM%3D&amp;x-signature-webp=AGcB3CKPyUuBBojNgYZF1yuPasA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/19/3048426c-97a8-4891-ad6a-9d3335136017.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=wWWgyjdUUDmRXyEl%2BiP61qIsvKY%3D&amp;x-signature-webp=Vdx9x%2B10qPVL%2BIpyFKw3Tmz7FD0%3D</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\209563a2d8da40e6b64f0dba83b08641.jpeg</t>
+          <t>Lib\hardware\data\images\36a19faa878b4b40a225fcfa67255c46.jpeg</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-2-0-anti-theft-backpack-briefcase-for-laptop-1731176367656371879?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-ransel-eco-flex-bag-for-laptop-untuk-kerja-sekolah-original-water-resistant-original-xd-design-1731176336923592359?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -9852,21 +9846,21 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>14960666592</v>
+        <v>10689379736</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bobby Edge Anti-Theft Backpack by XD Design Tas Ransel Backpack FOR Laptop Original</t>
+          <t>Original XD-Design Bobby Bizz 2.0 Anti theft Backpack Briefcase FOR Laptop</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1900000</v>
+        <v>2280000</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -9880,17 +9874,17 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/26/3934712d-a1d2-4f48-af1b-0b1037ea9e26.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2Bm5%2FXJTARw1xASeAjqb9tB1gCPs%3D&amp;x-signature-webp=A99AeSETYgp28v2xANHa%2BeXmMhg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/7/15/2a8e3008-0cc1-456c-a1eb-8712b4e3afef.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=tiB60JtJ4Gg5yxlTSj8iKNs0AR8%3D&amp;x-signature-webp=zZc9ETyGMeHKshJWgC6uBMX%2BJ7o%3D</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5cfb592e6e92415b89a059049e1c6d50.jpeg</t>
+          <t>Lib\hardware\data\images\d065a5353240434f8d9d3dc9b6ae4cc6.jpeg</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-backpack-for-laptop-original-1731176301652117159?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-2-0-anti-theft-backpack-briefcase-for-laptop-1731176367656371879?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -9901,48 +9895,45 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>100289507999</v>
+        <v>14960666592</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Pro Design Patron PATSLT 50 Meja Samping / Nakas / Meja Laptop</t>
+          <t>Bobby Edge Anti-Theft Backpack by XD Design Tas Ransel Backpack FOR Laptop Original</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>399000</v>
-      </c>
-      <c r="D189" t="n">
-        <v>643000</v>
+        <v>1900000</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pro Design Furniture</t>
+          <t>Luxer</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Kab. Gresik</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e0cb31b7859943a7818f516b7a76c398~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=zVft9RcgCN%2FdcW87RDllKTBrq%2BY%3D&amp;x-signature-webp=POELeab8%2F00SAuKmPvmLgIJO%2BOI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/26/3934712d-a1d2-4f48-af1b-0b1037ea9e26.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=HHBerVHg4NjZgxW9J0kxR8OanGw%3D&amp;x-signature-webp=zw9q%2BdINqxk2dJZRp%2BMm92F4kTE%3D</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d8ba75e20d5c440cb9c527c1f49e0176.jpeg</t>
+          <t>Lib\hardware\data\images\75388126d6be41288ff26674b3cfb936.jpeg</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/prodesign/pro-design-patron-patslt-50-meja-samping-nakas-meja-laptop-1729384439739745584?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-backpack-for-laptop-original-1731176301652117159?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -9953,48 +9944,48 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>100295676877</v>
+        <v>100289507999</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sleeve Nillkin Versatile for Laptop / Notebook / MacBook (Horizontal Design)</t>
+          <t>Pro Design Patron PATSLT 50 Meja Samping / Nakas / Meja Laptop</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>430000</v>
+        <v>399000</v>
       </c>
       <c r="D190" t="n">
-        <v>740000</v>
+        <v>643000</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>unomax</t>
+          <t>Pro Design Furniture</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bekasi</t>
+          <t>Kab. Gresik</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e100902e37f5405f95ab14ceca042fbe~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=hYWP1%2BchK%2BAV%2BIQPyePETkjUREQ%3D&amp;x-signature-webp=QA%2FVUBQ%2BKbc9EJwNq1UzGgBnUvg%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e0cb31b7859943a7818f516b7a76c398~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=x6cK2AEQoHg7U0K%2FywNJufmjgGA%3D&amp;x-signature-webp=HWBVBvzQzAXzEcojHx1Yd2qXjuQ%3D</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\146463122f4d4bc4874e19e808bd945d.jpeg</t>
+          <t>Lib\hardware\data\images\27d9cd110d4d4716a3fa8c822d3a9f1f.jpeg</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/unomax/sleeve-nillkin-versatile-for-laptop-notebook-macbook-horizontal-design-1729542909144501215?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/prodesign/pro-design-patron-patslt-50-meja-samping-nakas-meja-laptop-1729384439739745584?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -10005,45 +9996,48 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2166270847</v>
+        <v>100295676877</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Original XD-Design Bobby Bizz Anti theft Backpack Briefcase FOR Laptop 15"</t>
+          <t>Sleeve Nillkin Versatile for Laptop / Notebook / MacBook (Horizontal Design)</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1700000</v>
+        <v>430000</v>
+      </c>
+      <c r="D191" t="n">
+        <v>740000</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Luxer</t>
+          <t>unomax</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Bekasi</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/4/12/4a196eba-99a6-4d86-ba5d-42198ae0ae47.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=6xke75Z0lL3UiionZTeB8D9cU5Q%3D&amp;x-signature-webp=d%2FLKiZhVNWCTJq3rtoPnEAlh1QM%3D</t>
+          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e100902e37f5405f95ab14ceca042fbe~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=wyzMiqrcIQ8uRk7PbG5bSJgmAvY%3D&amp;x-signature-webp=3Bdlbl7hFH%2FIKZ8QHJo8YPA%2FAlg%3D</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0b811dc8eb4c4b2484dbf4bed3ab5cb5.jpeg</t>
+          <t>Lib\hardware\data\images\1046e8287d1340b79b0323e290f9926d.jpeg</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-anti-theft-backpack-briefcase-for-laptop-15-1731176360280164007?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/unomax/sleeve-nillkin-versatile-for-laptop-notebook-macbook-horizontal-design-1729542909144501215?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -10054,45 +10048,45 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>14639380063</v>
+        <v>2166270847</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>WIA XD Design Bobby Edge Anti-Theft Backpack Tas Ransel Laptop Unisex Original</t>
+          <t>Original XD-Design Bobby Bizz Anti theft Backpack Briefcase FOR Laptop 15"</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1900000</v>
+        <v>1700000</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>WIA OFFICIAL</t>
+          <t>Luxer</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Kab. Tangerang</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/65b3b9f2049f476ba5c95f176912c01f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=Pdd6WB75NH8t3nQ2g3Y7myJBwjU%3D&amp;x-signature-webp=ix0dvqJdrxmkUCgBeWeT5ylAH%2BQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/4/12/4a196eba-99a6-4d86-ba5d-42198ae0ae47.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=Fe%2BRh3%2BTS0cmZS452HgHv6niArE%3D&amp;x-signature-webp=hqW18QRFdhMdGA%2B5VxIH2ed5wkM%3D</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e43fc3b1ab924a68a04a3fec0fd151ee.jpeg</t>
+          <t>Lib\hardware\data\images\ea72aa3a718f491598efe4981cf6a11f.jpeg</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/wia-official/wia-xd-design-bobby-edge-anti-theft-backpack-tas-ransel-laptop-unisex-original-1729752607370544988?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-anti-theft-backpack-briefcase-for-laptop-15-1731176360280164007?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -10103,45 +10097,45 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>12557319829</v>
+        <v>14639380063</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>VRS DESIGN Ark BackpacK Organize Laptop Carry Bag Multi-use Up To 15.6</t>
+          <t>WIA XD Design Bobby Edge Anti-Theft Backpack Tas Ransel Laptop Unisex Original</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1499000</v>
+        <v>1900000</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Primary Cares Official</t>
+          <t>WIA OFFICIAL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Kab. Tangerang</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/1/16/61242af3-3630-4531-8d25-e625e9e80dea.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=aA98fWD%2BoJCe6hUYO%2FPM6HScXho%3D&amp;x-signature-webp=%2Fpf1eF1hIAEWhjr2nN1bFMWJqYk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/65b3b9f2049f476ba5c95f176912c01f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=1%2BTXlyNo8SBm%2BKDgjCYzFsET3rY%3D&amp;x-signature-webp=%2BTQQd1I2U8ZJ8fA71bny5RfVg6M%3D</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\01ebf442faba43f2b0e6703405daf068.jpeg</t>
+          <t>Lib\hardware\data\images\46fda67529ed44799cae5d920369b6d2.jpeg</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/primarycaresofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black-80565?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/wia-official/wia-xd-design-bobby-edge-anti-theft-backpack-tas-ransel-laptop-unisex-original-1729752607370544988?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -10152,28 +10146,25 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>15596117902</v>
+        <v>12557319829</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>POLO GODEN 62194-2B - Tas Ransel / Backpack / Tas Punggung / Tas Laptop / Tas Kantor / Tas Kerja - Premium Material, Sleek Design,  Multi Compartment, Banyak Tempat Penyimpanan, Hitam</t>
+          <t>VRS DESIGN Ark BackpacK Organize Laptop Carry Bag Multi-use Up To 15.6</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>598500</v>
-      </c>
-      <c r="D194" t="n">
-        <v>1197000</v>
+        <v>1499000</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sempana Bags</t>
+          <t>Primary Cares Official</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -10183,17 +10174,17 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/1d2dc8699f1a427e82b9077ea324a552~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=kfDaX4qmUrtCaub7dwNsZvE6TJM%3D&amp;x-signature-webp=ipDSanEmK%2FEf%2Fkfjfv4wy2vxqjE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/1/16/61242af3-3630-4531-8d25-e625e9e80dea.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=lXKhHzRrPJb6oO8RhKJM25ESWAs%3D&amp;x-signature-webp=fAthfWS0IHb5nq87h7aN5rsng%2Fg%3D</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7b27a0094a7047198af3ff29955b2b87.jpeg</t>
+          <t>Lib\hardware\data\images\e793ad944acc4748b76ba07508b9ad97.jpeg</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/sempanabags/polo-goden-62194-2b-tas-ransel-backpack-tas-punggung-tas-laptop-tas-kantor-tas-kerja-premium-material-sleek-design-multi-compartment-banyak-tempat-penyimpanan-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/primarycaresofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black-80565?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -10204,48 +10195,48 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>100553472793</v>
+        <v>15596117902</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Advan Laptop WorkPlus Heritage/AMD Ryzen 5-7535HS/8GB DDR4 (Upgrade)/512GB SSD (Upgrade)/AMD Radeon 660M/WIN 11/14" WUXGA (16:10)/Megamendung Batik Design</t>
+          <t>POLO GODEN 62194-2B - Tas Ransel / Backpack / Tas Punggung / Tas Laptop / Tas Kantor / Tas Kerja - Premium Material, Sleek Design,  Multi Compartment, Banyak Tempat Penyimpanan, Hitam</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>7399000</v>
+        <v>598500</v>
       </c>
       <c r="D195" t="n">
-        <v>7999000</v>
+        <v>1197000</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>ADVAN BY URBANLIFE</t>
+          <t>Sempana Bags</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a04b8b3b3b064a0fa6aaf3e379856c92~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=86gTLgzpfzWTdehoNN%2Fki9LXlfc%3D&amp;x-signature-webp=W3dyae%2F1iW6jbP1rdUzYDDZjz%2BA%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/1d2dc8699f1a427e82b9077ea324a552~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=XdScIS1C9LZxk4ivK1Lv62o6TMY%3D&amp;x-signature-webp=72ixtAekQ1gZfOEtp7QZzv7Eqdw%3D</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b9525a11605b4b14b080c735f8f78b13.jpeg</t>
+          <t>Lib\hardware\data\images\460c39fd95c0447ea85403066dc6bb03.jpeg</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/advan-by-urbanlife/advan-laptop-workplus-heritage-amd-ryzen-5-7535hs-8gb-ddr4-upgrade-512gb-ssd-upgrade-amd-radeon-660m-win-11-14-wuxga-16-10-megamendung-batik-design-1731557661886154575?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/sempanabags/polo-goden-62194-2b-tas-ransel-backpack-tas-punggung-tas-laptop-tas-kantor-tas-kerja-premium-material-sleek-design-multi-compartment-banyak-tempat-penyimpanan-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -10256,45 +10247,48 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>14786168852</v>
+        <v>100553472793</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>UGREEN Ergonomic Premium Mouse Pad With Arm Rest Design Bantal Tangan Anti Slip Mousepad Untuk Kerja Kantor Meja Komputer PC Laptop</t>
+          <t>Advan Laptop WorkPlus Heritage/AMD Ryzen 5-7535HS/8GB DDR4 (Upgrade)/512GB SSD (Upgrade)/AMD Radeon 660M/WIN 11/14" WUXGA (16:10)/Megamendung Batik Design</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>80000</v>
+        <v>7399000</v>
+      </c>
+      <c r="D196" t="n">
+        <v>7999000</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DERUMA TECHNOLOGY OFFICIAL</t>
+          <t>ADVAN BY URBANLIFE</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/12/ffd6e4db-90b2-4e80-b558-4833df06bfc3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=8wh19F9cNEND8mMIPjQPxou3TOQ%3D&amp;x-signature-webp=wKHE1BWZmRV03uRMz3TVWlz6pzE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a04b8b3b3b064a0fa6aaf3e379856c92~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=rTRd9G0rrwk43jfEWcmspMOpjGg%3D&amp;x-signature-webp=KLUVDer58%2Fqpt%2F6eHaB8q9KFlec%3D</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7bf295760d5e4f7eb6e117c1d402bfb3.png</t>
+          <t>Lib\hardware\data\images\388982a90777465d8b0f5be9882954a1.jpeg</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deermatech/ugreen-ergonomic-premium-mouse-pad-with-arm-rest-design-bantal-tangan-anti-slip-mousepad-untuk-kerja-kantor-meja-komputer-pc-laptop-black-faf99?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/advan-by-urbanlife/advan-laptop-workplus-heritage-amd-ryzen-5-7535hs-8gb-ddr4-upgrade-512gb-ssd-upgrade-amd-radeon-660m-win-11-14-wuxga-16-10-megamendung-batik-design-1731557661886154575?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -10305,28 +10299,25 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>100593801369</v>
+        <v>14786168852</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TaffHOME Meja Lipat Serbaguna Laptop Portable Desk Minimalist Design - I042767</t>
+          <t>UGREEN Ergonomic Premium Mouse Pad With Arm Rest Design Bantal Tangan Anti Slip Mousepad Untuk Kerja Kantor Meja Komputer PC Laptop</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>159000</v>
-      </c>
-      <c r="D197" t="n">
-        <v>295000</v>
+        <v>80000</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Usea Official Store</t>
+          <t>DERUMA TECHNOLOGY OFFICIAL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -10336,17 +10327,17 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/af145de2fcdb4ec3a9dc41740a920a72~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=mh%2FYwKETGFY4bQyWaacQqKFjWfk%3D&amp;x-signature-webp=anJCJNC7JGxMMkpVl2xhdzYqNbU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/12/ffd6e4db-90b2-4e80-b558-4833df06bfc3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=AB5b%2B%2FZasoqtyBHqHM61aJ49jZc%3D&amp;x-signature-webp=CHSdGiMnOSN20J2iMS7KhMtj6fU%3D</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b2df4381c96d4aa09ffafd1af700af97.jpeg</t>
+          <t>Lib\hardware\data\images\65111631915a4fd1b00f418d343fca09.png</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/usea/taffhome-meja-lipat-serbaguna-laptop-portable-desk-minimalist-design-i042767-1731655641388386299?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/deermatech/ugreen-ergonomic-premium-mouse-pad-with-arm-rest-design-bantal-tangan-anti-slip-mousepad-untuk-kerja-kantor-meja-komputer-pc-laptop-black-faf99?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -10357,45 +10348,48 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>100000060946</v>
+        <v>100593801369</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>WIA XD Design 14" / 16" Laptop Sleeve Black Tas Pelindung Laptop Original</t>
+          <t>TaffHOME Meja Lipat Serbaguna Laptop Portable Desk Minimalist Design - I042767</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>300000</v>
+        <v>159000</v>
+      </c>
+      <c r="D198" t="n">
+        <v>295000</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>WIA OFFICIAL</t>
+          <t>Usea Official Store</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Kab. Tangerang</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9d59757d49a84775a35c06bdeb14cede~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=0n6%2B5077gNAuCAfgV8dS7DgtVxM%3D&amp;x-signature-webp=hIumIcqnTR7EwczBs%2B92T00i0Mk%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/af145de2fcdb4ec3a9dc41740a920a72~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=DXdabmlB57SNw8Frr%2FjQb21YddE%3D&amp;x-signature-webp=2kI7lDp6%2BhyIMyvyP5g7aKGud4A%3D</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b29e2bd1e15b4481a6331bae25fc780f.jpeg</t>
+          <t>Lib\hardware\data\images\f3a554f5008a404291cd2b8655bf1bf5.jpeg</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/wia-official/wia-xd-design-14-16-laptop-sleeve-black-tas-pelindung-laptop-original-1729909128724056924?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/usea/taffhome-meja-lipat-serbaguna-laptop-portable-desk-minimalist-design-i042767-1731655641388386299?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -10406,45 +10400,45 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>7074049017</v>
+        <v>100000060946</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Tas Bobby Hero Anti Theft Backpack XL 17 inch Bag FOR Laptop XD Design Ori</t>
+          <t>WIA XD Design 14" / 16" Laptop Sleeve Black Tas Pelindung Laptop Original</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1780000</v>
+        <v>300000</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Luxer</t>
+          <t>WIA OFFICIAL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Kab. Tangerang</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/8/dd821518-9132-4894-82f2-34caf0bb2acc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=wBI%2Bkh%2FiIw5h7NIsAYJm7G3YzcE%3D&amp;x-signature-webp=c1ITsUSp58%2BLaFztJ30HMgacDhM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9d59757d49a84775a35c06bdeb14cede~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=j%2FRoY51Tcy6yqowzenWik6sSVBw%3D&amp;x-signature-webp=w6PtI3h9giDiX8PWTsilKRmZ3OM%3D</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6026c715af5a40b39d1adf1c8390b8d3.jpeg</t>
+          <t>Lib\hardware\data\images\6ed4e91748ce411dac85d8803c9739fe.jpeg</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-bobby-hero-anti-theft-backpack-xl-17-inch-bag-for-laptop-xd-design-ori-1731176367509243559?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/wia-official/wia-xd-design-14-16-laptop-sleeve-black-tas-pelindung-laptop-original-1729909128724056924?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -10455,25 +10449,25 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>7177223938</v>
+        <v>7074049017</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>VRS DESIGN Ark BackpacK Organize Laptop Carry Bag Multi-use Up To 15.6</t>
+          <t>Tas Bobby Hero Anti Theft Backpack XL 17 inch Bag FOR Laptop XD Design Ori</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1499000</v>
+        <v>1780000</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Supcase Official ID</t>
+          <t>Luxer</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10483,17 +10477,17 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/12/9/54c88793-1151-49b3-ae07-078a15223f01.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=BaHH7GpiKO6VkfiXWWUv0v1JhtA%3D&amp;x-signature-webp=XSd1Z%2BVsEjWoroubc57pv%2FVW87g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/8/dd821518-9132-4894-82f2-34caf0bb2acc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=mpOKUKLcQUQuJId1ZNTGeuNavVY%3D&amp;x-signature-webp=Opylf8yWu4DfjSsoELxK2P4FS88%3D</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\af20c72585e2469db46954246ac47954.jpeg</t>
+          <t>Lib\hardware\data\images\4eac502ee5fe4535bf7564287f4bb346.jpeg</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supcaseofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-bobby-hero-anti-theft-backpack-xl-17-inch-bag-for-laptop-xd-design-ori-1731176367509243559?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -10504,48 +10498,45 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>100556535366</v>
+        <v>7177223938</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Forgui kapasitas besar Koper 24 Inch 20''22 inch travel kabin &amp; bagasi laptop new design stand CUP / charger</t>
+          <t>VRS DESIGN Ark BackpacK Organize Laptop Carry Bag Multi-use Up To 15.6</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>349490</v>
-      </c>
-      <c r="D201" t="n">
-        <v>760000</v>
+        <v>1499000</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Forgui</t>
+          <t>Supcase Official ID</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Jakarta Utara</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/def128a136764f57b050b851ac499649~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1763992086&amp;x-signature=%2FyuftHRSOCK5yxkEf8j%2BwgbhZA4%3D&amp;x-signature-webp=pqVYGNIh%2Fbl3PJtYb2U2Zm9kMXM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/12/9/54c88793-1151-49b3-ae07-078a15223f01.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=i2oinTthPfxvS6Fbrq%2FsfTpEd20%3D&amp;x-signature-webp=YH5ByzHSDslffubAUZIneqe2h7I%3D</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\037e39b4c144419a9864ee348f4921e2.jpeg</t>
+          <t>Lib\hardware\data\images\4fe2d5f5503e49cb9a6fac8c66e47c42.jpeg</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731259837866738981?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112412480511B9842E0A271F3DFQ0W%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supcaseofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">

--- a/Lib/hardware/data/tokopedia_products_latest.xlsx
+++ b/Lib/hardware/data/tokopedia_products_latest.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/1/7aeb95bc-e841-4938-b4bc-170c843ec092.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=KRU%2FfpbJVFMEmC8dlzfEA7dNIbM%3D&amp;x-signature-webp=ChH%2FDAUQnTzAJKsgzT1AxDFoEyM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/1/7aeb95bc-e841-4938-b4bc-170c843ec092.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=UXgRbwwzRttdV93CO57l56vofXs%3D&amp;x-signature-webp=uSjkfiwAEn78vqu%2BHTrr95cmf2A%3D</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\81c882f3b26143538ce3cc9111e66a02.jpeg</t>
+          <t>Lib\hardware\data\images\342e757c013a4428909bc96568bc64a0.jpeg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomppurwokerto/speaker-gaming-pc-dan-laptop-nyk-sp-n02?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomppurwokerto/speaker-gaming-pc-dan-laptop-nyk-sp-n02?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/df0f4a61aed14dcb8da81f3c4f338f43~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=QWz7DcbxaXMndw1tSl6Qr7NDTiE%3D&amp;x-signature-webp=I%2FrWeO%2F0P3vpid%2BwUdlnYVXFnLc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/df0f4a61aed14dcb8da81f3c4f338f43~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=BRZL7%2BIly4XPb1Dl6JD4eTWPRyI%3D&amp;x-signature-webp=XgmssGrR8SGSy4yukQ4hwu3Fha0%3D</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9fa14261524b4bd3b45204fd78c19ed0.jpeg</t>
+          <t>Lib\hardware\data\images\3a1dd46a9f284a95b69e7d9dc4957e9b.jpeg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomppurwokerto/coolingpad-nyk-x6-thunderstorm-gaming-cooling-pad-laptop-2-fan-x-6-x-6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomppurwokerto/coolingpad-nyk-x6-thunderstorm-gaming-cooling-pad-laptop-2-fan-x-6-x-6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -606,17 +606,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/22/cc4b9584-80b6-44d6-87d5-f4611d98002d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=QGv4XZdo%2B41nl2CItDYcKuXcubc%3D&amp;x-signature-webp=Xrvj7MU65ws0AsL%2FG3Hg9ohp67Y%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/22/cc4b9584-80b6-44d6-87d5-f4611d98002d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=ibytxpFGoKpMzixU9hAQKhOzPHI%3D&amp;x-signature-webp=45NJJqQbyPscUJSptdW0jzR8lSA%3D</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\948f632c443e43ce93b56556938b39d4.png</t>
+          <t>Lib\hardware\data\images\90d98f836bdb4e6cafcb6e746285b6ea.png</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomp-semarang/rexus-gladius-gx2-gaming-pro-gamepad-joystick-laptop-pc-hitam-95b39?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomp-semarang/rexus-gladius-gx2-gaming-pro-gamepad-joystick-laptop-pc-hitam-95b39?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -655,17 +655,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/3/c0410e6b-f108-42d2-9b67-ea029ba1ab29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=LMKg6b0%2FyfVPYoTPTmzEFIcTp9k%3D&amp;x-signature-webp=2EhV%2B%2Fmp3cbqcXXqS4HD7JYzXgA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/3/c0410e6b-f108-42d2-9b67-ea029ba1ab29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=Gz5HbV4OcHQjy4mual2rJDKYl5Y%3D&amp;x-signature-webp=V1PqPhJmSZcFY78awynfi%2BydANY%3D</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\06d8c4837175412ba7f47d247acff939.png</t>
+          <t>Lib\hardware\data\images\af3e42b310c24a92bc9b88561d1c7904.png</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomp-semarang/nyk-x6-thunderstorm-gaming-coolingpad-laptop-2-fan-x-6-x6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomp-semarang/nyk-x6-thunderstorm-gaming-coolingpad-laptop-2-fan-x-6-x6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/13/35945633-babb-4760-81cb-d4986d80ec0f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=zhiUL9adOiqAIkjXQ0SaP1zzilA%3D&amp;x-signature-webp=hKNZfAgDbajsgsMyeQBYQwIKa1s%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/13/35945633-babb-4760-81cb-d4986d80ec0f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=qSCfXI3MGjH2euNFxdWO3YwQe6k%3D&amp;x-signature-webp=gW9E70SvrSnHigrfjesWpr9tuFk%3D</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cbc86a78b4404b598383fd186e5b3ec4.jpeg</t>
+          <t>Lib\hardware\data\images\6fdf19b399324c858a5de1fa27c6c0e9.jpeg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/oceanbike/headset-headphone-gaming-power-full-bass-hs04su-mic-3-5mm-earphone-komputer-laptop-pc?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/oceanbike/headset-headphone-gaming-power-full-bass-hs04su-mic-3-5mm-earphone-komputer-laptop-pc?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/16/f7f0720b-7ffd-4402-9d19-9a8e519ea683.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=hQeztLSdPSLS5oak%2BrJrjPZHY1I%3D&amp;x-signature-webp=bwGE%2Berw3dz61zSpApjfJu%2BlHCg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/16/f7f0720b-7ffd-4402-9d19-9a8e519ea683.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=uuQKl1Nk7jJzyoXTakTMVSwWyBE%3D&amp;x-signature-webp=iP7lzaDTkCoVclmduVN1I2y5mqA%3D</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\85e4e4fd83e4493597116e76b53c85d2.png</t>
+          <t>Lib\hardware\data\images\3b252b3cf29d47a6a6ab677e379c6573.png</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mrmaidstore/keyboard-gaming-and-mouse-8310-rgb-keyboard-and-mouse-gaming-for-laptop-komputer-pc-2-in-1-gaming-set-white-0fc1b?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mrmaidstore/keyboard-gaming-and-mouse-8310-rgb-keyboard-and-mouse-gaming-for-laptop-komputer-pc-2-in-1-gaming-set-white-0fc1b?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e55445b6e9a42439b246d1d5c9cc663~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=rIeSkJkdvP%2FKUx2rn%2BYZ77Uw%2FRQ%3D&amp;x-signature-webp=au%2F2bK%2Fy0%2FNgJ%2B1PtgV%2Bby9%2F0PA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e55445b6e9a42439b246d1d5c9cc663~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=uqm5Bht6%2BdE%2BkPW%2FU9yDuvWN2Ig%3D&amp;x-signature-webp=hT4NpN2FyVjoYonNOshq86MrLzw%3D</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\792ac80f837d45c6bddf239072962e78.jpeg</t>
+          <t>Lib\hardware\data\images\ca513a6ca91143b2ab6aa771690792ea.jpeg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fantech-official-store/fantech-carbon-7-1-hg30-headset-gaming-usb-7-1-virtual-surround-sound-mic-noise-cancelling-driver-40-mm-pc-laptop-mac-ps4-ps5-switch-1731357616041067843?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fantech-official-store/fantech-carbon-7-1-hg30-headset-gaming-usb-7-1-virtual-surround-sound-mic-noise-cancelling-driver-40-mm-pc-laptop-mac-ps4-ps5-switch-1731357616041067843?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/67226b19-6b3d-41f1-b2f3-c0c0d81b1319.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=yRNUEaLGphr0zM4%2BS1u%2Bik01aF4%3D&amp;x-signature-webp=rifDJTbQizJTDHl%2FHh99hc4gPlc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/67226b19-6b3d-41f1-b2f3-c0c0d81b1319.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=BenadELo%2FXQY0XYl3J942Q19ArA%3D&amp;x-signature-webp=UXUPbjEwZqvOHKx3bjuwbOJtEbc%3D</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4486392290d84c1daae41e1491050ada.png</t>
+          <t>Lib\hardware\data\images\08480807502242c38d58aaa1afc5e5bc.png</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-tv-home-theater-pc-monitor-gaming-laptop-hdmi-male-to-hdmi-male-2-1-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928891163543425?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-tv-home-theater-pc-monitor-gaming-laptop-hdmi-male-to-hdmi-male-2-1-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928891163543425?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -906,17 +906,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/9b61818c-7d6b-4657-b87b-cda3f5f9bcf3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=jk9bmmklbURDh0MRGPdbHGx0X3g%3D&amp;x-signature-webp=CYjT9%2Fq72pLP8YwjKBlbJdHCNFE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/9b61818c-7d6b-4657-b87b-cda3f5f9bcf3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=UlOCWbrnWAVd8LITumGAeGO3nX0%3D&amp;x-signature-webp=JXtjjGotq6QS7cqfAQiwaRM3GlA%3D</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c31a066837324731817608b79b1afecf.png</t>
+          <t>Lib\hardware\data\images\0599550196644043a754d6278a539615.png</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-pc-monitor-gaming-laptop-displayport-dp-1-4-to-displayport-dp-1-4-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928629547304833?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-pc-monitor-gaming-laptop-displayport-dp-1-4-to-displayport-dp-1-4-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928629547304833?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/5d1519ada63b4e6d9117033d63f53c0a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=5UKxXVjBMp4P7pEzFP%2FvDeKgMo0%3D&amp;x-signature-webp=0oaaF7QKRv3zp%2BSaOGn84u98FoA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/5d1519ada63b4e6d9117033d63f53c0a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=6T5k0o3oqzu77ar8oYfz1pwlgH4%3D&amp;x-signature-webp=jpxnSYaUDgles5IYpkzwo5%2B0Jw4%3D</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a1a3e90c3e164cb08cbabf9c165bb064.jpeg</t>
+          <t>Lib\hardware\data\images\9dc8d795111548d99e418aa3104296fb.jpeg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/himtech/hagibis-kabel-hdmi-to-hdmi-2-1-ultra-hd-2k-4k-8k-3d-hdr-earc-vrr-qms-allm-qft-displayhdr-tv-pc-gaming-monitor-laptop-video-audio-cable-1730928835618703202?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/himtech/hagibis-kabel-hdmi-to-hdmi-2-1-ultra-hd-2k-4k-8k-3d-hdr-earc-vrr-qms-allm-qft-displayhdr-tv-pc-gaming-monitor-laptop-video-audio-cable-1730928835618703202?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/de586d5ac89841249f0ded879ec5efcc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=G7qaZ2DHE8AjqqHbJZjEHGEie08%3D&amp;x-signature-webp=x23Ew4ayAgi%2BrgExB8Ha92rcK2E%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/de586d5ac89841249f0ded879ec5efcc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=%2BdwruyC14yBh0c%2F1rzocjQx4QHA%3D&amp;x-signature-webp=iEsCAyaOOwU7Ti0CN%2BaZIq1jC9U%3D</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\442006420e2445c39350f56ecbf51932.jpeg</t>
+          <t>Lib\hardware\data\images\179cc0e412c24cd39a93eed9aaba2bc8.jpeg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fantech-official-store/fantech-cooling-pad-rgb-nc22-notebook-cooler-with-phone-holder-adjustable-fan-speed-up-to-14kg-19-inch-laptop-gaming-1731339017679177162?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fantech-official-store/fantech-cooling-pad-rgb-nc22-notebook-cooler-with-phone-holder-adjustable-fan-speed-up-to-14kg-19-inch-laptop-gaming-1731339017679177162?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c93407def7484a1da7ab81928956adc0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=AED7b1oewe0dHbIxXXgmO7hy7Nk%3D&amp;x-signature-webp=6bzh5%2Fwd33dqNr2Vh2hmk2aL6p8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c93407def7484a1da7ab81928956adc0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=P%2BQZHrt0emZnRgMWxpU28WR9xKM%3D&amp;x-signature-webp=PCziBedujVrgA%2Bj6LJyeNCwQplc%3D</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6568a713ccbf4dc3bd402c9cc642471b.jpeg</t>
+          <t>Lib\hardware\data\images\565e620f10d2438babcbbf34efa8145f.jpeg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mousepad-gaming-premium-unitech-90cm-x-40cm-x-0-3cm-alas-mouse-pad-jumbo-anti-slip-untuk-laptop-pc-1731687141802083738?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/mousepad-gaming-premium-unitech-90cm-x-40cm-x-0-3cm-alas-mouse-pad-jumbo-anti-slip-untuk-laptop-pc-1731687141802083738?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/29/eeb6fab6-76fe-412e-a3af-dd3792478a70.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=juM%2BLOmhRKDu7YcIVoOfkTbOipo%3D&amp;x-signature-webp=S21fDWnJCQ5K8Sy07F9TcYu6p%2Bs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/29/eeb6fab6-76fe-412e-a3af-dd3792478a70.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=s4urvvisxUU9BxSExmwzN5tOPBI%3D&amp;x-signature-webp=HXpe342iarxGW0PuRyV%2FBoH6W8s%3D</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\de562a68a895415d90f13e5101632f6c.jpeg</t>
+          <t>Lib\hardware\data\images\e938a1f1a17848ba9ae2b3568c2d0b7d.jpeg</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/blisatu/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-komputer-laptop-garansi-1-tahun-hitam-39941?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/blisatu/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-komputer-laptop-garansi-1-tahun-hitam-39941?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1163,17 +1163,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/11/f1a5e8dc-36e6-41b1-b297-0871c88cdc8d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=DrFRLM0%2BOIzjMNJ99mmoFJNSYoU%3D&amp;x-signature-webp=Nq38tZZfZmAjG3ElHYmriRfrjaQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/11/f1a5e8dc-36e6-41b1-b297-0871c88cdc8d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=kFrfLyHXr2no392wpep1csDgsJM%3D&amp;x-signature-webp=NkpV4RgUkxjbpC20R689we9L5TY%3D</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\251db54fd1fe4952a683cea771e842f2.png</t>
+          <t>Lib\hardware\data\images\70fa0538654641b5b667cbdd0d2ed830.png</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/blisatu/speaker-robot-rs190-laptop-pc-gaming-soundbar-super-bass-portable-rgb?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/blisatu/speaker-robot-rs190-laptop-pc-gaming-soundbar-super-bass-portable-rgb?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/25/92ac9a5e-5d03-4584-82a7-00705b6f7bd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=KVGX%2BEOkqgXlGG0wLLQL8Y%2FQzN4%3D&amp;x-signature-webp=EAEATxqEf0NxExkHNSYeFVxLGNk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/25/92ac9a5e-5d03-4584-82a7-00705b6f7bd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=sBilIHcAKAq%2Fms6X3Trdokw2oZA%3D&amp;x-signature-webp=WEvbDjHQqRI6Ci5aIR5aPo%2F0Xz0%3D</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\880d5d6579b948c9b705bf6cb800bb27.jpeg</t>
+          <t>Lib\hardware\data\images\4d601aa56af14d3199a4a2ec9dcf515a.jpeg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/venusmobile/xiaomi-redmi-speaker-soundbar-komputer-bluetooth-aux-koneksi-desktop-laptop-gaming-rgb-computer?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/venusmobile/xiaomi-redmi-speaker-soundbar-komputer-bluetooth-aux-koneksi-desktop-laptop-gaming-rgb-computer?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=z3si6t1gUZe5kw1gL5kvjEp3s2s%3D&amp;x-signature-webp=CQ%2Fu1NAeoRaW9Vw0JdwjBh2keBU%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=vEZ2e0B2Lb4RGmpg2HTYLRy1ZVE%3D&amp;x-signature-webp=3l1McMimos5HeG75QDS%2Bx8xrxCI%3D</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9c759fc297ae4733bb5cee7f270e258e.jpeg</t>
+          <t>Lib\hardware\data\images\80f3819e1ecf40ca89b86c3863260328.jpeg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2023/11/11/c6e5f1ac-a7ee-42d3-b7f4-87e11a768173.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=DpbNqVulnByrf3jWpJcYijGRyrY%3D&amp;x-signature-webp=3i%2BLAmWtzracLeKZ0aNjMR4to88%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2023/11/11/c6e5f1ac-a7ee-42d3-b7f4-87e11a768173.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=1UH7wfAchV%2BWcufnIJiglHHjH7M%3D&amp;x-signature-webp=KnBtiVeChxX6GTjo6OUfgP9UZJg%3D</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b9689d4a71924e319b7c72d723318c9d.jpeg</t>
+          <t>Lib\hardware\data\images\069d66ed3f3d4ac78bc20ae0d501090a.jpeg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/expocomp/charger-innergie-by-delta-240w-gaming-adaptor-laptop-universal-t24?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/expocomp/charger-innergie-by-delta-240w-gaming-adaptor-laptop-universal-t24?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fa2db5fb271245a99a2a7fdaad38723b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=L8LLSU%2BGUkJGw77AcQlxP%2B8M6ZQ%3D&amp;x-signature-webp=Sw80SHZvweomAvzl9SWd8dYATNE%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fa2db5fb271245a99a2a7fdaad38723b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=v3W5p8%2B0E3Hn%2FWMRKZhVDVXp%2FRY%3D&amp;x-signature-webp=4FcXFY5cIaXiltU32Fya7cEzbfs%3D</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\54b8ec46125e48e18b9fc0be1609ad91.jpeg</t>
+          <t>Lib\hardware\data\images\87f629596a614ff4a71a539953cb9fb7.jpeg</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-kl332-kipas-pendingin-laptop-tornado-5-fan-tidak-licin-blue-1729729632344771388?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-kl332-kipas-pendingin-laptop-tornado-5-fan-tidak-licin-blue-1729729632344771388?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1420,17 +1420,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6ff3324cae5f46c3acb745a01c0de934~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=dGMwwKBFIAt0Yl8l7MMHnoQg034%3D&amp;x-signature-webp=z7tFr8IJh8Oq9GeFhDo1p0lpzdk%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6ff3324cae5f46c3acb745a01c0de934~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=oZcHKRTneqrcMynZAFZVSCWM%2Bog%3D&amp;x-signature-webp=Xt8xnGvZry5whcRpIBNm30KD0FM%3D</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f750e46a04b74e1a8490f75066b51ec5.jpeg</t>
+          <t>Lib\hardware\data\images\537f16b9726447bfb213f1603c9c54df.jpeg</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokobaru-s/skyworth-monitor-gaming-24-inch-h24g30q-2k-180hz-fast-ips-panel-1440x2560-16-9-hdr10-99-srgb-untuk-laptop-1731695301096015656?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch%26whid%3D18717103</t>
+          <t>https://www.tokopedia.com/tokobaru-s/skyworth-monitor-gaming-24-inch-h24g30q-2k-180hz-fast-ips-panel-1440x2560-16-9-hdr10-99-srgb-untuk-laptop-1731695301096015656?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch%26whid%3D18717103</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1472,17 +1472,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/3/28/1a2e9b92-8bfd-42a2-b3fb-6050eb6867b5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=2QwBstm6F%2FTE2VhmT9xNVzzVcOM%3D&amp;x-signature-webp=q51vUddtqapbUXHTDUg13KkwyiE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/3/28/1a2e9b92-8bfd-42a2-b3fb-6050eb6867b5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=pmXWUgLDjf6omuA8YhM0lsrroDM%3D&amp;x-signature-webp=JnQqFPU66ABpWY7p5%2B4VLz0Ql9c%3D</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b4218190bdb24780bcd349c19090c7b3.jpeg</t>
+          <t>Lib\hardware\data\images\dff7ee6619bf49c2a23e24dd22aac499.jpeg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/liemgroup/robot-m206s-wireless-mouse-optical-1600-dpi-silent-click-gaming-pc-laptop-new-m206-m206s-merah-muda-10503?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/liemgroup/robot-m206s-wireless-mouse-optical-1600-dpi-silent-click-gaming-pc-laptop-new-m206-m206s-merah-muda-10503?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/18/9b1c74c6-ffd2-45b1-bdd3-54758efb4bcf.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=xGKw5AIuZD1CB5c5QDfiI37eUyM%3D&amp;x-signature-webp=y5EtIA0FN4%2FbBJOh1VqLOMip2rQ%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/18/9b1c74c6-ffd2-45b1-bdd3-54758efb4bcf.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=A32LcdcgFpVOAEmVVjrW%2F2Z245A%3D&amp;x-signature-webp=OoQE4ngnntVVDQb3E1E0BnMkHmg%3D</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a211ea7d9221472a843b7c7f23e42105.jpeg</t>
+          <t>Lib\hardware\data\images\0bc201bacc8c46b3b8624a884eb0adff.jpeg</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/hagibis-indonesia-store/hagibis-8k-displayport-cable-1-4-high-refresh-rate-dp-cable-8k-60hz-4k-240hz-2k-360hz-for-gaming-monitor-graphics-card-pc-tv-laptop-1730797185172539267?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/hagibis-indonesia-store/hagibis-8k-displayport-cable-1-4-high-refresh-rate-dp-cable-8k-60hz-4k-240hz-2k-360hz-for-gaming-monitor-graphics-card-pc-tv-laptop-1730797185172539267?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/fe3c30b0c1da4d0fa9741d40670b6485~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=r5oEsc9UHYGMWn5vnyVmVHrQ%2BYU%3D&amp;x-signature-webp=7Bjc%2BkQ0Qf%2BqxMUAUG2%2FrU9HwVo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/fe3c30b0c1da4d0fa9741d40670b6485~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=d2YqKtj2YLyAaYg%2Bj2B%2BrfPMhBE%3D&amp;x-signature-webp=Qbr1Lr4oPwG2IsUFdng%2FHHUcx9U%3D</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\150fa24d465748118d06c6846ff2b3f7.jpeg</t>
+          <t>Lib\hardware\data\images\5d679a1811884fbe8d28263c2db3474c.jpeg</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/soruindonesia/soru-cooling-pad-stand-laptop-gaming-6-fan-kipas-pendingin-laptop-kipas-cooler-1729982466431355783?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/soruindonesia/soru-cooling-pad-stand-laptop-gaming-6-fan-kipas-pendingin-laptop-kipas-cooler-1729982466431355783?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1b714cec8f61478a99ddbdc25d4e5003~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=5vgco26ONLW5yy2fAi8TcwTWo5I%3D&amp;x-signature-webp=jmORWF2vXus8pxpvsl40kreqbww%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1b714cec8f61478a99ddbdc25d4e5003~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=5HcdBOLJ51khBuc171GWeU05BhE%3D&amp;x-signature-webp=4ULXDPK1jiJlheKIqwKt0h0PHms%3D</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8948b52ff0d5406385dfffc126f13575.jpeg</t>
+          <t>Lib\hardware\data\images\88ff07a117c14a509a6d789d8a6b782a.jpeg</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/onikumaindonesia/onikuma-cw902-mouse-gaming-hitam-kabel-original-untuk-laptop-komputer-pc-dengan-6400-dpi-tombol-rgb-dan-sensor-optik-tingkat-definisi-tinggi-button-1730338257921934858?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/onikumaindonesia/onikuma-cw902-mouse-gaming-hitam-kabel-original-untuk-laptop-komputer-pc-dengan-6400-dpi-tombol-rgb-dan-sensor-optik-tingkat-definisi-tinggi-button-1730338257921934858?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/13/31a814f6-f0bb-4d89-b3d4-0dafe63f22d7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=wt8juubHJa%2F5vXudCMD1RC879lo%3D&amp;x-signature-webp=QuxHB28jW04O3yNodgNr3hmWV4U%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/13/31a814f6-f0bb-4d89-b3d4-0dafe63f22d7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=PhuBWczb3vKLSYP96atH1xC4XzA%3D&amp;x-signature-webp=DjQGjZ8BZjiTpVbEg8swqBLA2%2FA%3D</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ba68760bce184c56b3b830fe53982182.jpeg</t>
+          <t>Lib\hardware\data\images\6aba8171719a4cf6b22c4da92f64984b.jpeg</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lenovo-authorized-surabaya/charger-innergie-by-delta-180w-gaming-adaptor-laptop-universal-t18?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch%26whid%3D11569999</t>
+          <t>https://www.tokopedia.com/lenovo-authorized-surabaya/charger-innergie-by-delta-180w-gaming-adaptor-laptop-universal-t18?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch%26whid%3D11569999</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/70a5e998-ee7d-48c8-b0f6-c652f9a12d32.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=b%2BRgS8Ore65%2B0pscSMOQDkPMGJY%3D&amp;x-signature-webp=WK5QX3qvF4q48eBe84x5iqJ%2FUVc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/70a5e998-ee7d-48c8-b0f6-c652f9a12d32.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=g%2FUfTr5cKD1rxmq71Y%2F%2F3IR%2FQZc%3D&amp;x-signature-webp=Fzo8qxr0PyozlHar5GexdsunWr8%3D</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b895f00d19b34c6a8cbdc63b7bc5f8ea.jpeg</t>
+          <t>Lib\hardware\data\images\5ea405343da14d548bd94ac9616392c8.jpeg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-innergie-gaming-universal-original-180w-150w-130w-65w-45w-1731234857708193451?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-innergie-gaming-universal-original-180w-150w-130w-65w-45w-1731234857708193451?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/15/373a1aa1-4150-4341-9439-debc881a4fd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=VC2F3ZYQN6vtFy0Yz1XDB84r7MQ%3D&amp;x-signature-webp=wx1%2F2SFX2jHRIcvul5ZtWUwVk4M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/15/373a1aa1-4150-4341-9439-debc881a4fd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=M4TPgQLv3CfTRg8D1KFmBOrHqSw%3D&amp;x-signature-webp=6DMUigapvmEUV%2Fxi45H2mcbkv2k%3D</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e2cc4acd7d25425c8191cb836045c754.jpeg</t>
+          <t>Lib\hardware\data\images\295d30c9aca74245a6788e3afc185395.jpeg</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-gaming-mechanical-87-keys-wired-keyboard-layout-rgb-light-universal-pc-laptop-1730787426880030393?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-gaming-mechanical-87-keys-wired-keyboard-layout-rgb-light-universal-pc-laptop-1730787426880030393?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5d662cb1-9633-4475-9bb5-82f645202a74.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=lvMFSZ1AUJ5KDjbQZgR%2FLDcMN0o%3D&amp;x-signature-webp=kHirZ%2B7gerTVGmjNGtsqcdD9twc%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5d662cb1-9633-4475-9bb5-82f645202a74.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=Fo74HylM2bAgLvYuZ7VkE%2BeDWzI%3D&amp;x-signature-webp=DOx7XqKIEAE5%2FcE2wipwX2JstVA%3D</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b140c4236b424ef283362f2d0741e593.jpeg</t>
+          <t>Lib\hardware\data\images\536ed4f57c6441eca0e6fb3145b666d7.jpeg</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adapter-innergie-charger-laptop-gaming-acer-asus-dell-hp-lenovo-280w-200w-1731234851512288939?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adapter-innergie-charger-laptop-gaming-acer-asus-dell-hp-lenovo-280w-200w-1731234851512288939?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/20/b4aa025b-29e1-44b1-b8e7-776a2899eef3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=CApA%2BtrN%2B4LdC%2FGKYQGxeLSUCfY%3D&amp;x-signature-webp=RB9yxUyi5xcwaSUQgZjYgkSm8JA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/20/b4aa025b-29e1-44b1-b8e7-776a2899eef3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=xUoHx0eZ110eBOz8EiSgAMD70zI%3D&amp;x-signature-webp=Rm8J5bFp6Lh%2BIS8y7PiBV%2Fcz32w%3D</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d388ea1220fa49f6b2227003f51f33ea.png</t>
+          <t>Lib\hardware\data\images\72eb1f6553ad4d53b809c798b47a312d.png</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-wireless-mouse-mechanical-gaming-bluetooth-5-0-dual-mode-silent-click-type-c-fast-charging-screen-display-3200dpi-untuk-pc-laptop-1730803778625832633?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-wireless-mouse-mechanical-gaming-bluetooth-5-0-dual-mode-silent-click-type-c-fast-charging-screen-display-3200dpi-untuk-pc-laptop-1730803778625832633?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5087391e11d74a6cbbd2950bf01e6539~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=eWommA%2FqcIeLaQlmre0G5XPAsbk%3D&amp;x-signature-webp=gtMvmabBYWdLiM9YQCe6z1%2Btb0A%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5087391e11d74a6cbbd2950bf01e6539~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=o7RLDNVKcMJYXVflGMptyaRJ3N4%3D&amp;x-signature-webp=PsrjNGcOjniC514cmnURVFTC7OQ%3D</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7559742216e1499080727dc80ea2981b.jpeg</t>
+          <t>Lib\hardware\data\images\ccc2a8eea00a498abedf84405e25d407.jpeg</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-pendingin-laptop-2-kipas-kl330-fan-1729636686228589372?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-pendingin-laptop-2-kipas-kl330-fan-1729636686228589372?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/1/26/4f9883a0-3d3f-4986-97f3-3f5751f7165c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=parm2WyIvvz8pCuidOXERQ33rek%3D&amp;x-signature-webp=6ufEIPIQv8ocPPsydAdtIjNar%2Fk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/1/26/4f9883a0-3d3f-4986-97f3-3f5751f7165c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=YHMa5VAvilhI%2FpBQMm0et%2BR76nc%3D&amp;x-signature-webp=crKwJOWuVP5T%2BF8SZl%2BweIEh8RA%3D</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4605611cd3a54af686a6e0441ba5c89d.jpeg</t>
+          <t>Lib\hardware\data\images\034f759729d147548ef8a3354a6e4c8c.jpeg</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/d-m-i/nyk-x1-wind-coaster-gaming-cooling-pad-laptop-with-3-fan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/d-m-i/nyk-x1-wind-coaster-gaming-cooling-pad-laptop-with-3-fan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/3/23/a52ecf75-8473-45e9-a91d-36c8da636f5e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=J2utVlde9XRDqGU6nZz1TWEm8Rk%3D&amp;x-signature-webp=jLW8P7zYOC0eeP8eabT2piLKl2M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/3/23/a52ecf75-8473-45e9-a91d-36c8da636f5e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=9f%2FjxdHuT1IHj6gCyEqdeEgxU0o%3D&amp;x-signature-webp=fnJeSjxOsofvRnS9DSFKP6homfk%3D</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bb8d5ad20465405d931e2ff3a7cac6ee.png</t>
+          <t>Lib\hardware\data\images\f2f35314afa14a91b77d770d23766fbf.png</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/andalassuryagemilang/fan-laptop-cooling-pad-notebook-gaming-nyk-x3-winterstorm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/andalassuryagemilang/fan-laptop-cooling-pad-notebook-gaming-nyk-x3-winterstorm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6b4457908324a2788e9a7da6815e258~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=1vluCvuzyD2sX%2BszqSO1HnvlgMA%3D&amp;x-signature-webp=bo4Ob5rjBm7aher2QihEYc5Hwh0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6b4457908324a2788e9a7da6815e258~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=C4oDT7t9SQ1wQCYp0KMrS73VIkQ%3D&amp;x-signature-webp=Yr21wKU%2FIgNCQQbsb0zl5d8OBa8%3D</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\39b636e5b64c45e0a2f472ddcdda8bfb.jpeg</t>
+          <t>Lib\hardware\data\images\c84f8c54d09844df960055c64695ee1e.jpeg</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mouse-gaming-kabel-unitech-s1-colorfull-rgb-light-3200-dpi-untuk-komputer-pc-laptop-1729643499823991194?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/mouse-gaming-kabel-unitech-s1-colorfull-rgb-light-3200-dpi-untuk-komputer-pc-laptop-1729643499823991194?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/25/98ce42ec-a8a6-4112-9380-10eadb2994f5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=vO6lOaeTQq4NtBruBn6Re1d8Uhg%3D&amp;x-signature-webp=3vWOH9dbEilCe4XZ05Jzp%2FQqGWQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/25/98ce42ec-a8a6-4112-9380-10eadb2994f5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=bqbWOUj3v60L9jnNWv1WgGSh64w%3D&amp;x-signature-webp=YHHboNBdTing9Yc0y6fiACsn24o%3D</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\652b6207570641718ecf2615d887f124.png</t>
+          <t>Lib\hardware\data\images\3b44a32928154f558994f4d7fe1084d3.png</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-gaming-kabel-usb-wired-rgb-light-optical-1200-1600dpi-ergonomic-untuk-pc-laptop-dengan-2-speed-dpi-adjustable-dan-tombol-6d-black-1731239865956402840?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-gaming-kabel-usb-wired-rgb-light-optical-1200-1600dpi-ergonomic-untuk-pc-laptop-dengan-2-speed-dpi-adjustable-dan-tombol-6d-black-1731239865956402840?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5c94cc2b-9899-4e95-ae52-c5f60a45630c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=kJhBXm%2BpZXtCTlpPm1OqLXBOuJ4%3D&amp;x-signature-webp=ImTvTwlF%2BZEmhtdBJN%2BJcie5Vmo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5c94cc2b-9899-4e95-ae52-c5f60a45630c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=T4XFhWr8tiSmydJvuTr6C34eYhw%3D&amp;x-signature-webp=u3K06YLeO4qxd0%2FkmZ5jv1Z6e%2BM%3D</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f85ef1d578e84caaaa45d81c0f93196a.jpeg</t>
+          <t>Lib\hardware\data\images\5c37a62eec5c497bb26b065ee5795860.jpeg</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-gaming-universal-innergie-240w-230w-200w-20v-12a-t24-1731234878706910891?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-gaming-universal-innergie-240w-230w-200w-20v-12a-t24-1731234878706910891?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0c39492bae8949e79deb61008e4da18c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=nmEjkd5Cs4RCKp419wnbAyakt1M%3D&amp;x-signature-webp=neD9Kfk48Fw%2FjsAoswCnKcQyHO0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0c39492bae8949e79deb61008e4da18c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=%2BlR5dP3WN8iPlfc%2Fw7OlRrw8zg8%3D&amp;x-signature-webp=Y45bVDk7lSwdZ2%2FZK0%2Fx5r%2BZPMQ%3D</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\110439d5ce0a4aec98d66491fbd171bd.jpeg</t>
+          <t>Lib\hardware\data\images\da05714d56364d57915fca0d5d3c6118.jpeg</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bikepremiumstore/headset-headphone-gaming-power-full-bass-hs04su-mic-earphone-komputer-laptop-pc-3-5mm?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bikepremiumstore/headset-headphone-gaming-power-full-bass-hs04su-mic-earphone-komputer-laptop-pc-3-5mm?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2258,48 +2258,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>102118726768</v>
+        <v>11689876861</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nemesis Coolingpad Gaming Turbo Air Compressed Up To 21 Inch Laptop BEIRUZ AX3 COOLING PAD RGB</t>
+          <t>CABLETIME Mouse Pad Aluminium Metal Premium Gaming Dekstop Laptop DeskMat Smooth</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>539000</v>
+        <v>136900</v>
       </c>
       <c r="D37" t="n">
-        <v>700000</v>
+        <v>150250</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Best Elektronik IT</t>
+          <t>CABLETIME Jakarta</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Jakarta Pusat</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6e153097f95486d892d9338928ef0fa~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=izZ0vzBMWu5Usm%2BwA%2BYimwVmT5M%3D&amp;x-signature-webp=Ts6PVQ968NsTXBQbrMsYZwlXNIk%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e190eea8efac4e969fd89e79beb0140f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=mzl%2BNhEQZmcZzsMEPMgTTXTOYt4%3D&amp;x-signature-webp=dW%2FeoL3%2BOPF2LLTSI16FwKmBdSQ%3D</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8a86036d8f294c3a9ef2477d44ad9391.jpeg</t>
+          <t>Lib\hardware\data\images\05e555b5e87f49c1a39645880d2d5a86.jpeg</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bestit/nemesis-coolingpad-gaming-turbo-air-compressed-up-to-21-inch-laptop-beiruz-ax3-cooling-pad-rgb-1732247682542044373?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/allitems-id/cabletime-mouse-pad-aluminium-metal-premium-gaming-dekstop-laptop-deskmat-smooth-1731201382108268433?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2310,48 +2310,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>11689876861</v>
+        <v>102118726768</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CABLETIME Mouse Pad Aluminium Metal Premium Gaming Dekstop Laptop DeskMat Smooth</t>
+          <t>Nemesis Coolingpad Gaming Turbo Air Compressed Up To 21 Inch Laptop BEIRUZ AX3 COOLING PAD RGB</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>136900</v>
+        <v>539000</v>
       </c>
       <c r="D38" t="n">
-        <v>150250</v>
+        <v>700000</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CABLETIME Jakarta</t>
+          <t>Best Elektronik IT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Jakarta Pusat</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e190eea8efac4e969fd89e79beb0140f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=VGG%2F5ZcB%2BfcT9lq4yW0WLk0NgRA%3D&amp;x-signature-webp=zsf9Qcntl2DhTL6KQy4101rwNrQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6e153097f95486d892d9338928ef0fa~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=OTeD7aRj2N%2FF2gmDwaFERdGWgW0%3D&amp;x-signature-webp=1mgoy%2BtBUADSukFVkv3veP%2BmNQo%3D</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0dbbed8d24c74437a3258db767489b85.jpeg</t>
+          <t>Lib\hardware\data\images\545f752fbb2848098fa70bf38c9d608a.jpeg</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/allitems-id/cabletime-mouse-pad-aluminium-metal-premium-gaming-dekstop-laptop-deskmat-smooth-1731201382108268433?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bestit/nemesis-coolingpad-gaming-turbo-air-compressed-up-to-21-inch-laptop-beiruz-ax3-cooling-pad-rgb-1732247682542044373?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3b54f1bf88024c7482a8a32e8c98eaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=%2BjSVu%2FasZWpDD365ZHNIHRc1vU8%3D&amp;x-signature-webp=CVB60jxmjgpPJz80jGMITjtarVU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3b54f1bf88024c7482a8a32e8c98eaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=8Ebv90KMWInXQxq%2BThRoDW%2FYL4M%3D&amp;x-signature-webp=WOGPcEQf7jL%2FVnYT2vDqACXi9lA%3D</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\991e6bca3ad440449a9b07d0ab767186.jpeg</t>
+          <t>Lib\hardware\data\images\d124fccd864848c490d757da7ebb11dc.jpeg</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bikepremiumstore/headset-gaming-headphone-mic-power-full-bass-hs-04su-earphone-komputer-laptop-pc-3-5mm-mobile-live-streaming?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bikepremiumstore/headset-gaming-headphone-mic-power-full-bass-hs-04su-earphone-komputer-laptop-pc-3-5mm-mobile-live-streaming?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/9/22/73b26064-75be-46de-b155-5535d7d164c0.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=WBelytEHJP6fIUFFBfRt%2Fs69jLc%3D&amp;x-signature-webp=N5vXTbKIVrO3AWgz3q2ywbDgqx4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/9/22/73b26064-75be-46de-b155-5535d7d164c0.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=uxEIrqyFZn7N2Ml6VkqchJgHQgo%3D&amp;x-signature-webp=qC0FtKKVgredUCHUIfuqz6Z%2FVEQ%3D</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\86177208348f4642b66b97b195e6b344.jpeg</t>
+          <t>Lib\hardware\data\images\ece31b38eb0a4090a4c5e02af7f2bcdc.jpeg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-laptop-cooler-gaming-cooling-pad-fan-cooler-turbo-silent-srq-019-32d50?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-laptop-cooler-gaming-cooling-pad-fan-cooler-turbo-silent-srq-019-32d50?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9863a40e2c6f4645a11e10bb72c0701c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=VIgZAUtu655r4eb8DVr%2BOHpHeA8%3D&amp;x-signature-webp=J2CRda1zcHdm4ZuAT88OYHSuQn8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9863a40e2c6f4645a11e10bb72c0701c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=oN0tA%2Fbhhh3NM3sgKwvQxmrc70Q%3D&amp;x-signature-webp=CfllMyOgS6FZT%2FZHZQ5O18a%2B1Ls%3D</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7ddc97312861442ab57b7fbca3fd2f3e.jpeg</t>
+          <t>Lib\hardware\data\images\07d29e40b1454073a830d8dd1ab2f291.jpeg</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tasairbone/tas-ransel-laptop-gaming-polofelix-anti-air-waterproof-soft-case-pelindung-laptop-macbook-size-besar-1731153071094466207?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tasairbone/tas-ransel-laptop-gaming-polofelix-anti-air-waterproof-soft-case-pelindung-laptop-macbook-size-besar-1731153071094466207?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2540,17 +2540,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/22/99a529bd-4693-440e-90e1-cf2b813f8692.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=6o5GckgMaexuS7hXlszYKQPia5U%3D&amp;x-signature-webp=dg809nuqYvyaMGz%2F3Dx9xcyIhB4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/22/99a529bd-4693-440e-90e1-cf2b813f8692.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=w3uz%2BGWul6vkZ45vPRT1UVYCrMU%3D&amp;x-signature-webp=Tq0kJdxSLZlHgAxFE%2FXEvk0yM%2BA%3D</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\52c5d6b608bc4aef92b4705143421d42.jpeg</t>
+          <t>Lib\hardware\data\images\7190c65e8bf540768b771a655793800d.jpeg</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/d-m-i/deepcool-n80-rgb-gaming-cooling-pad-for-laptop-cooler?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/d-m-i/deepcool-n80-rgb-gaming-cooling-pad-for-laptop-cooler?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/6/23/42a98edc-3f69-43a5-acb7-82cd258ba31a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=oCyDvC37OmjJSNCYuD5XbBmIwns%3D&amp;x-signature-webp=We8ufK1TKsIHtgJisQNtyAOopZY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/6/23/42a98edc-3f69-43a5-acb7-82cd258ba31a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=a%2Fn5mmmjT%2BT%2F1Ow0mnkzgUqmHXs%3D&amp;x-signature-webp=2wKTra7cSldnV6SeuvKwQQIRLSE%3D</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\18a9847b3bfc469bb113da447f9072ac.jpeg</t>
+          <t>Lib\hardware\data\images\93c16c7abe9b41b5aeb5da18193140bb.jpeg</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/affselv-now/affselv-cooler-laptop-cooling-pad-5-fan-17-inch-adjustable-speed-2600-rpm-kipas-pendingin-laptop-gaming-dengan-6-level-kecepatan-dan-4-level-ketinggian-untuk-laptop-hingga-15-6-inch-1733156196976723940?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/affselv-now/affselv-cooler-laptop-cooling-pad-5-fan-17-inch-adjustable-speed-2600-rpm-kipas-pendingin-laptop-gaming-dengan-6-level-kecepatan-dan-4-level-ketinggian-untuk-laptop-hingga-15-6-inch-1733156196976723940?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2641,17 +2641,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4c66596fc2ce4ad29797c2e977512d7f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=jGRaWuwj0HowZf7GPcriBZYWQ6Y%3D&amp;x-signature-webp=wz5lSKkJg9oqXGR4lJK3GkCbjVY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4c66596fc2ce4ad29797c2e977512d7f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=s8ekOpkBcm8VC7E0RCDg8NNWjIY%3D&amp;x-signature-webp=eru%2FcpTrqLFNbJzFdzct%2BQ%2B%2FMz0%3D</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bdcde03b6936497e91449ca03343bcc4.jpeg</t>
+          <t>Lib\hardware\data\images\7a7a17039a46425fb9d422d6a6f85f2a.jpeg</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olike-official/new-product-olike-desktop-speaker-sc07-6w-subwoofer-rgb-light-gaming-full-bass-360-surround-sound-portable-wired-connection-for-laptop-pc-1733184933872698864?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olike-official/new-product-olike-desktop-speaker-sc07-6w-subwoofer-rgb-light-gaming-full-bass-360-surround-sound-portable-wired-connection-for-laptop-pc-1733184933872698864?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/10/11/7d1054d5-ebac-4558-a9f0-204c541144bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=rwtNB8zsdzjJwuRb0pWDahKh6o8%3D&amp;x-signature-webp=EvhZGJNQx6RB7HMZkpuegpaTXN0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/10/11/7d1054d5-ebac-4558-a9f0-204c541144bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=OOqEpPl535QukP9%2BD3%2BSr%2FV3kBo%3D&amp;x-signature-webp=DS6UFJ6QohnHB%2BpC%2BBDZpnsmVyM%3D</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ee57a1ae0480425b89394a7ca70fd1a7.png</t>
+          <t>Lib\hardware\data\images\63811243d1614271a5c47709c18ed252.png</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fashionselular/headset-gaming-led-onesos-sy830-headphone-bass-with-mic-hp-pc-laptop-led-blue?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fashionselular/headset-gaming-led-onesos-sy830-headphone-bass-with-mic-hp-pc-laptop-led-blue?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2739,17 +2739,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/152cf82999ae4c61845620b1616abb22~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=6OP9ETg55WveHtayI%2BHcuTMwAUA%3D&amp;x-signature-webp=B6%2BRTJhoYOfWGNOJSMSjY%2BxG1rU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/152cf82999ae4c61845620b1616abb22~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=Ye4YeYv4SZZDclJpNlbhpdK2VcA%3D&amp;x-signature-webp=UqMkVGb%2Fxv2zCfC7yh%2BApOCyXTE%3D</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a2558b3f03814856a334fd2bf99bd384.jpeg</t>
+          <t>Lib\hardware\data\images\20dd576e75434f879af87bffaa34a249.jpeg</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dell-premium-official/dell-backpack-alienware-vindicator-17-3inch-armored-tas-gaming-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dell-premium-official/dell-backpack-alienware-vindicator-17-3inch-armored-tas-gaming-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/d1ef1c4a86a7447988bcbdce4d35fa2b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=0ov9Vb9Cmpvm9ROfThlMh%2B7iHvw%3D&amp;x-signature-webp=r1N78QHfQaeAJwhO1JzRtlttS5c%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/d1ef1c4a86a7447988bcbdce4d35fa2b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=MIvZribycsz3ETRDvuiCyQT%2FrOA%3D&amp;x-signature-webp=KZjpFsVHKKYsNmy9XdwFVE0K8%2BA%3D</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c4bb3a9232774618968d0b7951391467.jpeg</t>
+          <t>Lib\hardware\data\images\932ab6face0c4a5784782bfc0f9d6db6.jpeg</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-keyboard-gaming-k358-led-rgb-bachlight-support-all-komputer-laptop-hitam-7a474?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-keyboard-gaming-k358-led-rgb-bachlight-support-all-komputer-laptop-hitam-7a474?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/f9a4449e-bfff-4df1-b18f-c1e2af70c4b4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=ao6x8BB0HW%2Bzd3pbXyGgmUAw8HU%3D&amp;x-signature-webp=zGvM6bBwS4l1BK1F%2FDxXR9WJiuY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/f9a4449e-bfff-4df1-b18f-c1e2af70c4b4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=rHrJwDuVxmRHrSljn0F7o3YM8W4%3D&amp;x-signature-webp=vOw90N7ZZuVhvbcEal2JvRyOeaM%3D</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\83b25822e8024ca5b72e9e61f9b17567.png</t>
+          <t>Lib\hardware\data\images\ef1f848a7fe24ce0966dd3edf90c0e55.png</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/promodazzle/terlaris-ugreen-headset-kabel-mfi-iphone-android-type-c-lightning-3-5mm-original-100-garansi-resmi-24-bulan-official-store-mall-ori-murah-termurah-terbaik-tablet-samsung-xiaomi-macbook-laptop-pc-typec-earphone-handsfree-super-extra-full-bass-gaming-typec-60700-a7403?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/promodazzle/terlaris-ugreen-headset-kabel-mfi-iphone-android-type-c-lightning-3-5mm-original-100-garansi-resmi-24-bulan-official-store-mall-ori-murah-termurah-terbaik-tablet-samsung-xiaomi-macbook-laptop-pc-typec-earphone-handsfree-super-extra-full-bass-gaming-typec-60700-a7403?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2895,17 +2895,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/16/59db287d-8254-4933-b80e-ef38ff1ddbb7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=HxbMUdficcq79UTBb8LAVbPil9g%3D&amp;x-signature-webp=SHdem%2FN9DNZsr%2BN556%2Bi5e7gj30%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/16/59db287d-8254-4933-b80e-ef38ff1ddbb7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=csBTWl7VA5ADDHoAPJYXN2pdLAE%3D&amp;x-signature-webp=mC15C8Zj8qjPMAFD7qqaKsqja2k%3D</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\887caf6424514d229d119f52b2cccbb5.jpeg</t>
+          <t>Lib\hardware\data\images\51c3ba26b94d417799faaf8180a48752.jpeg</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-pc-komputer-laptop-garansi-1-tahun-bisa-cod-1731162798337328677?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-pc-komputer-laptop-garansi-1-tahun-bisa-cod-1731162798337328677?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/3/16/62a45061-18e3-48fb-ba3f-42dd8d84b589.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=%2FQU7U3CKCKyicxBYUWCA8MVbTMo%3D&amp;x-signature-webp=L6upgV8P02%2FH3SP%2Bhzk9V%2B2i8Qo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/3/16/62a45061-18e3-48fb-ba3f-42dd8d84b589.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=gitvOgUBw8RDOhosAqvELQ770X8%3D&amp;x-signature-webp=F71Ny2vxmyi6DFCCG%2BM7ze20boE%3D</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cbeaeb2a372c4b8f844809ce96ad6892.png</t>
+          <t>Lib\hardware\data\images\2fb0adca4638463eb7edebc2e704ffb8.png</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/donatur/robot-rs200-speaker-e-sports-gaming-for-pc-laptop-smartphone-ori?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/donatur/robot-rs200-speaker-e-sports-gaming-for-pc-laptop-smartphone-ori?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -2996,17 +2996,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/6/9/09ab3d23-47ae-4005-ab4a-cfbc36d7fa4d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046951&amp;x-signature=NYJwXL%2F0eEbbA8STd63fbJuAEF4%3D&amp;x-signature-webp=LZR39mh5Y%2BLCmHDBJ7EOufYxHeU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/6/9/09ab3d23-47ae-4005-ab4a-cfbc36d7fa4d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=xU0Wn6GWXmULTAbsCRfz%2FSjrBLQ%3D&amp;x-signature-webp=5Gd1ItNet7vrxYjXcGTQqQeH%2BG0%3D</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cd869595b1824c6fb7c7f2c167bfd26c.png</t>
+          <t>Lib\hardware\data\images\36fefe33ac20443fa034fd1649ce0d71.png</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supermallori/supermall-mouse-pad-gaming-mousepad-alas-laptop-xl-900-x-400mm-blue-dora?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504023137BC2F75BF1BCF10B10Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supermallori/supermall-mouse-pad-gaming-mousepad-alas-laptop-xl-900-x-400mm-blue-dora?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3048,17 +3048,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9060d5fb44cf4b2faa8e9864b1542c37~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=Bjj7rr2AcAfQEfbPJzmJaUUs35k%3D&amp;x-signature-webp=05kPhjPtmCl6W%2BpMLJPRkCPXLiI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9060d5fb44cf4b2faa8e9864b1542c37~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=%2FpzVsjUfUO1vyqF2sY%2BVwReac8I%3D&amp;x-signature-webp=BmLNfASbDcrobYOkamvyw0%2FxURU%3D</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a74e6761c08944f89c79a0db7c7f44cf.jpeg</t>
+          <t>Lib\hardware\data\images\46ab812d2906416d9988f3cdb2ea4175.jpeg</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocofficialstore/tomtoc-t60-explorer-laptop-backpack-office-bag-size-22l-1732719801450137078?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocofficialstore/tomtoc-t60-explorer-laptop-backpack-office-bag-size-22l-1732719801450137078?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3097,17 +3097,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/11/28/265f544d-72eb-43c7-8a97-1756f4f7fcb6.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=flRqNG4WgquBf4E3pSOBg7xySJ4%3D&amp;x-signature-webp=kBlKUA%2BaX0ylnvLtj7A4Esfvmc4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/11/28/265f544d-72eb-43c7-8a97-1756f4f7fcb6.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=tR19gY4jFPDA2j5wzg%2B8HcSxir0%3D&amp;x-signature-webp=3i%2FksXG4G8SjK4ftomO8k6HZ%2BEI%3D</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c5fe51c9cfb249659a3db62f8ec6410f.jpeg</t>
+          <t>Lib\hardware\data\images\dadc8d201f264a5faa6a624f0a9f98be.jpeg</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcompsolo/mikuso-kb-052u-wired-usb-keyboard-104-key-pc-laptop-office-ergonomic-hitam-6ac76?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D16130095</t>
+          <t>https://www.tokopedia.com/starcompsolo/mikuso-kb-052u-wired-usb-keyboard-104-key-pc-laptop-office-ergonomic-hitam-6ac76?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D16130095</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3149,17 +3149,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/26f44dfba5404212ad862b746e42857a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=UPK7tBCmLcuAkXn3iTaVE%2BVLRkg%3D&amp;x-signature-webp=c6sio%2FRgTFQZ0AsQD53EiuKJMlM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/26f44dfba5404212ad862b746e42857a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=U7PLK5zlnwq6xRWVPU2Jljk%2BMgI%3D&amp;x-signature-webp=2nF4vhnUNGEEhgRthTgIz7F7t6Q%3D</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f8061192e69543aa8bb774c7d9947c90.jpeg</t>
+          <t>Lib\hardware\data\images\8d4c26997dd9452bba90ca0fe0abbcdd.jpeg</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitechone-keyboard-mouse-combo-set-office-master-keyboard-mouse-for-pc-laptop-gadget?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitechone-keyboard-mouse-combo-set-office-master-keyboard-mouse-for-pc-laptop-gadget?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3201,17 +3201,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e59a9d3733e44c89e422d639b080b4b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=B77OM70uMhuny0lkGinqaftVywk%3D&amp;x-signature-webp=1uFD%2Fw%2Baf5h3OuydKxqpF8iVAOA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e59a9d3733e44c89e422d639b080b4b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=aMaJk5Di%2FUFuCt%2FDD8ftMwVn2dg%3D&amp;x-signature-webp=VbWC77XBiP6b8J45frQehTurzjA%3D</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a4fd4da530e54c778711d45a886251fe.jpeg</t>
+          <t>Lib\hardware\data\images\98b4ef638aaf410db0e4f38d55403992.jpeg</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/gameridsurabaya/laptop-lenovo-legion-5-15-intel-core-i7-13650hx-rtx-5050-8-gb-ram-16-gb-ssd-512-gb-windows-11-office-home-student-15-3-wuxga-165hz-100srgb-1732195924137248723?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/gameridsurabaya/laptop-lenovo-legion-5-15-intel-core-i7-13650hx-rtx-5050-8-gb-ram-16-gb-ssd-512-gb-windows-11-office-home-student-15-3-wuxga-165hz-100srgb-1732195924137248723?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/9/4/92698dcd-813c-417b-a377-062feb24f1da.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=xKOcJr5q9cqLu2ixCp1WT%2F0cHLE%3D&amp;x-signature-webp=9V2UGnSJ1BON%2FUdq7nXnl%2BWI%2FzI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/9/4/92698dcd-813c-417b-a377-062feb24f1da.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=Z2jrVurAxZUmvseyS%2BOKwL0g%2FRM%3D&amp;x-signature-webp=uNSdlvEWdH27x9WlABUkD76ls1o%3D</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bfaf9e148d8745eca88f14ade228aad6.png</t>
+          <t>Lib\hardware\data\images\bbb6f5b8fb9d42e7aeeed7e7c925a5e4.png</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-gradaz-office-bundle-tas-ransel-kerja-backpack-laptop-tas-selempang-ipad-organizer-charger-pouch-multifungsi-only-bag-black-0e00a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-gradaz-office-bundle-tas-ransel-kerja-backpack-laptop-tas-selempang-ipad-organizer-charger-pouch-multifungsi-only-bag-black-0e00a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3302,17 +3302,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=f%2FQXafuG7Qx25tMmPnh93NIYdX8%3D&amp;x-signature-webp=i3ik5DjSX3XQySejU5fe2I2Qq3o%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=l9LtwZxrJ977TmmHMi2mJ7eoxak%3D&amp;x-signature-webp=XcYJp%2BQuqwJsH6eeMCHo2eQwxnY%3D</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5d60a166211e44ec9da3dd77163a37e8.png</t>
+          <t>Lib\hardware\data\images\361e1294a9444d6dab438142cae298d9.png</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/13/c3ad5491-fc3d-4b80-b80a-59b49374ce68.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=YMBiEnoNJCmPARmpyCxCmV6Uzmo%3D&amp;x-signature-webp=uJ84FBok0zKdZUnhlUOMiXSlzA0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/13/c3ad5491-fc3d-4b80-b80a-59b49374ce68.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=3TQb38fYktkyr5kNBBLnrQlAI3I%3D&amp;x-signature-webp=mFzvuWgCXHS0Biuy%2FVL%2F7QBidrI%3D</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d41eecbb7279491f9c5190ebd557802d.jpeg</t>
+          <t>Lib\hardware\data\images\dac2eb935e7641afa603868b679d54d6.jpeg</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/backpack-tas-ransel-office-punggung-sekolah-kuliah-kerja-laptop-15-inch-torch-loka-1730777953781646394?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/backpack-tas-ransel-office-punggung-sekolah-kuliah-kerja-laptop-15-inch-torch-loka-1730777953781646394?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/15/a0091498-b7ce-4323-9e2d-682fd5afcdde.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=tpD0WqZke8OzouMO9vWEzGRc4GY%3D&amp;x-signature-webp=kmz46w68MsHaisng%2FCvRMp7Ks6E%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/15/a0091498-b7ce-4323-9e2d-682fd5afcdde.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=L4PccphTQwRBOt9mcD8UGPi5lBI%3D&amp;x-signature-webp=TnM9y0XfNrJR57zfJOz9MTnbMJc%3D</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bc1279a69ac64e18afd1f8af129b150d.png</t>
+          <t>Lib\hardware\data\images\92a23b2983624d0697078896416a5581.png</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-office-collection-tas-ransel-kerja-kantor-laptop-stylish-pria-wanita-hongcheon-black-eaee2?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-office-collection-tas-ransel-kerja-kantor-laptop-stylish-pria-wanita-hongcheon-black-eaee2?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3458,17 +3458,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/45db327a9c23430aa3e9f3da70e0d1af~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=hzjrIfNKBO3pTrN6HmmluwdtEYQ%3D&amp;x-signature-webp=2XUzn6SYH30HFm8k%2FxJWcZQeJmI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/45db327a9c23430aa3e9f3da70e0d1af~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=ufQRnDUahqJozI%2FonX7WkzcNmaU%3D&amp;x-signature-webp=eSQgFSFX01rz3a8fgi8LpDExzkA%3D</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f1c7e6e378aa4377859db3a17422d211.jpeg</t>
+          <t>Lib\hardware\data\images\ba49b6282d1c42dabd2b9c2c093a29ca.jpeg</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-g6-untuk-komputer-laptop-pc-1000-dpi-mouse-office-computer-1729590282578069914?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-g6-untuk-komputer-laptop-pc-1000-dpi-mouse-office-computer-1729590282578069914?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3510,17 +3510,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f1f4aa17bf5c43cc9eea095c93d0bf11~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=PcfdUTWWORYWoPTZwqjGMbwLuSE%3D&amp;x-signature-webp=sTkj5tW2o33VF9ufVxFlFEUcaio%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f1f4aa17bf5c43cc9eea095c93d0bf11~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=5GP6N1kUKxzj%2BAuEm3DQjf9yTPA%3D&amp;x-signature-webp=M7SMZQ0fk584eWeMdY26Zr7VWgw%3D</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e4ef8823fbd34e8ba838b806b4e80c85.jpeg</t>
+          <t>Lib\hardware\data\images\f6e14ae1b5d3448ba5f0f4cdf4b340b7.jpeg</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/optical-mouse-office-kabel-usb-unitech-g5-1000-dpi-untuk-laptop-pc-computer-1729588341583546778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/optical-mouse-office-kabel-usb-unitech-g5-1000-dpi-untuk-laptop-pc-computer-1729588341583546778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3559,17 +3559,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3baef23e7214219af4e67c58e42992c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=G1K2EyZ0nC2m4q%2FLdwZpeQB01FE%3D&amp;x-signature-webp=o5umcjNdhDUiEEYzvfOey1%2BXJdM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3baef23e7214219af4e67c58e42992c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=g%2BKZ%2B%2BBTqf0ice9cyh%2F972rA9eE%3D&amp;x-signature-webp=J4AM%2BakMIgSml%2BWSFJcAJUGmlJQ%3D</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\947761a14e93474d9bd62bdaba5be1d9.jpeg</t>
+          <t>Lib\hardware\data\images\6678c24f9a344ab592fb870547ad620c.jpeg</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-wired-usb-portable-office-keyboard-for-pc-laptop-computer-hitam-keyboard-1731239918096844440?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-wired-usb-portable-office-keyboard-for-pc-laptop-computer-hitam-keyboard-1731239918096844440?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/4/5/a58e1a18-1f10-4a59-a55a-fd1832f3e691.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=U6%2F2os3bwEpmyA9cp58NYQEsVcw%3D&amp;x-signature-webp=Jj%2B9YbkyOlLzk33emnaQ1ZrpakY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/4/5/a58e1a18-1f10-4a59-a55a-fd1832f3e691.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=gJGEg6HCPo2g2NqNzmAYZtTlT5A%3D&amp;x-signature-webp=NP8hhM9EupH3Vzt0i2X1jdn6ODg%3D</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7afdd8435eec4b9183fefb421bac4c64.png</t>
+          <t>Lib\hardware\data\images\2a8d10f4a3264d628874dc068a9c4126.png</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-loka-backpack-office-tas-ransel-punggung-kuliah-kerja-laptop-15-inch-black-a2f1a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-loka-backpack-office-tas-ransel-punggung-kuliah-kerja-laptop-15-inch-black-a2f1a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/11/e53481e1-2aa7-4a54-b392-ca8165e0854d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=FOGpqt%2BBokdxtuieKVdLxDt1qZA%3D&amp;x-signature-webp=T8OWyZaR%2BiAdUkAcqh36ySVwcKo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/11/e53481e1-2aa7-4a54-b392-ca8165e0854d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=0v52REvnRUhHkHOJmhvc%2FEsfZk4%3D&amp;x-signature-webp=LPm4yS2TGkX9GvQgZfn4mEkQ8b8%3D</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0ebdf0706bf1469faaf5f6d4159b0d5a.jpeg</t>
+          <t>Lib\hardware\data\images\fbfa793d9e7f4ecdb254fe2e02dc9fbe.jpeg</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/toko1973/brewyn-kremlin-mens-office-laptop-bag-tas-sekolah-kuliah-kerja-new-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/toko1973/brewyn-kremlin-mens-office-laptop-bag-tas-sekolah-kuliah-kerja-new-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3712,17 +3712,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfea1365d2224b02b0cd6e3066c04563~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=n%2FGTy9yj%2F8x3F1gyuDO%2BGp5qvy4%3D&amp;x-signature-webp=AKlnEJwKrDPHcEAgEqaAo8G24Go%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfea1365d2224b02b0cd6e3066c04563~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=TTc8MLFow4F5DKYUeWeyCM4AOf8%3D&amp;x-signature-webp=hshYk4Mu427OhNNVmlHvVr2IYi0%3D</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\49bdcd4f9a8a46f0baecdf38a657b5d4.jpeg</t>
+          <t>Lib\hardware\data\images\8ca92d7371914c718d2e9ece88bcb37a.jpeg</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fashionselular/onesos-mouse-bluetooth-wireless-office-silent-click-dual-mode-2-4ghz-receiver-usb-for-pc-laptop-black-97680?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fashionselular/onesos-mouse-bluetooth-wireless-office-silent-click-dual-mode-2-4ghz-receiver-usb-for-pc-laptop-black-97680?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/b431006e2c274740a5d254c732987c47~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=fNPBPpITb5GPufpa2PKTHxBfzXg%3D&amp;x-signature-webp=CUlZaA0VMXeX0%2BRIfNubpb%2BIn78%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/b431006e2c274740a5d254c732987c47~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=OXR5NBlhJppPK%2FeEDe8vM6XQe4E%3D&amp;x-signature-webp=W0uNN5yJMx8nC9XHPEwqPmeDxhc%3D</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\017c3cb00cf04ac69fa7d939e7681231.jpeg</t>
+          <t>Lib\hardware\data\images\af7f0302c7544481876d9485d3f41131.jpeg</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/thekingdomshop/taffware-meja-laptop-42x26cm-portable-desk-table-besi-alumunium-bed-hospital-ranjang-tempat-tidur?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/thekingdomshop/taffware-meja-laptop-42x26cm-portable-desk-table-besi-alumunium-bed-hospital-ranjang-tempat-tidur?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/25/e5d80580-d276-4193-95c2-467a317bbbce.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=BqqonlJzsqE%2BcCTcZQsowisXb7g%3D&amp;x-signature-webp=oSQ0KKnlZM39hRsx9b50fhvLPjE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/25/e5d80580-d276-4193-95c2-467a317bbbce.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=Juis5i396QWC6PDvTwXfnwfTSGE%3D&amp;x-signature-webp=YrBL8wbXYyV%2BTwFNpNOMcPhmano%3D</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a40bab678cfc4b62b7ad03f68e7d0ee1.jpeg</t>
+          <t>Lib\hardware\data\images\ba0e61e1759249769617e93dc0366523.jpeg</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-malvern-tas-ransel-laptop-14-backpack-office-sekolah-hitam-bfe09?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-malvern-tas-ransel-laptop-14-backpack-office-sekolah-hitam-bfe09?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -3859,17 +3859,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/6fde5fe1-e2aa-4dae-9a14-e22668d1df63.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=dKc9n%2BtwFB7lSLAaFL5tUXOHVxU%3D&amp;x-signature-webp=B%2Fz299%2BD7JbWqMIx9TWTq2bPmDo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/6fde5fe1-e2aa-4dae-9a14-e22668d1df63.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=3%2BHbDBKaKhI6Q9%2Bu6ymAy4w%2FF1g%3D&amp;x-signature-webp=0UogXxvDmbDQUE0CE3IS6F6PQgM%3D</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0a2b9737d9fd49868894442501ad746f.jpeg</t>
+          <t>Lib\hardware\data\images\762198d0b5ee43b8ab2ee6437ba74002.jpeg</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-malware-ransel-tas-backpack-laptop-14-inch-unisex-for-school-office-travel-hitam-e60e8?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-malware-ransel-tas-backpack-laptop-14-inch-unisex-for-school-office-travel-hitam-e60e8?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -3908,17 +3908,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/a1b6a357-020a-40c2-82e1-1a04455a483d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=ICbldsdIBTTCc8xbMmHhHewv1pk%3D&amp;x-signature-webp=X1djDHPqqwiDxhv0ZvBon6syMLU%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/a1b6a357-020a-40c2-82e1-1a04455a483d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=crh9%2BLKbQ3yCu4IU4nHg%2FSx3ywM%3D&amp;x-signature-webp=LCdy6tyzYGz%2F4IKZCg96vwcK%2BOY%3D</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\742896bbad814ef29fe93191cbaa2229.jpeg</t>
+          <t>Lib\hardware\data\images\3c78c658a19346c6a7a87fc665cb93d8.jpeg</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-munich-tas-ransel-laptop-outdoor-backpack-travel-22l-office?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-munich-tas-ransel-laptop-outdoor-backpack-travel-22l-office?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/10/80613ad1-822a-420c-b539-8982c04fd198.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=e%2FV%2BfQkA%2BXAIBed23YV009PFjQU%3D&amp;x-signature-webp=N24TW16dq81YzYIxNbs0Bhp1EDA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/10/80613ad1-822a-420c-b539-8982c04fd198.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=sqBwm2smC5oCX0jh4MLz%2BqxhXKc%3D&amp;x-signature-webp=OsncJiIEE6ZKsKwIZF1F2o27lks%3D</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3b3f95c25f994d3ab62b9c284b2eb07c.jpeg</t>
+          <t>Lib\hardware\data\images\8a6a04a3cfa84542b1c034f15773c68e.jpeg</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/delioa/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-20619?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D8108753</t>
+          <t>https://www.tokopedia.com/delioa/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-20619?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D8108753</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/31f0e7ca2307423d9af05931721c8709~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=EH3G7GXdnoF2qXQQPjHYcRUQQ2U%3D&amp;x-signature-webp=0Cbklfqe6QfO1hQNJZIjSJRFdCg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/31f0e7ca2307423d9af05931721c8709~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=fI%2B5atOtLZUEG8E5vJJi2oIKfho%3D&amp;x-signature-webp=bqsDAmard%2B2Q7wQnmFRNfUtN%2BJU%3D</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\72454860b3df490eb8201db2f84a7253.jpeg</t>
+          <t>Lib\hardware\data\images\b9341ce46e4b4cfe91906fcab18bdf3c.jpeg</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-field-of-view-ransel-backpack-outdoor-travel-laptop-14inch-office-sekolah-22-24l-1729771080242594987?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-field-of-view-ransel-backpack-outdoor-travel-laptop-14inch-office-sekolah-22-24l-1729771080242594987?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4058,17 +4058,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/2/a4358b69-68cb-47b5-a840-f1b889e39e24.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=%2BBgrBmNKof8COZwkwJc2CS0cJz4%3D&amp;x-signature-webp=hETIAwwJeMaG2wa2%2B8by%2BHBckbo%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/2/a4358b69-68cb-47b5-a840-f1b889e39e24.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=tBxQnfJcimXTmd%2FRzF%2F%2FEeePh%2F0%3D&amp;x-signature-webp=cW33Uq%2FYdgGzV%2BhXnNYfe2q1jgc%3D</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c4ccb8f484874529a7c60420646c373e.jpeg</t>
+          <t>Lib\hardware\data\images\e7dfca793e744191a6a141891d79fbf9.jpeg</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-yerevan-tas-ransel-laptop-urban-14inch-sekolah-office-merah-b6b5a?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-yerevan-tas-ransel-laptop-urban-14inch-sekolah-office-merah-b6b5a?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4110,17 +4110,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1e1c78d14ba1493b9ddd5c8bded02385~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=Z6XQBgEu4hGjK9MBLoF%2BxN2sBRA%3D&amp;x-signature-webp=4sZCBnfp2Z0F9ua%2FiNNeGhXFyQ8%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1e1c78d14ba1493b9ddd5c8bded02385~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=K5n9ZOEnt%2FsbWElqFbPXPIQyLuc%3D&amp;x-signature-webp=1vT61BpCoVk9d%2FfjNfbVZ2x4Jnw%3D</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a306f85053864b3584bf62aec35a8202.jpeg</t>
+          <t>Lib\hardware\data\images\e04661c197924946a94e73d0f3e93318.jpeg</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-enrekang-ransel-tas-laptop-15-inch-backpack-travel-28l-office-sekolah-kampus-1731143360590087339?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-enrekang-ransel-tas-laptop-15-inch-backpack-travel-28l-office-sekolah-kampus-1731143360590087339?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4159,17 +4159,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/614ebd8bb1c04a7eb3fd1b4df55f7237~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=oEH%2FOGDHnrACKdxCnbhGY50WqYY%3D&amp;x-signature-webp=zorKx0i16puo1ZE1gnmI55FfZN0%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/614ebd8bb1c04a7eb3fd1b4df55f7237~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=TLT0sFXtL4AA6J%2B%2BZltPAxBBtKQ%3D&amp;x-signature-webp=4FCudkIyGdjVRJXP9rWey4NXONw%3D</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\21e4679056344fa78011e2119b91cf38.jpeg</t>
+          <t>Lib\hardware\data\images\72b01a324f5e4c15ade7d720ba45b9ae.jpeg</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/reformasicompute/mouse-wireless-rexus-office-q30-silent-mouse-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/reformasicompute/mouse-wireless-rexus-office-q30-silent-mouse-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4208,17 +4208,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5e73c1ebd62c4a558d22d17793191345~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=j8uYKQh9t8im5SqrO5wYfJagpgo%3D&amp;x-signature-webp=01QhHIRMaAC0Qd4e04bUXlZwPo0%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5e73c1ebd62c4a558d22d17793191345~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=ajkq75ASLshLYh3lXOglRK1YafE%3D&amp;x-signature-webp=ZqztR2wjHIAogkNR%2B837l97qirs%3D</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\95052edbfa6b492597fb99fcadfcfc6f.jpeg</t>
+          <t>Lib\hardware\data\images\f7cc744473e8450689a53e37acbcfecd.jpeg</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/reformasicompute/rexus-q10-mouse-wireless-office-silent-click-biru-muda?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/reformasicompute/rexus-q10-mouse-wireless-office-silent-click-biru-muda?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4260,17 +4260,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/21/8bbc37d0-0a5e-4c6e-8b65-594ce61d6773.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=3cKpa0xM1w6QGzlgDF%2BbxuobrEE%3D&amp;x-signature-webp=itBZAKq3Nl1aMdzcmEN14U5iAJs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/21/8bbc37d0-0a5e-4c6e-8b65-594ce61d6773.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=1Q%2FC%2FlKoItT6k7Yuvv3EkGuGfZE%3D&amp;x-signature-webp=%2FIUaQzKL5%2BYPWps%2BAaZHHYpgU1I%3D</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5d9db68df7a94639a1deb96902384ecd.jpeg</t>
+          <t>Lib\hardware\data\images\dd48c3071e07443da79f8c0cefdd8bf7.jpeg</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dnd-olshop/baseus-smart-desk-mat-pad-with-wireless-charger-for-gaming-office-wrist-rest-laptop-phone-stand-holder-keyboard-mouse-pad-basic-edition-3ec7d?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dnd-olshop/baseus-smart-desk-mat-pad-with-wireless-charger-for-gaming-office-wrist-rest-laptop-phone-stand-holder-keyboard-mouse-pad-basic-edition-3ec7d?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4312,17 +4312,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=aR2fz1a3Ti%2Fz7OFS%2Bs2YoREZB1U%3D&amp;x-signature-webp=vEmNmQtQnPTn397Zpqk7gQkH5L8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=S5yQpc%2F9cwPCE9e4OfcWrlYApy8%3D&amp;x-signature-webp=tMDumeZZc8b4NOF%2BkFCFoKRUekk%3D</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a72efae45e474a65b8e0ddc13817a2cc.jpeg</t>
+          <t>Lib\hardware\data\images\b773198ea7b34f5c8e07190b83b05e11.jpeg</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-x-aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1732911892490716709?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-x-aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1732911892490716709?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f4b1f90a2d4f48fc91d0262d2c72a43e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=DV9JafyQ%2F%2BQsJg9pppbVgPvzGwM%3D&amp;x-signature-webp=Aj9bxQHB4spPWGoSgE49%2B4MsFiw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f4b1f90a2d4f48fc91d0262d2c72a43e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=wZpRcLnILuaAGZb56ER2%2FNyPByQ%3D&amp;x-signature-webp=Q%2BPjfHjjXEgqTaVkN7ifCylrw50%3D</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\232e173b81914bbb84a9877770fb6771.jpeg</t>
+          <t>Lib\hardware\data\images\c860c0426dc64894bb9efb8dc7e3d222.jpeg</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-optical-g8-wired-kabel-usb-1000dpi-for-laptop-pc-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-optical-g8-wired-kabel-usb-1000dpi-for-laptop-pc-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/27/da8fc5bd-5e79-432a-9e9e-71dccf3a3137.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=6pHL0ZcGGhVbDshpg6IHDpiRFHg%3D&amp;x-signature-webp=MnLzdPkxvpgwC6lOhyhV9pCwbCQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/27/da8fc5bd-5e79-432a-9e9e-71dccf3a3137.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=VVdRDfoiBcZzwTYGDphPgUnT%2BYE%3D&amp;x-signature-webp=6DX5eL0DIfV5hNfUpziqLqUrzs8%3D</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\275c63368c3a42eaa6a0a896c66a4859.png</t>
+          <t>Lib\hardware\data\images\1205d9e1bedb43feb030a790eb186225.png</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supermallori/office-desk-mat-alas-laptop-meja-kerja-mouse-pad-xl-anti-slip-hitam-87010?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supermallori/office-desk-mat-alas-laptop-meja-kerja-mouse-pad-xl-anti-slip-hitam-87010?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4465,17 +4465,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/dd1c7673e9244b86998b388fcfb3086e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=xd%2F86WtjsmjG9xv8LZd%2B5mnd0Jo%3D&amp;x-signature-webp=vH6XYnQmnpD1qzUlUxjZzl47pvs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/dd1c7673e9244b86998b388fcfb3086e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=d0HT2tzv9BLAMXbwo5lknkBt%2FiI%3D&amp;x-signature-webp=6BcvSZ1A7hneVawIwq2dkB6%2Fmjc%3D</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cdf5033ac8174d508419a071a9ff7e6b.jpeg</t>
+          <t>Lib\hardware\data\images\0e89a668d9414646be6746b60696e83e.jpeg</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/suryatama/mouse-quinton-e100-hitam-kabel-usb-for-laptop-pc-computer-1730805992441873603?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/suryatama/mouse-quinton-e100-hitam-kabel-usb-for-laptop-pc-computer-1730805992441873603?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4514,17 +4514,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/3f12aef7d5d541d8a166d75fb1e151fd~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=D5tyFLDj%2FQu2Z7KNy8P8awVSnd0%3D&amp;x-signature-webp=fjRS%2BUIz%2BqL2aCCYmwHrx8ICOVU%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/3f12aef7d5d541d8a166d75fb1e151fd~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=4F%2BJirqQYzsZF%2ByOLC3FAGvJ8mk%3D&amp;x-signature-webp=d7CIJmmDCelv2Q8KUaOIcpcYvs8%3D</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\187e2f3886dc4b54980fabb5ad7bd585.jpeg</t>
+          <t>Lib\hardware\data\images\636e479f6e824348b20139d7d928fd88.jpeg</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-tongkonan-ransel-backpack-laptop-14inch-urban-traveling-22-24l-top-load-sekolah-office-corporate-1729641642932603051?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-tongkonan-ransel-backpack-laptop-14inch-urban-traveling-22-24l-top-load-sekolah-office-corporate-1729641642932603051?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -4563,17 +4563,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/7/46bf75d3-fdb9-44d8-b4ac-0fc2de7f5648.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=JHKBGdOuk6vWMLlu6agiIHHdfGE%3D&amp;x-signature-webp=Zp7DUZV95xPHWLEuYk7FLNvXQrw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/7/46bf75d3-fdb9-44d8-b4ac-0fc2de7f5648.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=FMRUVNOT7BjEGjgZscRp%2BejPcWE%3D&amp;x-signature-webp=bOSqf4TVXiQCHOOGzoBF9l6E8X0%3D</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1dd56810ae2c4756b0c418c9ad4d6c36.jpeg</t>
+          <t>Lib\hardware\data\images\153879b938724ea2a8a78b8e7f2c397c.jpeg</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-56342?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-56342?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/9/db166b0e-7561-45c4-8f94-c7e1fd6b5ca3.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=g9ehUeu81hWRnfDha5lIZVMuBVg%3D&amp;x-signature-webp=cIfWX6%2BLCO0RXDFYrxD9ID5fPPg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/9/db166b0e-7561-45c4-8f94-c7e1fd6b5ca3.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=%2F76p3sNRa1INAWfJDoD1hTO1n2Q%3D&amp;x-signature-webp=wWqyAOFNJQTFJsa8zbT0Gm0Dhas%3D</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\836a8c4f4dc847e28e688510b649c32d.jpeg</t>
+          <t>Lib\hardware\data\images\f5d6a779796444ab8450a62abdbf215b.jpeg</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-laptop-kerja-kantor-selempang-office-briefcase-14-bg106-abu-abu-f6cb7?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D4203398</t>
+          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-laptop-kerja-kantor-selempang-office-briefcase-14-bg106-abu-abu-f6cb7?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D4203398</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d837c49cb2a5448a810541ddc84ee84c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=8UWk2hbXaBi8RBaR0NmGcxYs5pU%3D&amp;x-signature-webp=ygWJH9fLJm%2BBQjJ3aHs5Xaflbko%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d837c49cb2a5448a810541ddc84ee84c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=8982aZZIdiN7i0gZuwSwHkrY6lc%3D&amp;x-signature-webp=G8XeuS%2BuC8AB7rMi4TDGuVY9osA%3D</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f15a5141fae54c389e3987cd1dc832d7.jpeg</t>
+          <t>Lib\hardware\data\images\112fcac249cc432daff4bfdfb7f395d3.jpeg</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laptopmurahid/laptop-murah-zyrex-lifebook-n4020-8gb-128gb-w11pro-14-0-gry-office-1731531184748463382?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laptopmurahid/laptop-murah-zyrex-lifebook-n4020-8gb-128gb-w11pro-14-0-gry-office-1731531184748463382?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4713,17 +4713,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6338aa902f724277b3c5004260b37911~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=J49WoBjoty8qt4rdf8CO%2Bcadyaw%3D&amp;x-signature-webp=PRh6FIQzpI3lNX80NBdX%2FXFhXM4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6338aa902f724277b3c5004260b37911~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=gowdASI7De4mM0WFXOhIgJwwjOY%3D&amp;x-signature-webp=GKCdMqlBN4gTYAXNf3RhUxo36k0%3D</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0ca7c26307e944a09fdb7e9c47a388b5.jpeg</t>
+          <t>Lib\hardware\data\images\157af33c1632403ea6ce7aa441d17551.jpeg</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/philips-voicetracer-store/philips-mouse-meetion-kabel-usb-office-mouse-kabel-usb-1200dpi-kursor-halus-dan-presisi-untuk-pc-laptop-1732408374889449090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/philips-voicetracer-store/philips-mouse-meetion-kabel-usb-office-mouse-kabel-usb-1200dpi-kursor-halus-dan-presisi-untuk-pc-laptop-1732408374889449090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -4762,17 +4762,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/20/d54e8ffa-2df9-4c94-af64-9dfd3427faa1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=A5iXq0uloBhaFugarKgR3tfPISQ%3D&amp;x-signature-webp=OEXBgGwml3PVGxSWTQ8mkJy40UQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/20/d54e8ffa-2df9-4c94-af64-9dfd3427faa1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=xyqE56DXpAXIScfoHFmp3brytX8%3D&amp;x-signature-webp=XP2OL4rKo3UawYLa%2FZwhoaPu9w0%3D</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\43c5247008264bac9642c50cb787a307.png</t>
+          <t>Lib\hardware\data\images\b9e9a3a823344d6d8a892a40010a3e37.png</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/technosify/robot-m102-optical-mouse-wired-pc-laptop-office-1200-dpi-new-m100-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/technosify/robot-m102-optical-mouse-wired-pc-laptop-office-1200-dpi-new-m100-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -4814,17 +4814,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43a06819c1b648dc99f1a089d8642d3e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=mD9EroDwODT%2FXaMTROHEgRFnMLU%3D&amp;x-signature-webp=LH9fqUslwPd6kSKxj03a4thrccY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43a06819c1b648dc99f1a089d8642d3e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=RfM0L%2BVQMvnw3BP2WLlke1386y8%3D&amp;x-signature-webp=rF0UW2BcZTjqG0mar2288EpbTiE%3D</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f18cf2579caa480b9f854a802119b204.jpeg</t>
+          <t>Lib\hardware\data\images\d2afad625acb4e23ae6b099918bb608f.jpeg</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/huaiwen-pc-store/hw-keyboard-mouse-set-kabel-usb-portable-104-key-full-size-office-wired-keyboard-for-pc-laptop-1731395301317248711?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/huaiwen-pc-store/hw-keyboard-mouse-set-kabel-usb-portable-104-key-full-size-office-wired-keyboard-for-pc-laptop-1731395301317248711?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8e46ce56c02d46fabf7d0c8d97fe2c48~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=nLUKsguBqp1XXEZZi95FMgnrYGA%3D&amp;x-signature-webp=S7iNiOlf0XpFME3y1pTy5lTgQB8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8e46ce56c02d46fabf7d0c8d97fe2c48~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=6q5vn4BNfWkXrDyLK9Xlc1MfhCo%3D&amp;x-signature-webp=NpHo46Aktv5F0X0m%2Fta6Oh1Tdfc%3D</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6e6a3e2b571a4659afbc3e0aebf0493f.jpeg</t>
+          <t>Lib\hardware\data\images\1168a5877dc54ed49c3bb5fac861bdb4.jpeg</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dap-indonesia-official-store/dap-keyboard-kabel-usb-2-0-portable-104-key-full-size-office-wired-keyboard-bass-button-for-pc-laptop-d-k02-garansi-1-tahun-1729677965436487996?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dap-indonesia-official-store/dap-keyboard-kabel-usb-2-0-portable-104-key-full-size-office-wired-keyboard-bass-button-for-pc-laptop-d-k02-garansi-1-tahun-1729677965436487996?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a0501ec6bd9b4b99a2538ce910e8d7cf~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=FpX3ND%2BCxi2dMy8tpW5IjRkbYNs%3D&amp;x-signature-webp=higA5ahpCih3nLEMij1hZhtjZd4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a0501ec6bd9b4b99a2538ce910e8d7cf~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=zkPI5IwhPJQ8oc6uK1uboRwT4x0%3D&amp;x-signature-webp=3VCLeF7C8ePeSypVtLxL7c5s%2Bq8%3D</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bbcc2f3b4bb64c0d97b6ce2ab269a945.jpeg</t>
+          <t>Lib\hardware\data\images\6eb2a40b3a444feb8bb5df19d8e7c3a5.jpeg</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-florin-ransel-tas-laptop-15-inch-backpack-travel-office-sekolah-kampus-1732937353765881003?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-florin-ransel-tas-laptop-15-inch-backpack-travel-office-sekolah-kampus-1732937353765881003?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -4967,17 +4967,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1f52c929a7754ed4aacff0b2d2a0aaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=Hs3FWxsmamBngxsiDA%2BqbpkQD9Q%3D&amp;x-signature-webp=4OMR4W3PAkg%2BxkUXDsDWBab0SQc%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1f52c929a7754ed4aacff0b2d2a0aaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=3tKVxuSo%2F1wvebzm%2Fr8hnVJ%2FqFI%3D&amp;x-signature-webp=EfvEOSg%2BWFoC%2FS3ply8cL93YDrs%3D</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\badbc581c7a3467d8cda2581f83de6d2.jpeg</t>
+          <t>Lib\hardware\data\images\14a5b20c33bf40fba9deb2503a484e65.jpeg</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/royalltech/asus-vivobook-x1404va-intel-core-i7-1355-i5-1335-i5-1334-16gb-512gb-w11-office-14-0fhd-ips-laptop-ultrabook-laptop-tipis-nyaman-untuk-kerja-kuliah-1732832432834512375?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D4029903</t>
+          <t>https://www.tokopedia.com/royalltech/asus-vivobook-x1404va-intel-core-i7-1355-i5-1335-i5-1334-16gb-512gb-w11-office-14-0fhd-ips-laptop-ultrabook-laptop-tipis-nyaman-untuk-kerja-kuliah-1732832432834512375?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D4029903</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/11/5/dbc78023-d6f5-4a1c-b574-362511ab85b9.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=67A54E%2F%2BIn1A5AT1V5ZL7qY7CtU%3D&amp;x-signature-webp=e%2F9sD4jv%2B9O4r6dfiN5ij%2BRrbSI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/11/5/dbc78023-d6f5-4a1c-b574-362511ab85b9.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=TsCg9GDvThScjbbeuDYQFj6XHfY%3D&amp;x-signature-webp=nsrM%2Fv4Sbh0Wzr0P8XLKISK19RU%3D</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ff8f12814ad14b519ab979ffa4149877.png</t>
+          <t>Lib\hardware\data\images\6054fedf7c1345c09b1cfbf997e38d97.png</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/movioofficialstore/movio-desk-mat-leather-office-deskmate-mouse-pad-gaming-alas-laptop-1730814937146492460?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/movioofficialstore/movio-desk-mat-leather-office-deskmate-mouse-pad-gaming-alas-laptop-1730814937146492460?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=aR2fz1a3Ti%2Fz7OFS%2Bs2YoREZB1U%3D&amp;x-signature-webp=vEmNmQtQnPTn397Zpqk7gQkH5L8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=S5yQpc%2F9cwPCE9e4OfcWrlYApy8%3D&amp;x-signature-webp=tMDumeZZc8b4NOF%2BkFCFoKRUekk%3D</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b0f0e9ae4ad348c18703bee1489ca327.jpeg</t>
+          <t>Lib\hardware\data\images\f03cb34a93764d6e94a904d00856e8ac.jpeg</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/aula-indonesia/aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1730707911523271760?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/aula-indonesia/aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1730707911523271760?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5123,17 +5123,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9574249e5aa14f9e9ff0ec25065ea773~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=m4Gg16xC6mtpWRUT7zQXn1dtZAI%3D&amp;x-signature-webp=eVP1oGu5K3L57S3jH1FJYbvtlSs%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9574249e5aa14f9e9ff0ec25065ea773~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=%2Fj2Iz1VsHebBKLeHtxulzgDCO2s%3D&amp;x-signature-webp=I2iB5jQRd0syfYrEbqPeXEpthnM%3D</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\07655a03c0b84a13a9313916a3baca0f.jpeg</t>
+          <t>Lib\hardware\data\images\16677dc57d0f45f8893f17a003b93307.jpeg</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-t23-women-tote-bag-for-laptop-macbook-ladies-shoulder-bag-office-bag-beg-perempuan-1732147400330019985?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-t23-women-tote-bag-for-laptop-macbook-ladies-shoulder-bag-office-bag-beg-perempuan-1732147400330019985?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5172,17 +5172,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/142ebd455039474c9b6a28130ac65ab9~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=lCCh%2FadrTd9WlMBUbRP04IYiQbY%3D&amp;x-signature-webp=WsV%2Bca6vjKhLmAj%2B1SgbfBKegAk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/142ebd455039474c9b6a28130ac65ab9~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=YWA7oUMMhq8LZ4D6oSUUMxTAIpM%3D&amp;x-signature-webp=3cDu7q84jVW7dZZbfq9sZDfIm4E%3D</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e1f8a6c39cec406e8e0e46d3ae8f198f.jpeg</t>
+          <t>Lib\hardware\data\images\a98bd97b0ce547b4a216339a90a5c061.jpeg</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-a40-defender-laptop-messenger-bag-14-16-inch-business-shoulder-bag-office-briefcase-beg-silang-lelaki-1732455130755335313?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-a40-defender-laptop-messenger-bag-14-16-inch-business-shoulder-bag-office-briefcase-beg-silang-lelaki-1732455130755335313?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5224,17 +5224,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8cb82b7c455e4e0fa79003e51a3c33c3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=LHcYvVAaWC1QfMbyQj0gk9gEPV4%3D&amp;x-signature-webp=U0R4%2Bl4aVY0JvNLVP6%2FBNXK6a3w%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8cb82b7c455e4e0fa79003e51a3c33c3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=45oJ%2FOO39lXGJ4PtQT2VeNsv8v8%3D&amp;x-signature-webp=WZyE2EwTxTgp9qgT00nTVIsu31Y%3D</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f191f8ec3592409598989c058a0788ca.jpeg</t>
+          <t>Lib\hardware\data\images\72213f1b7574446190c59f1fa85756b2.jpeg</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a30-defender-messenger-bag-14-16-inch-laptop-bag-business-briefcase-office-bag-for-macbook-beg-silang-lelaki-1732460964531569809?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a30-defender-messenger-bag-14-16-inch-laptop-bag-business-briefcase-office-bag-for-macbook-beg-silang-lelaki-1732460964531569809?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/697f15b91d5a4320a3484f2b65beb688~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=cJRb8yXD3y32uWUjb6SNMcVLraw%3D&amp;x-signature-webp=uAo4NViddGih%2B%2Flh%2BiU831c%2BJVE%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/697f15b91d5a4320a3484f2b65beb688~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=qUUg7GeYkssrKIDXVpSU9YIqR8k%3D&amp;x-signature-webp=k8kS1WYyLFaosVkckWAVXhX4HKM%3D</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ec0677bb7aff4cbdb0bee5ac2d0d4f84.jpeg</t>
+          <t>Lib\hardware\data\images\822e076b355248a19571a191eb489bc6.jpeg</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-t71-premium-laptop-backpack-urban-fashion-bag-15-6-17-3-inch-macbook-bag-office-laptop-bag-beg-lelaki-1732140544120292497?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-t71-premium-laptop-backpack-urban-fashion-bag-15-6-17-3-inch-macbook-bag-office-laptop-bag-beg-lelaki-1732140544120292497?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5328,17 +5328,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e73d1e41c3be4c94b13dca55172a7763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=6f%2B0pnGvs767wDGoGOazX19ndYk%3D&amp;x-signature-webp=BYwjS7PJHO0srQ5v73jEE57NaYc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e73d1e41c3be4c94b13dca55172a7763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=3H42j7YCp2jYzCoshNtydkFf2go%3D&amp;x-signature-webp=k789Ki04WzvgSHEIcBzc65i7lBI%3D</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3597a5a30c8747439938b4277f665612.jpeg</t>
+          <t>Lib\hardware\data\images\a11e98e42a1f4e269d0bbea78a9b92c9.jpeg</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a33-navigator-messenger-bag-14-16-inch-laptop-bag-men-business-briefcase-office-bag-beg-silang-lelaki-1732460907579016337?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a33-navigator-messenger-bag-14-16-inch-laptop-bag-men-business-briefcase-office-bag-beg-silang-lelaki-1732460907579016337?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5380,17 +5380,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2860a24a9e3b43bc827afade643aa71a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=uLhPlV2%2FswAILb4sZIuOFyve9LY%3D&amp;x-signature-webp=VWUgcHzZFSmettE64i%2B7u0h1NSw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2860a24a9e3b43bc827afade643aa71a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=DS4dj5%2F0gAi%2BCM16NrngvHSfeuU%3D&amp;x-signature-webp=OtFlMvqBePJQMSb2gDr7v3ZA2GA%3D</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ed5690f7038941f3b0ba6f035f68714c.jpeg</t>
+          <t>Lib\hardware\data\images\1ffe1b1a7ce842f28827de2ff3eda5cf.jpeg</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/goojodoq/goojodoq-gm0001-office-use-usb-wired-mouse-for-pc-laptop-tablet-w-led-1731786143330567436?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/goojodoq/goojodoq-gm0001-office-use-usb-wired-mouse-for-pc-laptop-tablet-w-led-1731786143330567436?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5432,17 +5432,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6d81861615c94e9d9a2c35ef160645a6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=A%2FdJtBvWo1fKs1q5O%2BSsXNKnEK4%3D&amp;x-signature-webp=KvUhSxLbw20rARWXh2ChWnUPFl0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6d81861615c94e9d9a2c35ef160645a6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=Ywt4RX1Vm6tWsUFCpXICCVg%2FhoQ%3D&amp;x-signature-webp=oE9sB93u1f8S6%2Bw0qWTipIqe4EE%3D</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fe401c2092e54a4a8387aa8180fd0be4.jpeg</t>
+          <t>Lib\hardware\data\images\d1254f764a824e90bbb67ddf1596b2cb.jpeg</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-office-automation/deli-office-vusign-folding-table-meja-belajar-laptop-lipat-warna-warni-dengan-cup-holder-dan-phone-tab-holder-vs860-computer-1729434977497286678?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D18379622</t>
+          <t>https://www.tokopedia.com/deli-office-automation/deli-office-vusign-folding-table-meja-belajar-laptop-lipat-warna-warni-dengan-cup-holder-dan-phone-tab-holder-vs860-computer-1729434977497286678?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D18379622</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -5484,17 +5484,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2a42027251e44e9ca4d6b1aa02296fd0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=iSSvwpYX9AVPAQ5yoRJq%2BegKnog%3D&amp;x-signature-webp=fRTKlKWHS0LL5uHwveRCutRTj%2FQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2a42027251e44e9ca4d6b1aa02296fd0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=N4Qcx8aZbXEs%2BEm8XQzjV%2B48oI4%3D&amp;x-signature-webp=E1SMN2%2F31CV1DzkqWLAEmk2LAcI%3D</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\360771de16ef4b449d3215a7352f8c26.jpeg</t>
+          <t>Lib\hardware\data\images\0b5d5e6a65af4ba08d919547463c3880.jpeg</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/royalltech/lenovo-ideapad-5-2in1-14-touch-amd-ryzen-ai-7-350-16gb-1tb-w11-office-14-0fhd-ips-laptop-2in1-touch-screen-notebook-1733282836276479479?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/royalltech/lenovo-ideapad-5-2in1-14-touch-amd-ryzen-ai-7-350-16gb-1tb-w11-office-14-0fhd-ips-laptop-2in1-touch-screen-notebook-1733282836276479479?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c9d8b76508d243b68d6b5ad417ae9f60~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046971&amp;x-signature=hTnWad9%2Bv7w9GfTV4GlgYF%2FP2tg%3D&amp;x-signature-webp=%2FdsAVB5yVTCrNq2fqO5kSYhI4tk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c9d8b76508d243b68d6b5ad417ae9f60~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=i2eUz7VCUgORXN1IsxCuSe2eB%2Fc%3D&amp;x-signature-webp=tpBc7CkxsMSavn5UCemZ%2B%2B0PP24%3D</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9c3e8ae6dc3b42c8b5e3d432e0a31bab.jpeg</t>
+          <t>Lib\hardware\data\images\b16da6f479ac488f9d83480aad820d12.jpeg</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deliindonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-1729461164801230362?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125040251B3967A0E938DC22956RH%26src%3Dsearch%26whid%3D18553129</t>
+          <t>https://www.tokopedia.com/deliindonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-1729461164801230362?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D18553129</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5582,17 +5582,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_d335da00-22f5-4912-8bef-32b3775be378.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=OKbilnldnH7LxF3V2zhkVGOR%2FeM%3D&amp;x-signature-webp=Y%2BLkmMZpcbXwcjWRlYESwEaqcLQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_d335da00-22f5-4912-8bef-32b3775be378.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=3oKVAIRDkGd5GxbwQXDM6dl10Ns%3D&amp;x-signature-webp=J7xfCaI2bOs9OZQhRuZ%2FLfO2PKs%3D</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f7912089da88486eb09bc8ad24117ab5.jpeg</t>
+          <t>Lib\hardware\data\images\dee72ae50ad8445ca7aeee044e455a78.jpeg</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-sharp-programming-language-untuk-pc-laptop-hp?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-sharp-programming-language-untuk-pc-laptop-hp?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_fb1a930f-e114-4bd2-8224-e722de4ed1ac.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=QIQ1hGuWb0DLgSPRwNxFUbIyhi4%3D&amp;x-signature-webp=cB0N3S%2FCD%2FmSA%2BP7oGqdNnXjOoM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_fb1a930f-e114-4bd2-8224-e722de4ed1ac.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=hYzF2O%2FyiuBQxJd7QIWJvS6ZBNY%3D&amp;x-signature-webp=oz7likYAu43IGEx%2BtnIH12EXn8k%3D</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cd7a4174b9774592835ed5fd3eb72d60.jpeg</t>
+          <t>Lib\hardware\data\images\4d332b33fe3d4fa38c47a7ee5b796d90.jpeg</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-go-golang-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-go-golang-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_57fb509a-be23-471e-989e-1f4d6e8d6456.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=4t9UwJCwauq%2BpUEuIDbzSHECVXA%3D&amp;x-signature-webp=mU2XBVBDQmYx7P60HFzAz3HX2%2FU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_57fb509a-be23-471e-989e-1f4d6e8d6456.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=Nz08DJ45hIhBJZApnxI5ka0KO%2BE%3D&amp;x-signature-webp=lsmRfaHg0xvoTT%2BUwSgwIgQHVH8%3D</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a4afa4fcb22e4cf09f0e97d715e70adb.jpeg</t>
+          <t>Lib\hardware\data\images\8d306336e377440e91bc3ee637623d2a.jpeg</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0cdf5c85ae0a40a69404e6a02408149c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=NXN%2B9P5rVPEsmQwvbwACCbyp87s%3D&amp;x-signature-webp=SB2faH587wKZI99%2B9Rg40BvSwcQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0cdf5c85ae0a40a69404e6a02408149c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=bvw5tcfNDCgSI5F8KALb6UrtOGM%3D&amp;x-signature-webp=JlFN4G2GOEoxpQ8j8RDl85S3ZfM%3D</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cae1e965ff6f440195c81d1fb7f16045.jpeg</t>
+          <t>Lib\hardware\data\images\df59e0c6de514b52a81707f8d890c5a2.jpeg</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/inlinefoursticker/sticker-pack-premium-it-stiker-program-teknologi-tema-coding-programming-coder-programmer-waterproof-tumblr-laptop-case-hp-koper-helm-sepeda-motor-1729660102472074470?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/inlinefoursticker/sticker-pack-premium-it-stiker-program-teknologi-tema-coding-programming-coder-programmer-waterproof-tumblr-laptop-case-hp-koper-helm-sepeda-motor-1729660102472074470?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5781,17 +5781,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/2/a80e659e-9b9a-4c2a-b57a-50ed8cf2ff65.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=m6sO%2B2iyd4x6z6RuLeq%2Fcq6k6a8%3D&amp;x-signature-webp=x8pY%2B%2BmC%2Bm412xw5yJiPuB5WKr8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/2/a80e659e-9b9a-4c2a-b57a-50ed8cf2ff65.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=TF%2Bq%2FHiVO0bNDfHM4bo8Sy%2F7zUA%3D&amp;x-signature-webp=OEqT5%2BaQIwMHtm0kkKyFPYPzV6g%3D</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ebff40b4e23d44659df1a60f00a44380.png</t>
+          <t>Lib\hardware\data\images\095fb0185107488796875f42379d59f6.png</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/yeagerart/sticker-pack-programming-coding-sticker-koper-sticker-tumbler-sticker-laptop-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/yeagerart/sticker-pack-programming-coding-sticker-koper-sticker-tumbler-sticker-laptop-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/21/3f892503-b128-4c98-81cb-00fb5661f466.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=WE2ltecM7O%2FcFBxnGcC6r1DEQWg%3D&amp;x-signature-webp=IHnh9aXI745siQ91IojA1wNoj3g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/21/3f892503-b128-4c98-81cb-00fb5661f466.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=yZDbtdJBQKJlncIErhGD2QDYBdo%3D&amp;x-signature-webp=Z6Tv9E8AIk3UtGsPwVGI3tA%2FIBE%3D</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cccbe2b351b54c5ba5af30b6603323bb.jpeg</t>
+          <t>Lib\hardware\data\images\b9ddcfa5acd3478fb71236359f3a97e1.jpeg</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerplus/sticker-programming-2-sticker-laptop-sticker-pack-stiker-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerplus/sticker-programming-2-sticker-laptop-sticker-pack-stiker-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -5879,17 +5879,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_1e2c0c59-fda9-45b4-ae3a-ff69cf747612.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=0d55mQKF8wuf3ueuEuwCBiBC%2FJU%3D&amp;x-signature-webp=Z1FqQkCkCHaGxIeQaWVx7%2FkBm0E%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_1e2c0c59-fda9-45b4-ae3a-ff69cf747612.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=YNqRnlFwfKQlcy8Y%2BLJj5oPa2Xk%3D&amp;x-signature-webp=JCWA7kTMRcQWeU6AXGRn5YADWnQ%3D</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\31a419806cab4f88b82989a740a1f799.jpeg</t>
+          <t>Lib\hardware\data\images\f731f86d228141cea4735a5a461b45df.jpeg</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-plus-plus-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-plus-plus-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -5928,17 +5928,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_e96fd7ec-b826-46fb-9e12-bf86a0adc00a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=Dr54KpKnYzSXHE%2BHalZcKP%2FPAjg%3D&amp;x-signature-webp=7ESjhNM0R2ov%2FZYJFmElvihEzzk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_e96fd7ec-b826-46fb-9e12-bf86a0adc00a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=W3vBXvDrRoFNrMnaxoSuJkzrF8Q%3D&amp;x-signature-webp=5gjiPTdvvWo1HD2kD9TFOPBTPWw%3D</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\41d9e45d9a0e493c84450d8db46c497e.jpeg</t>
+          <t>Lib\hardware\data\images\bcd40c55d31649c5926ae384c77216be.jpeg</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-r-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-r-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -5977,17 +5977,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/2c485272-3bc8-4c64-a8f0-baf8415b97e1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=OVt%2B62Y3D%2F9DOidY%2FLkSNFapioo%3D&amp;x-signature-webp=7ETSHH50cFbv1jkiPMlvcMI%2BOHY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/2c485272-3bc8-4c64-a8f0-baf8415b97e1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=8TWBG0KHS8BH2G3dTidceZC%2FHkA%3D&amp;x-signature-webp=QYX4iD9ajYW%2F9qikMcCrm8HZUMI%3D</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\158fc34c28d74095b70dccd6bd4a2530.png</t>
+          <t>Lib\hardware\data\images\a10750ecb2894755a24b44aa9409a17c.png</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/cutting-sticker-it-programming-programmer-coding-stiker-laptop-vue-js?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/cutting-sticker-it-programming-programmer-coding-stiker-laptop-vue-js?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6026,17 +6026,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/77ae15f3-c056-41f7-94f4-c008303a79f3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=ddfOEjrbneVwOR7BngysGsNWkIc%3D&amp;x-signature-webp=eRpjif2wryUkoUUHLRBoCz9%2FWao%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/77ae15f3-c056-41f7-94f4-c008303a79f3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=6w6%2B%2BL7UGpTGciRyEY75fGQ8gEc%3D&amp;x-signature-webp=LuwdJXBq0yc4wvkc1SRrxeBH41Q%3D</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d53a74b3166a4d69ac29cc048271390b.png</t>
+          <t>Lib\hardware\data\images\661f710267cb4a4e9bc109a23aef37d2.png</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/bootstrap-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/bootstrap-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/674d0478-bc6d-4c09-b6b9-88af31fea1d1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=DydUmmkXMk%2FkplJC9iLveBBg%2BKA%3D&amp;x-signature-webp=A5wr0TZLC1FjpwHTGwFOWFFDfyo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/674d0478-bc6d-4c09-b6b9-88af31fea1d1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=6eZwPp4XmFmHle6S%2FqNb4dV8n84%3D&amp;x-signature-webp=1AChVoJN%2F%2FHi5ADVKKLiBF%2FbDw8%3D</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1c3d543714bc46109557358baf055024.png</t>
+          <t>Lib\hardware\data\images\32ac21c85b6b463184c0f4e012a74e66.png</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/linux-mint-cutting-sticker-it-programming-stiker-satuan-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/linux-mint-cutting-sticker-it-programming-stiker-satuan-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/22/d6a5263e-e87f-4f56-b43e-3b9544f68e28.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=7OGZTpL8BHh%2FuHt2vTWgZJZr%2FXk%3D&amp;x-signature-webp=h4ejyiUSMOoZM72qVGAc5hh6sQI%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/22/d6a5263e-e87f-4f56-b43e-3b9544f68e28.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=zy%2BHKTX3eN%2F3OEdGeqRkw62vxAw%3D&amp;x-signature-webp=PK0dvZCaZhq6duF739NadGEqpBE%3D</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b104a28d68d04a6aa9e9d20e2d135e59.png</t>
+          <t>Lib\hardware\data\images\7a127d9dd41c4ba8bf771d28d8e0f695.png</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-stiker-tumbler-laptop-stiker-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-stiker-tumbler-laptop-stiker-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6173,17 +6173,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/356b601d-1120-43ac-bc8d-f91265fff9b2.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=npjVYYojjqfN7g69T1CIkCpq3mg%3D&amp;x-signature-webp=gX%2FiPbWxF0ZywsUCmYfByFT3YaE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/356b601d-1120-43ac-bc8d-f91265fff9b2.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=JDHaQPCCcDHmrgXnnphN4oQsVjo%3D&amp;x-signature-webp=jcMdhwNjmDLhEOSr9eNLn6JOa%2BQ%3D</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6851c97a6ceb40a78cad32d74d014635.png</t>
+          <t>Lib\hardware\data\images\ec130220510543da8161f68d3fb5b14e.png</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/java-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/java-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6222,17 +6222,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/28/82978a46-7432-4e38-9f63-c39dee0f3ba4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=nfJUFTNBhfpzv9FsJaIHdiikFZI%3D&amp;x-signature-webp=jGPdP9UtNW%2FgVe%2BcUhXFXnenXbg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/28/82978a46-7432-4e38-9f63-c39dee0f3ba4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=EvKkAI6eB8GA6YentB07EjWtbDA%3D&amp;x-signature-webp=xzfQFD8nY97NRRdYBqJdTBGJn1Q%3D</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ae9c99a40f7f4eecbc5d20e90d361d43.png</t>
+          <t>Lib\hardware\data\images\0c8d2becbaf942d8b6910e9ccf8ffd4b.png</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6243,11 +6243,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>15614737477</v>
+        <v>15608613564</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Spring Boot - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>IntelliJ Idea - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -6257,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6271,17 +6271,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/148d053d-e670-4ddd-bd5b-c5489f84c28f.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=Te9fBAncdDcYmRzTn0W8M7VvrfQ%3D&amp;x-signature-webp=0nvHFkZ4RXUJi0E5yQqMrXcIBd0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/3b45f322-32f5-4b0c-858f-59219a51c153.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=LWjFs0RDv2EX%2FzBFBy69rdfprL4%3D&amp;x-signature-webp=sUaKNtQyWej1s8fV7PlEWx7cRoU%3D</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d648cfb0bb4c480db4a07c3cae2d7387.png</t>
+          <t>Lib\hardware\data\images\79328516e79c4f839da51edea8cd817c.png</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/spring-boot-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/intellij-idea-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6292,11 +6292,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>15608613564</v>
+        <v>15614737477</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IntelliJ Idea - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>Spring Boot - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6320,17 +6320,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/3b45f322-32f5-4b0c-858f-59219a51c153.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=%2FeiCcByGsvZSQcYZ%2BckkE1sUOYs%3D&amp;x-signature-webp=HMkMF%2FyXVmHq87a3KncEEl0d2zM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/148d053d-e670-4ddd-bd5b-c5489f84c28f.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=xCBllS%2FZu6lXAMwewyHV3KJSX3Q%3D&amp;x-signature-webp=WZ9KNMq9fuvJHekDlLuZ0SGgXJ0%3D</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9043348431574da8a5940bc4c5ba3971.png</t>
+          <t>Lib\hardware\data\images\91af879ec6a24667aa37c2e0af2d1482.png</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/intellij-idea-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/spring-boot-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/bd6bf479-e882-4ed2-a264-28c75b168c29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=n%2BySOa%2B8CkVf%2BM%2BHqYJqNfnMx38%3D&amp;x-signature-webp=yb8hizbZn35QOWxrUaMbzK3O3RY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/bd6bf479-e882-4ed2-a264-28c75b168c29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=AGHHPN86VHeFiLohh%2BvOUfhr9IA%3D&amp;x-signature-webp=CvyYnTpeELzc2AZoQAUNEtW1h4c%3D</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e8a3296c27ca451b9ffe2e0747e9b346.png</t>
+          <t>Lib\hardware\data\images\d1fc26607aec43eca9d95ab3acba6260.png</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/css-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/css-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -6418,17 +6418,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/722bc896-e581-4919-9192-737948477d10.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=BoOyR3lAGPF%2FicM%2BJ87qtm5iheE%3D&amp;x-signature-webp=T6pq1ZWq3L7lO4QcaSJmXBtg4hU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/722bc896-e581-4919-9192-737948477d10.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=WCWNDmZcKEVMFUf%2F0teuqAnPwGg%3D&amp;x-signature-webp=DcSBOoM3iQ7gMs6yuG4sQb2pd4M%3D</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ec04dcf2d96a46c3af8402146351e3c4.png</t>
+          <t>Lib\hardware\data\images\317ce037ad744499a438fb66201ad6b0.png</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/meta-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/meta-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -6467,17 +6467,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/32a21bef-6229-4a57-8094-a707c4210ac4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=nGEne89u6sQztNQYCIkw0FDyNRg%3D&amp;x-signature-webp=4GDprLUP0MSfa1JtN4aEwz39tkw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/32a21bef-6229-4a57-8094-a707c4210ac4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=ikX5XkFrc5uua4TnAL9hb47E6sA%3D&amp;x-signature-webp=KP8a3cZ26K3R4vhmgwhknhEyUIU%3D</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ac6734bb540045f68457a6825d155ee4.png</t>
+          <t>Lib\hardware\data\images\b65a419640044150949e06f34fdc9f55.png</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/php-cutting-sticker-it-programming-stiker-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/php-cutting-sticker-it-programming-stiker-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/247f6d04-d1b7-4b0a-b69d-44df83a98403.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=pOUOofBL%2F0Bc6b2y65kjJgJ4SsE%3D&amp;x-signature-webp=712b7%2BdCKat3JCXqhW8RHVIdR4I%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/247f6d04-d1b7-4b0a-b69d-44df83a98403.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=qF%2FmVGisgxoS%2FeSmDJYhVAHEzLw%3D&amp;x-signature-webp=i%2BIhVM1Pzix8WPenUsTbYZSfq04%3D</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b16a0fb83d8f4749ba4cea0c7ba638fa.png</t>
+          <t>Lib\hardware\data\images\481ca9433d164cfba09b2681a8f4f3be.png</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/ubuntu-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/ubuntu-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/fd492c8b-c24d-42f6-9532-4ec429fe91c5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=248LWiRCs1SlzHUJswd3BDRPycY%3D&amp;x-signature-webp=HioBfj%2B2cIo6CzqaXwU8G5oE9bc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/fd492c8b-c24d-42f6-9532-4ec429fe91c5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=xfOvv%2BK%2Beq%2BazSEafS7FyVwTSW0%3D&amp;x-signature-webp=2mNmMSGXDBTRgyGOZ8wcbBB9KiU%3D</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\aa80faeba01e4e0b9f982af440d1117a.png</t>
+          <t>Lib\hardware\data\images\4e5c8858a58b4fb4bf63dd217ba9c0a8.png</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/kali-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/kali-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -6617,17 +6617,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e016ed68c334c7cbc4f8e994d90718b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=vvYqP2yuXkDDT6BA0I4HF8BFm6A%3D&amp;x-signature-webp=Q41PdTSl1REtd9PAbOhvpeg3rBM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e016ed68c334c7cbc4f8e994d90718b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=E%2BOz5xQ5X7kdQk9Ks%2F0cGjMaGjc%3D&amp;x-signature-webp=SYvYqEw%2B%2B2OQOdSVOdGavuNMvD4%3D</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5ccdac0d295548f99ce75ae2c756fd3d.jpeg</t>
+          <t>Lib\hardware\data\images\70b4987d7fbb4a1890d5f589e61ddce3.jpeg</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/indoluxdigiprint/programmer-sticker-pack-50-pcs-stiker-code-komputer-anti-air-sticker-coding-computer-it-programming-laptop-hp-paper-1729751165829088355?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/indoluxdigiprint/programmer-sticker-pack-50-pcs-stiker-code-komputer-anti-air-sticker-coding-computer-it-programming-laptop-hp-paper-1729751165829088355?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -6666,17 +6666,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/6dc31a5b-13dc-461c-affd-cb836b3d7649.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=bV6JWckb8%2BQtdh3WxropwKY6bCo%3D&amp;x-signature-webp=LA4t3KjyUh7x0126lxssNbLj2uo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/6dc31a5b-13dc-461c-affd-cb836b3d7649.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=rYKszUSDnx7ZU35pHerWysERNko%3D&amp;x-signature-webp=FEKoqQIzWA4QNJyjhlrQJqcJeTQ%3D</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\018e3c5c23174d78abf5d9210abe7dc2.png</t>
+          <t>Lib\hardware\data\images\3e1fbfd0c3564453b506365d08e548d1.png</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/html-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/html-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -6715,17 +6715,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9e56cad1-941e-4da1-b48a-271cbe36ab77.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=LroUuXoGhAerwItPaWnLYzEwIOY%3D&amp;x-signature-webp=nfkGv6Y3OXFZQdMF5NXlkRbjWPA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9e56cad1-941e-4da1-b48a-271cbe36ab77.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=acI8QC6yFDl4VForObFjMiYQJK8%3D&amp;x-signature-webp=C4xsf%2BfCzHRvv2vpu76cZS85wfQ%3D</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f7b194db1bb948fdb9cb69bb0ae1b11d.png</t>
+          <t>Lib\hardware\data\images\708c37f18d44469799f1e5a6f6baf071.png</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/debian-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/debian-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -6764,17 +6764,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a26ba20e-d4b0-45e2-8d41-247e37e6a478.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=cLif2IJZSGap%2FKas1DfL%2FYiktjo%3D&amp;x-signature-webp=ZDlk61ABpHF3%2FsOdzbTiRfvDGFs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a26ba20e-d4b0-45e2-8d41-247e37e6a478.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=EvJeTmDdOu%2FcCB51Q7BOhjTKPzc%3D&amp;x-signature-webp=dCqGFRU4Y%2B4IWOxwvirJM6Xip3g%3D</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f282e53bb6e64a388fb6db5c8f435b19.png</t>
+          <t>Lib\hardware\data\images\5079294dd229409d9cd63c7608a31ef1.png</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/cpanel-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/cpanel-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4aa5f4f-ae42-4541-81f3-1421c0a92ee8.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=bHXzHCAzigygjrnRMH0caeCG8i0%3D&amp;x-signature-webp=ht%2FglEMGoUJ845yH9aNG97b%2BttQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4aa5f4f-ae42-4541-81f3-1421c0a92ee8.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=uHjb9znLh%2BZZLCTZTf1kRMbaCng%3D&amp;x-signature-webp=FgFz7x79MvMa%2BSEP7wwW2er%2Bagw%3D</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\55fd024974dd4b1a86100b764898c3ee.png</t>
+          <t>Lib\hardware\data\images\68186272887b453a856491ca1885ffe1.png</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/js-javascript-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/js-javascript-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4f53049-4d44-4b49-ae9e-b4a06d7aa864.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=%2BSidVcVk7zFWM5TRi3H0OQwIPm4%3D&amp;x-signature-webp=fUzgF%2BGkU9KVWCJxadrzbuZjbgI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4f53049-4d44-4b49-ae9e-b4a06d7aa864.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=f19ZwV%2FSemLzjPNDjp7mvmRnw9c%3D&amp;x-signature-webp=Uh8ZJXEHmqOIz9yG%2F20MfPvD6zo%3D</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\849f8ea03d74492e8e4812fa9aa31386.png</t>
+          <t>Lib\hardware\data\images\0517c2bbe88e43d39c8c8507b4ea1679.png</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/python-language-sticker-laptop-programming-vinyl-waterproof-1730910518060090930?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/python-language-sticker-laptop-programming-vinyl-waterproof-1730910518060090930?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -6911,17 +6911,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/52e270bf-8f13-4743-989a-135d563c7c13.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=YWsjuC2tj4hMi3cyOQHEGhNE3Y0%3D&amp;x-signature-webp=D%2FVI9EMooxyDDpr5BB0azyAnlgE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/52e270bf-8f13-4743-989a-135d563c7c13.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=FvOJyh5twsVcbUsX3XtJbPYqFQo%3D&amp;x-signature-webp=VqKZiiHK4PBQfLTWxpAXMldelW8%3D</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d24860ceb5ea40e1956f638e0114bbcc.png</t>
+          <t>Lib\hardware\data\images\97d2e19d50c44df6a73774c18847bd32.png</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/c-plus-plus-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/c-plus-plus-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -6960,17 +6960,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9441c648-abf5-4189-bda6-523c5625881e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=6g8jSS0p7V2%2FgALUYHsjVvbAFzc%3D&amp;x-signature-webp=B0ASe53DEccE%2Bv00XOfQWprek6o%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9441c648-abf5-4189-bda6-523c5625881e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=s6CmK7mmiisf9e1n2EoPYFxZ5nk%3D&amp;x-signature-webp=hoksGo%2B0jTMrS369ybxoGUH7zds%3D</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\342714d1a24749f787a6509a490bfc46.png</t>
+          <t>Lib\hardware\data\images\53798eb063fa4dd792a37acd0ddff77e.png</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/jetbrains-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/jetbrains-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -7009,17 +7009,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/487fec30-5abd-485d-90e1-97aa59e4dc8e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=9llais5eSC8rzcFuZ1YzoI7rJ9o%3D&amp;x-signature-webp=l2n61o2mhoMKrMlpVFvAac2dIwc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/487fec30-5abd-485d-90e1-97aa59e4dc8e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=CUw36cfM5UYSPs3Rid9a%2BrMVoNw%3D&amp;x-signature-webp=cUk7fdpH6az8ZJMUoM9MtU85xF4%3D</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\61bad602417f4103bc533f81698d1db5.png</t>
+          <t>Lib\hardware\data\images\2d4d5e17964b40e0bcbb9f4a8d0016b9.png</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/android-developer-cutting-sticker-it-programming-coding-programmer-laptop-1730925852202665522?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/android-developer-cutting-sticker-it-programming-coding-programmer-laptop-1730925852202665522?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -7058,17 +7058,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/5e031a76-a3f2-4fc1-940b-4150386d8618.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=RzfAIhMQ24r%2BAdWkULcPryqhJLQ%3D&amp;x-signature-webp=%2F7BDE4Jr924yd2tO%2FYvpgLBoe9c%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/5e031a76-a3f2-4fc1-940b-4150386d8618.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=zjs5RbKwVcVUnPJvJ7zdBbQxPLg%3D&amp;x-signature-webp=5Wlf0kHD8OWJmUDdgza4Sb%2Bhv3w%3D</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ade8c1988d8647069f910ee5b28f5905.png</t>
+          <t>Lib\hardware\data\images\731a0fe3916d4866be361d2c5ca074c4.png</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/tux-linux-penguin-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/tux-linux-penguin-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -7107,17 +7107,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9f70aa88-0b3e-4f1a-b1e2-ff8c1f724f83.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=KbZR51mLXTiCkWi%2BqEIexk7GZcQ%3D&amp;x-signature-webp=yEJX5WQ2KO%2FPnknZuBX4tTD%2Frtg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9f70aa88-0b3e-4f1a-b1e2-ff8c1f724f83.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=aIBnysuMKKlSE7GxuZY1BWMmvTw%3D&amp;x-signature-webp=QLWsAmd5tGsg8nlTPKNERzHl23w%3D</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ea9f2aeb60d644ee83358c91b5eb96a2.png</t>
+          <t>Lib\hardware\data\images\83f83d6ad1eb4d149063f99738f0d933.png</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/google-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/google-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -7156,17 +7156,17 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/05097cce-f0d3-41a1-9a3e-dc787f21a1bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=2Bxh35LVOUYGNqroHdNxNT1ETn8%3D&amp;x-signature-webp=%2FGAzPOwZIS60z8prEooZu68M7vk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/05097cce-f0d3-41a1-9a3e-dc787f21a1bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=gu2OCqohf8usN1YbeB2iGjQODDs%3D&amp;x-signature-webp=edK4G%2BdYYXyZRxoUxbtGOZYsfg0%3D</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\541468fa04a74b65bdaf108f0afb4962.png</t>
+          <t>Lib\hardware\data\images\bd765a3b08714f1d871ecd89c805aedb.png</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/arch-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan-1730778695673939506?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/arch-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan-1730778695673939506?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/d2e910e6-71e1-493a-9ad0-7e644045fa68.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=zK%2BVrXVq0J6jqGaI1NOY2w6arjo%3D&amp;x-signature-webp=ojtkPW0VmSS8Y3kthURtwJEQ01M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/d2e910e6-71e1-493a-9ad0-7e644045fa68.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=9zGfP7ZTVRYS3BLKhKlxUv7oEys%3D&amp;x-signature-webp=ACOlM4bSMJdzyr7cwkTL1JlQE9k%3D</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9c609fd41d054e7e9b6644dcf42ab989.png</t>
+          <t>Lib\hardware\data\images\237f8a5fef6d4a26b2307028da04de32.png</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/fedora-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/fedora-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/9/29/f8d3eab6-1d0d-4a33-8e74-ee48be7014e1.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=UbggHrLguGU1qV9LXtdWVIS12MU%3D&amp;x-signature-webp=3kB5yzBR2t4OL504R7PLOxFrULc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/9/29/f8d3eab6-1d0d-4a33-8e74-ee48be7014e1.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=F5Qa94qg%2BkvX96EKMG6tlukZV6U%3D&amp;x-signature-webp=lKJ%2BNx%2F2ycoDMhIIoLrFFnAk9jc%3D</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d502dbcd494e4779832ba220aca068c6.jpeg</t>
+          <t>Lib\hardware\data\images\7c8bf7b278e843ab8587d730f7b0f927.jpeg</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/archive-zhanghua-1630738705/stiker-programming-java-php-linux-bitcoin-ubuntu-geek-untuk-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/archive-zhanghua-1630738705/stiker-programming-java-php-linux-bitcoin-ubuntu-geek-untuk-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -7303,17 +7303,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/d7dbbf07-cde0-4b81-a809-7c268bac8704.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=KVuZwgblPIqvoJck4G1m%2FmrZwgc%3D&amp;x-signature-webp=QaqcMFOTBvK%2F8Yd%2F4a7l9J%2FldH0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/d7dbbf07-cde0-4b81-a809-7c268bac8704.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=7n%2F3tjPjRRtaFjKxicQ8Vad9z4s%3D&amp;x-signature-webp=Czib1NKOsbiXFWaYOUj6VL2XJmI%3D</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6f0855c7518946349d3865ba0f492767.jpeg</t>
+          <t>Lib\hardware\data\images\7ee1dff1dc7f4a4ea081e83726537c82.jpeg</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/coffee-sleep-coding-game-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/coffee-sleep-coding-game-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -7352,17 +7352,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/3c9c2511-b651-4389-846a-da1c078d510d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=Hjx5xXtEV702tWghN4dcRAwREzM%3D&amp;x-signature-webp=Gv%2F9YUaET7XMyLDLYkxSGBa7K%2FQ%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/3c9c2511-b651-4389-846a-da1c078d510d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=xjH5a0nwVPc8E%2FhVl4J6KiiCGn8%3D&amp;x-signature-webp=EV7YhIIm7wixM1S0FSNOIZtaNXE%3D</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a0b1892d9579477f89e3dce966fb2f78.png</t>
+          <t>Lib\hardware\data\images\65106fe776564988b31cbec84ba85510.png</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/sticker-sheet-a6-vinyl-waterproof-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/sticker-sheet-a6-vinyl-waterproof-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/c6cbe66b-30fb-4b15-9a7b-cdba7bdb6344.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=8mt6Q0tcaWB6ZGpwu4hL%2B%2Fs%2Bu0Q%3D&amp;x-signature-webp=9n9mB40sF3TaSjoueFxGl32gdwI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/c6cbe66b-30fb-4b15-9a7b-cdba7bdb6344.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=gIYPa3o0oyGgqMkqEFEZS4klAlQ%3D&amp;x-signature-webp=YPJcBhAMj14%2B4v0TYbva9p0AryQ%3D</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\230fd8d8122c45f9bc4fae2fbb2ac66b.png</t>
+          <t>Lib\hardware\data\images\926e827095a44f7da99a6043ff71764d.png</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/full-stack-developer-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/full-stack-developer-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e83fe7fc87c4ce6ad067de5078f19f5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=dawYfT%2FNkEW3lrWfWoy7KJCDd2w%3D&amp;x-signature-webp=2GNpzxDQZqn6%2FaDILEb%2BQU%2F0DxM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e83fe7fc87c4ce6ad067de5078f19f5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=IN6SMKCODZMuooEkJyaO7VDR3wA%3D&amp;x-signature-webp=q4Xkg61%2FCp%2B0XsV0UbRkjlL4W50%3D</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c9cdf5c835f7433b8adce0a0b0158e7a.jpeg</t>
+          <t>Lib\hardware\data\images\a8ed407dba234532918e6328851578c9.jpeg</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-untuk-scrapbook-tumbler-hp-laptop-motor-helm-koper-1730766186130146514?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-untuk-scrapbook-tumbler-hp-laptop-motor-helm-koper-1730766186130146514?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -7505,17 +7505,17 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/364156f76e624431b6c3dc72dd64ecdc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=4gIjG5a7A1aA25U46aDU8Hyu3Tg%3D&amp;x-signature-webp=lwrLQKq3vjulkIynpfd37O5Nzi4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/364156f76e624431b6c3dc72dd64ecdc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=RwRYi1rryt08K81lw4pwMBnQ32w%3D&amp;x-signature-webp=Bv5MMqLmtFdH2DPhb9xAWIZM7IY%3D</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d6ec1290f97d4c26ab4fa1b7e67aaf52.jpeg</t>
+          <t>Lib\hardware\data\images\c105d7cdc3574440bfc3405f78bd572c.jpeg</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-meme-plesetan-untuk-scrapbook-tumbler-hp-laptop-koper-motor-1730770027949688018?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-meme-plesetan-untuk-scrapbook-tumbler-hp-laptop-koper-motor-1730770027949688018?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -7554,17 +7554,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/265be12a-181a-4c2e-85ad-c6544f36203e.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=vTb6oDywaW56oWyFTzDaZOWWuCg%3D&amp;x-signature-webp=x%2BGoWwvG4MwDtfDNM8Urv%2Bc5sjw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/265be12a-181a-4c2e-85ad-c6544f36203e.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=kRjTQFDjN%2FK%2B52Adi%2F30xoNktyU%3D&amp;x-signature-webp=4OnftUqqxvxlc7LrbsIe%2BZHUjTY%3D</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\44d5074ffd154f718a495318e0bbd574.jpeg</t>
+          <t>Lib\hardware\data\images\30756f122c2a48ffb4139a11c75e4600.jpeg</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/vnylarc/saas-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/vnylarc/saas-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/4020a1f4-6c92-4356-8439-3db0af377f5f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=7cRebCkXSd0DRhrlcWMdoVh6hJE%3D&amp;x-signature-webp=1VoupfHHuqDi7%2BdnjUncrnaJ%2BP4%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/4020a1f4-6c92-4356-8439-3db0af377f5f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=1QwBD7DTxQD3R6IEcK4W%2BtaOjNM%3D&amp;x-signature-webp=ViStWLy%2FhWS2omA7CER7d7Pehvc%3D</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7f371efec9de418aa5b0b4020f21ecb8.jpeg</t>
+          <t>Lib\hardware\data\images\664d9d08ed4547239ec5e30d1f9fb8bf.jpeg</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/vnylarc/golang-icon-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/vnylarc/golang-icon-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -7652,17 +7652,17 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/4/4d205830-0c3f-4681-a668-c1d10845afb5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=voiVC%2FUGYzIM2PV7%2FE9SOwcuKr8%3D&amp;x-signature-webp=O1KVkmod1EUHm5RaPZZkpluA6X8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/4/4d205830-0c3f-4681-a668-c1d10845afb5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=91VPzA4rW8xdNtArwbL4FFwAYt0%3D&amp;x-signature-webp=RQbZ%2BGjZpSDRM9C3QdplKb4ig%2Fk%3D</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2198932893b944e0b6d25d61b83eadd3.jpeg</t>
+          <t>Lib\hardware\data\images\d3938afab9a742afb4b9fa3da3127e08.jpeg</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokopedia-tokolaris/sticker-pack-20-pcs-teknologi-programming-untuk-laptop-tumblr-helm-first-edition?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokopedia-tokolaris/sticker-pack-20-pcs-teknologi-programming-untuk-laptop-tumblr-helm-first-edition?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -7701,17 +7701,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/0bd6c17c643c4ba8875360f0f7dedf05~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=zeW3pqrWS3I%2Bbbee5fAI4cve9PQ%3D&amp;x-signature-webp=IqqJaQlnB4xD7YMle%2FcBYTd9S6w%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/0bd6c17c643c4ba8875360f0f7dedf05~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=P3wH5ELz%2BjePVeo9bzAXc4bnCZE%3D&amp;x-signature-webp=CmNdZvAV5QXRKuTuiV3%2FtGpjiBM%3D</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2fd5a55ce893450bbf82f3dfba22da93.jpeg</t>
+          <t>Lib\hardware\data\images\83c9bc137b9a46528954a0babff24c03.jpeg</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -7750,17 +7750,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fe66c8e873de4883aa66c310f1cb065a~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=Fmoiq1SwZFu157oV%2BgDaocXYDg0%3D&amp;x-signature-webp=7sdf2fHpoCvsRxtvotfOCET8eJE%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fe66c8e873de4883aa66c310f1cb065a~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=fAGfw1Vg7YmYRldsjVXuLpVDs9g%3D&amp;x-signature-webp=wDbQrUhlqTUea10H3v5Sy3GbSpE%3D</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4ca037f34377469dbbf50eaeddca01eb.jpeg</t>
+          <t>Lib\hardware\data\images\ad19e4d5e45c4ae98de3e437a5eb8a40.jpeg</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programmer-coding-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programmer-coding-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d1f458121310473e8394b993711abd3b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=sRkYAPtuktITZ%2Fz4XxmPSv%2FHWQM%3D&amp;x-signature-webp=XBHjAlUj3YIlp8Ip2T%2BeuNktZ98%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d1f458121310473e8394b993711abd3b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=%2F0p0qB%2BhHFXdZAS%2BM0oLrSmiI8k%3D&amp;x-signature-webp=iZK9Ecsbo3uX8MpG809NA9o8HNk%3D</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1e166743dc4f4d3ca04bbc5516744d7d.jpeg</t>
+          <t>Lib\hardware\data\images\9e1b7717aaa349beb3819868a604a6d3.jpeg</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/auto-diagnostic-programming-tool-expert-mode-for-icom-next-software-v2023-09-1tb-mini-ssd-windows10-laptop-cf-ax2-8g-d-4-43-1732688398569998202?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/auto-diagnostic-programming-tool-expert-mode-for-icom-next-software-v2023-09-1tb-mini-ssd-windows10-laptop-cf-ax2-8g-d-4-43-1732688398569998202?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -7848,17 +7848,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/10d441e1e3db48d184effed1bc09575b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=kNGiGm6RnzOTcd3%2BmDqOf1OtukU%3D&amp;x-signature-webp=olFtVEoGYEYUnw3AAnoO7ZHb6do%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/10d441e1e3db48d184effed1bc09575b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=tkl%2FCkxgqkfuvphAVTREHWDdjwE%3D&amp;x-signature-webp=IbBsNh7oWxI8q3D%2BDFYRV3Zn9lg%3D</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\93b07a07077f4845aa082a163847a1fb.jpeg</t>
+          <t>Lib\hardware\data\images\9a39743583f74e15ba503fa135147082.jpeg</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/new-for-icom-next-a-b-c-with-v2023-09-software-expert-mode-installed-d630-4g-laptop-for-icom-next-programming-tool-1732688989206054778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/new-for-icom-next-a-b-c-with-v2023-09-software-expert-mode-installed-d630-4g-laptop-for-icom-next-programming-tool-1732688989206054778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -7897,17 +7897,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e5f3a470390d4bcc88c465e59babd2ea~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=wgxi%2Bo0Om97%2FEQHJmEuA5ecSUN4%3D&amp;x-signature-webp=vvPw727qksx6k6k7xOcKEA8Ad0Q%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e5f3a470390d4bcc88c465e59babd2ea~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=Z6sGaVlzjuLJkPcSYC%2BbmKGMQkE%3D&amp;x-signature-webp=F6DevEzZoT6%2BCHWVMt5xnrMRaXw%3D</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\657a84720dc84ba68e6dae686958d736.jpeg</t>
+          <t>Lib\hardware\data\images\4d996eb07b9a49259c223fb6628f53aa.jpeg</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/cfc2-laptop-for-jlr-doip-wifi-car-diagnostic-tool-support-new-car-profesional-auto-programming-tool-1732690386628020090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/cfc2-laptop-for-jlr-doip-wifi-car-diagnostic-tool-support-new-car-profesional-auto-programming-tool-1732690386628020090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -7946,17 +7946,17 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43b554c10baa4e20a7f9e75f23312185~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=ECyEztQUr6uylrgA9ZD0qbqz0W0%3D&amp;x-signature-webp=Br6RuE23mxndt%2BVvBJLjwKhmSWM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43b554c10baa4e20a7f9e75f23312185~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=elw9iBTTlT2Z2zHJEb9q3vYS%2FXI%3D&amp;x-signature-webp=FkOgGBKFJlWCeynVSX9RMMDe%2FMk%3D</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e9781ee4e4824b9c8d4d2e0033faf2e1.jpeg</t>
+          <t>Lib\hardware\data\images\1c2bdae39e87404cba7895513e32d4b6.jpeg</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/car-diagnostic-tool-for-jlr-doip-v-ci-wifi-with-cf19-laptop-support-new-car-profesional-auto-programming-tool-1732690368491587450?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/car-diagnostic-tool-for-jlr-doip-v-ci-wifi-with-cf19-laptop-support-new-car-profesional-auto-programming-tool-1732690368491587450?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -7995,17 +7995,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c27b24e4e8a149f8afdec0aef9a21471~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764046991&amp;x-signature=l%2FAygdCJ%2FE86rSD%2B790TR7ergpg%3D&amp;x-signature-webp=h0fBfmKIIBMk2rb4HuLHBXcI7tc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c27b24e4e8a149f8afdec0aef9a21471~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=Fz5UP9WOH0I4%2FDYEHFPHR%2FIPXxM%3D&amp;x-signature-webp=fdsdwst3wlwHIaZI6vXHxr5Dkss%3D</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\36c70f92f2454a3582272119ef84ca15.jpeg</t>
+          <t>Lib\hardware\data\images\b85cac57405c4025b1b17538f9f5e934.jpeg</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/for-icom-a2-with-full-cables-professional-for-diagnostic-programming-tool-with-software-720gb-ssd-win10-in-x220t-laptop-1732688342876587898?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D20251125040311B3967A0E938DC21AAM2Z%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/for-icom-a2-with-full-cables-professional-for-diagnostic-programming-tool-with-software-720gb-ssd-win10-in-x220t-laptop-1732688342876587898?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -8047,17 +8047,17 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/0e0094f8-4e21-4aab-b63e-25e6f39a9a2d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=bolxUY%2FMBXtIR%2F7oZtbBG9w0eEU%3D&amp;x-signature-webp=X8teRCQEIelW%2BZ8%2Fdjzr%2FWmA4jU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/0e0094f8-4e21-4aab-b63e-25e6f39a9a2d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=qcncaOvRYAgTHtXdOMmSAbVL9gs%3D&amp;x-signature-webp=JjxGS8zyRQVY0SL93r%2F8aCIA%2FSs%3D</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0fcb688670b04e7099c2ee717cfb57e7.jpeg</t>
+          <t>Lib\hardware\data\images\7e7b50ebd8234cca8d9d2b46af14f0f8.jpeg</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/housesparepart/jakemy-jm-8183-145in1-obeng-set-hp-torx-laptop-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/housesparepart/jakemy-jm-8183-145in1-obeng-set-hp-torx-laptop-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -8096,17 +8096,17 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/18/2e15fe28-10bf-41e9-868d-6cb423cd4c8c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=qgKshWK20I%2ByKeCRimNfxvHRTX8%3D&amp;x-signature-webp=SzAMBXjIl82DOzVManiqYCDBxSY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/18/2e15fe28-10bf-41e9-868d-6cb423cd4c8c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=QxznoELXg9S2N2MUmIOU8XFwLlI%3D&amp;x-signature-webp=9TLrwipt1HExS637yLzze8a1dNg%3D</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7bae09a49cab4d0ea393f1b7b06f85a8.jpeg</t>
+          <t>Lib\hardware\data\images\b90d62a7e42447e4ae9f1fa34edbb328.jpeg</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/ezren/jakemy-jm-8183-screwdriver-set-hp-torx-laptop-computer-new-design-145in1-1730880897306690560?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/ezren/jakemy-jm-8183-screwdriver-set-hp-torx-laptop-computer-new-design-145in1-1730880897306690560?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -8148,17 +8148,17 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/660a3068-b7f9-418c-8ac3-25c629b1e0c7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=Uab5sskUDosc1kS70xPT7oS5wvs%3D&amp;x-signature-webp=n4ZZg6Le1nnSvZ0%2Bw5NelX4Z5Ws%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/660a3068-b7f9-418c-8ac3-25c629b1e0c7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=U5EEYwkF4fBMv5hOgHSM0V51eGc%3D&amp;x-signature-webp=UzqaE0YoSitlMKukDZXE2vIy4wM%3D</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f6f8992d3bac4e02b18170d4daf2d4fd.jpeg</t>
+          <t>Lib\hardware\data\images\f6862267ac0a4eb9ad449fa7cc4e2c9c.jpeg</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jakemy-official-store/jakemy-jm-8183-145in1-obeng-set-hp-laptop-macbook-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jakemy-official-store/jakemy-jm-8183-145in1-obeng-set-hp-laptop-macbook-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8200,17 +8200,17 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=mE17jNqUeNsts5SpGaXD75817bE%3D&amp;x-signature-webp=Rhx7x9kQ5b%2FGkTPRPBJZC3ES2oc%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=g33bqfOHOh7mKNrYc5dZuE%2BPy3A%3D&amp;x-signature-webp=H%2BYsiS6JZOZEnUgdxWInr62hnDM%3D</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4d061f45531348afa5a07d014e5b7b61.jpeg</t>
+          <t>Lib\hardware\data\images\0a11c5db0476426a838e7bc41d1cabac.jpeg</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8249,17 +8249,17 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f261db1a485a484fb269a53c633ed896~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=WRYQfRSaAWTobriDKGh7xNJWOb8%3D&amp;x-signature-webp=ELOGKTKwBkfLlKbz9yLDt9rz2eo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f261db1a485a484fb269a53c633ed896~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=oszW8RHu0rDokjxqJ0LoXDqWO7A%3D&amp;x-signature-webp=t3f1OoT8986qGc3J9vc5lS0BtYI%3D</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b1d66123cb1d48b68ba888306905b7c3.jpeg</t>
+          <t>Lib\hardware\data\images\dd0b250ad5334c08826366cea84ef87f.jpeg</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/bobby-soft-daypack-water-repellant-backpack-by-xd-design-tas-ransel-laptop-original-unisex-black-bfd8e?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/bobby-soft-daypack-water-repellant-backpack-by-xd-design-tas-ransel-laptop-original-unisex-black-bfd8e?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -8298,17 +8298,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/8b7fcd6f-843a-4f43-9ed7-23b395be8bf8.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=h%2FZInJU%2BuhupqwmzHTPbzZjTr%2FA%3D&amp;x-signature-webp=ma35NsC7Hl817PU0NXhTkgEYrcE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/8b7fcd6f-843a-4f43-9ed7-23b395be8bf8.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=%2FDlw6vuOqivafUfdw6v7C4DC%2BeM%3D&amp;x-signature-webp=XqSjEtQLI0zm48Uet5i4XKZ3awc%3D</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\cf840eb2cef84d5287abbc238d8bba2a.jpeg</t>
+          <t>Lib\hardware\data\images\eab7fd671bcc4771a5a358a12ab26118.jpeg</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-bag-black-1731594664039319238?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-bag-black-1731594664039319238?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -8347,17 +8347,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/32274fe1-96e5-4c4b-b9a1-8a54ed3cd196.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=IOnk2vg47P%2BjaZ6p5g5mE%2F6jeBE%3D&amp;x-signature-webp=T6ORs0VZA%2FZhO%2Fb5wF9c29vBEQw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/32274fe1-96e5-4c4b-b9a1-8a54ed3cd196.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=kfD%2Bo6ViaJ1hUYFP9dvyRPKy06w%3D&amp;x-signature-webp=pz%2BKKowIiacIIfvvrFUWxP%2FEEi8%3D</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\35e51725059a4909aaeebe20c428c3ed.jpeg</t>
+          <t>Lib\hardware\data\images\1b975a00a55f429c9fd8a5dcad2c86fe.jpeg</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-sleeve-1731594608912926406?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-sleeve-1731594608912926406?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/20/d1423af4-f39b-45ce-a5e1-4e98654a57a9.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=rbXb7tIrdorRzmmySfq5v0MRWmM%3D&amp;x-signature-webp=pKiRr%2B9fWlfFjv4Eu4o4uRLiYW8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/20/d1423af4-f39b-45ce-a5e1-4e98654a57a9.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=7yL8JPerLSpxRz4nOqP9rTw3pJI%3D&amp;x-signature-webp=5sONKb7%2FYbo2LiEzroEb5D4dA0E%3D</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6e8916eb5bb246eea5179a592b305d13.jpeg</t>
+          <t>Lib\hardware\data\images\7b01f268038241fba71c45fd017a3d5c.jpeg</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-laptop-original-off-white-987cc?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-laptop-original-off-white-987cc?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -8445,17 +8445,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/74672521-d63c-4345-8d7c-1a4c6d44107d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=QKgC3WhaiI%2BX3k6CISW3d216eNA%3D&amp;x-signature-webp=sANKFb5hF9eUnkLZPOxYSRvhjVI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/74672521-d63c-4345-8d7c-1a4c6d44107d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=tFxZdfAqJeATTBVXpjj62qa1p8Y%3D&amp;x-signature-webp=FgJYJ6PH73F57QEqjUhOxe8CNpY%3D</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e488bd4b22594145a19782a0f8034831.jpeg</t>
+          <t>Lib\hardware\data\images\82c1b3e52e1c4ba6a9a382f60e9c5753.jpeg</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-14-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-14-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -8494,17 +8494,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/0cb9f188-7016-4eff-b964-b13b4f39e7be.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=uijPizvB9%2F65IkgLEy0f%2Fd9l1EY%3D&amp;x-signature-webp=wEVpFnjo5urq0d6nX2PkkhMIG%2F0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/0cb9f188-7016-4eff-b964-b13b4f39e7be.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=A8bxQ44CBfSS4s39l1bBi%2BBPf1k%3D&amp;x-signature-webp=WRsuUtL84p02WYZvyhmERQuFGWc%3D</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\161924ed571442c6aa91d8f03592bb79.jpeg</t>
+          <t>Lib\hardware\data\images\97e51951c0a8418ca6fd17c3874248a7.jpeg</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-15-6-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-15-6-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -8543,17 +8543,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=q35wBCJwwUAV5l2njQtoP0XW5VI%3D&amp;x-signature-webp=NdIQq1k3oyk9%2FaYaTnvuD6yFCDM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=Tjv7UFx%2FQYtMeU7soCcwTCzMAsQ%3D&amp;x-signature-webp=qej7m8r5TbxqqA6pMQ8WT7qaWZ0%3D</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\211a2cf57432441f9c830c3209b1354e.png</t>
+          <t>Lib\hardware\data\images\858c149d0e784970be5cea899f27eec9.png</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -8592,17 +8592,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/4/211ca921-7a59-4d54-b8a4-b0a866a8a1fc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=%2BZY63JjNzdhlrFitt%2FXa%2FLh6jjo%3D&amp;x-signature-webp=EEWu5H28Z7SFjArzEm7gNjpZXeg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/4/211ca921-7a59-4d54-b8a4-b0a866a8a1fc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=2JKMG5gLGaXkSceGB3Rb7whMdfU%3D&amp;x-signature-webp=eImU0q2IyB0bTELKV9axKp4xGUY%3D</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2e89feef37f34125aa88b562722d07e6.jpeg</t>
+          <t>Lib\hardware\data\images\b1166d276588406abd4c8d47ce948791.jpeg</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-2-4g-wireless-optical-mous-1600dpi-ergonomic-design-for-pc-laptop-portable-usb-receiver-connection-mou19-blue-549c3?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-2-4g-wireless-optical-mous-1600dpi-ergonomic-design-for-pc-laptop-portable-usb-receiver-connection-mou19-blue-549c3?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3f70bf285cdd4ba78101ac0ce308ca29~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=SXUjP5f6P%2F%2BOJnq9KlhFJ1IqeaA%3D&amp;x-signature-webp=P%2FO2sHA9RbPdxcPKH7GqAnXM76k%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3f70bf285cdd4ba78101ac0ce308ca29~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=n%2Fh5ahTKXWlwwIaiPMb6IVXYV9Q%3D&amp;x-signature-webp=8MEY0DIB3b07aupBIaopEk4KMr4%3D</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\18f20f9faf55441e993dd930f311046b.jpeg</t>
+          <t>Lib\hardware\data\images\359d85f041954c258d705d838508e072.jpeg</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/poloalvisofficial/polo-alvis-urban-stanford-tas-ransel-waterproof-laptop-15-inch-sma-kampus-cowok-23-l-minimalis-design-1732445419512170430?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/poloalvisofficial/polo-alvis-urban-stanford-tas-ransel-waterproof-laptop-15-inch-sma-kampus-cowok-23-l-minimalis-design-1732445419512170430?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -8693,17 +8693,17 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/66c11c4fd34d4d6882e98ed086d9b763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=pFPI%2BGQ7xpOPyJBSx8SDZ5qUWlY%3D&amp;x-signature-webp=7EyZguq%2F94koymHnnHZPATBEpoo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/66c11c4fd34d4d6882e98ed086d9b763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=uhQ%2B%2BSmPmjbaDN7p8l0Rwdv9ra0%3D&amp;x-signature-webp=F4sMYf8ihYFhOhYaUvxj1bQxpc4%3D</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bc84643d09524aed8e1984d8fd29aae2.jpeg</t>
+          <t>Lib\hardware\data\images\fef11a388167408ba26830f2b92c5510.jpeg</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/asterosofficial/ugreen-mouse-wireless-2-4gh-dongle-slim-design-silent-click-4-level-dpi-for-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/asterosofficial/ugreen-mouse-wireless-2-4gh-dongle-slim-design-silent-click-4-level-dpi-for-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -8745,17 +8745,17 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4cebea9086a44f65b64de3af3ab65a97~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=WxgpKMvIodqY1B3ATIqF9jXxTsA%3D&amp;x-signature-webp=MQbrzcZkug09aw4%2BmmHoywPEhXs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4cebea9086a44f65b64de3af3ab65a97~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=PsBRkl45b18Vw7IueiNW8lHG0xo%3D&amp;x-signature-webp=GiO9zB%2FDJOV61gCAqEMqcoWW4mM%3D</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d6631dde14c04d9c803896335e709836.jpeg</t>
+          <t>Lib\hardware\data\images\9fa0b2bf218b450b8e18a08ec22178ff.jpeg</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-koper-2-in-1-mini-14-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charge-1731259158583739685?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-koper-2-in-1-mini-14-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charge-1731259158583739685?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -8794,17 +8794,17 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/2/12/79679dee-c94c-4311-bcd5-4f2eff9ffde0.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=hBwK2Vg0SWL4LBSp2mgvCX08n18%3D&amp;x-signature-webp=%2Bn2nZnMWirb%2FQ6QPFElubQWrOIM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/2/12/79679dee-c94c-4311-bcd5-4f2eff9ffde0.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=AojSBVJq39dGoPH8ykxxrQl7otk%3D&amp;x-signature-webp=msTICFu9vS4fGqN9QsuGXDAkeqY%3D</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\96769d24c3424535ac6e45d9adfb190a.png</t>
+          <t>Lib\hardware\data\images\e4f6c32a200348a789f5c59d2d990105.png</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mitra-visual-store/magnus-computer-hand-elbow-bracket-ergonomic-design-untuk-laptop-dengan-kapasitas-beban-50kg-instalasi-tanpa-lubang-dan-desain-penyimpanan-aman-dan-terpercaya-1730001110731359391?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mitra-visual-store/magnus-computer-hand-elbow-bracket-ergonomic-design-untuk-laptop-dengan-kapasitas-beban-50kg-instalasi-tanpa-lubang-dan-desain-penyimpanan-aman-dan-terpercaya-1730001110731359391?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -8846,17 +8846,17 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/619af75ea7304f43b85045a7eb5d04d6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=OylnSfczUUpwLnM3hQJAx6hA3Mo%3D&amp;x-signature-webp=LqVRF5PDa%2B7rbT8T3E0DbMvmKYc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/619af75ea7304f43b85045a7eb5d04d6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=QOaJ7gKiSNdo0l5O7v7FED1duMw%3D&amp;x-signature-webp=2hHGya7hikfpwZRh5kubFudo3Ds%3D</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\135e2b444ee54a88a79482b9f0b8190d.jpeg</t>
+          <t>Lib\hardware\data\images\6520c3280d2d4b5296265723fd099fd4.jpeg</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732093254842418725?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732093254842418725?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -8898,17 +8898,17 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/551a82aed56c47eb9e3ee0fba57f90b2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=iE9T1poJyO33nETLZ%2F9xvvCVu9g%3D&amp;x-signature-webp=AtLFZuFdDMNeI2%2ByJdDdquyvI7Q%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/551a82aed56c47eb9e3ee0fba57f90b2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=cVnxYn6yclEEkmJbSF1IEjX4hiQ%3D&amp;x-signature-webp=lg5OajJqtKHciV%2Fx2PbTfGP16gY%3D</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d575f3b77f934e1f9bd32e87718aa921.jpeg</t>
+          <t>Lib\hardware\data\images\c9d6d7003a6e4020907b3e578df8a395.jpeg</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/freeknight/freeknight-tas-ransel-pria-jumbo-tas-backpack-rain-cover-scalable-design-tas-laptop-anti-air-kokoh-expandable-usb-anti-maling-for-working-traveling-kulit-sekolah-hitam-tr748-1731255717575886209?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/freeknight/freeknight-tas-ransel-pria-jumbo-tas-backpack-rain-cover-scalable-design-tas-laptop-anti-air-kokoh-expandable-usb-anti-maling-for-working-traveling-kulit-sekolah-hitam-tr748-1731255717575886209?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -8950,17 +8950,17 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4fcd798501a442ba8d7d822ab4ca3653~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=kZEaSWhFHCVgIKAAFGMdJMloH4E%3D&amp;x-signature-webp=1uE74nW4SY9QINdETH37%2FPhBFFM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4fcd798501a442ba8d7d822ab4ca3653~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=bfGmryYw3%2FuWvKKjju%2B%2F4xPoDXY%3D&amp;x-signature-webp=wBMpkQclioVlciPso8FFIExSx1M%3D</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\704df4e70b9648d797fb6df0f1a05060.jpeg</t>
+          <t>Lib\hardware\data\images\2cbe5a2f1d0941d5a817b45c79f4a651.jpeg</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1731286329775916501?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1731286329775916501?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9002,17 +9002,17 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4a7f13da9aad455ab9fdba3f50b1c198~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=x2CqTAyWdZMOWWmIOX02a6lK3B8%3D&amp;x-signature-webp=JHSRKP2byi3o%2BpZEYmSGEXitofM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4a7f13da9aad455ab9fdba3f50b1c198~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=l0g1eeN0TC87SKfzEbK%2BRo9QHzM%3D&amp;x-signature-webp=yS31ETEqfU21gVCrBf1I%2FkauSFk%3D</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7765959d33c048d7a5d3538193d7b0a1.jpeg</t>
+          <t>Lib\hardware\data\images\5e5df43b4ca0426d9d8a49f2fe12f6e8.jpeg</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-koper-2-in-1mini-14-inch-1730797361031578784?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-koper-2-in-1mini-14-inch-1730797361031578784?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3252748fff24ac1b364458644770abc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=HqIuAQppCBNNgezLyzRjaYypaUs%3D&amp;x-signature-webp=vdrEwn%2BGBZfyjoDljNP8UY%2BhmVs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3252748fff24ac1b364458644770abc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=I5BIJNT3rhbOwbq49PCgREQuulM%3D&amp;x-signature-webp=aZMutTiN4mI52wYLsL2GvLtNUQY%3D</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\32f6d60b61e9400f8eaccbd028f498c7.jpeg</t>
+          <t>Lib\hardware\data\images\c513b9f659e24613b7d8e0d11b649059.jpeg</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-laptop-komputer-a909-design-ergonomic-with-volume-control-pc-spiker-speker-bass-1729384758482863585?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-laptop-komputer-a909-design-ergonomic-with-volume-control-pc-spiker-speker-bass-1729384758482863585?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -9106,17 +9106,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfeae6c1c6224919b5aa8184f6d941d3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=caC0fHzk8driHavrFKj42SIpVEA%3D&amp;x-signature-webp=KuJtmZm6vD05Biyn9nn%2FmSlu%2FhM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfeae6c1c6224919b5aa8184f6d941d3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=njkFfcoPlHaZxdJjBaYb3wOFnWI%3D&amp;x-signature-webp=2%2B%2Fga14EPbA%2B84ZcI6O00LAMzxE%3D</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bb9419066376419a97efeb001e33ef32.jpeg</t>
+          <t>Lib\hardware\data\images\d08cc151d7f14a64bae7715c25448251.jpeg</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robot-powerbank-indonesia/robot-m315-mouse-pc-laptop-computer-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-bergaransi-resmi-1-tahun-1732091684148970925?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robot-powerbank-indonesia/robot-m315-mouse-pc-laptop-computer-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-bergaransi-resmi-1-tahun-1732091684148970925?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/761cf6e500cc429b8864a69dc5572e5c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=CWyvAJ2C%2FiZdVB56qJnF6Rj56zs%3D&amp;x-signature-webp=jWbAK%2BIA2C8ZRfiP7%2F01VXZXWpk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/761cf6e500cc429b8864a69dc5572e5c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=pLnU145EOweGRKXEL1r1NkIKv6Q%3D&amp;x-signature-webp=VLCh4VPQT4eo1m1p05rl%2Bzt5ecg%3D</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4e47f908f9be4233b2080f5b7353ae57.jpeg</t>
+          <t>Lib\hardware\data\images\083da5c572bf4ecda8b1f86cb4578f6e.jpeg</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotsmartpower/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732092778590929924?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch%26whid%3D18553152</t>
+          <t>https://www.tokopedia.com/robotsmartpower/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732092778590929924?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch%26whid%3D18553152</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -9210,17 +9210,17 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1cfc199626c74270b7f2df4afa4837df~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=0Enc2oyvNHZOt1REM0aWzN6YZLY%3D&amp;x-signature-webp=32t3om9EErg%2B484ZBQ%2FSQP2nyn4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1cfc199626c74270b7f2df4afa4837df~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=wILPQu0VenFdRmiLgAPW2q1%2FRJ0%3D&amp;x-signature-webp=Zes1F9XYP%2FY9tK9vBDVoeoxGyF0%3D</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\712ba8788f5f4a25bdca84144036e49e.jpeg</t>
+          <t>Lib\hardware\data\images\18fd1161acb44e55b269a90cc2729b12.jpeg</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robot-official-surabaya/robot-mouse-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-robot-m315-mouse-nirkabel-kompatibel-pc-computer-laptop-original-bergaransi-resmi-1-tahun-1732189678655407803?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch%26whid%3D20644317</t>
+          <t>https://www.tokopedia.com/robot-official-surabaya/robot-mouse-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-robot-m315-mouse-nirkabel-kompatibel-pc-computer-laptop-original-bergaransi-resmi-1-tahun-1732189678655407803?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch%26whid%3D20644317</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -9262,17 +9262,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cdba5499d0c541eabd966bd3251dd080~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=bEUKYO92LxY2A44qTrCsoqs%2BtO8%3D&amp;x-signature-webp=Hvp1fnUdeWfOR4XUpzrfhPRSS30%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cdba5499d0c541eabd966bd3251dd080~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=svi6NMQI0lQfa0CDTBU0s%2FooX1s%3D&amp;x-signature-webp=peEGF23ZwukEhlPTn0O5FExzr6M%3D</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e94e10488e0a4e5586768d516b30de68.jpeg</t>
+          <t>Lib\hardware\data\images\38f0ac1ba7db49eabd6944098d2c18d6.jpeg</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731285332222182869?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731285332222182869?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -9314,17 +9314,17 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/736c25698fe647b7b3a2740fc3a0941d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=apj37RrAoompMX%2FRw1r7LBo3lJE%3D&amp;x-signature-webp=DoA0f6DdHP8iIVomReolzDrsFLw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/736c25698fe647b7b3a2740fc3a0941d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=fMb%2F4ju1T8EmpMTQJKZdK6R%2BBMs%3D&amp;x-signature-webp=QP41l6LXfTf8Vc1Mj0ONYj7RLeg%3D</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\da018455ba094f1e9f8fb63a402e518e.jpeg</t>
+          <t>Lib\hardware\data\images\27b064c4a3c7488b9316d19a375f7c59.jpeg</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730915957094909397?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730915957094909397?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -9366,17 +9366,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/38dcad3fe4a041af8676ce38b7af63c5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=jDYEBidCJrOMG%2Ffs%2Bjp3YkatNDI%3D&amp;x-signature-webp=A%2FXGhdTFu5Uqe%2FV3%2FoJKQvm5EX8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/38dcad3fe4a041af8676ce38b7af63c5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=zZZybHssT7qH%2F3najUjj57P93jc%3D&amp;x-signature-webp=aQE0qi4Aa%2FnfOAa1I5%2BsMEcLbDM%3D</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7629727146cc4554b6f94ff0e59a8237.jpeg</t>
+          <t>Lib\hardware\data\images\5a4dfc50a0694531a11c2508c7778ec6.jpeg</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1730932169696708053?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1730932169696708053?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -9418,17 +9418,17 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0765aa228c7e4eb98f5cddffb3cd161e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=mV2a8R6AmiLILaFiowaWy3zh4DU%3D&amp;x-signature-webp=OGiF6wjYBIg5JXcAAycoP71H8vg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0765aa228c7e4eb98f5cddffb3cd161e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=unJN2oGT13W%2FPEZtGmw19kP7pxw%3D&amp;x-signature-webp=6T4z7u%2FI4qbh5837g2LS8GNeZgw%3D</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\586744b0aae14546bbd4a9232960cf27.jpeg</t>
+          <t>Lib\hardware\data\images\6be02d29b617417b8bd6c5d512f7eb02.jpeg</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730797091346285728?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730797091346285728?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -9470,17 +9470,17 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/15dbf2c96f3e48028a7d92838124dd06~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=fiaVEqY3HgHo%2Bl11pcQL7SO46rs%3D&amp;x-signature-webp=z4DF4%2FGchbd%2B46Vn%2BMzSTMkPysI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/15dbf2c96f3e48028a7d92838124dd06~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=6pX0ZP8iINP6jt6WVapXU6zh90U%3D&amp;x-signature-webp=qBHRzgBpoVmHUdmpt9WZmVYo%2FdM%3D</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\23cd0e4dfb364d039adc03a8bf74fb51.jpeg</t>
+          <t>Lib\hardware\data\images\61b6b79809e14d838cf64c56e6dc27d1.jpeg</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-led-for-laptop-komputer-pc-cpu-i560-1729692448934234593?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-led-for-laptop-komputer-pc-cpu-i560-1729692448934234593?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -9522,17 +9522,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/6/559a865b-d5dc-46a6-b4cc-1cbcaac99452.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=%2FNWnyw44jqsBOX%2BRpq4GQdYZjHM%3D&amp;x-signature-webp=iK0HOmX%2FnfthmZ438kSUvVPpoOE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/6/559a865b-d5dc-46a6-b4cc-1cbcaac99452.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=TsICb1nFARUIyJNt97DXCqhtFYg%3D&amp;x-signature-webp=EZKkR3u%2FGmIs5dDSfAnu4B14Ypo%3D</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4a2b639003434be2838a79ca3dae5ef4.jpeg</t>
+          <t>Lib\hardware\data\images\b9415393f7f044c2830bfc609d84f5cf.jpeg</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-for-laptop-komputer-pc-i600-1730809914258851297?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-for-laptop-komputer-pc-i600-1730809914258851297?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -9574,17 +9574,17 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9b778382d9e042acbbf6fc51f0b4b3cc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=OuLm3AGIg2rV66eGsx8YFfeuJj8%3D&amp;x-signature-webp=AVbP87ZBIAAyW5TMSIX6PgNirxY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9b778382d9e042acbbf6fc51f0b4b3cc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=pd1MQGbP8K8XbRu6b77g7zgMsPo%3D&amp;x-signature-webp=PhP3DlSo17lXJRHDDhm1enc%2FPrY%3D</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ec227ed725224434ad7413e71403cd77.jpeg</t>
+          <t>Lib\hardware\data\images\4ad70f8ec2894f7a9a363fc1a46811a9.jpeg</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-soundbar-laptop-pc-komputer-i520-design-long-strip-with-volume-control-1729384483568911841?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-soundbar-laptop-pc-komputer-i520-design-long-strip-with-volume-control-1729384483568911841?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -9626,17 +9626,17 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/08a5710421f849f0ba33f538d160f9fb~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=XQzRHMIeo4MhYZOaLdxrBw2gP70%3D&amp;x-signature-webp=16SVPvgnfvbEle%2FS2FKjEYkjOYc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/08a5710421f849f0ba33f538d160f9fb~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=XS25Uxnt3rK8bARZYncMIpD0Tvs%3D&amp;x-signature-webp=hCQlKikJLdMInERRJenAK9%2B9YQQ%3D</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a456246c013748dab66c957873e6ef17.jpeg</t>
+          <t>Lib\hardware\data\images\8768a67f00ab437d95e55dbb41201ffa.jpeg</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-1730797282857354400?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-1730797282857354400?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -9678,17 +9678,17 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3a7b9972f596402094058c182b8ba340~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=LCQm4hz5FfFrjeLof7qrMuXmSEQ%3D&amp;x-signature-webp=0d%2BpBKy16jZ7Kqd2vg%2FOQlJKYoU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3a7b9972f596402094058c182b8ba340~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=9P369b5dX2zFLSdjtRtc8iJVQPk%3D&amp;x-signature-webp=VmFSTQaRQPhWOyOz4ck0vi5h868%3D</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\46c28ce64c384eefb823ef9f9230e5c9.jpeg</t>
+          <t>Lib\hardware\data\images\d07d6372fba44cec88759f018a460a62.jpeg</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730755375298348501?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730755375298348501?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/92ffb7bcb5ba4243bf5aa5c96cd90e61~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=zfhI%2FYQdltvkYxwifzTTYkQiUeg%3D&amp;x-signature-webp=GObyPc8C6A%2BSCTKsETgVQyBwVoI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/92ffb7bcb5ba4243bf5aa5c96cd90e61~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=hHyPACPqx8UkdLOW%2F0e2lLIbiYk%3D&amp;x-signature-webp=6CRMINryflSqPGUfwckrVvwzN7g%3D</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c882f954b66b43d3a13e53f85cf0ba9b.jpeg</t>
+          <t>Lib\hardware\data\images\da18c90ff15a4a1ba8c5e160fe4cdecd.jpeg</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/orashare/orashare-a01-decorative-assorted-cartoon-stickers-for-power-bank-wall-charger-laptop-tablet-aquaflask-and-so-on-decoration-long-lasting-waterproof-aesthetic-cute-cartoon-design-magic-paper-stickers-random-1pc-sticker-1732799857834428193?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/orashare/orashare-a01-decorative-assorted-cartoon-stickers-for-power-bank-wall-charger-laptop-tablet-aquaflask-and-so-on-decoration-long-lasting-waterproof-aesthetic-cute-cartoon-design-magic-paper-stickers-random-1pc-sticker-1732799857834428193?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -9776,17 +9776,17 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/9/14/e90d0ad0-232f-4503-9d30-433258dedbd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=06OMgs0CAHa5TSbO7XLgIRtb2%2B0%3D&amp;x-signature-webp=VIVFokt%2BGy2yTqZhiANXlsw2KDM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/9/14/e90d0ad0-232f-4503-9d30-433258dedbd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=gjqWdnkFK%2BN%2FwneBQvwMN8LXZyM%3D&amp;x-signature-webp=E5ECwSMo8%2Bae%2Fh8Nmu8nfw9aEKM%3D</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\09af97b68ba748498115c57af66e5f15.jpeg</t>
+          <t>Lib\hardware\data\images\5f8c033abca546dbac5b77ea6dd8b6c3.jpeg</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-bobby-explore-backpack-by-xd-design-for-laptop-17-inch-ransel-original-1731176351546115751?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-bobby-explore-backpack-by-xd-design-for-laptop-17-inch-ransel-original-1731176351546115751?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -9825,17 +9825,17 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/19/3048426c-97a8-4891-ad6a-9d3335136017.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=wWWgyjdUUDmRXyEl%2BiP61qIsvKY%3D&amp;x-signature-webp=Vdx9x%2B10qPVL%2BIpyFKw3Tmz7FD0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/19/3048426c-97a8-4891-ad6a-9d3335136017.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=EfLF%2BK9VXrvvu2at5bYopUzcYxI%3D&amp;x-signature-webp=W%2Fw3AcYgLdE1%2FaMvZPwTBQvQRaY%3D</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\36a19faa878b4b40a225fcfa67255c46.jpeg</t>
+          <t>Lib\hardware\data\images\6a36f0b33fbe48a0860e19dd5800c533.jpeg</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-ransel-eco-flex-bag-for-laptop-untuk-kerja-sekolah-original-water-resistant-original-xd-design-1731176336923592359?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-ransel-eco-flex-bag-for-laptop-untuk-kerja-sekolah-original-water-resistant-original-xd-design-1731176336923592359?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/7/15/2a8e3008-0cc1-456c-a1eb-8712b4e3afef.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=tiB60JtJ4Gg5yxlTSj8iKNs0AR8%3D&amp;x-signature-webp=zZc9ETyGMeHKshJWgC6uBMX%2BJ7o%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/7/15/2a8e3008-0cc1-456c-a1eb-8712b4e3afef.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=7%2FPnbic7sBAmk3okEeEKAsnyb%2BI%3D&amp;x-signature-webp=yak5YcxwOPXoTI%2FhljClKyT9uQY%3D</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d065a5353240434f8d9d3dc9b6ae4cc6.jpeg</t>
+          <t>Lib\hardware\data\images\0bea127c2a384c96be62b366985c0482.jpeg</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-2-0-anti-theft-backpack-briefcase-for-laptop-1731176367656371879?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-2-0-anti-theft-backpack-briefcase-for-laptop-1731176367656371879?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/26/3934712d-a1d2-4f48-af1b-0b1037ea9e26.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=HHBerVHg4NjZgxW9J0kxR8OanGw%3D&amp;x-signature-webp=zw9q%2BdINqxk2dJZRp%2BMm92F4kTE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/26/3934712d-a1d2-4f48-af1b-0b1037ea9e26.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=kn3tTDPHBBZjf7dsWcjHO%2FnJuNc%3D&amp;x-signature-webp=%2BxQX0HXPqYTbWJjeQ%2BM4GfzGK0s%3D</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\75388126d6be41288ff26674b3cfb936.jpeg</t>
+          <t>Lib\hardware\data\images\718839f416b74589bb569739dce73db2.jpeg</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-backpack-for-laptop-original-1731176301652117159?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-backpack-for-laptop-original-1731176301652117159?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e0cb31b7859943a7818f516b7a76c398~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=x6cK2AEQoHg7U0K%2FywNJufmjgGA%3D&amp;x-signature-webp=HWBVBvzQzAXzEcojHx1Yd2qXjuQ%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e0cb31b7859943a7818f516b7a76c398~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=aRaxNEpKTZcnqRS9lI%2FtSpk7U2Q%3D&amp;x-signature-webp=bA2U0qh1sYqtl5YZtFR3AR%2Ft7GQ%3D</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\27d9cd110d4d4716a3fa8c822d3a9f1f.jpeg</t>
+          <t>Lib\hardware\data\images\26ef3f6b87b247fa8118823a1289d271.jpeg</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/prodesign/pro-design-patron-patslt-50-meja-samping-nakas-meja-laptop-1729384439739745584?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/prodesign/pro-design-patron-patslt-50-meja-samping-nakas-meja-laptop-1729384439739745584?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -10027,17 +10027,17 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e100902e37f5405f95ab14ceca042fbe~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=wyzMiqrcIQ8uRk7PbG5bSJgmAvY%3D&amp;x-signature-webp=3Bdlbl7hFH%2FIKZ8QHJo8YPA%2FAlg%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e100902e37f5405f95ab14ceca042fbe~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=1SIOoxOSope0sEiQD5cZ3ceiUeE%3D&amp;x-signature-webp=r61RaMW%2B1t9%2FqzB4J56JUTi4JKY%3D</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1046e8287d1340b79b0323e290f9926d.jpeg</t>
+          <t>Lib\hardware\data\images\66ea92593ed943ce9170ab5888de6251.jpeg</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/unomax/sleeve-nillkin-versatile-for-laptop-notebook-macbook-horizontal-design-1729542909144501215?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/unomax/sleeve-nillkin-versatile-for-laptop-notebook-macbook-horizontal-design-1729542909144501215?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -10076,17 +10076,17 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/4/12/4a196eba-99a6-4d86-ba5d-42198ae0ae47.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=Fe%2BRh3%2BTS0cmZS452HgHv6niArE%3D&amp;x-signature-webp=hqW18QRFdhMdGA%2B5VxIH2ed5wkM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/4/12/4a196eba-99a6-4d86-ba5d-42198ae0ae47.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=TbRaip26l3pWT%2BYkRGHp6y2jSi0%3D&amp;x-signature-webp=R1ovOHvHKC0MTAvnkhD0wHd11sc%3D</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ea72aa3a718f491598efe4981cf6a11f.jpeg</t>
+          <t>Lib\hardware\data\images\a08dc59520bd41d59fc095ba4cd6a923.jpeg</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-anti-theft-backpack-briefcase-for-laptop-15-1731176360280164007?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-anti-theft-backpack-briefcase-for-laptop-15-1731176360280164007?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/65b3b9f2049f476ba5c95f176912c01f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=1%2BTXlyNo8SBm%2BKDgjCYzFsET3rY%3D&amp;x-signature-webp=%2BTQQd1I2U8ZJ8fA71bny5RfVg6M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/65b3b9f2049f476ba5c95f176912c01f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=jFoEROsQRG2rjiZLRAJK%2F0dzatE%3D&amp;x-signature-webp=q%2BS3d5UOBopLIffqpkoZoIPkKds%3D</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\46fda67529ed44799cae5d920369b6d2.jpeg</t>
+          <t>Lib\hardware\data\images\3e4403f4430349268775b906798eb42a.jpeg</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/wia-official/wia-xd-design-bobby-edge-anti-theft-backpack-tas-ransel-laptop-unisex-original-1729752607370544988?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/wia-official/wia-xd-design-bobby-edge-anti-theft-backpack-tas-ransel-laptop-unisex-original-1729752607370544988?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -10174,17 +10174,17 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/1/16/61242af3-3630-4531-8d25-e625e9e80dea.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=lXKhHzRrPJb6oO8RhKJM25ESWAs%3D&amp;x-signature-webp=fAthfWS0IHb5nq87h7aN5rsng%2Fg%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/1/16/61242af3-3630-4531-8d25-e625e9e80dea.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=ijldVPog0iMal9CI0%2BNjgqo3W9k%3D&amp;x-signature-webp=fYyLHNyI8qKi2jrWH8XR8JbVwvY%3D</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e793ad944acc4748b76ba07508b9ad97.jpeg</t>
+          <t>Lib\hardware\data\images\3d786c14abe04234a272b597165a6f36.jpeg</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/primarycaresofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black-80565?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/primarycaresofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black-80565?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/1d2dc8699f1a427e82b9077ea324a552~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=XdScIS1C9LZxk4ivK1Lv62o6TMY%3D&amp;x-signature-webp=72ixtAekQ1gZfOEtp7QZzv7Eqdw%3D</t>
+          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/1d2dc8699f1a427e82b9077ea324a552~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=J%2BwV9JQZ4cKekzb%2B5jg5NgWIOxM%3D&amp;x-signature-webp=D%2B%2BXxDEZS3KF%2BRNIa9VH%2FisLbG4%3D</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\460c39fd95c0447ea85403066dc6bb03.jpeg</t>
+          <t>Lib\hardware\data\images\c34bc9e3f3734a4cbbaccf7d93df3cae.jpeg</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/sempanabags/polo-goden-62194-2b-tas-ransel-backpack-tas-punggung-tas-laptop-tas-kantor-tas-kerja-premium-material-sleek-design-multi-compartment-banyak-tempat-penyimpanan-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/sempanabags/polo-goden-62194-2b-tas-ransel-backpack-tas-punggung-tas-laptop-tas-kantor-tas-kerja-premium-material-sleek-design-multi-compartment-banyak-tempat-penyimpanan-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -10278,17 +10278,17 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a04b8b3b3b064a0fa6aaf3e379856c92~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=rTRd9G0rrwk43jfEWcmspMOpjGg%3D&amp;x-signature-webp=KLUVDer58%2Fqpt%2F6eHaB8q9KFlec%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a04b8b3b3b064a0fa6aaf3e379856c92~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=U5%2FfGRNZ%2FS0XVqczo%2B9eK991UPc%3D&amp;x-signature-webp=ITcgDAxiK7tNGznhxoaF%2BokMD1k%3D</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\388982a90777465d8b0f5be9882954a1.jpeg</t>
+          <t>Lib\hardware\data\images\76fb77b891a741fc8604ea51ad351cc1.jpeg</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/advan-by-urbanlife/advan-laptop-workplus-heritage-amd-ryzen-5-7535hs-8gb-ddr4-upgrade-512gb-ssd-upgrade-amd-radeon-660m-win-11-14-wuxga-16-10-megamendung-batik-design-1731557661886154575?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/advan-by-urbanlife/advan-laptop-workplus-heritage-amd-ryzen-5-7535hs-8gb-ddr4-upgrade-512gb-ssd-upgrade-amd-radeon-660m-win-11-14-wuxga-16-10-megamendung-batik-design-1731557661886154575?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -10327,17 +10327,17 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/12/ffd6e4db-90b2-4e80-b558-4833df06bfc3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=AB5b%2B%2FZasoqtyBHqHM61aJ49jZc%3D&amp;x-signature-webp=CHSdGiMnOSN20J2iMS7KhMtj6fU%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/12/ffd6e4db-90b2-4e80-b558-4833df06bfc3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=cDLtRdCyvev5KpoUBhWJ2oTmKx0%3D&amp;x-signature-webp=U4exwXrEBpmjOAxndFOJJrulLwc%3D</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\65111631915a4fd1b00f418d343fca09.png</t>
+          <t>Lib\hardware\data\images\7314291999a443bda3963e174de8f659.png</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deermatech/ugreen-ergonomic-premium-mouse-pad-with-arm-rest-design-bantal-tangan-anti-slip-mousepad-untuk-kerja-kantor-meja-komputer-pc-laptop-black-faf99?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/deermatech/ugreen-ergonomic-premium-mouse-pad-with-arm-rest-design-bantal-tangan-anti-slip-mousepad-untuk-kerja-kantor-meja-komputer-pc-laptop-black-faf99?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -10379,17 +10379,17 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/af145de2fcdb4ec3a9dc41740a920a72~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=DXdabmlB57SNw8Frr%2FjQb21YddE%3D&amp;x-signature-webp=2kI7lDp6%2BhyIMyvyP5g7aKGud4A%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/af145de2fcdb4ec3a9dc41740a920a72~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=0%2F0I%2BLrOh80NAmZzEN%2FatEtLwwQ%3D&amp;x-signature-webp=%2FZ3J%2F%2FxFTESJOxy%2BsadNhOmqwuY%3D</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f3a554f5008a404291cd2b8655bf1bf5.jpeg</t>
+          <t>Lib\hardware\data\images\62a73f9287ee4a7384b409b0eece30bb.jpeg</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/usea/taffhome-meja-lipat-serbaguna-laptop-portable-desk-minimalist-design-i042767-1731655641388386299?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/usea/taffhome-meja-lipat-serbaguna-laptop-portable-desk-minimalist-design-i042767-1731655641388386299?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9d59757d49a84775a35c06bdeb14cede~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=j%2FRoY51Tcy6yqowzenWik6sSVBw%3D&amp;x-signature-webp=w6PtI3h9giDiX8PWTsilKRmZ3OM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9d59757d49a84775a35c06bdeb14cede~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=zzZSbYhTZBrsbuVF8m%2BchOXHDtw%3D&amp;x-signature-webp=Tl1%2F3DqD3fiM08AYTdfDqIQPma0%3D</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6ed4e91748ce411dac85d8803c9739fe.jpeg</t>
+          <t>Lib\hardware\data\images\2b2baad911294308b5976944168d688f.jpeg</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/wia-official/wia-xd-design-14-16-laptop-sleeve-black-tas-pelindung-laptop-original-1729909128724056924?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/wia-official/wia-xd-design-14-16-laptop-sleeve-black-tas-pelindung-laptop-original-1729909128724056924?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -10477,17 +10477,17 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/8/dd821518-9132-4894-82f2-34caf0bb2acc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=mpOKUKLcQUQuJId1ZNTGeuNavVY%3D&amp;x-signature-webp=Opylf8yWu4DfjSsoELxK2P4FS88%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/8/dd821518-9132-4894-82f2-34caf0bb2acc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=IdKApFJotvhcyx4xFGCorAA0SFs%3D&amp;x-signature-webp=XMRn9ECR6P3u8ifcqt7kRO%2FxZ%2B4%3D</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4eac502ee5fe4535bf7564287f4bb346.jpeg</t>
+          <t>Lib\hardware\data\images\2e56d226e7f642eeb82dbb2e97ad7fd0.jpeg</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-bobby-hero-anti-theft-backpack-xl-17-inch-bag-for-laptop-xd-design-ori-1731176367509243559?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-bobby-hero-anti-theft-backpack-xl-17-inch-bag-for-laptop-xd-design-ori-1731176367509243559?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -10526,17 +10526,17 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/12/9/54c88793-1151-49b3-ae07-078a15223f01.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047011&amp;x-signature=i2oinTthPfxvS6Fbrq%2FsfTpEd20%3D&amp;x-signature-webp=YH5ByzHSDslffubAUZIneqe2h7I%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/12/9/54c88793-1151-49b3-ae07-078a15223f01.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=DV9779apLss9WjUzHXHjDd%2FWj1E%3D&amp;x-signature-webp=SpGViU%2F8XZqruH1DVf3n0GSOt%2Bo%3D</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4fe2d5f5503e49cb9a6fac8c66e47c42.jpeg</t>
+          <t>Lib\hardware\data\images\b1a81cc67fc94f948bd0250e2ec0cb8e.jpeg</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supcaseofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125040331371BCE7DC8381713CS5Y%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supcaseofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">

--- a/Lib/hardware/data/tokopedia_products_latest.xlsx
+++ b/Lib/hardware/data/tokopedia_products_latest.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/1/7aeb95bc-e841-4938-b4bc-170c843ec092.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=UXgRbwwzRttdV93CO57l56vofXs%3D&amp;x-signature-webp=uSjkfiwAEn78vqu%2BHTrr95cmf2A%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/1/7aeb95bc-e841-4938-b4bc-170c843ec092.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=pISHeXaxSPfh%2BFBEGgPE8F4uO4Q%3D&amp;x-signature-webp=805p1i47VQMerHjPhrECOxmkrVE%3D</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\342e757c013a4428909bc96568bc64a0.jpeg</t>
+          <t>Lib\hardware\data\images\2f283174c2d14f6485f9a82cd6c82976.jpeg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomppurwokerto/speaker-gaming-pc-dan-laptop-nyk-sp-n02?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomppurwokerto/speaker-gaming-pc-dan-laptop-nyk-sp-n02?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/df0f4a61aed14dcb8da81f3c4f338f43~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=BRZL7%2BIly4XPb1Dl6JD4eTWPRyI%3D&amp;x-signature-webp=XgmssGrR8SGSy4yukQ4hwu3Fha0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/df0f4a61aed14dcb8da81f3c4f338f43~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=J%2B3jCMBZt3%2FhZLR4TlrZGvc93LA%3D&amp;x-signature-webp=64tt9DSov3PUNceqtXkGBSD3%2FKY%3D</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3a1dd46a9f284a95b69e7d9dc4957e9b.jpeg</t>
+          <t>Lib\hardware\data\images\238a4e5243a14709bceb5522daafe9f5.jpeg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomppurwokerto/coolingpad-nyk-x6-thunderstorm-gaming-cooling-pad-laptop-2-fan-x-6-x-6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomppurwokerto/coolingpad-nyk-x6-thunderstorm-gaming-cooling-pad-laptop-2-fan-x-6-x-6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -606,17 +606,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/22/cc4b9584-80b6-44d6-87d5-f4611d98002d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=ibytxpFGoKpMzixU9hAQKhOzPHI%3D&amp;x-signature-webp=45NJJqQbyPscUJSptdW0jzR8lSA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/22/cc4b9584-80b6-44d6-87d5-f4611d98002d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=JVFne%2BveVaQFQpMfAa65tuJY9wQ%3D&amp;x-signature-webp=Cbm4kyGC2oqVe%2FL5zAV%2FbKqURO0%3D</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\90d98f836bdb4e6cafcb6e746285b6ea.png</t>
+          <t>Lib\hardware\data\images\ccad8e816f2c4fb5889737d5ae54d666.png</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomp-semarang/rexus-gladius-gx2-gaming-pro-gamepad-joystick-laptop-pc-hitam-95b39?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomp-semarang/rexus-gladius-gx2-gaming-pro-gamepad-joystick-laptop-pc-hitam-95b39?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -655,17 +655,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/3/c0410e6b-f108-42d2-9b67-ea029ba1ab29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=Gz5HbV4OcHQjy4mual2rJDKYl5Y%3D&amp;x-signature-webp=V1PqPhJmSZcFY78awynfi%2BydANY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/3/c0410e6b-f108-42d2-9b67-ea029ba1ab29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=f4gX8Rm%2FygzoWAlEMS6t7bNstfg%3D&amp;x-signature-webp=P%2FiseALc5h80TtjhGwDhvZJS2qU%3D</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\af3e42b310c24a92bc9b88561d1c7904.png</t>
+          <t>Lib\hardware\data\images\35b4e300d51447b4aebb191fe00be821.png</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcomp-semarang/nyk-x6-thunderstorm-gaming-coolingpad-laptop-2-fan-x-6-x6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/starcomp-semarang/nyk-x6-thunderstorm-gaming-coolingpad-laptop-2-fan-x-6-x6?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/13/35945633-babb-4760-81cb-d4986d80ec0f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=qSCfXI3MGjH2euNFxdWO3YwQe6k%3D&amp;x-signature-webp=gW9E70SvrSnHigrfjesWpr9tuFk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/13/35945633-babb-4760-81cb-d4986d80ec0f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=CaX%2BXVUO8AUIThyThdM492k4iGo%3D&amp;x-signature-webp=gmf6UP4LRzcfcHPsOscd31w%2BcrI%3D</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6fdf19b399324c858a5de1fa27c6c0e9.jpeg</t>
+          <t>Lib\hardware\data\images\57ea1f1635464c518530840799a5609a.jpeg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/oceanbike/headset-headphone-gaming-power-full-bass-hs04su-mic-3-5mm-earphone-komputer-laptop-pc?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/oceanbike/headset-headphone-gaming-power-full-bass-hs04su-mic-3-5mm-earphone-komputer-laptop-pc?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/16/f7f0720b-7ffd-4402-9d19-9a8e519ea683.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=uuQKl1Nk7jJzyoXTakTMVSwWyBE%3D&amp;x-signature-webp=iP7lzaDTkCoVclmduVN1I2y5mqA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/16/f7f0720b-7ffd-4402-9d19-9a8e519ea683.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=JUfNfBWwjTrxRCWfzt37sreFAf4%3D&amp;x-signature-webp=NDb0c5NjMApHprAhR5VMrEuT3iQ%3D</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3b252b3cf29d47a6a6ab677e379c6573.png</t>
+          <t>Lib\hardware\data\images\49431ead7f81478cb4d5cd9c27487cf5.png</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mrmaidstore/keyboard-gaming-and-mouse-8310-rgb-keyboard-and-mouse-gaming-for-laptop-komputer-pc-2-in-1-gaming-set-white-0fc1b?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mrmaidstore/keyboard-gaming-and-mouse-8310-rgb-keyboard-and-mouse-gaming-for-laptop-komputer-pc-2-in-1-gaming-set-white-0fc1b?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e55445b6e9a42439b246d1d5c9cc663~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=uqm5Bht6%2BdE%2BkPW%2FU9yDuvWN2Ig%3D&amp;x-signature-webp=hT4NpN2FyVjoYonNOshq86MrLzw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e55445b6e9a42439b246d1d5c9cc663~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=dGSdiFjMKZ6QV0kUWcGWwfz%2FDA0%3D&amp;x-signature-webp=8cMrd2lUUtlOpw02QGIzBzmRvfw%3D</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ca513a6ca91143b2ab6aa771690792ea.jpeg</t>
+          <t>Lib\hardware\data\images\e3471b6b87644e52843dffaa174bf284.jpeg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fantech-official-store/fantech-carbon-7-1-hg30-headset-gaming-usb-7-1-virtual-surround-sound-mic-noise-cancelling-driver-40-mm-pc-laptop-mac-ps4-ps5-switch-1731357616041067843?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fantech-official-store/fantech-carbon-7-1-hg30-headset-gaming-usb-7-1-virtual-surround-sound-mic-noise-cancelling-driver-40-mm-pc-laptop-mac-ps4-ps5-switch-1731357616041067843?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/67226b19-6b3d-41f1-b2f3-c0c0d81b1319.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=BenadELo%2FXQY0XYl3J942Q19ArA%3D&amp;x-signature-webp=UXUPbjEwZqvOHKx3bjuwbOJtEbc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/67226b19-6b3d-41f1-b2f3-c0c0d81b1319.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=mfHeG0WI1p%2F%2FOT1qkGrMb6SadAs%3D&amp;x-signature-webp=gtzCYT9VVCA9jKjc1z8lyeJKn6I%3D</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\08480807502242c38d58aaa1afc5e5bc.png</t>
+          <t>Lib\hardware\data\images\8c24ca489b8d4b34a5166d118e0dd2d9.png</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-tv-home-theater-pc-monitor-gaming-laptop-hdmi-male-to-hdmi-male-2-1-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928891163543425?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-tv-home-theater-pc-monitor-gaming-laptop-hdmi-male-to-hdmi-male-2-1-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928891163543425?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -906,17 +906,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/9b61818c-7d6b-4657-b87b-cda3f5f9bcf3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=UlOCWbrnWAVd8LITumGAeGO3nX0%3D&amp;x-signature-webp=JXtjjGotq6QS7cqfAQiwaRM3GlA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/9b61818c-7d6b-4657-b87b-cda3f5f9bcf3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=A5onzuCS6008trzE7s9p4P0Dqx4%3D&amp;x-signature-webp=CAs%2FgoR6v7%2FheTpTpIWmJ86SLeY%3D</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0599550196644043a754d6278a539615.png</t>
+          <t>Lib\hardware\data\images\ba71a9ecdb894b1d811d0666db8ff5fa.png</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-pc-monitor-gaming-laptop-displayport-dp-1-4-to-displayport-dp-1-4-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928629547304833?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/koboitech/hagibis-kabel-pc-monitor-gaming-laptop-displayport-dp-1-4-to-displayport-dp-1-4-ultra-hd-2k-4k-8k-hdr-earc-3d-vrr-qms-allm-qft-displayhdr-1730928629547304833?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/5d1519ada63b4e6d9117033d63f53c0a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=6T5k0o3oqzu77ar8oYfz1pwlgH4%3D&amp;x-signature-webp=jpxnSYaUDgles5IYpkzwo5%2B0Jw4%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/5d1519ada63b4e6d9117033d63f53c0a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=tpXI7oPHxu5SIwHoOk0pwoAM76M%3D&amp;x-signature-webp=1K4tYEe2sBiEZO6ACd8jI5fVLss%3D</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9dc8d795111548d99e418aa3104296fb.jpeg</t>
+          <t>Lib\hardware\data\images\8e69bdf793e64bf590d8aa3b332969e6.jpeg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/himtech/hagibis-kabel-hdmi-to-hdmi-2-1-ultra-hd-2k-4k-8k-3d-hdr-earc-vrr-qms-allm-qft-displayhdr-tv-pc-gaming-monitor-laptop-video-audio-cable-1730928835618703202?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/himtech/hagibis-kabel-hdmi-to-hdmi-2-1-ultra-hd-2k-4k-8k-3d-hdr-earc-vrr-qms-allm-qft-displayhdr-tv-pc-gaming-monitor-laptop-video-audio-cable-1730928835618703202?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/de586d5ac89841249f0ded879ec5efcc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=%2BdwruyC14yBh0c%2F1rzocjQx4QHA%3D&amp;x-signature-webp=iEsCAyaOOwU7Ti0CN%2BaZIq1jC9U%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/de586d5ac89841249f0ded879ec5efcc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=MpSzVqQlhMoQStgNyC2V0Fm%2FqC4%3D&amp;x-signature-webp=c6zHBT4D759W6Picu5CUcjScAFg%3D</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\179cc0e412c24cd39a93eed9aaba2bc8.jpeg</t>
+          <t>Lib\hardware\data\images\9e9276d50ce74a91ae1232e01befaabc.jpeg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fantech-official-store/fantech-cooling-pad-rgb-nc22-notebook-cooler-with-phone-holder-adjustable-fan-speed-up-to-14kg-19-inch-laptop-gaming-1731339017679177162?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fantech-official-store/fantech-cooling-pad-rgb-nc22-notebook-cooler-with-phone-holder-adjustable-fan-speed-up-to-14kg-19-inch-laptop-gaming-1731339017679177162?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c93407def7484a1da7ab81928956adc0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=P%2BQZHrt0emZnRgMWxpU28WR9xKM%3D&amp;x-signature-webp=PCziBedujVrgA%2Bj6LJyeNCwQplc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c93407def7484a1da7ab81928956adc0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=B54zmHxqIaFrqAXz7UFPIi4GPBc%3D&amp;x-signature-webp=S3XIu%2FRyoZ4nbQE%2BwquWmi0hl9M%3D</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\565e620f10d2438babcbbf34efa8145f.jpeg</t>
+          <t>Lib\hardware\data\images\2360794bf57f40d0afeed9c13190523b.jpeg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mousepad-gaming-premium-unitech-90cm-x-40cm-x-0-3cm-alas-mouse-pad-jumbo-anti-slip-untuk-laptop-pc-1731687141802083738?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/mousepad-gaming-premium-unitech-90cm-x-40cm-x-0-3cm-alas-mouse-pad-jumbo-anti-slip-untuk-laptop-pc-1731687141802083738?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/29/eeb6fab6-76fe-412e-a3af-dd3792478a70.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=s4urvvisxUU9BxSExmwzN5tOPBI%3D&amp;x-signature-webp=HXpe342iarxGW0PuRyV%2FBoH6W8s%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/29/eeb6fab6-76fe-412e-a3af-dd3792478a70.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=Gy%2FHGejbaEO9FIEVe2Ep2dn13jI%3D&amp;x-signature-webp=Kkcc7788CwmNQYeVhF0QWKvmH2I%3D</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e938a1f1a17848ba9ae2b3568c2d0b7d.jpeg</t>
+          <t>Lib\hardware\data\images\46aa8d3a51f942c191d909ccc467cf8b.jpeg</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/blisatu/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-komputer-laptop-garansi-1-tahun-hitam-39941?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/blisatu/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-komputer-laptop-garansi-1-tahun-hitam-39941?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1163,17 +1163,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/11/f1a5e8dc-36e6-41b1-b297-0871c88cdc8d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=kFrfLyHXr2no392wpep1csDgsJM%3D&amp;x-signature-webp=NkpV4RgUkxjbpC20R689we9L5TY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/11/f1a5e8dc-36e6-41b1-b297-0871c88cdc8d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=Cf4g9IDYw0M6wmQomm0fS8RprpY%3D&amp;x-signature-webp=6VcNzA%2BubAsRtlN4EQUIufzOOuA%3D</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\70fa0538654641b5b667cbdd0d2ed830.png</t>
+          <t>Lib\hardware\data\images\dd7d5c759f99408aaab26322992aacfb.png</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/blisatu/speaker-robot-rs190-laptop-pc-gaming-soundbar-super-bass-portable-rgb?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/blisatu/speaker-robot-rs190-laptop-pc-gaming-soundbar-super-bass-portable-rgb?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/25/92ac9a5e-5d03-4584-82a7-00705b6f7bd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=sBilIHcAKAq%2Fms6X3Trdokw2oZA%3D&amp;x-signature-webp=WEvbDjHQqRI6Ci5aIR5aPo%2F0Xz0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/25/92ac9a5e-5d03-4584-82a7-00705b6f7bd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=2FCNheI%2B3ryA%2FRMIV8MJxOfl%2F5Y%3D&amp;x-signature-webp=oeIhO1576buNR3KTuVmnXGzSQCU%3D</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4d601aa56af14d3199a4a2ec9dcf515a.jpeg</t>
+          <t>Lib\hardware\data\images\d3b9ff9fe3c0490c9a13c017ab69e519.jpeg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/venusmobile/xiaomi-redmi-speaker-soundbar-komputer-bluetooth-aux-koneksi-desktop-laptop-gaming-rgb-computer?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/venusmobile/xiaomi-redmi-speaker-soundbar-komputer-bluetooth-aux-koneksi-desktop-laptop-gaming-rgb-computer?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=vEZ2e0B2Lb4RGmpg2HTYLRy1ZVE%3D&amp;x-signature-webp=3l1McMimos5HeG75QDS%2Bx8xrxCI%3D</t>
+          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=%2B3wWcGt%2BrNc9rwuGCgprOkJx52s%3D&amp;x-signature-webp=TIk99TiGyAaV5I8piann7zANgXw%3D</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\80f3819e1ecf40ca89b86c3863260328.jpeg</t>
+          <t>Lib\hardware\data\images\5dcf2bd2a3144e61b50c1658cf9167bc.jpeg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2023/11/11/c6e5f1ac-a7ee-42d3-b7f4-87e11a768173.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=1UH7wfAchV%2BWcufnIJiglHHjH7M%3D&amp;x-signature-webp=KnBtiVeChxX6GTjo6OUfgP9UZJg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2023/11/11/c6e5f1ac-a7ee-42d3-b7f4-87e11a768173.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=PHJ%2FfT80Ecaf5dLfF%2BhJr21Ktuk%3D&amp;x-signature-webp=aR8J2yMgAF70Zwe9cDdLhxt5MNg%3D</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\069d66ed3f3d4ac78bc20ae0d501090a.jpeg</t>
+          <t>Lib\hardware\data\images\671bed6b99c44fed998bdae5532927a7.jpeg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/expocomp/charger-innergie-by-delta-240w-gaming-adaptor-laptop-universal-t24?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/expocomp/charger-innergie-by-delta-240w-gaming-adaptor-laptop-universal-t24?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fa2db5fb271245a99a2a7fdaad38723b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=v3W5p8%2B0E3Hn%2FWMRKZhVDVXp%2FRY%3D&amp;x-signature-webp=4FcXFY5cIaXiltU32Fya7cEzbfs%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fa2db5fb271245a99a2a7fdaad38723b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=VwKfBULcavEN9BxQLIEmn2Eke2I%3D&amp;x-signature-webp=2yv1JVljgcn67zSjLdu3QtAL6Go%3D</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\87f629596a614ff4a71a539953cb9fb7.jpeg</t>
+          <t>Lib\hardware\data\images\014b126fbae4443e826ff06fea91a4b9.jpeg</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-kl332-kipas-pendingin-laptop-tornado-5-fan-tidak-licin-blue-1729729632344771388?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-kl332-kipas-pendingin-laptop-tornado-5-fan-tidak-licin-blue-1729729632344771388?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1420,17 +1420,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6ff3324cae5f46c3acb745a01c0de934~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=oZcHKRTneqrcMynZAFZVSCWM%2Bog%3D&amp;x-signature-webp=Xt8xnGvZry5whcRpIBNm30KD0FM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6ff3324cae5f46c3acb745a01c0de934~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=t7jqX9cmL05y%2FiA54su8JNmqwQc%3D&amp;x-signature-webp=s%2B39vyFUjRlufQFDrmXa2czJLl4%3D</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\537f16b9726447bfb213f1603c9c54df.jpeg</t>
+          <t>Lib\hardware\data\images\79ce1a6086024fcc8f184b31da40a0a0.jpeg</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokobaru-s/skyworth-monitor-gaming-24-inch-h24g30q-2k-180hz-fast-ips-panel-1440x2560-16-9-hdr10-99-srgb-untuk-laptop-1731695301096015656?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch%26whid%3D18717103</t>
+          <t>https://www.tokopedia.com/tokobaru-s/skyworth-monitor-gaming-24-inch-h24g30q-2k-180hz-fast-ips-panel-1440x2560-16-9-hdr10-99-srgb-untuk-laptop-1731695301096015656?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch%26whid%3D18717103</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1472,17 +1472,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/3/28/1a2e9b92-8bfd-42a2-b3fb-6050eb6867b5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=pmXWUgLDjf6omuA8YhM0lsrroDM%3D&amp;x-signature-webp=JnQqFPU66ABpWY7p5%2B4VLz0Ql9c%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/3/28/1a2e9b92-8bfd-42a2-b3fb-6050eb6867b5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=2qe3Qznw9VgM2pstsNVGYWpMlW8%3D&amp;x-signature-webp=qPfIVCf9FKkIx0VHq2Tdn728xCk%3D</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dff7ee6619bf49c2a23e24dd22aac499.jpeg</t>
+          <t>Lib\hardware\data\images\1ef0dca451ee4b938016b8bbafa9884d.jpeg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/liemgroup/robot-m206s-wireless-mouse-optical-1600-dpi-silent-click-gaming-pc-laptop-new-m206-m206s-merah-muda-10503?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/liemgroup/robot-m206s-wireless-mouse-optical-1600-dpi-silent-click-gaming-pc-laptop-new-m206-m206s-merah-muda-10503?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/18/9b1c74c6-ffd2-45b1-bdd3-54758efb4bcf.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=A32LcdcgFpVOAEmVVjrW%2F2Z245A%3D&amp;x-signature-webp=OoQE4ngnntVVDQb3E1E0BnMkHmg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/18/9b1c74c6-ffd2-45b1-bdd3-54758efb4bcf.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=EL1bb%2FI7k9SXJmbA2UycK9pLo6o%3D&amp;x-signature-webp=tC5YTRn5W9PThnia%2FVihmy%2Br0Qg%3D</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0bc201bacc8c46b3b8624a884eb0adff.jpeg</t>
+          <t>Lib\hardware\data\images\294ad9a7389f412db3dbc79a007118e8.jpeg</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/hagibis-indonesia-store/hagibis-8k-displayport-cable-1-4-high-refresh-rate-dp-cable-8k-60hz-4k-240hz-2k-360hz-for-gaming-monitor-graphics-card-pc-tv-laptop-1730797185172539267?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/hagibis-indonesia-store/hagibis-8k-displayport-cable-1-4-high-refresh-rate-dp-cable-8k-60hz-4k-240hz-2k-360hz-for-gaming-monitor-graphics-card-pc-tv-laptop-1730797185172539267?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/fe3c30b0c1da4d0fa9741d40670b6485~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=d2YqKtj2YLyAaYg%2Bj2B%2BrfPMhBE%3D&amp;x-signature-webp=Qbr1Lr4oPwG2IsUFdng%2FHHUcx9U%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/fe3c30b0c1da4d0fa9741d40670b6485~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=UhMdErRFLLLmd2HEMf2zX5tPJR8%3D&amp;x-signature-webp=njc5HwcRXYkGQ7ljXIzW8I5k3j4%3D</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5d679a1811884fbe8d28263c2db3474c.jpeg</t>
+          <t>Lib\hardware\data\images\6f5ee48add394e16b45772657c0ce6c0.jpeg</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/soruindonesia/soru-cooling-pad-stand-laptop-gaming-6-fan-kipas-pendingin-laptop-kipas-cooler-1729982466431355783?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/soruindonesia/soru-cooling-pad-stand-laptop-gaming-6-fan-kipas-pendingin-laptop-kipas-cooler-1729982466431355783?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1b714cec8f61478a99ddbdc25d4e5003~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=5HcdBOLJ51khBuc171GWeU05BhE%3D&amp;x-signature-webp=4ULXDPK1jiJlheKIqwKt0h0PHms%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1b714cec8f61478a99ddbdc25d4e5003~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=dL9WmtCqeT%2FP0oc01ofCXJ%2BVeHg%3D&amp;x-signature-webp=g8K85X10cG09mQ6bKcbSb8ft1NQ%3D</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\88ff07a117c14a509a6d789d8a6b782a.jpeg</t>
+          <t>Lib\hardware\data\images\f3267a81729848bb99ede049025170ca.jpeg</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/onikumaindonesia/onikuma-cw902-mouse-gaming-hitam-kabel-original-untuk-laptop-komputer-pc-dengan-6400-dpi-tombol-rgb-dan-sensor-optik-tingkat-definisi-tinggi-button-1730338257921934858?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/onikumaindonesia/onikuma-cw902-mouse-gaming-hitam-kabel-original-untuk-laptop-komputer-pc-dengan-6400-dpi-tombol-rgb-dan-sensor-optik-tingkat-definisi-tinggi-button-1730338257921934858?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/13/31a814f6-f0bb-4d89-b3d4-0dafe63f22d7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=PhuBWczb3vKLSYP96atH1xC4XzA%3D&amp;x-signature-webp=DjQGjZ8BZjiTpVbEg8swqBLA2%2FA%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/13/31a814f6-f0bb-4d89-b3d4-0dafe63f22d7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=tgDsvsAlfiGgop3Hlh36oLXF8UY%3D&amp;x-signature-webp=uodSrwr1MK8WHPd6%2FqyHCerLyNg%3D</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6aba8171719a4cf6b22c4da92f64984b.jpeg</t>
+          <t>Lib\hardware\data\images\694bf2eaf1364d9aa6a7ec46e115cb13.jpeg</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lenovo-authorized-surabaya/charger-innergie-by-delta-180w-gaming-adaptor-laptop-universal-t18?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch%26whid%3D11569999</t>
+          <t>https://www.tokopedia.com/lenovo-authorized-surabaya/charger-innergie-by-delta-180w-gaming-adaptor-laptop-universal-t18?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch%26whid%3D11569999</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/70a5e998-ee7d-48c8-b0f6-c652f9a12d32.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=g%2FUfTr5cKD1rxmq71Y%2F%2F3IR%2FQZc%3D&amp;x-signature-webp=Fzo8qxr0PyozlHar5GexdsunWr8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/70a5e998-ee7d-48c8-b0f6-c652f9a12d32.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=7Hx0H2FacgX07OsbiG34XsOBgj8%3D&amp;x-signature-webp=mhu8rCxXZiuCvRlxTlnpRa3NmSc%3D</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5ea405343da14d548bd94ac9616392c8.jpeg</t>
+          <t>Lib\hardware\data\images\cfedc86df8524e4b8c89dd3d6559ef68.jpeg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-innergie-gaming-universal-original-180w-150w-130w-65w-45w-1731234857708193451?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-innergie-gaming-universal-original-180w-150w-130w-65w-45w-1731234857708193451?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/15/373a1aa1-4150-4341-9439-debc881a4fd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=M4TPgQLv3CfTRg8D1KFmBOrHqSw%3D&amp;x-signature-webp=6DMUigapvmEUV%2Fxi45H2mcbkv2k%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/15/373a1aa1-4150-4341-9439-debc881a4fd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=RTFqOXpFqWopjNYC%2FxVIa8schsk%3D&amp;x-signature-webp=LNFr17yRRveV0JwJtTka3u4ZbhI%3D</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\295d30c9aca74245a6788e3afc185395.jpeg</t>
+          <t>Lib\hardware\data\images\0bec53b121bf4d57a5769fd6c041ed9e.jpeg</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-gaming-mechanical-87-keys-wired-keyboard-layout-rgb-light-universal-pc-laptop-1730787426880030393?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-gaming-mechanical-87-keys-wired-keyboard-layout-rgb-light-universal-pc-laptop-1730787426880030393?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5d662cb1-9633-4475-9bb5-82f645202a74.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=Fo74HylM2bAgLvYuZ7VkE%2BeDWzI%3D&amp;x-signature-webp=DOx7XqKIEAE5%2FcE2wipwX2JstVA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5d662cb1-9633-4475-9bb5-82f645202a74.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=gaZxobF5wlOWphu48tsb91Xa7g0%3D&amp;x-signature-webp=JFJEcosl%2BmvPyfIy63Sk0khcqzM%3D</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\536ed4f57c6441eca0e6fb3145b666d7.jpeg</t>
+          <t>Lib\hardware\data\images\17bf02753b764fceaa9b49b21fd423dc.jpeg</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adapter-innergie-charger-laptop-gaming-acer-asus-dell-hp-lenovo-280w-200w-1731234851512288939?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adapter-innergie-charger-laptop-gaming-acer-asus-dell-hp-lenovo-280w-200w-1731234851512288939?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/20/b4aa025b-29e1-44b1-b8e7-776a2899eef3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=xUoHx0eZ110eBOz8EiSgAMD70zI%3D&amp;x-signature-webp=Rm8J5bFp6Lh%2BIS8y7PiBV%2Fcz32w%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/20/b4aa025b-29e1-44b1-b8e7-776a2899eef3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=d1pq2em91zoUq2lxCTp7KQJAjnc%3D&amp;x-signature-webp=gsWOcdDvxPzMsRKagNX18gYOVW4%3D</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\72eb1f6553ad4d53b809c798b47a312d.png</t>
+          <t>Lib\hardware\data\images\6ffea2b9d91547ae92846ceb22097af4.png</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-wireless-mouse-mechanical-gaming-bluetooth-5-0-dual-mode-silent-click-type-c-fast-charging-screen-display-3200dpi-untuk-pc-laptop-1730803778625832633?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-wireless-mouse-mechanical-gaming-bluetooth-5-0-dual-mode-silent-click-type-c-fast-charging-screen-display-3200dpi-untuk-pc-laptop-1730803778625832633?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5087391e11d74a6cbbd2950bf01e6539~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=o7RLDNVKcMJYXVflGMptyaRJ3N4%3D&amp;x-signature-webp=PsrjNGcOjniC514cmnURVFTC7OQ%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5087391e11d74a6cbbd2950bf01e6539~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=GsbqrZXCY4BHyzXMnao4oiJRU7w%3D&amp;x-signature-webp=nfEFXwmuI8QZLdjgqmEcaN10qiM%3D</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ccc2a8eea00a498abedf84405e25d407.jpeg</t>
+          <t>Lib\hardware\data\images\dafc85c3ee9c429787dcaf308a1c88f3.jpeg</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-pendingin-laptop-2-kipas-kl330-fan-1729636686228589372?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-coolerpad-laptop-gaming-pendingin-laptop-2-kipas-kl330-fan-1729636686228589372?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/1/26/4f9883a0-3d3f-4986-97f3-3f5751f7165c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=YHMa5VAvilhI%2FpBQMm0et%2BR76nc%3D&amp;x-signature-webp=crKwJOWuVP5T%2BF8SZl%2BweIEh8RA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/1/26/4f9883a0-3d3f-4986-97f3-3f5751f7165c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=HStfGaO97T9%2BLlCg3DVi1VYa7FI%3D&amp;x-signature-webp=bOB2ql%2BflN12YZ0OUcM67z472%2BI%3D</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\034f759729d147548ef8a3354a6e4c8c.jpeg</t>
+          <t>Lib\hardware\data\images\97ebf047de084761afd2f305c3882dd8.jpeg</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/d-m-i/nyk-x1-wind-coaster-gaming-cooling-pad-laptop-with-3-fan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/d-m-i/nyk-x1-wind-coaster-gaming-cooling-pad-laptop-with-3-fan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/3/23/a52ecf75-8473-45e9-a91d-36c8da636f5e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=9f%2FjxdHuT1IHj6gCyEqdeEgxU0o%3D&amp;x-signature-webp=fnJeSjxOsofvRnS9DSFKP6homfk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/3/23/a52ecf75-8473-45e9-a91d-36c8da636f5e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=%2F0qxwLQQwERnoGUGvJFxZxQgn%2Fo%3D&amp;x-signature-webp=iizLdj80eShFmvzJ5CV486Rrcbk%3D</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f2f35314afa14a91b77d770d23766fbf.png</t>
+          <t>Lib\hardware\data\images\601bbd0edd594ecfa7939177d1a868dc.png</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/andalassuryagemilang/fan-laptop-cooling-pad-notebook-gaming-nyk-x3-winterstorm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/andalassuryagemilang/fan-laptop-cooling-pad-notebook-gaming-nyk-x3-winterstorm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6b4457908324a2788e9a7da6815e258~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=C4oDT7t9SQ1wQCYp0KMrS73VIkQ%3D&amp;x-signature-webp=Yr21wKU%2FIgNCQQbsb0zl5d8OBa8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6b4457908324a2788e9a7da6815e258~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=bH0mKt1gixVOzp3befGMMPXsdAs%3D&amp;x-signature-webp=L1CfVpolL5KpD4Le%2Fa1HNyC%2FrWw%3D</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c84f8c54d09844df960055c64695ee1e.jpeg</t>
+          <t>Lib\hardware\data\images\6af1ce336771475cb4f275e7e5d0f0b1.jpeg</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/mouse-gaming-kabel-unitech-s1-colorfull-rgb-light-3200-dpi-untuk-komputer-pc-laptop-1729643499823991194?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/mouse-gaming-kabel-unitech-s1-colorfull-rgb-light-3200-dpi-untuk-komputer-pc-laptop-1729643499823991194?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/25/98ce42ec-a8a6-4112-9380-10eadb2994f5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=bqbWOUj3v60L9jnNWv1WgGSh64w%3D&amp;x-signature-webp=YHHboNBdTing9Yc0y6fiACsn24o%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/25/98ce42ec-a8a6-4112-9380-10eadb2994f5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=TGUSqsvUPx7Z6Cp%2BxxMN01pfEOo%3D&amp;x-signature-webp=Sh7TQviOt%2BlaaOI6jxJ8uJ%2BIhRQ%3D</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3b44a32928154f558994f4d7fe1084d3.png</t>
+          <t>Lib\hardware\data\images\edbf95a3181a40edaeb444ebab22e2b0.png</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-gaming-kabel-usb-wired-rgb-light-optical-1200-1600dpi-ergonomic-untuk-pc-laptop-dengan-2-speed-dpi-adjustable-dan-tombol-6d-black-1731239865956402840?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-gaming-kabel-usb-wired-rgb-light-optical-1200-1600dpi-ergonomic-untuk-pc-laptop-dengan-2-speed-dpi-adjustable-dan-tombol-6d-black-1731239865956402840?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5c94cc2b-9899-4e95-ae52-c5f60a45630c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=T4XFhWr8tiSmydJvuTr6C34eYhw%3D&amp;x-signature-webp=u3K06YLeO4qxd0%2FkmZ5jv1Z6e%2BM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/28/5c94cc2b-9899-4e95-ae52-c5f60a45630c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=m%2Bu%2BXuSXEGmdEyBC%2Fx%2FjV%2F19Vzw%3D&amp;x-signature-webp=aXLwnpFwthvg1QLlt2iYmCglN48%3D</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5c37a62eec5c497bb26b065ee5795860.jpeg</t>
+          <t>Lib\hardware\data\images\9a36f5cd21504f54a0088952ee6869ec.jpeg</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-gaming-universal-innergie-240w-230w-200w-20v-12a-t24-1731234878706910891?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lindy-official/power-adaptor-charger-laptop-gaming-universal-innergie-240w-230w-200w-20v-12a-t24-1731234878706910891?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0c39492bae8949e79deb61008e4da18c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=%2BlR5dP3WN8iPlfc%2Fw7OlRrw8zg8%3D&amp;x-signature-webp=Y45bVDk7lSwdZ2%2FZK0%2Fx5r%2BZPMQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0c39492bae8949e79deb61008e4da18c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=hCfrinK1S%2FVrpxEJ36iyVqdNpn0%3D&amp;x-signature-webp=2STN6SWLebgNFJciC%2FC%2FVEQ2s78%3D</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\da05714d56364d57915fca0d5d3c6118.jpeg</t>
+          <t>Lib\hardware\data\images\a717a77991d0482fb4376383147776f6.jpeg</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bikepremiumstore/headset-headphone-gaming-power-full-bass-hs04su-mic-earphone-komputer-laptop-pc-3-5mm?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bikepremiumstore/headset-headphone-gaming-power-full-bass-hs04su-mic-earphone-komputer-laptop-pc-3-5mm?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2258,48 +2258,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>11689876861</v>
+        <v>102118726768</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CABLETIME Mouse Pad Aluminium Metal Premium Gaming Dekstop Laptop DeskMat Smooth</t>
+          <t>Nemesis Coolingpad Gaming Turbo Air Compressed Up To 21 Inch Laptop BEIRUZ AX3 COOLING PAD RGB</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>136900</v>
+        <v>539000</v>
       </c>
       <c r="D37" t="n">
-        <v>150250</v>
+        <v>700000</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CABLETIME Jakarta</t>
+          <t>Best Elektronik IT</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Jakarta Barat</t>
+          <t>Jakarta Pusat</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e190eea8efac4e969fd89e79beb0140f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=mzl%2BNhEQZmcZzsMEPMgTTXTOYt4%3D&amp;x-signature-webp=dW%2FeoL3%2BOPF2LLTSI16FwKmBdSQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6e153097f95486d892d9338928ef0fa~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=4jQIZ0q53XJaACPGgW3802qwcCA%3D&amp;x-signature-webp=CNgRdpLhLIvrWJXl6MbQP%2B588Ec%3D</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\05e555b5e87f49c1a39645880d2d5a86.jpeg</t>
+          <t>Lib\hardware\data\images\aef6b67ff0ca4267b0801ff90f986ee9.jpeg</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/allitems-id/cabletime-mouse-pad-aluminium-metal-premium-gaming-dekstop-laptop-deskmat-smooth-1731201382108268433?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bestit/nemesis-coolingpad-gaming-turbo-air-compressed-up-to-21-inch-laptop-beiruz-ax3-cooling-pad-rgb-1732247682542044373?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2310,48 +2310,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>102118726768</v>
+        <v>11689876861</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nemesis Coolingpad Gaming Turbo Air Compressed Up To 21 Inch Laptop BEIRUZ AX3 COOLING PAD RGB</t>
+          <t>CABLETIME Mouse Pad Aluminium Metal Premium Gaming Dekstop Laptop DeskMat Smooth</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>539000</v>
+        <v>136900</v>
       </c>
       <c r="D38" t="n">
-        <v>700000</v>
+        <v>150250</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Best Elektronik IT</t>
+          <t>CABLETIME Jakarta</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jakarta Pusat</t>
+          <t>Jakarta Barat</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a6e153097f95486d892d9338928ef0fa~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=OTeD7aRj2N%2FF2gmDwaFERdGWgW0%3D&amp;x-signature-webp=1mgoy%2BtBUADSukFVkv3veP%2BmNQo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e190eea8efac4e969fd89e79beb0140f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=nrT0ET4GIgXFyNGoaTcK2bvuMCU%3D&amp;x-signature-webp=dqgPs9brd0pMAANQ%2Bw3bVNUWs6Y%3D</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\545f752fbb2848098fa70bf38c9d608a.jpeg</t>
+          <t>Lib\hardware\data\images\3c285f3073d4485e8e6bb15d0b654df7.jpeg</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bestit/nemesis-coolingpad-gaming-turbo-air-compressed-up-to-21-inch-laptop-beiruz-ax3-cooling-pad-rgb-1732247682542044373?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/allitems-id/cabletime-mouse-pad-aluminium-metal-premium-gaming-dekstop-laptop-deskmat-smooth-1731201382108268433?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3b54f1bf88024c7482a8a32e8c98eaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=8Ebv90KMWInXQxq%2BThRoDW%2FYL4M%3D&amp;x-signature-webp=WOGPcEQf7jL%2FVnYT2vDqACXi9lA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3b54f1bf88024c7482a8a32e8c98eaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=PyujEUvUjEBUDi0s1PIOoBfbzrE%3D&amp;x-signature-webp=7ayx09Ms%2Bj2xuq%2FtohqLCYDnhds%3D</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d124fccd864848c490d757da7ebb11dc.jpeg</t>
+          <t>Lib\hardware\data\images\59d85dcb815b453b91135b2162a64fa0.jpeg</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/bikepremiumstore/headset-gaming-headphone-mic-power-full-bass-hs-04su-earphone-komputer-laptop-pc-3-5mm-mobile-live-streaming?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/bikepremiumstore/headset-gaming-headphone-mic-power-full-bass-hs-04su-earphone-komputer-laptop-pc-3-5mm-mobile-live-streaming?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/9/22/73b26064-75be-46de-b155-5535d7d164c0.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=uxEIrqyFZn7N2Ml6VkqchJgHQgo%3D&amp;x-signature-webp=qC0FtKKVgredUCHUIfuqz6Z%2FVEQ%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/9/22/73b26064-75be-46de-b155-5535d7d164c0.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=Ysg%2Fgyi3Z2H9ECkKCrQ1WuCvNrg%3D&amp;x-signature-webp=E2HkjWET9tNdhiqmn0X56E65MRI%3D</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ece31b38eb0a4090a4c5e02af7f2bcdc.jpeg</t>
+          <t>Lib\hardware\data\images\93b95621439b4445a877d4a32cd346ac.jpeg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-laptop-cooler-gaming-cooling-pad-fan-cooler-turbo-silent-srq-019-32d50?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-laptop-cooler-gaming-cooling-pad-fan-cooler-turbo-silent-srq-019-32d50?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9863a40e2c6f4645a11e10bb72c0701c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=oN0tA%2Fbhhh3NM3sgKwvQxmrc70Q%3D&amp;x-signature-webp=CfllMyOgS6FZT%2FZHZQ5O18a%2B1Ls%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9863a40e2c6f4645a11e10bb72c0701c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=2lvQ3BAYGPD3iuL1vUq0NAucL2E%3D&amp;x-signature-webp=KqynzoQk6zHk8j4gRMY%2BuPnh3jM%3D</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\07d29e40b1454073a830d8dd1ab2f291.jpeg</t>
+          <t>Lib\hardware\data\images\91a0e975f8834a059274459c9a347d0b.jpeg</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tasairbone/tas-ransel-laptop-gaming-polofelix-anti-air-waterproof-soft-case-pelindung-laptop-macbook-size-besar-1731153071094466207?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tasairbone/tas-ransel-laptop-gaming-polofelix-anti-air-waterproof-soft-case-pelindung-laptop-macbook-size-besar-1731153071094466207?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2540,17 +2540,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/22/99a529bd-4693-440e-90e1-cf2b813f8692.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=w3uz%2BGWul6vkZ45vPRT1UVYCrMU%3D&amp;x-signature-webp=Tq0kJdxSLZlHgAxFE%2FXEvk0yM%2BA%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/22/99a529bd-4693-440e-90e1-cf2b813f8692.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=JTYC6Ij4gO%2Fex0eE4i80r9SOJAk%3D&amp;x-signature-webp=20uzuNS2MsHvVaMP%2B95hcNK7kmQ%3D</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7190c65e8bf540768b771a655793800d.jpeg</t>
+          <t>Lib\hardware\data\images\b81d88f289cb44329d5f79bf3ef14ad9.jpeg</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/d-m-i/deepcool-n80-rgb-gaming-cooling-pad-for-laptop-cooler?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/d-m-i/deepcool-n80-rgb-gaming-cooling-pad-for-laptop-cooler?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/6/23/42a98edc-3f69-43a5-acb7-82cd258ba31a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=a%2Fn5mmmjT%2BT%2F1Ow0mnkzgUqmHXs%3D&amp;x-signature-webp=2wKTra7cSldnV6SeuvKwQQIRLSE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/6/23/42a98edc-3f69-43a5-acb7-82cd258ba31a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=Ggd1GU4flIqfxNI8xi1y76Qj4Pk%3D&amp;x-signature-webp=sqYVjrsGIQLIrfuMl9Ohapj1Wt0%3D</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\93c16c7abe9b41b5aeb5da18193140bb.jpeg</t>
+          <t>Lib\hardware\data\images\153ec53f34ea4a2e90782c2b20c14b33.jpeg</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/affselv-now/affselv-cooler-laptop-cooling-pad-5-fan-17-inch-adjustable-speed-2600-rpm-kipas-pendingin-laptop-gaming-dengan-6-level-kecepatan-dan-4-level-ketinggian-untuk-laptop-hingga-15-6-inch-1733156196976723940?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/affselv-now/affselv-cooler-laptop-cooling-pad-5-fan-17-inch-adjustable-speed-2600-rpm-kipas-pendingin-laptop-gaming-dengan-6-level-kecepatan-dan-4-level-ketinggian-untuk-laptop-hingga-15-6-inch-1733156196976723940?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2641,17 +2641,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4c66596fc2ce4ad29797c2e977512d7f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=s8ekOpkBcm8VC7E0RCDg8NNWjIY%3D&amp;x-signature-webp=eru%2FcpTrqLFNbJzFdzct%2BQ%2B%2FMz0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4c66596fc2ce4ad29797c2e977512d7f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=PAnOqCczR60UzqSuRWcByVc9H9Q%3D&amp;x-signature-webp=GiNN329KVdI2%2FzBkygx4sV%2F%2FCpw%3D</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7a7a17039a46425fb9d422d6a6f85f2a.jpeg</t>
+          <t>Lib\hardware\data\images\7b6ef8e5139842859bb589edce621c61.jpeg</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olike-official/new-product-olike-desktop-speaker-sc07-6w-subwoofer-rgb-light-gaming-full-bass-360-surround-sound-portable-wired-connection-for-laptop-pc-1733184933872698864?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olike-official/new-product-olike-desktop-speaker-sc07-6w-subwoofer-rgb-light-gaming-full-bass-360-surround-sound-portable-wired-connection-for-laptop-pc-1733184933872698864?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/10/11/7d1054d5-ebac-4558-a9f0-204c541144bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=OOqEpPl535QukP9%2BD3%2BSr%2FV3kBo%3D&amp;x-signature-webp=DS6UFJ6QohnHB%2BpC%2BBDZpnsmVyM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/10/11/7d1054d5-ebac-4558-a9f0-204c541144bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=vhSqVagj%2BudeZS6uuWbnJYLoLXE%3D&amp;x-signature-webp=y0M8wpSgBbrtjVaA099z2AcRLoU%3D</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\63811243d1614271a5c47709c18ed252.png</t>
+          <t>Lib\hardware\data\images\5dc867e0d93646c6a27bb23c4245905c.png</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fashionselular/headset-gaming-led-onesos-sy830-headphone-bass-with-mic-hp-pc-laptop-led-blue?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fashionselular/headset-gaming-led-onesos-sy830-headphone-bass-with-mic-hp-pc-laptop-led-blue?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2739,17 +2739,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/152cf82999ae4c61845620b1616abb22~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=Ye4YeYv4SZZDclJpNlbhpdK2VcA%3D&amp;x-signature-webp=UqMkVGb%2Fxv2zCfC7yh%2BApOCyXTE%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/152cf82999ae4c61845620b1616abb22~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=EX5Lbz%2BD0uGrjk5109yh8Q%2F5G1w%3D&amp;x-signature-webp=HOFTrs6XYyQydVfaZ%2BKIP3q5N60%3D</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\20dd576e75434f879af87bffaa34a249.jpeg</t>
+          <t>Lib\hardware\data\images\011c3ba336e44cceb71c87faf9471f94.jpeg</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dell-premium-official/dell-backpack-alienware-vindicator-17-3inch-armored-tas-gaming-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dell-premium-official/dell-backpack-alienware-vindicator-17-3inch-armored-tas-gaming-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/d1ef1c4a86a7447988bcbdce4d35fa2b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=MIvZribycsz3ETRDvuiCyQT%2FrOA%3D&amp;x-signature-webp=KZjpFsVHKKYsNmy9XdwFVE0K8%2BA%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/d1ef1c4a86a7447988bcbdce4d35fa2b~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=gBx2hiKwctR6oQTRnfbeBa6RJnU%3D&amp;x-signature-webp=4Y%2B6GcvpX0Jk5GymNV2Y0Xh1duU%3D</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\932ab6face0c4a5784782bfc0f9d6db6.jpeg</t>
+          <t>Lib\hardware\data\images\16ff7bc873fe4adda7e41e9fd1a45b55.jpeg</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/jertech-keyboard-gaming-k358-led-rgb-bachlight-support-all-komputer-laptop-hitam-7a474?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/jertech-keyboard-gaming-k358-led-rgb-bachlight-support-all-komputer-laptop-hitam-7a474?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/f9a4449e-bfff-4df1-b18f-c1e2af70c4b4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=rHrJwDuVxmRHrSljn0F7o3YM8W4%3D&amp;x-signature-webp=vOw90N7ZZuVhvbcEal2JvRyOeaM%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/f9a4449e-bfff-4df1-b18f-c1e2af70c4b4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=2TENbFRl5ee5XiqYDUyzcQFnN0c%3D&amp;x-signature-webp=XqYwtuLvqrJHl3KjT%2F9Y0x1F0to%3D</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ef1f848a7fe24ce0966dd3edf90c0e55.png</t>
+          <t>Lib\hardware\data\images\b071cd5c2f4d4b0aafd0343afc618436.png</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/promodazzle/terlaris-ugreen-headset-kabel-mfi-iphone-android-type-c-lightning-3-5mm-original-100-garansi-resmi-24-bulan-official-store-mall-ori-murah-termurah-terbaik-tablet-samsung-xiaomi-macbook-laptop-pc-typec-earphone-handsfree-super-extra-full-bass-gaming-typec-60700-a7403?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/promodazzle/terlaris-ugreen-headset-kabel-mfi-iphone-android-type-c-lightning-3-5mm-original-100-garansi-resmi-24-bulan-official-store-mall-ori-murah-termurah-terbaik-tablet-samsung-xiaomi-macbook-laptop-pc-typec-earphone-handsfree-super-extra-full-bass-gaming-typec-60700-a7403?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2895,17 +2895,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/16/59db287d-8254-4933-b80e-ef38ff1ddbb7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=csBTWl7VA5ADDHoAPJYXN2pdLAE%3D&amp;x-signature-webp=mC15C8Zj8qjPMAFD7qqaKsqja2k%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/16/59db287d-8254-4933-b80e-ef38ff1ddbb7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=TUuKGiQDrDM0lRim3moAdQjTYl0%3D&amp;x-signature-webp=OBx6LcklBBYgczinmLrLw%2FwsQ1Q%3D</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\51c3ba26b94d417799faaf8180a48752.jpeg</t>
+          <t>Lib\hardware\data\images\b5e879b11dd544af94eb67cb9e1f2190.jpeg</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-pc-komputer-laptop-garansi-1-tahun-bisa-cod-1731162798337328677?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-speaker-komputer-rs260-deep-bass-35mm-audio-usb-jack-portable-music-mini-for-gaming-pc-komputer-laptop-garansi-1-tahun-bisa-cod-1731162798337328677?extParam=ivf%3Dtrue%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/3/16/62a45061-18e3-48fb-ba3f-42dd8d84b589.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=gitvOgUBw8RDOhosAqvELQ770X8%3D&amp;x-signature-webp=F71Ny2vxmyi6DFCCG%2BM7ze20boE%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/3/16/62a45061-18e3-48fb-ba3f-42dd8d84b589.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=Mv1RmZEl%2BqJE1vwD34QSCt9%2FxQs%3D&amp;x-signature-webp=0FBu1Ci4RyZwNyvfzjwthBUWBd0%3D</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2fb0adca4638463eb7edebc2e704ffb8.png</t>
+          <t>Lib\hardware\data\images\f52a48df56b343e5b65d9db3e73b2f81.png</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/donatur/robot-rs200-speaker-e-sports-gaming-for-pc-laptop-smartphone-ori?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/donatur/robot-rs200-speaker-e-sports-gaming-for-pc-laptop-smartphone-ori?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -2996,17 +2996,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/6/9/09ab3d23-47ae-4005-ab4a-cfbc36d7fa4d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047459&amp;x-signature=xU0Wn6GWXmULTAbsCRfz%2FSjrBLQ%3D&amp;x-signature-webp=5Gd1ItNet7vrxYjXcGTQqQeH%2BG0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/6/9/09ab3d23-47ae-4005-ab4a-cfbc36d7fa4d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047754&amp;x-signature=FpOc%2Fju3gKpqYp8JpypAEmefZD0%3D&amp;x-signature-webp=jMppyzMQnfwrpvjJyuHOSL3PFas%3D</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\36fefe33ac20443fa034fd1649ce0d71.png</t>
+          <t>Lib\hardware\data\images\b59d83f43d2f44c9ae7398a61d58fcf1.png</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supermallori/supermall-mouse-pad-gaming-mousepad-alas-laptop-xl-900-x-400mm-blue-dora?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504105958238E9AE2DD3013E3E5%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supermallori/supermall-mouse-pad-gaming-mousepad-alas-laptop-xl-900-x-400mm-blue-dora?extParam=ivf%3Dfalse%26keyword%3Dlaptop+gaming%26search_id%3D2025112504155411B9842E0A271F15BT3K%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3048,17 +3048,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9060d5fb44cf4b2faa8e9864b1542c37~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=%2FpzVsjUfUO1vyqF2sY%2BVwReac8I%3D&amp;x-signature-webp=BmLNfASbDcrobYOkamvyw0%2FxURU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9060d5fb44cf4b2faa8e9864b1542c37~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=ffpJJOLduPS2PC4ETQeDqs6olHw%3D&amp;x-signature-webp=oPsWYoC3bwvmHRtWUOHbRGWLlvY%3D</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\46ab812d2906416d9988f3cdb2ea4175.jpeg</t>
+          <t>Lib\hardware\data\images\7b0a5b97de8f4a8585f4f4f43ee81c83.jpeg</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocofficialstore/tomtoc-t60-explorer-laptop-backpack-office-bag-size-22l-1732719801450137078?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocofficialstore/tomtoc-t60-explorer-laptop-backpack-office-bag-size-22l-1732719801450137078?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3097,17 +3097,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/11/28/265f544d-72eb-43c7-8a97-1756f4f7fcb6.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=tR19gY4jFPDA2j5wzg%2B8HcSxir0%3D&amp;x-signature-webp=3i%2FksXG4G8SjK4ftomO8k6HZ%2BEI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/11/28/265f544d-72eb-43c7-8a97-1756f4f7fcb6.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=iGH8AqSghw5ETRKLGVpywV%2BW3R4%3D&amp;x-signature-webp=8GMlqHb7i8W2vJ%2F7ltZLa77Cf2Y%3D</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dadc8d201f264a5faa6a624f0a9f98be.jpeg</t>
+          <t>Lib\hardware\data\images\3fc1327fc0ba4ff8b9020654cc9e1f57.jpeg</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/starcompsolo/mikuso-kb-052u-wired-usb-keyboard-104-key-pc-laptop-office-ergonomic-hitam-6ac76?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D16130095</t>
+          <t>https://www.tokopedia.com/starcompsolo/mikuso-kb-052u-wired-usb-keyboard-104-key-pc-laptop-office-ergonomic-hitam-6ac76?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch%26whid%3D16130095</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3149,17 +3149,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/26f44dfba5404212ad862b746e42857a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=U7PLK5zlnwq6xRWVPU2Jljk%2BMgI%3D&amp;x-signature-webp=2nF4vhnUNGEEhgRthTgIz7F7t6Q%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/26f44dfba5404212ad862b746e42857a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=JQcYYz%2B7c%2FUwXoQ03roUB9b2gpk%3D&amp;x-signature-webp=%2FsKb97c5La1tb2uejfSu5c7r2Hc%3D</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8d4c26997dd9452bba90ca0fe0abbcdd.jpeg</t>
+          <t>Lib\hardware\data\images\6d2e823b152c41099f1da5919fd40e63.jpeg</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitechone-keyboard-mouse-combo-set-office-master-keyboard-mouse-for-pc-laptop-gadget?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitechone-keyboard-mouse-combo-set-office-master-keyboard-mouse-for-pc-laptop-gadget?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3201,17 +3201,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e59a9d3733e44c89e422d639b080b4b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=aMaJk5Di%2FUFuCt%2FDD8ftMwVn2dg%3D&amp;x-signature-webp=VbWC77XBiP6b8J45frQehTurzjA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e59a9d3733e44c89e422d639b080b4b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=XgSjYxXrHevAgAQYMdTwAn1iT4s%3D&amp;x-signature-webp=1WyC9QLuEG8p9dAoatqL0u%2FCPiI%3D</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\98b4ef638aaf410db0e4f38d55403992.jpeg</t>
+          <t>Lib\hardware\data\images\7515c34184724dad8e0e9b349e2e248d.jpeg</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/gameridsurabaya/laptop-lenovo-legion-5-15-intel-core-i7-13650hx-rtx-5050-8-gb-ram-16-gb-ssd-512-gb-windows-11-office-home-student-15-3-wuxga-165hz-100srgb-1732195924137248723?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/gameridsurabaya/laptop-lenovo-legion-5-15-intel-core-i7-13650hx-rtx-5050-8-gb-ram-16-gb-ssd-512-gb-windows-11-office-home-student-15-3-wuxga-165hz-100srgb-1732195924137248723?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/9/4/92698dcd-813c-417b-a377-062feb24f1da.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=Z2jrVurAxZUmvseyS%2BOKwL0g%2FRM%3D&amp;x-signature-webp=uNSdlvEWdH27x9WlABUkD76ls1o%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/9/4/92698dcd-813c-417b-a377-062feb24f1da.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=AgiRQDrLIiXpRWW5Q2wr6h0hWRs%3D&amp;x-signature-webp=KP8Fgoym3G8kOpD2%2F7SD2Mj7rLA%3D</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bbb6f5b8fb9d42e7aeeed7e7c925a5e4.png</t>
+          <t>Lib\hardware\data\images\1dc8c59f5d9a4480a2f1834b8e59a348.png</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-gradaz-office-bundle-tas-ransel-kerja-backpack-laptop-tas-selempang-ipad-organizer-charger-pouch-multifungsi-only-bag-black-0e00a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-gradaz-office-bundle-tas-ransel-kerja-backpack-laptop-tas-selempang-ipad-organizer-charger-pouch-multifungsi-only-bag-black-0e00a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3302,17 +3302,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=l9LtwZxrJ977TmmHMi2mJ7eoxak%3D&amp;x-signature-webp=XcYJp%2BQuqwJsH6eeMCHo2eQwxnY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=IXglrRh4uw6U7SorUbe9Lk8mbn8%3D&amp;x-signature-webp=neODR%2FrBSZg%2F13iHkfE6TxB99nk%3D</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\361e1294a9444d6dab438142cae298d9.png</t>
+          <t>Lib\hardware\data\images\67dfd130ae3e42b4bb5d56b59915f71d.png</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/13/c3ad5491-fc3d-4b80-b80a-59b49374ce68.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=3TQb38fYktkyr5kNBBLnrQlAI3I%3D&amp;x-signature-webp=mFzvuWgCXHS0Biuy%2FVL%2F7QBidrI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/13/c3ad5491-fc3d-4b80-b80a-59b49374ce68.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=q7DeEceTMrUu67KefSArFoW3Wo8%3D&amp;x-signature-webp=Ozf%2FVljuJbzv%2BncBe5kVanI%2FWPw%3D</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dac2eb935e7641afa603868b679d54d6.jpeg</t>
+          <t>Lib\hardware\data\images\45e073df61014e359e42cb2e1d1e5b11.jpeg</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/backpack-tas-ransel-office-punggung-sekolah-kuliah-kerja-laptop-15-inch-torch-loka-1730777953781646394?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/backpack-tas-ransel-office-punggung-sekolah-kuliah-kerja-laptop-15-inch-torch-loka-1730777953781646394?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/15/a0091498-b7ce-4323-9e2d-682fd5afcdde.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=L4PccphTQwRBOt9mcD8UGPi5lBI%3D&amp;x-signature-webp=TnM9y0XfNrJR57zfJOz9MTnbMJc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/15/a0091498-b7ce-4323-9e2d-682fd5afcdde.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=LNIoln9LVHux6%2BZn81O8R%2BDJ%2Bj8%3D&amp;x-signature-webp=Tja90tADzKBOMi%2FSo5Bj0ndVEAM%3D</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\92a23b2983624d0697078896416a5581.png</t>
+          <t>Lib\hardware\data\images\8d4a24491bf14b9abbe3562564a44288.png</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-office-collection-tas-ransel-kerja-kantor-laptop-stylish-pria-wanita-hongcheon-black-eaee2?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-office-collection-tas-ransel-kerja-kantor-laptop-stylish-pria-wanita-hongcheon-black-eaee2?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3458,17 +3458,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/45db327a9c23430aa3e9f3da70e0d1af~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=ufQRnDUahqJozI%2FonX7WkzcNmaU%3D&amp;x-signature-webp=eSQgFSFX01rz3a8fgi8LpDExzkA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/45db327a9c23430aa3e9f3da70e0d1af~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=FNRcL1PSnUd1FQFAeoqaUTJyS08%3D&amp;x-signature-webp=MyMkWALFXj8MfLUAxzkNNM4lcjA%3D</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ba49b6282d1c42dabd2b9c2c093a29ca.jpeg</t>
+          <t>Lib\hardware\data\images\22539decb52d46b8a9925d85cf783da4.jpeg</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-g6-untuk-komputer-laptop-pc-1000-dpi-mouse-office-computer-1729590282578069914?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-g6-untuk-komputer-laptop-pc-1000-dpi-mouse-office-computer-1729590282578069914?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3510,17 +3510,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f1f4aa17bf5c43cc9eea095c93d0bf11~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=5GP6N1kUKxzj%2BAuEm3DQjf9yTPA%3D&amp;x-signature-webp=M7SMZQ0fk584eWeMdY26Zr7VWgw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f1f4aa17bf5c43cc9eea095c93d0bf11~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=K4V1dPWvghIy%2FKjgCOi9US%2BEB3E%3D&amp;x-signature-webp=nmHoT%2BykJfYSjFmVVqp5dEK86io%3D</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f6e14ae1b5d3448ba5f0f4cdf4b340b7.jpeg</t>
+          <t>Lib\hardware\data\images\9e3d80d02ac74d16b4938890f32f6440.jpeg</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/optical-mouse-office-kabel-usb-unitech-g5-1000-dpi-untuk-laptop-pc-computer-1729588341583546778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/optical-mouse-office-kabel-usb-unitech-g5-1000-dpi-untuk-laptop-pc-computer-1729588341583546778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3559,17 +3559,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3baef23e7214219af4e67c58e42992c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=g%2BKZ%2B%2BBTqf0ice9cyh%2F972rA9eE%3D&amp;x-signature-webp=J4AM%2BakMIgSml%2BWSFJcAJUGmlJQ%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3baef23e7214219af4e67c58e42992c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=a59fNgBM1VLWvdDfIgk7lSttZ%2Fo%3D&amp;x-signature-webp=a3pibL5GKMscUx9GBkWPQ8cTCaA%3D</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6678c24f9a344ab592fb870547ad620c.jpeg</t>
+          <t>Lib\hardware\data\images\4a8e5f0d66194916bd8d9766a9824965.jpeg</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-wired-usb-portable-office-keyboard-for-pc-laptop-computer-hitam-keyboard-1731239918096844440?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-keyboard-wired-usb-portable-office-keyboard-for-pc-laptop-computer-hitam-keyboard-1731239918096844440?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/4/5/a58e1a18-1f10-4a59-a55a-fd1832f3e691.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=gJGEg6HCPo2g2NqNzmAYZtTlT5A%3D&amp;x-signature-webp=NP8hhM9EupH3Vzt0i2X1jdn6ODg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/4/5/a58e1a18-1f10-4a59-a55a-fd1832f3e691.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=w8EH8cdWUIUybxkmliXEJMjDV04%3D&amp;x-signature-webp=IGgQ0TbtOxxjN5s8MO%2FnJf751Dw%3D</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2a8d10f4a3264d628874dc068a9c4126.png</t>
+          <t>Lib\hardware\data\images\96a6ffd463384b80abd20003e7912d2e.png</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/torch-id/torch-loka-backpack-office-tas-ransel-punggung-kuliah-kerja-laptop-15-inch-black-a2f1a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/torch-id/torch-loka-backpack-office-tas-ransel-punggung-kuliah-kerja-laptop-15-inch-black-a2f1a?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/11/e53481e1-2aa7-4a54-b392-ca8165e0854d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=0v52REvnRUhHkHOJmhvc%2FEsfZk4%3D&amp;x-signature-webp=LPm4yS2TGkX9GvQgZfn4mEkQ8b8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/11/e53481e1-2aa7-4a54-b392-ca8165e0854d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=xzbQIuGEQn3qlyHylT35SyPc3Q8%3D&amp;x-signature-webp=rWDs4Jbqqwml7IrG0fOu1u1MOCU%3D</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fbfa793d9e7f4ecdb254fe2e02dc9fbe.jpeg</t>
+          <t>Lib\hardware\data\images\49b3761e503b4e368a057a74e9c716f4.jpeg</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/toko1973/brewyn-kremlin-mens-office-laptop-bag-tas-sekolah-kuliah-kerja-new-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/toko1973/brewyn-kremlin-mens-office-laptop-bag-tas-sekolah-kuliah-kerja-new-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3712,17 +3712,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfea1365d2224b02b0cd6e3066c04563~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=TTc8MLFow4F5DKYUeWeyCM4AOf8%3D&amp;x-signature-webp=hshYk4Mu427OhNNVmlHvVr2IYi0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfea1365d2224b02b0cd6e3066c04563~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=bU9XxVHPw%2BRT67COSMegy3O0cBY%3D&amp;x-signature-webp=dgSynXO5atDqeRcJq2QT9ZfOMVQ%3D</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8ca92d7371914c718d2e9ece88bcb37a.jpeg</t>
+          <t>Lib\hardware\data\images\97fd3fd825134a7dbd27bb69588130a6.jpeg</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/fashionselular/onesos-mouse-bluetooth-wireless-office-silent-click-dual-mode-2-4ghz-receiver-usb-for-pc-laptop-black-97680?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/fashionselular/onesos-mouse-bluetooth-wireless-office-silent-click-dual-mode-2-4ghz-receiver-usb-for-pc-laptop-black-97680?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/b431006e2c274740a5d254c732987c47~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=OXR5NBlhJppPK%2FeEDe8vM6XQe4E%3D&amp;x-signature-webp=W0uNN5yJMx8nC9XHPEwqPmeDxhc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/b431006e2c274740a5d254c732987c47~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=o8MkjzIliNE6zesHLgtDOfFoacw%3D&amp;x-signature-webp=aQ47i4Ez6hLKQQR32o22D3CPpX0%3D</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\af7f0302c7544481876d9485d3f41131.jpeg</t>
+          <t>Lib\hardware\data\images\23a10e3d82744bc9b1e503af012411b9.jpeg</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/thekingdomshop/taffware-meja-laptop-42x26cm-portable-desk-table-besi-alumunium-bed-hospital-ranjang-tempat-tidur?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/thekingdomshop/taffware-meja-laptop-42x26cm-portable-desk-table-besi-alumunium-bed-hospital-ranjang-tempat-tidur?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/25/e5d80580-d276-4193-95c2-467a317bbbce.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=Juis5i396QWC6PDvTwXfnwfTSGE%3D&amp;x-signature-webp=YrBL8wbXYyV%2BTwFNpNOMcPhmano%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/1/25/e5d80580-d276-4193-95c2-467a317bbbce.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=HZRxdR7L3uTsPz83yFu0yN3Xvnc%3D&amp;x-signature-webp=dm6FGaNGxSxOkruDFNVZCTB1yfU%3D</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ba0e61e1759249769617e93dc0366523.jpeg</t>
+          <t>Lib\hardware\data\images\bdd124fbb8374c7e9a12f5094a2d6c29.jpeg</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-malvern-tas-ransel-laptop-14-backpack-office-sekolah-hitam-bfe09?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-malvern-tas-ransel-laptop-14-backpack-office-sekolah-hitam-bfe09?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -3859,17 +3859,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/6fde5fe1-e2aa-4dae-9a14-e22668d1df63.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=3%2BHbDBKaKhI6Q9%2Bu6ymAy4w%2FF1g%3D&amp;x-signature-webp=0UogXxvDmbDQUE0CE3IS6F6PQgM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/6fde5fe1-e2aa-4dae-9a14-e22668d1df63.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=sX8i5UxIA%2B%2FCxlNdRtPfyzCb8ps%3D&amp;x-signature-webp=OSPkxTfVfk8OrNtuCa4lseupN2U%3D</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\762198d0b5ee43b8ab2ee6437ba74002.jpeg</t>
+          <t>Lib\hardware\data\images\b4923c5611334412a2241f1dc7fc5f9a.jpeg</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-malware-ransel-tas-backpack-laptop-14-inch-unisex-for-school-office-travel-hitam-e60e8?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-malware-ransel-tas-backpack-laptop-14-inch-unisex-for-school-office-travel-hitam-e60e8?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -3908,17 +3908,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/a1b6a357-020a-40c2-82e1-1a04455a483d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=crh9%2BLKbQ3yCu4IU4nHg%2FSx3ywM%3D&amp;x-signature-webp=LCdy6tyzYGz%2F4IKZCg96vwcK%2BOY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/23/a1b6a357-020a-40c2-82e1-1a04455a483d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=J%2FDo7meYLsqODnlBCvV8KONyjRo%3D&amp;x-signature-webp=8kpjzRFYPKxdAoSOYcJQ%2BkN6PP4%3D</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3c78c658a19346c6a7a87fc665cb93d8.jpeg</t>
+          <t>Lib\hardware\data\images\808db35399524313bd21ec93fdc6e849.jpeg</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-munich-tas-ransel-laptop-outdoor-backpack-travel-22l-office?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-munich-tas-ransel-laptop-outdoor-backpack-travel-22l-office?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/10/80613ad1-822a-420c-b539-8982c04fd198.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=sqBwm2smC5oCX0jh4MLz%2BqxhXKc%3D&amp;x-signature-webp=OsncJiIEE6ZKsKwIZF1F2o27lks%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/10/80613ad1-822a-420c-b539-8982c04fd198.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=Gs%2BsQRyenVQf953f0Dnlzf1JVyg%3D&amp;x-signature-webp=E9n05ngx2Ehc2wbxYAWGftmiCI8%3D</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8a6a04a3cfa84542b1c034f15773c68e.jpeg</t>
+          <t>Lib\hardware\data\images\4f0d555992344c2fb9448ff5db32c38c.jpeg</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/delioa/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-20619?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D8108753</t>
+          <t>https://www.tokopedia.com/delioa/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-20619?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch%26whid%3D8108753</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/31f0e7ca2307423d9af05931721c8709~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=fI%2B5atOtLZUEG8E5vJJi2oIKfho%3D&amp;x-signature-webp=bqsDAmard%2B2Q7wQnmFRNfUtN%2BJU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/31f0e7ca2307423d9af05931721c8709~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=D0bEz23P02xRhe4QgsH7kRX4Ceo%3D&amp;x-signature-webp=jy2QFyh%2Fmm3aBs4BcAe5vIjlgYw%3D</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b9341ce46e4b4cfe91906fcab18bdf3c.jpeg</t>
+          <t>Lib\hardware\data\images\4ac1e09372fc4819ba227f4dc83976d3.jpeg</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-field-of-view-ransel-backpack-outdoor-travel-laptop-14inch-office-sekolah-22-24l-1729771080242594987?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-field-of-view-ransel-backpack-outdoor-travel-laptop-14inch-office-sekolah-22-24l-1729771080242594987?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4058,17 +4058,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/2/a4358b69-68cb-47b5-a840-f1b889e39e24.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=tBxQnfJcimXTmd%2FRzF%2F%2FEeePh%2F0%3D&amp;x-signature-webp=cW33Uq%2FYdgGzV%2BhXnNYfe2q1jgc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/10/2/a4358b69-68cb-47b5-a840-f1b889e39e24.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=OS3ltVF6tY5EKdAuJB9BLzQR7lQ%3D&amp;x-signature-webp=1taeCoBFNoYUodtw%2B6MFmKOh4S0%3D</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e7dfca793e744191a6a141891d79fbf9.jpeg</t>
+          <t>Lib\hardware\data\images\671fdfc1c8954adbaa8da3dca1cb24dc.jpeg</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-yerevan-tas-ransel-laptop-urban-14inch-sekolah-office-merah-b6b5a?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-yerevan-tas-ransel-laptop-urban-14inch-sekolah-office-merah-b6b5a?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4110,17 +4110,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1e1c78d14ba1493b9ddd5c8bded02385~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=K5n9ZOEnt%2FsbWElqFbPXPIQyLuc%3D&amp;x-signature-webp=1vT61BpCoVk9d%2FfjNfbVZ2x4Jnw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1e1c78d14ba1493b9ddd5c8bded02385~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=IfNY8IXrdWw4mT1cvIYSgpD91wY%3D&amp;x-signature-webp=fyqm7Y%2FVDFureD7PPhTS0J43BDA%3D</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e04661c197924946a94e73d0f3e93318.jpeg</t>
+          <t>Lib\hardware\data\images\628631365a3642be8d8d9e33cc79b50e.jpeg</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-enrekang-ransel-tas-laptop-15-inch-backpack-travel-28l-office-sekolah-kampus-1731143360590087339?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-enrekang-ransel-tas-laptop-15-inch-backpack-travel-28l-office-sekolah-kampus-1731143360590087339?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4159,17 +4159,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/614ebd8bb1c04a7eb3fd1b4df55f7237~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=TLT0sFXtL4AA6J%2B%2BZltPAxBBtKQ%3D&amp;x-signature-webp=4FCudkIyGdjVRJXP9rWey4NXONw%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/614ebd8bb1c04a7eb3fd1b4df55f7237~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=kgtIJ%2BFNaxC5niuXGD%2F3QAc3Pwc%3D&amp;x-signature-webp=cCom0kaQVDSYWp7zCdL4wLnZa%2Fg%3D</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\72b01a324f5e4c15ade7d720ba45b9ae.jpeg</t>
+          <t>Lib\hardware\data\images\c3af37e9fea2483aabf32b218ce84c53.jpeg</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/reformasicompute/mouse-wireless-rexus-office-q30-silent-mouse-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/reformasicompute/mouse-wireless-rexus-office-q30-silent-mouse-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4208,17 +4208,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5e73c1ebd62c4a558d22d17793191345~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=ajkq75ASLshLYh3lXOglRK1YafE%3D&amp;x-signature-webp=ZqztR2wjHIAogkNR%2B837l97qirs%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/5e73c1ebd62c4a558d22d17793191345~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=WAaweQot%2BC%2FE0guFuVV7u4qme1w%3D&amp;x-signature-webp=Ph08C%2FzZc1LKKq6XBrufBPzvSnQ%3D</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f7cc744473e8450689a53e37acbcfecd.jpeg</t>
+          <t>Lib\hardware\data\images\0fc2ea8f9d9d47e985a2c506bc8f838e.jpeg</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/reformasicompute/rexus-q10-mouse-wireless-office-silent-click-biru-muda?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/reformasicompute/rexus-q10-mouse-wireless-office-silent-click-biru-muda?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4260,17 +4260,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/21/8bbc37d0-0a5e-4c6e-8b65-594ce61d6773.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=1Q%2FC%2FlKoItT6k7Yuvv3EkGuGfZE%3D&amp;x-signature-webp=%2FIUaQzKL5%2BYPWps%2BAaZHHYpgU1I%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/21/8bbc37d0-0a5e-4c6e-8b65-594ce61d6773.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=iwglcnK7QA7tHFUgtMJ%2FttXzA9E%3D&amp;x-signature-webp=oplHS5OWQXj%2Bmg5nK%2B7tZ6Xhm%2Bw%3D</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dd48c3071e07443da79f8c0cefdd8bf7.jpeg</t>
+          <t>Lib\hardware\data\images\f5ef7de8039e4dc7a892d2acc2744e45.jpeg</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dnd-olshop/baseus-smart-desk-mat-pad-with-wireless-charger-for-gaming-office-wrist-rest-laptop-phone-stand-holder-keyboard-mouse-pad-basic-edition-3ec7d?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dnd-olshop/baseus-smart-desk-mat-pad-with-wireless-charger-for-gaming-office-wrist-rest-laptop-phone-stand-holder-keyboard-mouse-pad-basic-edition-3ec7d?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4312,17 +4312,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=S5yQpc%2F9cwPCE9e4OfcWrlYApy8%3D&amp;x-signature-webp=tMDumeZZc8b4NOF%2BkFCFoKRUekk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=Z4l4ZIKyekBI9WJHQg%2BDvQ2wdLM%3D&amp;x-signature-webp=l8Ti%2BPNrxh%2Bs%2FRmdVr1Vk3QClXE%3D</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b773198ea7b34f5c8e07190b83b05e11.jpeg</t>
+          <t>Lib\hardware\data\images\bbab8d94e9c4443d8f870665c5bd64b2.jpeg</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-x-aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1732911892490716709?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-x-aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1732911892490716709?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f4b1f90a2d4f48fc91d0262d2c72a43e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=wZpRcLnILuaAGZb56ER2%2FNyPByQ%3D&amp;x-signature-webp=Q%2BPjfHjjXEgqTaVkN7ifCylrw50%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f4b1f90a2d4f48fc91d0262d2c72a43e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=npNmHkBrexZmlI4sxmg8OzHDhVc%3D&amp;x-signature-webp=i2a2WVZ1cE0IrFqR80d6iyEtYAw%3D</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c860c0426dc64894bb9efb8dc7e3d222.jpeg</t>
+          <t>Lib\hardware\data\images\3bbceae2609343539bb412bc659866d3.jpeg</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-optical-g8-wired-kabel-usb-1000dpi-for-laptop-pc-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/divipard/unitech-mouse-kabel-optical-g8-wired-kabel-usb-1000dpi-for-laptop-pc-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/27/da8fc5bd-5e79-432a-9e9e-71dccf3a3137.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=VVdRDfoiBcZzwTYGDphPgUnT%2BYE%3D&amp;x-signature-webp=6DX5eL0DIfV5hNfUpziqLqUrzs8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/12/27/da8fc5bd-5e79-432a-9e9e-71dccf3a3137.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=1F%2BTBxT9SaYRwNjhukDEmd%2Bjtqk%3D&amp;x-signature-webp=HopGSk6Fa%2BUyh1qVcfYTyM%2FoUJo%3D</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1205d9e1bedb43feb030a790eb186225.png</t>
+          <t>Lib\hardware\data\images\e3bdcda316a04d40860c5a96e1434a8c.png</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supermallori/office-desk-mat-alas-laptop-meja-kerja-mouse-pad-xl-anti-slip-hitam-87010?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supermallori/office-desk-mat-alas-laptop-meja-kerja-mouse-pad-xl-anti-slip-hitam-87010?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4465,17 +4465,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/dd1c7673e9244b86998b388fcfb3086e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=d0HT2tzv9BLAMXbwo5lknkBt%2FiI%3D&amp;x-signature-webp=6BcvSZ1A7hneVawIwq2dkB6%2Fmjc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/dd1c7673e9244b86998b388fcfb3086e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=dMcvbbtRuJfoIq%2FH1baipUyTNCo%3D&amp;x-signature-webp=CpKW3LnDW6mGde6w81jCJatXs%2FE%3D</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0e89a668d9414646be6746b60696e83e.jpeg</t>
+          <t>Lib\hardware\data\images\2770e27098bc486db29d7e6736487eaf.jpeg</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/suryatama/mouse-quinton-e100-hitam-kabel-usb-for-laptop-pc-computer-1730805992441873603?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/suryatama/mouse-quinton-e100-hitam-kabel-usb-for-laptop-pc-computer-1730805992441873603?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4514,17 +4514,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/3f12aef7d5d541d8a166d75fb1e151fd~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=4F%2BJirqQYzsZF%2ByOLC3FAGvJ8mk%3D&amp;x-signature-webp=d7CIJmmDCelv2Q8KUaOIcpcYvs8%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/3f12aef7d5d541d8a166d75fb1e151fd~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=Q0HVa7EoJhXH6kizCWf0dJNGhnw%3D&amp;x-signature-webp=pr7fH%2FKZIljPS4X8h4dv5G6d4Bs%3D</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\636e479f6e824348b20139d7d928fd88.jpeg</t>
+          <t>Lib\hardware\data\images\866ab3c0029a48f18332f944d4564fc5.jpeg</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-tongkonan-ransel-backpack-laptop-14inch-urban-traveling-22-24l-top-load-sekolah-office-corporate-1729641642932603051?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-tongkonan-ransel-backpack-laptop-14inch-urban-traveling-22-24l-top-load-sekolah-office-corporate-1729641642932603051?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -4563,17 +4563,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/7/46bf75d3-fdb9-44d8-b4ac-0fc2de7f5648.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=FMRUVNOT7BjEGjgZscRp%2BejPcWE%3D&amp;x-signature-webp=bOSqf4TVXiQCHOOGzoBF9l6E8X0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/7/46bf75d3-fdb9-44d8-b4ac-0fc2de7f5648.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=d8tZ4WeJNyiJgexFUTX3tLVzCaM%3D&amp;x-signature-webp=ABFbwy%2BlXbLEpMC1oNrgJwM0Vpc%3D</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\153879b938724ea2a8a78b8e7f2c397c.jpeg</t>
+          <t>Lib\hardware\data\images\7f824d8c8ddb4d7fbe64c951922973c0.jpeg</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-56342?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-abu-abu-56342?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/9/db166b0e-7561-45c4-8f94-c7e1fd6b5ca3.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=%2F76p3sNRa1INAWfJDoD1hTO1n2Q%3D&amp;x-signature-webp=wWqyAOFNJQTFJsa8zbT0Gm0Dhas%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/9/db166b0e-7561-45c4-8f94-c7e1fd6b5ca3.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=khRTOCWZ19jZIjRmG%2FFJWbU6DY8%3D&amp;x-signature-webp=WPl2zJN3263PeqQlHBTGGJH2gLY%3D</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f5d6a779796444ab8450a62abdbf215b.jpeg</t>
+          <t>Lib\hardware\data\images\2f44687b4c93474a91a1c0eec745ec5c.jpeg</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-laptop-kerja-kantor-selempang-office-briefcase-14-bg106-abu-abu-f6cb7?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D4203398</t>
+          <t>https://www.tokopedia.com/deli-indonesia/deli-tas-laptop-kerja-kantor-selempang-office-briefcase-14-bg106-abu-abu-f6cb7?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch%26whid%3D4203398</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d837c49cb2a5448a810541ddc84ee84c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=8982aZZIdiN7i0gZuwSwHkrY6lc%3D&amp;x-signature-webp=G8XeuS%2BuC8AB7rMi4TDGuVY9osA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d837c49cb2a5448a810541ddc84ee84c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=sbUwyMs6s7loEk%2Bmvt24LV7kQmc%3D&amp;x-signature-webp=exvbH7HdOjZZWPwtH7GV3wXw2nk%3D</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\112fcac249cc432daff4bfdfb7f395d3.jpeg</t>
+          <t>Lib\hardware\data\images\c5f6d19d94f74623bc995188e0a8b29a.jpeg</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laptopmurahid/laptop-murah-zyrex-lifebook-n4020-8gb-128gb-w11pro-14-0-gry-office-1731531184748463382?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laptopmurahid/laptop-murah-zyrex-lifebook-n4020-8gb-128gb-w11pro-14-0-gry-office-1731531184748463382?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4713,17 +4713,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6338aa902f724277b3c5004260b37911~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=gowdASI7De4mM0WFXOhIgJwwjOY%3D&amp;x-signature-webp=GKCdMqlBN4gTYAXNf3RhUxo36k0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6338aa902f724277b3c5004260b37911~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=1YmxTK2dLCds9qk0GhGFvowhNDY%3D&amp;x-signature-webp=wJRpUVzies4vYNQ6loIePnMZ1rQ%3D</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\157af33c1632403ea6ce7aa441d17551.jpeg</t>
+          <t>Lib\hardware\data\images\cd5454bb5a7840b38619371e19045389.jpeg</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/philips-voicetracer-store/philips-mouse-meetion-kabel-usb-office-mouse-kabel-usb-1200dpi-kursor-halus-dan-presisi-untuk-pc-laptop-1732408374889449090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/philips-voicetracer-store/philips-mouse-meetion-kabel-usb-office-mouse-kabel-usb-1200dpi-kursor-halus-dan-presisi-untuk-pc-laptop-1732408374889449090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -4762,17 +4762,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/20/d54e8ffa-2df9-4c94-af64-9dfd3427faa1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=xyqE56DXpAXIScfoHFmp3brytX8%3D&amp;x-signature-webp=XP2OL4rKo3UawYLa%2FZwhoaPu9w0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/20/d54e8ffa-2df9-4c94-af64-9dfd3427faa1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=xMyY74nBeqqlSOca1KSzkFGkjd0%3D&amp;x-signature-webp=BB0HGcF0v93PmFywHE3IgRqIQhY%3D</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b9e9a3a823344d6d8a892a40010a3e37.png</t>
+          <t>Lib\hardware\data\images\c3c327b07f9d4f288d77df2c638470ce.png</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/technosify/robot-m102-optical-mouse-wired-pc-laptop-office-1200-dpi-new-m100-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/technosify/robot-m102-optical-mouse-wired-pc-laptop-office-1200-dpi-new-m100-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -4814,17 +4814,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43a06819c1b648dc99f1a089d8642d3e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=RfM0L%2BVQMvnw3BP2WLlke1386y8%3D&amp;x-signature-webp=rF0UW2BcZTjqG0mar2288EpbTiE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43a06819c1b648dc99f1a089d8642d3e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=t1YolSrEPjfiKRfWPZ1OmZOgDSw%3D&amp;x-signature-webp=TK8ZcXgu5ueTwt2mmvaliAP%2B8a4%3D</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d2afad625acb4e23ae6b099918bb608f.jpeg</t>
+          <t>Lib\hardware\data\images\da5a98438a924fbba18d53fc5948ddfb.jpeg</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/huaiwen-pc-store/hw-keyboard-mouse-set-kabel-usb-portable-104-key-full-size-office-wired-keyboard-for-pc-laptop-1731395301317248711?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/huaiwen-pc-store/hw-keyboard-mouse-set-kabel-usb-portable-104-key-full-size-office-wired-keyboard-for-pc-laptop-1731395301317248711?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8e46ce56c02d46fabf7d0c8d97fe2c48~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=6q5vn4BNfWkXrDyLK9Xlc1MfhCo%3D&amp;x-signature-webp=NpHo46Aktv5F0X0m%2Fta6Oh1Tdfc%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8e46ce56c02d46fabf7d0c8d97fe2c48~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=ozcI8U%2FPN0NP0s5AEPc3YJ83IYw%3D&amp;x-signature-webp=ieoSEncEx103bUVrHv8%2BBnpslOY%3D</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1168a5877dc54ed49c3bb5fac861bdb4.jpeg</t>
+          <t>Lib\hardware\data\images\8237e7f22f2840d3af38060e57ab5505.jpeg</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/dap-indonesia-official-store/dap-keyboard-kabel-usb-2-0-portable-104-key-full-size-office-wired-keyboard-bass-button-for-pc-laptop-d-k02-garansi-1-tahun-1729677965436487996?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/dap-indonesia-official-store/dap-keyboard-kabel-usb-2-0-portable-104-key-full-size-office-wired-keyboard-bass-button-for-pc-laptop-d-k02-garansi-1-tahun-1729677965436487996?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a0501ec6bd9b4b99a2538ce910e8d7cf~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=zkPI5IwhPJQ8oc6uK1uboRwT4x0%3D&amp;x-signature-webp=3VCLeF7C8ePeSypVtLxL7c5s%2Bq8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a0501ec6bd9b4b99a2538ce910e8d7cf~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=KbiEMZbXIvOUMwIVEthGjqAHw4Q%3D&amp;x-signature-webp=%2F3Qm1%2F8%2F%2BBIVxBvlo9QIiYT8rdM%3D</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6eb2a40b3a444feb8bb5df19d8e7c3a5.jpeg</t>
+          <t>Lib\hardware\data\images\7a8a4e9880054ed6b2c48dac735c1d7c.jpeg</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/consina-official-store/consina-florin-ransel-tas-laptop-15-inch-backpack-travel-office-sekolah-kampus-1732937353765881003?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/consina-official-store/consina-florin-ransel-tas-laptop-15-inch-backpack-travel-office-sekolah-kampus-1732937353765881003?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -4967,17 +4967,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1f52c929a7754ed4aacff0b2d2a0aaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=3tKVxuSo%2F1wvebzm%2Fr8hnVJ%2FqFI%3D&amp;x-signature-webp=EfvEOSg%2BWFoC%2FS3ply8cL93YDrs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1f52c929a7754ed4aacff0b2d2a0aaa2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=ym2VretfwCg%2FIW1rbGOyjHd77Fk%3D&amp;x-signature-webp=rKbFgg3r1TpPfmW%2FAmC2sxKgw04%3D</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\14a5b20c33bf40fba9deb2503a484e65.jpeg</t>
+          <t>Lib\hardware\data\images\df46c17d8db34e628c01af86b7e82cdb.jpeg</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/royalltech/asus-vivobook-x1404va-intel-core-i7-1355-i5-1335-i5-1334-16gb-512gb-w11-office-14-0fhd-ips-laptop-ultrabook-laptop-tipis-nyaman-untuk-kerja-kuliah-1732832432834512375?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D4029903</t>
+          <t>https://www.tokopedia.com/royalltech/asus-vivobook-x1404va-intel-core-i7-1355-i5-1335-i5-1334-16gb-512gb-w11-office-14-0fhd-ips-laptop-ultrabook-laptop-tipis-nyaman-untuk-kerja-kuliah-1732832432834512375?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch%26whid%3D4029903</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/11/5/dbc78023-d6f5-4a1c-b574-362511ab85b9.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=TsCg9GDvThScjbbeuDYQFj6XHfY%3D&amp;x-signature-webp=nsrM%2Fv4Sbh0Wzr0P8XLKISK19RU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/11/5/dbc78023-d6f5-4a1c-b574-362511ab85b9.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=raEVL05Al7yjF8udCsRUoymR4aU%3D&amp;x-signature-webp=3rWyjz%2Fa4U9c2l98YnYunU8rtHg%3D</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6054fedf7c1345c09b1cfbf997e38d97.png</t>
+          <t>Lib\hardware\data\images\77fa47a673b046d3984ab42bc6c443b7.png</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/movioofficialstore/movio-desk-mat-leather-office-deskmate-mouse-pad-gaming-alas-laptop-1730814937146492460?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/movioofficialstore/movio-desk-mat-leather-office-deskmate-mouse-pad-gaming-alas-laptop-1730814937146492460?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=S5yQpc%2F9cwPCE9e4OfcWrlYApy8%3D&amp;x-signature-webp=tMDumeZZc8b4NOF%2BkFCFoKRUekk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cf4725af4405492cb0be34ef425eab0d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=Z4l4ZIKyekBI9WJHQg%2BDvQ2wdLM%3D&amp;x-signature-webp=l8Ti%2BPNrxh%2Bs%2FRmdVr1Vk3QClXE%3D</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f03cb34a93764d6e94a904d00856e8ac.jpeg</t>
+          <t>Lib\hardware\data\images\e7baf3f177af45648d0cdf94ea5add16.jpeg</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/aula-indonesia/aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1730707911523271760?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/aula-indonesia/aula-s12-mouse-gaming-wired-professional-office-mouse-click-rgb-4800dpi-low-latency-esports-gaming-drag-mouse-laptop-pc-garansi-1-tahun-computer-button-1730707911523271760?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5123,17 +5123,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9574249e5aa14f9e9ff0ec25065ea773~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=%2Fj2Iz1VsHebBKLeHtxulzgDCO2s%3D&amp;x-signature-webp=I2iB5jQRd0syfYrEbqPeXEpthnM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9574249e5aa14f9e9ff0ec25065ea773~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=hsszMixj47Rk3dmSamV7ZMZy%2Frw%3D&amp;x-signature-webp=vfMyQCX3ZoEIMp5GVftfQOJYfSA%3D</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\16677dc57d0f45f8893f17a003b93307.jpeg</t>
+          <t>Lib\hardware\data\images\7650392cebcd48a39a5b6a312a5380fc.jpeg</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-t23-women-tote-bag-for-laptop-macbook-ladies-shoulder-bag-office-bag-beg-perempuan-1732147400330019985?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-t23-women-tote-bag-for-laptop-macbook-ladies-shoulder-bag-office-bag-beg-perempuan-1732147400330019985?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5172,17 +5172,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/142ebd455039474c9b6a28130ac65ab9~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=YWA7oUMMhq8LZ4D6oSUUMxTAIpM%3D&amp;x-signature-webp=3cDu7q84jVW7dZZbfq9sZDfIm4E%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/142ebd455039474c9b6a28130ac65ab9~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=ET%2ByEc2B0OM%2FrGVFCyv7dJnLZ54%3D&amp;x-signature-webp=O47R%2BAUCkscMsOOHlJiwajOFxaQ%3D</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a98bd97b0ce547b4a216339a90a5c061.jpeg</t>
+          <t>Lib\hardware\data\images\2da88c7f665c4a708844842aaa2477c5.jpeg</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-a40-defender-laptop-messenger-bag-14-16-inch-business-shoulder-bag-office-briefcase-beg-silang-lelaki-1732455130755335313?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/new-tomtoc-a40-defender-laptop-messenger-bag-14-16-inch-business-shoulder-bag-office-briefcase-beg-silang-lelaki-1732455130755335313?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5224,17 +5224,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8cb82b7c455e4e0fa79003e51a3c33c3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=45oJ%2FOO39lXGJ4PtQT2VeNsv8v8%3D&amp;x-signature-webp=WZyE2EwTxTgp9qgT00nTVIsu31Y%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/8cb82b7c455e4e0fa79003e51a3c33c3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=UiATPlyacfU0C%2BC5bkuwT05KPSk%3D&amp;x-signature-webp=NlftugRs6rMQBG64XkLESX%2Fx9JE%3D</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\72213f1b7574446190c59f1fa85756b2.jpeg</t>
+          <t>Lib\hardware\data\images\de9c1ebc3ba64e7b8316a0f5e082398e.jpeg</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a30-defender-messenger-bag-14-16-inch-laptop-bag-business-briefcase-office-bag-for-macbook-beg-silang-lelaki-1732460964531569809?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a30-defender-messenger-bag-14-16-inch-laptop-bag-business-briefcase-office-bag-for-macbook-beg-silang-lelaki-1732460964531569809?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/697f15b91d5a4320a3484f2b65beb688~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=qUUg7GeYkssrKIDXVpSU9YIqR8k%3D&amp;x-signature-webp=k8kS1WYyLFaosVkckWAVXhX4HKM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/697f15b91d5a4320a3484f2b65beb688~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=NVNrCWc35q10rbxSKWZam0UQQuU%3D&amp;x-signature-webp=11Kv5ooHHNpmSKn1wCc3Urqslcs%3D</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\822e076b355248a19571a191eb489bc6.jpeg</t>
+          <t>Lib\hardware\data\images\fdf36f165dfb49f8b76917580cf9a56f.jpeg</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-t71-premium-laptop-backpack-urban-fashion-bag-15-6-17-3-inch-macbook-bag-office-laptop-bag-beg-lelaki-1732140544120292497?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-t71-premium-laptop-backpack-urban-fashion-bag-15-6-17-3-inch-macbook-bag-office-laptop-bag-beg-lelaki-1732140544120292497?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5328,17 +5328,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e73d1e41c3be4c94b13dca55172a7763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=3H42j7YCp2jYzCoshNtydkFf2go%3D&amp;x-signature-webp=k789Ki04WzvgSHEIcBzc65i7lBI%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e73d1e41c3be4c94b13dca55172a7763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=QaXidOqF%2BIpAhWObtkqp38TAaK8%3D&amp;x-signature-webp=k9r%2BQohQV3FevyPIfer9O67fpyo%3D</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a11e98e42a1f4e269d0bbea78a9b92c9.jpeg</t>
+          <t>Lib\hardware\data\images\a116d6e76a674708942f4336622a50eb.jpeg</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a33-navigator-messenger-bag-14-16-inch-laptop-bag-men-business-briefcase-office-bag-beg-silang-lelaki-1732460907579016337?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tomtocidn/tomtoc-a33-navigator-messenger-bag-14-16-inch-laptop-bag-men-business-briefcase-office-bag-beg-silang-lelaki-1732460907579016337?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5380,17 +5380,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2860a24a9e3b43bc827afade643aa71a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=DS4dj5%2F0gAi%2BCM16NrngvHSfeuU%3D&amp;x-signature-webp=OtFlMvqBePJQMSb2gDr7v3ZA2GA%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2860a24a9e3b43bc827afade643aa71a~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=gLANJxADdx4%2BUBKJwv%2BmJlbK4jQ%3D&amp;x-signature-webp=vb%2FVcenOJ0sjyX42OaFvk%2FY8tQM%3D</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1ffe1b1a7ce842f28827de2ff3eda5cf.jpeg</t>
+          <t>Lib\hardware\data\images\6ec7358f5e304b3f9c0928f9f3db1210.jpeg</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/goojodoq/goojodoq-gm0001-office-use-usb-wired-mouse-for-pc-laptop-tablet-w-led-1731786143330567436?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/goojodoq/goojodoq-gm0001-office-use-usb-wired-mouse-for-pc-laptop-tablet-w-led-1731786143330567436?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5432,17 +5432,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6d81861615c94e9d9a2c35ef160645a6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=Ywt4RX1Vm6tWsUFCpXICCVg%2FhoQ%3D&amp;x-signature-webp=oE9sB93u1f8S6%2Bw0qWTipIqe4EE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6d81861615c94e9d9a2c35ef160645a6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=WnNEzUHlg4ZN9pXOtWzwCuudWa4%3D&amp;x-signature-webp=0xK7u20IEdpzSAw3jOtRfvUAjl4%3D</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d1254f764a824e90bbb67ddf1596b2cb.jpeg</t>
+          <t>Lib\hardware\data\images\489790cca2ab4e8a9c573ad024938f2e.jpeg</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deli-office-automation/deli-office-vusign-folding-table-meja-belajar-laptop-lipat-warna-warni-dengan-cup-holder-dan-phone-tab-holder-vs860-computer-1729434977497286678?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D18379622</t>
+          <t>https://www.tokopedia.com/deli-office-automation/deli-office-vusign-folding-table-meja-belajar-laptop-lipat-warna-warni-dengan-cup-holder-dan-phone-tab-holder-vs860-computer-1729434977497286678?extParam=ivf%3Dtrue%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch%26whid%3D18379622</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -5484,17 +5484,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2a42027251e44e9ca4d6b1aa02296fd0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=N4Qcx8aZbXEs%2BEm8XQzjV%2B48oI4%3D&amp;x-signature-webp=E1SMN2%2F31CV1DzkqWLAEmk2LAcI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/2a42027251e44e9ca4d6b1aa02296fd0~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=35FbokKhbrFv4XNkm8W3CpLzXUM%3D&amp;x-signature-webp=vzqzLG%2Bp%2FiDjvLp%2BZSkHlX8ZpXs%3D</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0b5d5e6a65af4ba08d919547463c3880.jpeg</t>
+          <t>Lib\hardware\data\images\cf6566b71d554e3aa7252cfc53f80765.jpeg</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/royalltech/lenovo-ideapad-5-2in1-14-touch-amd-ryzen-ai-7-350-16gb-1tb-w11-office-14-0fhd-ips-laptop-2in1-touch-screen-notebook-1733282836276479479?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/royalltech/lenovo-ideapad-5-2in1-14-touch-amd-ryzen-ai-7-350-16gb-1tb-w11-office-14-0fhd-ips-laptop-2in1-touch-screen-notebook-1733282836276479479?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c9d8b76508d243b68d6b5ad417ae9f60~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047479&amp;x-signature=i2eUz7VCUgORXN1IsxCuSe2eB%2Fc%3D&amp;x-signature-webp=tpBc7CkxsMSavn5UCemZ%2B%2B0PP24%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c9d8b76508d243b68d6b5ad417ae9f60~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047773&amp;x-signature=6ADwW%2BhhCpIar2s46%2BudBxwVdUg%3D&amp;x-signature-webp=2ZsIQCrtHWp8tr2tTyUD8zNng0o%3D</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b16da6f479ac488f9d83480aad820d12.jpeg</t>
+          <t>Lib\hardware\data\images\d1513618068b43e28755833b8ce601cb.jpeg</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deliindonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-1729461164801230362?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041119B3967A0E938DC229D2CR%26src%3Dsearch%26whid%3D18553129</t>
+          <t>https://www.tokopedia.com/deliindonesia/deli-tas-dokumen-laptop-office-briefcase-14-inch-multifungsi-63788-1729461164801230362?extParam=ivf%3Dfalse%26keyword%3Dlaptop+office%26search_id%3D20251125041613EDDEA82AD2755B06CXOU%26src%3Dsearch%26whid%3D18553129</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5554,11 +5554,11 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>459067759</v>
+        <v>459067732</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sticker - Stiker Logo C Sharp Programming Language untuk PC Laptop HP</t>
+          <t>Sticker - Stiker Logo Go Golang Programming Language untuk PC Laptop</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -5568,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5582,17 +5582,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_d335da00-22f5-4912-8bef-32b3775be378.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=3oKVAIRDkGd5GxbwQXDM6dl10Ns%3D&amp;x-signature-webp=J7xfCaI2bOs9OZQhRuZ%2FLfO2PKs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_fb1a930f-e114-4bd2-8224-e722de4ed1ac.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=FrO4MLrgohssrLZr9yPeRoaVbtA%3D&amp;x-signature-webp=8lsERkfPsbodPM880hdfvuvkSuQ%3D</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dee72ae50ad8445ca7aeee044e455a78.jpeg</t>
+          <t>Lib\hardware\data\images\911addc15e37456bbd0d557fd2f37149.jpeg</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-sharp-programming-language-untuk-pc-laptop-hp?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-go-golang-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5603,11 +5603,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>459067732</v>
+        <v>459067759</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sticker - Stiker Logo Go Golang Programming Language untuk PC Laptop</t>
+          <t>Sticker - Stiker Logo C Sharp Programming Language untuk PC Laptop HP</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -5617,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_fb1a930f-e114-4bd2-8224-e722de4ed1ac.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=hYzF2O%2FyiuBQxJd7QIWJvS6ZBNY%3D&amp;x-signature-webp=oz7likYAu43IGEx%2BtnIH12EXn8k%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_d335da00-22f5-4912-8bef-32b3775be378.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=rRBqQ6l3cUB6o5cX0X%2Ffgb22AmE%3D&amp;x-signature-webp=Z5FUuTlaCFI2kgfhEsPvpz8q3V8%3D</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4d332b33fe3d4fa38c47a7ee5b796d90.jpeg</t>
+          <t>Lib\hardware\data\images\59103de2967240949d54f7e2306872e1.jpeg</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-go-golang-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-sharp-programming-language-untuk-pc-laptop-hp?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_57fb509a-be23-471e-989e-1f4d6e8d6456.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=Nz08DJ45hIhBJZApnxI5ka0KO%2BE%3D&amp;x-signature-webp=lsmRfaHg0xvoTT%2BUwSgwIgQHVH8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_57fb509a-be23-471e-989e-1f4d6e8d6456.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=tJdjMvm1r13m6uOdVrKypsF8ZOU%3D&amp;x-signature-webp=y8%2F9qeWmwRaAQMBhorkzm160iJ0%3D</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8d306336e377440e91bc3ee637623d2a.jpeg</t>
+          <t>Lib\hardware\data\images\2bc48d5014b64e92be8d3999802986bd.jpeg</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0cdf5c85ae0a40a69404e6a02408149c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=bvw5tcfNDCgSI5F8KALb6UrtOGM%3D&amp;x-signature-webp=JlFN4G2GOEoxpQ8j8RDl85S3ZfM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0cdf5c85ae0a40a69404e6a02408149c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=fWfsoR2dF3KSe3fOI7jWf59JvLs%3D&amp;x-signature-webp=1rSugsqMKZfvF6Aqp%2F0lP6QrBGE%3D</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\df59e0c6de514b52a81707f8d890c5a2.jpeg</t>
+          <t>Lib\hardware\data\images\09a28bb210324ad4bcb56e3a84d23642.jpeg</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/inlinefoursticker/sticker-pack-premium-it-stiker-program-teknologi-tema-coding-programming-coder-programmer-waterproof-tumblr-laptop-case-hp-koper-helm-sepeda-motor-1729660102472074470?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/inlinefoursticker/sticker-pack-premium-it-stiker-program-teknologi-tema-coding-programming-coder-programmer-waterproof-tumblr-laptop-case-hp-koper-helm-sepeda-motor-1729660102472074470?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5781,17 +5781,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/2/a80e659e-9b9a-4c2a-b57a-50ed8cf2ff65.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=TF%2Bq%2FHiVO0bNDfHM4bo8Sy%2F7zUA%3D&amp;x-signature-webp=OEqT5%2BaQIwMHtm0kkKyFPYPzV6g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/2/a80e659e-9b9a-4c2a-b57a-50ed8cf2ff65.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=xr2%2Fu31U6SqBb3fQnDKuvniVy4Y%3D&amp;x-signature-webp=82WMzKzYFz0xjjaWuZby%2FYx3ykM%3D</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\095fb0185107488796875f42379d59f6.png</t>
+          <t>Lib\hardware\data\images\bbd608b0645c438694690df300e2f254.png</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/yeagerart/sticker-pack-programming-coding-sticker-koper-sticker-tumbler-sticker-laptop-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/yeagerart/sticker-pack-programming-coding-sticker-koper-sticker-tumbler-sticker-laptop-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/21/3f892503-b128-4c98-81cb-00fb5661f466.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=yZDbtdJBQKJlncIErhGD2QDYBdo%3D&amp;x-signature-webp=Z6Tv9E8AIk3UtGsPwVGI3tA%2FIBE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/6/21/3f892503-b128-4c98-81cb-00fb5661f466.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=iySJaoPZuVoUinwJtHBbMeJZf0I%3D&amp;x-signature-webp=xSn5l2rFFYBd0xRdltY7boRFbTg%3D</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b9ddcfa5acd3478fb71236359f3a97e1.jpeg</t>
+          <t>Lib\hardware\data\images\3b5b08e2b70a401589042e4b918efee0.jpeg</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerplus/sticker-programming-2-sticker-laptop-sticker-pack-stiker-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerplus/sticker-programming-2-sticker-laptop-sticker-pack-stiker-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -5879,17 +5879,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_1e2c0c59-fda9-45b4-ae3a-ff69cf747612.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=YNqRnlFwfKQlcy8Y%2BLJj5oPa2Xk%3D&amp;x-signature-webp=JCWA7kTMRcQWeU6AXGRn5YADWnQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_1e2c0c59-fda9-45b4-ae3a-ff69cf747612.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=ep6GWnSSbr8KzQ4Dtq%2B9snHvx5A%3D&amp;x-signature-webp=iuv6JPOwgPbZYSvSmxS15j7nU08%3D</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f731f86d228141cea4735a5a461b45df.jpeg</t>
+          <t>Lib\hardware\data\images\18b3111e015547db89657d09e8c8f6bf.jpeg</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-plus-plus-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-c-plus-plus-programming-language-untuk-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -5928,17 +5928,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_e96fd7ec-b826-46fb-9e12-bf86a0adc00a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=W3vBXvDrRoFNrMnaxoSuJkzrF8Q%3D&amp;x-signature-webp=5gjiPTdvvWo1HD2kD9TFOPBTPWw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/product-1/2019/4/28/2445779/2445779_e96fd7ec-b826-46fb-9e12-bf86a0adc00a.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=Ret1JnHdAao6x7ErJfxnHBxmSJ4%3D&amp;x-signature-webp=Kw9xnMXW3YqApN0zAF3HkW73psQ%3D</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bcd40c55d31649c5926ae384c77216be.jpeg</t>
+          <t>Lib\hardware\data\images\f80b412be5364acfbb7fcce597ec6f52.jpeg</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-r-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokorizkiaryanto/sticker-stiker-logo-r-programming-language-untuk-pc-laptop-hp-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -5977,17 +5977,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/2c485272-3bc8-4c64-a8f0-baf8415b97e1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=8TWBG0KHS8BH2G3dTidceZC%2FHkA%3D&amp;x-signature-webp=QYX4iD9ajYW%2F9qikMcCrm8HZUMI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/2c485272-3bc8-4c64-a8f0-baf8415b97e1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=1RRwOkn1gmEXGhkDdz4jYQVgOnY%3D&amp;x-signature-webp=1yVCmmF%2BXeRcRCObAa%2FfXp1cuAQ%3D</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a10750ecb2894755a24b44aa9409a17c.png</t>
+          <t>Lib\hardware\data\images\5e78bcb3022941448b634794d955feb6.png</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/cutting-sticker-it-programming-programmer-coding-stiker-laptop-vue-js?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/cutting-sticker-it-programming-programmer-coding-stiker-laptop-vue-js?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6026,17 +6026,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/77ae15f3-c056-41f7-94f4-c008303a79f3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=6w6%2B%2BL7UGpTGciRyEY75fGQ8gEc%3D&amp;x-signature-webp=LuwdJXBq0yc4wvkc1SRrxeBH41Q%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/77ae15f3-c056-41f7-94f4-c008303a79f3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=liSddN1NWvgFfM%2BEPLa7JwPw0I4%3D&amp;x-signature-webp=%2FcSG8ATsIj9ncg4JD17fjO40p7U%3D</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\661f710267cb4a4e9bc109a23aef37d2.png</t>
+          <t>Lib\hardware\data\images\cd1dffdee0a44776a3f323108d2449fb.png</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/bootstrap-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/bootstrap-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/674d0478-bc6d-4c09-b6b9-88af31fea1d1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=6eZwPp4XmFmHle6S%2FqNb4dV8n84%3D&amp;x-signature-webp=1AChVoJN%2F%2FHi5ADVKKLiBF%2FbDw8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/674d0478-bc6d-4c09-b6b9-88af31fea1d1.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=JYCw4WAmbIQWZ0S5ThdaVe%2Fw6FQ%3D&amp;x-signature-webp=WfE5%2Brc0VyT1cDVmpvF1wevaV%2Bo%3D</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\32ac21c85b6b463184c0f4e012a74e66.png</t>
+          <t>Lib\hardware\data\images\56711a089c274d7889ad2acfa538d36e.png</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/linux-mint-cutting-sticker-it-programming-stiker-satuan-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/linux-mint-cutting-sticker-it-programming-stiker-satuan-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/22/d6a5263e-e87f-4f56-b43e-3b9544f68e28.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=zy%2BHKTX3eN%2F3OEdGeqRkw62vxAw%3D&amp;x-signature-webp=PK0dvZCaZhq6duF739NadGEqpBE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/22/d6a5263e-e87f-4f56-b43e-3b9544f68e28.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=K74oHeaGePskxhY3BgEVTxH6t6E%3D&amp;x-signature-webp=CtrBvkkrAIpPMMpGUbHQ3mYXXeI%3D</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7a127d9dd41c4ba8bf771d28d8e0f695.png</t>
+          <t>Lib\hardware\data\images\3c86e36b33514ec99135422b001f4c8c.png</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-stiker-tumbler-laptop-stiker-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-stiker-tumbler-laptop-stiker-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6173,17 +6173,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/356b601d-1120-43ac-bc8d-f91265fff9b2.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=JDHaQPCCcDHmrgXnnphN4oQsVjo%3D&amp;x-signature-webp=jcMdhwNjmDLhEOSr9eNLn6JOa%2BQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/356b601d-1120-43ac-bc8d-f91265fff9b2.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=4DOvuURuQ8D0MkdVaFJlpAdj7as%3D&amp;x-signature-webp=nLAKa7SbXR6xgmSczqh3TAOA9g0%3D</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ec130220510543da8161f68d3fb5b14e.png</t>
+          <t>Lib\hardware\data\images\1a4973d07019423ab27cdd8e15b2425b.png</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/java-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/java-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6222,17 +6222,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/28/82978a46-7432-4e38-9f63-c39dee0f3ba4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=EvKkAI6eB8GA6YentB07EjWtbDA%3D&amp;x-signature-webp=xzfQFD8nY97NRRdYBqJdTBGJn1Q%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/28/82978a46-7432-4e38-9f63-c39dee0f3ba4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=26MAOPI1URVTxMDEMC9Tk0sB1Y4%3D&amp;x-signature-webp=%2F5Rj1TewsJdqqfoj2bvt52lxRqw%3D</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0c8d2becbaf942d8b6910e9ccf8ffd4b.png</t>
+          <t>Lib\hardware\data\images\215aa0cd3bae44cc8737861907a1379c.png</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/stickerours/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6243,11 +6243,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>15608613564</v>
+        <v>15614737477</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IntelliJ Idea - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>Spring Boot - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -6257,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6271,17 +6271,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/3b45f322-32f5-4b0c-858f-59219a51c153.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=LWjFs0RDv2EX%2FzBFBy69rdfprL4%3D&amp;x-signature-webp=sUaKNtQyWej1s8fV7PlEWx7cRoU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/148d053d-e670-4ddd-bd5b-c5489f84c28f.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=xQPs1MQ4i74jrJAvXunNVm%2Fkibw%3D&amp;x-signature-webp=C1ZWkHorY98SZ4oEdKkzxPRGjTg%3D</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\79328516e79c4f839da51edea8cd817c.png</t>
+          <t>Lib\hardware\data\images\c0fc89aee974466183a4d7ba4e215316.png</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/intellij-idea-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/spring-boot-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6292,11 +6292,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>15614737477</v>
+        <v>15608613564</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Spring Boot - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>IntelliJ Idea - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6320,17 +6320,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/148d053d-e670-4ddd-bd5b-c5489f84c28f.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=xCBllS%2FZu6lXAMwewyHV3KJSX3Q%3D&amp;x-signature-webp=WZ9KNMq9fuvJHekDlLuZ0SGgXJ0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/3b45f322-32f5-4b0c-858f-59219a51c153.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=X2jdMED6VtdCeuzd%2FIKnvIOq6AA%3D&amp;x-signature-webp=gEiy3%2B6B%2BXZ4I7OdILrcFwGhVr0%3D</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\91af879ec6a24667aa37c2e0af2d1482.png</t>
+          <t>Lib\hardware\data\images\f1816da5da1e49beb0d40775dcc498a1.png</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/spring-boot-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/intellij-idea-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/bd6bf479-e882-4ed2-a264-28c75b168c29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=AGHHPN86VHeFiLohh%2BvOUfhr9IA%3D&amp;x-signature-webp=CvyYnTpeELzc2AZoQAUNEtW1h4c%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/bd6bf479-e882-4ed2-a264-28c75b168c29.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=X4MmZRePgC8Mex4LAbRUtTwDcM4%3D&amp;x-signature-webp=U4UMRW%2FimrcKO75O4uq87OLt6OA%3D</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d1fc26607aec43eca9d95ab3acba6260.png</t>
+          <t>Lib\hardware\data\images\8e143c95fd4d4669afc07696cb661646.png</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/css-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/css-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -6390,11 +6390,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>15029253978</v>
+        <v>15614711766</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Meta - Sticker Laptop Programming Vinyl Waterproof</t>
+          <t>PHP - Cutting Sticker IT Programming Stiker Programmer Coding Laptop</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -6404,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6418,17 +6418,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/722bc896-e581-4919-9192-737948477d10.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=WCWNDmZcKEVMFUf%2F0teuqAnPwGg%3D&amp;x-signature-webp=DcSBOoM3iQ7gMs6yuG4sQb2pd4M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/32a21bef-6229-4a57-8094-a707c4210ac4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=TPM3NveihL42MoElurC2%2BEl8DGY%3D&amp;x-signature-webp=TAeJ3ykj7FxbY2naWX964VC8UrQ%3D</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\317ce037ad744499a438fb66201ad6b0.png</t>
+          <t>Lib\hardware\data\images\c0ccf4c394df42019cdc0d88b398be5b.png</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/meta-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/php-cutting-sticker-it-programming-stiker-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -6439,11 +6439,11 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>15614711766</v>
+        <v>15029253978</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PHP - Cutting Sticker IT Programming Stiker Programmer Coding Laptop</t>
+          <t>Meta - Sticker Laptop Programming Vinyl Waterproof</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -6453,7 +6453,7 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6467,17 +6467,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/32a21bef-6229-4a57-8094-a707c4210ac4.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=ikX5XkFrc5uua4TnAL9hb47E6sA%3D&amp;x-signature-webp=KP8a3cZ26K3R4vhmgwhknhEyUIU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/722bc896-e581-4919-9192-737948477d10.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=WA5jgYbRJvcFYTfeJBhNUJ57ipw%3D&amp;x-signature-webp=Q1gJGjzBAsO0q6eBilxrOJ74cEE%3D</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b65a419640044150949e06f34fdc9f55.png</t>
+          <t>Lib\hardware\data\images\b64472373f7f4dfa85154bc0f762654a.png</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/php-cutting-sticker-it-programming-stiker-programmer-coding-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/meta-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/247f6d04-d1b7-4b0a-b69d-44df83a98403.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=qF%2FmVGisgxoS%2FeSmDJYhVAHEzLw%3D&amp;x-signature-webp=i%2BIhVM1Pzix8WPenUsTbYZSfq04%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/247f6d04-d1b7-4b0a-b69d-44df83a98403.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=kKozr5l0sQZkdjnZquX7grjooJE%3D&amp;x-signature-webp=ks%2FVQlSEkP5J5Og7Sp6OxwimSnY%3D</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\481ca9433d164cfba09b2681a8f4f3be.png</t>
+          <t>Lib\hardware\data\images\84ef16cb41b4448aa0bfa9358584645d.png</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/ubuntu-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/ubuntu-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/fd492c8b-c24d-42f6-9532-4ec429fe91c5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=xfOvv%2BK%2Beq%2BazSEafS7FyVwTSW0%3D&amp;x-signature-webp=2mNmMSGXDBTRgyGOZ8wcbBB9KiU%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/fd492c8b-c24d-42f6-9532-4ec429fe91c5.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=SXORFr0L1es3PpF3JHggtuYCRqU%3D&amp;x-signature-webp=s%2BPRh5CkEN5R%2FFdBgWygqfakmv0%3D</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4e5c8858a58b4fb4bf63dd217ba9c0a8.png</t>
+          <t>Lib\hardware\data\images\249305444b9c4492a60a161df6765489.png</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/kali-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/kali-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -6617,17 +6617,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e016ed68c334c7cbc4f8e994d90718b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=E%2BOz5xQ5X7kdQk9Ks%2F0cGjMaGjc%3D&amp;x-signature-webp=SYvYqEw%2B%2B2OQOdSVOdGavuNMvD4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9e016ed68c334c7cbc4f8e994d90718b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=FnKPJPh6rg8nV4YlKgaNQ6GC2oc%3D&amp;x-signature-webp=h%2BkV8ODqXa32uBwyeDn%2FejFrV58%3D</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\70b4987d7fbb4a1890d5f589e61ddce3.jpeg</t>
+          <t>Lib\hardware\data\images\6ed8eebd8e984dc181b335ed848fd6e1.jpeg</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/indoluxdigiprint/programmer-sticker-pack-50-pcs-stiker-code-komputer-anti-air-sticker-coding-computer-it-programming-laptop-hp-paper-1729751165829088355?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/indoluxdigiprint/programmer-sticker-pack-50-pcs-stiker-code-komputer-anti-air-sticker-coding-computer-it-programming-laptop-hp-paper-1729751165829088355?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -6666,17 +6666,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/6dc31a5b-13dc-461c-affd-cb836b3d7649.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=rYKszUSDnx7ZU35pHerWysERNko%3D&amp;x-signature-webp=FEKoqQIzWA4QNJyjhlrQJqcJeTQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/6dc31a5b-13dc-461c-affd-cb836b3d7649.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=2eFRoHOKgJWE8Hxtlalv14K4R9M%3D&amp;x-signature-webp=8Ww7iQuq%2B1tuuI7Sva5nMvMoE5Q%3D</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3e1fbfd0c3564453b506365d08e548d1.png</t>
+          <t>Lib\hardware\data\images\3c0db0bc2be74ee3878194990d00547f.png</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/html-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/html-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -6715,17 +6715,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9e56cad1-941e-4da1-b48a-271cbe36ab77.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=acI8QC6yFDl4VForObFjMiYQJK8%3D&amp;x-signature-webp=C4xsf%2BfCzHRvv2vpu76cZS85wfQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9e56cad1-941e-4da1-b48a-271cbe36ab77.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=NmXq9mmpZcdbpTm%2FmjBc4858gzI%3D&amp;x-signature-webp=jNz89tOW%2Bi49woAsrsKVkieyB5s%3D</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\708c37f18d44469799f1e5a6f6baf071.png</t>
+          <t>Lib\hardware\data\images\72d461eb52b74c7dae552ae804089ac4.png</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/debian-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/debian-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -6764,17 +6764,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a26ba20e-d4b0-45e2-8d41-247e37e6a478.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=EvJeTmDdOu%2FcCB51Q7BOhjTKPzc%3D&amp;x-signature-webp=dCqGFRU4Y%2B4IWOxwvirJM6Xip3g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a26ba20e-d4b0-45e2-8d41-247e37e6a478.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=u4pO5qrgiejlnNp62wgDC9ATijY%3D&amp;x-signature-webp=Tuo%2FF8FgZWyIZsG2OolRD0ajSbg%3D</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5079294dd229409d9cd63c7608a31ef1.png</t>
+          <t>Lib\hardware\data\images\15be2d689a9147ed8e399309c6f75a9e.png</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/cpanel-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/cpanel-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4aa5f4f-ae42-4541-81f3-1421c0a92ee8.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=uHjb9znLh%2BZZLCTZTf1kRMbaCng%3D&amp;x-signature-webp=FgFz7x79MvMa%2BSEP7wwW2er%2Bagw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4aa5f4f-ae42-4541-81f3-1421c0a92ee8.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=oPpSbu9xST7cOdDVQzSESS%2F%2FGnA%3D&amp;x-signature-webp=PXKd0%2F42GxMk8nksV6gk4ID3Vfw%3D</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\68186272887b453a856491ca1885ffe1.png</t>
+          <t>Lib\hardware\data\images\8649a5beea1d42028ca46201eb66ef5f.png</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/js-javascript-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/js-javascript-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -6834,11 +6834,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>16316426699</v>
+        <v>15608655266</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Python Language - Sticker Laptop Programming Vinyl Waterproof</t>
+          <t>JetBrains - Cutting Sticker IT Programming Stiker Laptop</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -6848,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6862,17 +6862,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4f53049-4d44-4b49-ae9e-b4a06d7aa864.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=f19ZwV%2FSemLzjPNDjp7mvmRnw9c%3D&amp;x-signature-webp=Uh8ZJXEHmqOIz9yG%2F20MfPvD6zo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9441c648-abf5-4189-bda6-523c5625881e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=6ncU4xauMQUa7TlK9NdQZUXtlOw%3D&amp;x-signature-webp=98vT2RzOBcALsx7sT09jyn1imsc%3D</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0517c2bbe88e43d39c8c8507b4ea1679.png</t>
+          <t>Lib\hardware\data\images\00f62dec82a24b2b9a03a2228288375c.png</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/python-language-sticker-laptop-programming-vinyl-waterproof-1730910518060090930?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/jetbrains-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -6883,21 +6883,21 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>15029163749</v>
+        <v>16334892715</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>C++ (Plus Plus) Language - Sticker Laptop Programming Vinyl Waterproof</t>
+          <t>Android Developer - Cutting Sticker IT Programming Coding Programmer Laptop</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6911,17 +6911,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/52e270bf-8f13-4743-989a-135d563c7c13.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=FvOJyh5twsVcbUsX3XtJbPYqFQo%3D&amp;x-signature-webp=VqKZiiHK4PBQfLTWxpAXMldelW8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/487fec30-5abd-485d-90e1-97aa59e4dc8e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=%2FMBa2Y%2F1EcPxxGT3a9vyWzAPUVY%3D&amp;x-signature-webp=ahx7N3HIzVLizn2f1GHdl8vJ3%2FU%3D</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\97d2e19d50c44df6a73774c18847bd32.png</t>
+          <t>Lib\hardware\data\images\c6ccdc8274a2467abb1581eb053f917d.png</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/c-plus-plus-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/android-developer-cutting-sticker-it-programming-coding-programmer-laptop-1730925852202665522?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -6932,11 +6932,11 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>15608655266</v>
+        <v>15029163749</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JetBrains - Cutting Sticker IT Programming Stiker Laptop</t>
+          <t>C++ (Plus Plus) Language - Sticker Laptop Programming Vinyl Waterproof</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -6946,7 +6946,7 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6960,17 +6960,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9441c648-abf5-4189-bda6-523c5625881e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=s6CmK7mmiisf9e1n2EoPYFxZ5nk%3D&amp;x-signature-webp=hoksGo%2B0jTMrS369ybxoGUH7zds%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/52e270bf-8f13-4743-989a-135d563c7c13.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=TYSDDbcAcjIjShqQQN4cVvBItDg%3D&amp;x-signature-webp=em%2FWX08ImzXSZZANekg7GCGTNxQ%3D</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\53798eb063fa4dd792a37acd0ddff77e.png</t>
+          <t>Lib\hardware\data\images\1623c941f8b647bdb3aefde228ac0032.png</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/jetbrains-cutting-sticker-it-programming-stiker-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/c-plus-plus-language-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -6981,21 +6981,21 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>16334892715</v>
+        <v>16316426699</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Android Developer - Cutting Sticker IT Programming Coding Programmer Laptop</t>
+          <t>Python Language - Sticker Laptop Programming Vinyl Waterproof</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -7009,17 +7009,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/27/487fec30-5abd-485d-90e1-97aa59e4dc8e.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=CUw36cfM5UYSPs3Rid9a%2BrMVoNw%3D&amp;x-signature-webp=cUk7fdpH6az8ZJMUoM9MtU85xF4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/a4f53049-4d44-4b49-ae9e-b4a06d7aa864.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=ew8cZfBPDdGB0E5vZOobVM%2FKtBY%3D&amp;x-signature-webp=eukfEx5yHznTM93GAxKAvajKVXQ%3D</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2d4d5e17964b40e0bcbb9f4a8d0016b9.png</t>
+          <t>Lib\hardware\data\images\a8e5495c75d642cd92981f8c0ab1b0b3.png</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/android-developer-cutting-sticker-it-programming-coding-programmer-laptop-1730925852202665522?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/python-language-sticker-laptop-programming-vinyl-waterproof-1730910518060090930?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -7058,17 +7058,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/5e031a76-a3f2-4fc1-940b-4150386d8618.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=zjs5RbKwVcVUnPJvJ7zdBbQxPLg%3D&amp;x-signature-webp=5Wlf0kHD8OWJmUDdgza4Sb%2Bhv3w%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/5e031a76-a3f2-4fc1-940b-4150386d8618.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=QgVoTfa0PbHnBKzeJIE%2FmPAbOsU%3D&amp;x-signature-webp=9J0HqSWmJSxmbkmpi0zjz2JnCq4%3D</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\731a0fe3916d4866be361d2c5ca074c4.png</t>
+          <t>Lib\hardware\data\images\3de950463f844976b8b12bf48dd6295b.png</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/tux-linux-penguin-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/tux-linux-penguin-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -7107,17 +7107,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9f70aa88-0b3e-4f1a-b1e2-ff8c1f724f83.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=aIBnysuMKKlSE7GxuZY1BWMmvTw%3D&amp;x-signature-webp=QLWsAmd5tGsg8nlTPKNERzHl23w%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/9f70aa88-0b3e-4f1a-b1e2-ff8c1f724f83.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=gZKMGBxLYIP3VKKL1FfBMeGiMfw%3D&amp;x-signature-webp=oytb%2Bfhg2lYUshd6XAuFXCD3Vx8%3D</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\83f83d6ad1eb4d149063f99738f0d933.png</t>
+          <t>Lib\hardware\data\images\42e7c0aa28e24c52a1063047cbae5f6e.png</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/google-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/google-sticker-laptop-programming-vinyl-waterproof?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -7156,17 +7156,17 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/05097cce-f0d3-41a1-9a3e-dc787f21a1bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=gu2OCqohf8usN1YbeB2iGjQODDs%3D&amp;x-signature-webp=edK4G%2BdYYXyZRxoUxbtGOZYsfg0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/05097cce-f0d3-41a1-9a3e-dc787f21a1bf.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=ZyPScztjpJsFiqSZYJu3O4rwEYU%3D&amp;x-signature-webp=YvpqrrCK%2F6d0JV89O6Y89%2F1i0wg%3D</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\bd765a3b08714f1d871ecd89c805aedb.png</t>
+          <t>Lib\hardware\data\images\d9e30dbd70da49de9e550718dec34b06.png</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/arch-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan-1730778695673939506?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/arch-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan-1730778695673939506?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/d2e910e6-71e1-493a-9ad0-7e644045fa68.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=9zGfP7ZTVRYS3BLKhKlxUv7oEys%3D&amp;x-signature-webp=ACOlM4bSMJdzyr7cwkTL1JlQE9k%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/14/d2e910e6-71e1-493a-9ad0-7e644045fa68.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=DJbdGHbCFPCq68QDdSNZAsB7OKQ%3D&amp;x-signature-webp=aIPw%2B%2BGB%2FDs9V1U2M4Zp6VDcC9o%3D</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\237f8a5fef6d4a26b2307028da04de32.png</t>
+          <t>Lib\hardware\data\images\91f97b7701ea4ccf84e736ed6dd97cb4.png</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/iq-sticker-co/fedora-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/iq-sticker-co/fedora-linux-cutting-sticker-it-programming-stiker-programmer-coding-laptop-stiker-satuan?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/9/29/f8d3eab6-1d0d-4a33-8e74-ee48be7014e1.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=F5Qa94qg%2BkvX96EKMG6tlukZV6U%3D&amp;x-signature-webp=lKJ%2BNx%2F2ycoDMhIIoLrFFnAk9jc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/9/29/f8d3eab6-1d0d-4a33-8e74-ee48be7014e1.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=j3%2FbiLAAcc1ibMnOpfIkKwiaYpM%3D&amp;x-signature-webp=%2FbRWTjf63uprHgsi%2B72ghYh7gmE%3D</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7c8bf7b278e843ab8587d730f7b0f927.jpeg</t>
+          <t>Lib\hardware\data\images\ef0e213336104ee7b92a9092f3e65716.jpeg</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/archive-zhanghua-1630738705/stiker-programming-java-php-linux-bitcoin-ubuntu-geek-untuk-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/archive-zhanghua-1630738705/stiker-programming-java-php-linux-bitcoin-ubuntu-geek-untuk-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -7303,17 +7303,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/d7dbbf07-cde0-4b81-a809-7c268bac8704.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=7n%2F3tjPjRRtaFjKxicQ8Vad9z4s%3D&amp;x-signature-webp=Czib1NKOsbiXFWaYOUj6VL2XJmI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/8/d7dbbf07-cde0-4b81-a809-7c268bac8704.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=L40ZWEWZNfyaFsbK9OeCZwovGCU%3D&amp;x-signature-webp=%2F88sjU5NBKXvQSrZ5suX1usHluo%3D</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7ee1dff1dc7f4a4ea081e83726537c82.jpeg</t>
+          <t>Lib\hardware\data\images\76359d3bf20348919233e76e64da6bee.jpeg</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/coffee-sleep-coding-game-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/coffee-sleep-coding-game-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -7352,17 +7352,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/3c9c2511-b651-4389-846a-da1c078d510d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=xjH5a0nwVPc8E%2FhVl4J6KiiCGn8%3D&amp;x-signature-webp=EV7YhIIm7wixM1S0FSNOIZtaNXE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/3c9c2511-b651-4389-846a-da1c078d510d.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=pxMbwYySBYkbwaQfe3sCfesqts4%3D&amp;x-signature-webp=XAc%2FXmYqw11oeE9ZZPMAvZxNKGw%3D</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\65106fe776564988b31cbec84ba85510.png</t>
+          <t>Lib\hardware\data\images\7bb9909f33fd4ed787523bfa09f0aae3.png</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/sticker-sheet-a6-vinyl-waterproof-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/sticker-sheet-a6-vinyl-waterproof-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/c6cbe66b-30fb-4b15-9a7b-cdba7bdb6344.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=gIYPa3o0oyGgqMkqEFEZS4klAlQ%3D&amp;x-signature-webp=YPJcBhAMj14%2B4v0TYbva9p0AryQ%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/7/21/c6cbe66b-30fb-4b15-9a7b-cdba7bdb6344.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=%2BS4nlbjsJS8KzptXjakmR8sIj0Y%3D&amp;x-signature-webp=JQcdB43%2BFDq%2BeLfM1%2FkZrzgUp3Y%3D</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\926e827095a44f7da99a6043ff71764d.png</t>
+          <t>Lib\hardware\data\images\c423fcd0aef84a338ce07e3f5fe4769a.png</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/texhgoods/full-stack-developer-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/texhgoods/full-stack-developer-mug-gelas-programmer-developer-programming-language-bahasa-pemograman-komputer-teknologi-it-coding-aksesoris-gaming-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e83fe7fc87c4ce6ad067de5078f19f5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=IN6SMKCODZMuooEkJyaO7VDR3wA%3D&amp;x-signature-webp=q4Xkg61%2FCp%2B0XsV0UbRkjlL4W50%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/6e83fe7fc87c4ce6ad067de5078f19f5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=VqbGI9ajuPHVEiCAib35jIbBoxk%3D&amp;x-signature-webp=6iGeSH%2BQsS6GkIaiu0AupwFTxkc%3D</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a8ed407dba234532918e6328851578c9.jpeg</t>
+          <t>Lib\hardware\data\images\514c822be3da4e978102a73589b5772e.jpeg</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-untuk-scrapbook-tumbler-hp-laptop-motor-helm-koper-1730766186130146514?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-untuk-scrapbook-tumbler-hp-laptop-motor-helm-koper-1730766186130146514?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -7505,17 +7505,17 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/364156f76e624431b6c3dc72dd64ecdc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=RwRYi1rryt08K81lw4pwMBnQ32w%3D&amp;x-signature-webp=Bv5MMqLmtFdH2DPhb9xAWIZM7IY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/364156f76e624431b6c3dc72dd64ecdc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=o2a8ODTEjn7oKDaulgZTbrgjMBg%3D&amp;x-signature-webp=grCFV2IpVMDi6gfoYCq0QKWo6h8%3D</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c105d7cdc3574440bfc3405f78bd572c.jpeg</t>
+          <t>Lib\hardware\data\images\dfc92925564f43aabb62f7bdfe9a25dd.jpeg</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-meme-plesetan-untuk-scrapbook-tumbler-hp-laptop-koper-motor-1730770027949688018?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mizoku-art/sticker-pack-anti-air-programming-programmer-meme-plesetan-untuk-scrapbook-tumbler-hp-laptop-koper-motor-1730770027949688018?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -7554,17 +7554,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/265be12a-181a-4c2e-85ad-c6544f36203e.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=kRjTQFDjN%2FK%2B52Adi%2F30xoNktyU%3D&amp;x-signature-webp=4OnftUqqxvxlc7LrbsIe%2BZHUjTY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/265be12a-181a-4c2e-85ad-c6544f36203e.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=Q0DGqp0I5MFyxk6kOSVjPKb%2FjkU%3D&amp;x-signature-webp=IFIrv8vK8XHEs6BpwhQxv2YJlJI%3D</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\30756f122c2a48ffb4139a11c75e4600.jpeg</t>
+          <t>Lib\hardware\data\images\53b6d0a751b74006957ff1289990b075.jpeg</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/vnylarc/saas-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/vnylarc/saas-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/4020a1f4-6c92-4356-8439-3db0af377f5f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=1QwBD7DTxQD3R6IEcK4W%2BtaOjNM%3D&amp;x-signature-webp=ViStWLy%2FhWS2omA7CER7d7Pehvc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/1/2/4020a1f4-6c92-4356-8439-3db0af377f5f.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=ySnFJWN94EAqTmNmzarDJQUgy5k%3D&amp;x-signature-webp=w30jYmnmGY7XA1r8s7I9%2BekzQc4%3D</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\664d9d08ed4547239ec5e30d1f9fb8bf.jpeg</t>
+          <t>Lib\hardware\data\images\c4b45c12a09b4a8c9e23678e49d76222.jpeg</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/vnylarc/golang-icon-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/vnylarc/golang-icon-it-programming-coding-cutting-stiker-sticker-laptop-tumbler-dll?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -7652,17 +7652,17 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/4/4d205830-0c3f-4681-a668-c1d10845afb5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=91VPzA4rW8xdNtArwbL4FFwAYt0%3D&amp;x-signature-webp=RQbZ%2BGjZpSDRM9C3QdplKb4ig%2Fk%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/4/4d205830-0c3f-4681-a668-c1d10845afb5.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=W%2ByaCl9gFbN87e6f4ztN0ol8QRk%3D&amp;x-signature-webp=10GZL%2BsDBKtgG38kOWF%2BWVxoKXg%3D</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d3938afab9a742afb4b9fa3da3127e08.jpeg</t>
+          <t>Lib\hardware\data\images\83cecd7f405145899f18b943e899aca3.jpeg</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tokopedia-tokolaris/sticker-pack-20-pcs-teknologi-programming-untuk-laptop-tumblr-helm-first-edition?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tokopedia-tokolaris/sticker-pack-20-pcs-teknologi-programming-untuk-laptop-tumblr-helm-first-edition?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -7701,17 +7701,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/0bd6c17c643c4ba8875360f0f7dedf05~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=P3wH5ELz%2BjePVeo9bzAXc4bnCZE%3D&amp;x-signature-webp=CmNdZvAV5QXRKuTuiV3%2FtGpjiBM%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/0bd6c17c643c4ba8875360f0f7dedf05~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=l6J%2BsgZzjBkTBogYvqj8jo3cD%2Bw%3D&amp;x-signature-webp=PN86ikzVcTvsq33TTVhsqUs64uQ%3D</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\83c9bc137b9a46528954a0babff24c03.jpeg</t>
+          <t>Lib\hardware\data\images\84c242b93cbf48c3852b68f3de15cbb2.jpeg</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programming-2-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -7750,17 +7750,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fe66c8e873de4883aa66c310f1cb065a~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=fAGfw1Vg7YmYRldsjVXuLpVDs9g%3D&amp;x-signature-webp=wDbQrUhlqTUea10H3v5Sy3GbSpE%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/fe66c8e873de4883aa66c310f1cb065a~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=AqzObY8sEaGttdvbapZK%2FvL0FAE%3D&amp;x-signature-webp=AD4rVTN%2FGvPBh3Bcfbmdhzyixo0%3D</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\ad19e4d5e45c4ae98de3e437a5eb8a40.jpeg</t>
+          <t>Lib\hardware\data\images\610dbdeaf87f4171bb8a3e61545860fb.jpeg</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programmer-coding-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/influincmerch/sticker-pack-programmer-coding-sticker-tumbler-stiker-laptop-koper-helm?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d1f458121310473e8394b993711abd3b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=%2F0p0qB%2BhHFXdZAS%2BM0oLrSmiI8k%3D&amp;x-signature-webp=iZK9Ecsbo3uX8MpG809NA9o8HNk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d1f458121310473e8394b993711abd3b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=CRe34FrIpHCMK4zeGmuw3CvqHf0%3D&amp;x-signature-webp=tmJMXZWxhgl%2Ff7X%2Fgd3OG0NLADQ%3D</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9e1b7717aaa349beb3819868a604a6d3.jpeg</t>
+          <t>Lib\hardware\data\images\5be9ed0deec043999e687656a61ab228.jpeg</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/auto-diagnostic-programming-tool-expert-mode-for-icom-next-software-v2023-09-1tb-mini-ssd-windows10-laptop-cf-ax2-8g-d-4-43-1732688398569998202?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/auto-diagnostic-programming-tool-expert-mode-for-icom-next-software-v2023-09-1tb-mini-ssd-windows10-laptop-cf-ax2-8g-d-4-43-1732688398569998202?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -7848,17 +7848,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/10d441e1e3db48d184effed1bc09575b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=tkl%2FCkxgqkfuvphAVTREHWDdjwE%3D&amp;x-signature-webp=IbBsNh7oWxI8q3D%2BDFYRV3Zn9lg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/10d441e1e3db48d184effed1bc09575b~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=xxZZtizPh7hr2M0KBV7q31Rh5wk%3D&amp;x-signature-webp=33noO9ccBE02i%2BI7RAKrOeAQgpg%3D</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9a39743583f74e15ba503fa135147082.jpeg</t>
+          <t>Lib\hardware\data\images\a0cd1aa741114611b18b9c3516bd689b.jpeg</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/new-for-icom-next-a-b-c-with-v2023-09-software-expert-mode-installed-d630-4g-laptop-for-icom-next-programming-tool-1732688989206054778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/new-for-icom-next-a-b-c-with-v2023-09-software-expert-mode-installed-d630-4g-laptop-for-icom-next-programming-tool-1732688989206054778?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -7897,17 +7897,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e5f3a470390d4bcc88c465e59babd2ea~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=Z6sGaVlzjuLJkPcSYC%2BbmKGMQkE%3D&amp;x-signature-webp=F6DevEzZoT6%2BCHWVMt5xnrMRaXw%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/e5f3a470390d4bcc88c465e59babd2ea~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=xMH0mTMoxPj2oemIC5dOYu8O5TE%3D&amp;x-signature-webp=EYh2TGYhVW8uEf3YdxqIh%2FMm87c%3D</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4d996eb07b9a49259c223fb6628f53aa.jpeg</t>
+          <t>Lib\hardware\data\images\c253b321464d4be38449767e2d51167c.jpeg</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/cfc2-laptop-for-jlr-doip-wifi-car-diagnostic-tool-support-new-car-profesional-auto-programming-tool-1732690386628020090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/cfc2-laptop-for-jlr-doip-wifi-car-diagnostic-tool-support-new-car-profesional-auto-programming-tool-1732690386628020090?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -7946,17 +7946,17 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43b554c10baa4e20a7f9e75f23312185~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=elw9iBTTlT2Z2zHJEb9q3vYS%2FXI%3D&amp;x-signature-webp=FkOgGBKFJlWCeynVSX9RMMDe%2FMk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/43b554c10baa4e20a7f9e75f23312185~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=VFBaywQXLolf2uQCnWR6jcgKiHg%3D&amp;x-signature-webp=0Tv8k%2FY%2FXkhYMC5UHmV0SXYILpY%3D</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1c2bdae39e87404cba7895513e32d4b6.jpeg</t>
+          <t>Lib\hardware\data\images\ab419ab9aae749e989bb79337f4aae76.jpeg</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/car-diagnostic-tool-for-jlr-doip-v-ci-wifi-with-cf19-laptop-support-new-car-profesional-auto-programming-tool-1732690368491587450?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/car-diagnostic-tool-for-jlr-doip-v-ci-wifi-with-cf19-laptop-support-new-car-profesional-auto-programming-tool-1732690368491587450?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -7995,17 +7995,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c27b24e4e8a149f8afdec0aef9a21471~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047499&amp;x-signature=Fz5UP9WOH0I4%2FDYEHFPHR%2FIPXxM%3D&amp;x-signature-webp=fdsdwst3wlwHIaZI6vXHxr5Dkss%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/c27b24e4e8a149f8afdec0aef9a21471~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047793&amp;x-signature=0LWU2rZm7fBqzjPAyKJU2rg9Utk%3D&amp;x-signature-webp=L4bhmuu0IYb8co0YiGbdLMPtEZY%3D</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b85cac57405c4025b1b17538f9f5e934.jpeg</t>
+          <t>Lib\hardware\data\images\5b5984f426f74874945b30d04a62cf5f.jpeg</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/arknights/for-icom-a2-with-full-cables-professional-for-diagnostic-programming-tool-with-software-720gb-ssd-win10-in-x220t-laptop-1732688342876587898?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D202511250411385B8ADD2A5D98B1358DXK%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/arknights/for-icom-a2-with-full-cables-professional-for-diagnostic-programming-tool-with-software-720gb-ssd-win10-in-x220t-laptop-1732688342876587898?extParam=ivf%3Dfalse%26keyword%3Dlaptop+programming%26search_id%3D2025112504163358238E9AE2DD301E8IRT%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -8047,17 +8047,17 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/0e0094f8-4e21-4aab-b63e-25e6f39a9a2d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=qcncaOvRYAgTHtXdOMmSAbVL9gs%3D&amp;x-signature-webp=JjxGS8zyRQVY0SL93r%2F8aCIA%2FSs%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/0e0094f8-4e21-4aab-b63e-25e6f39a9a2d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=wSb4Pz2BNInmzITaMjcxxp2yVHE%3D&amp;x-signature-webp=w6x2JtGGw6vU7iSHnroHnZUjvPg%3D</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7e7b50ebd8234cca8d9d2b46af14f0f8.jpeg</t>
+          <t>Lib\hardware\data\images\35be2a3b24c44a898437d9926398179b.jpeg</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/housesparepart/jakemy-jm-8183-145in1-obeng-set-hp-torx-laptop-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/housesparepart/jakemy-jm-8183-145in1-obeng-set-hp-torx-laptop-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -8096,17 +8096,17 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/18/2e15fe28-10bf-41e9-868d-6cb423cd4c8c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=QxznoELXg9S2N2MUmIOU8XFwLlI%3D&amp;x-signature-webp=9TLrwipt1HExS637yLzze8a1dNg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2025/2/18/2e15fe28-10bf-41e9-868d-6cb423cd4c8c.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=CbkZ%2BUmagt4KCzJl1I%2F%2FkHES6DE%3D&amp;x-signature-webp=4xW3bBMMG39nZilREslE0wTMS2g%3D</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b90d62a7e42447e4ae9f1fa34edbb328.jpeg</t>
+          <t>Lib\hardware\data\images\1c0f39721e6242a6b452d6303a7b6502.jpeg</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/ezren/jakemy-jm-8183-screwdriver-set-hp-torx-laptop-computer-new-design-145in1-1730880897306690560?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/ezren/jakemy-jm-8183-screwdriver-set-hp-torx-laptop-computer-new-design-145in1-1730880897306690560?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -8148,17 +8148,17 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/660a3068-b7f9-418c-8ac3-25c629b1e0c7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=U5EEYwkF4fBMv5hOgHSM0V51eGc%3D&amp;x-signature-webp=UzqaE0YoSitlMKukDZXE2vIy4wM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/10/11/660a3068-b7f9-418c-8ac3-25c629b1e0c7.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=WVqzDGNufdDGbfCWzNdWKPGMdck%3D&amp;x-signature-webp=FrgNvmw7Es3bRKuqrRObyxH9zso%3D</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\f6862267ac0a4eb9ad449fa7cc4e2c9c.jpeg</t>
+          <t>Lib\hardware\data\images\a612c5f1dc0f40ab9172c70b7558c685.jpeg</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jakemy-official-store/jakemy-jm-8183-145in1-obeng-set-hp-laptop-macbook-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jakemy-official-store/jakemy-jm-8183-145in1-obeng-set-hp-laptop-macbook-komputer-new-design?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8200,17 +8200,17 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=g33bqfOHOh7mKNrYc5dZuE%2BPy3A%3D&amp;x-signature-webp=H%2BYsiS6JZOZEnUgdxWInr62hnDM%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/294d068d13174f7c82507afaebd42652~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=8Ky6wk0bXDHmMZSmRVITCAuq7cw%3D&amp;x-signature-webp=HWVoOCh8xfDY5CoxGcZmzPcPqoQ%3D</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0a11c5db0476426a838e7bc41d1cabac.jpeg</t>
+          <t>Lib\hardware\data\images\ba755e6ccb61405a9e49c3d3cb25dd4b.jpeg</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/jertech/speaker-2-0-gaming-komputer-laptop-jertech-s4?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8249,17 +8249,17 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f261db1a485a484fb269a53c633ed896~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=oszW8RHu0rDokjxqJ0LoXDqWO7A%3D&amp;x-signature-webp=t3f1OoT8986qGc3J9vc5lS0BtYI%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/f261db1a485a484fb269a53c633ed896~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=%2BANfVLp%2Fa80iTSlCXfLj4cc8vsA%3D&amp;x-signature-webp=9jUqD6X2KSw8kIsNy239wnC%2Barw%3D</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\dd0b250ad5334c08826366cea84ef87f.jpeg</t>
+          <t>Lib\hardware\data\images\aa4e28a7e2184d428aee71e823e79624.jpeg</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/bobby-soft-daypack-water-repellant-backpack-by-xd-design-tas-ransel-laptop-original-unisex-black-bfd8e?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/bobby-soft-daypack-water-repellant-backpack-by-xd-design-tas-ransel-laptop-original-unisex-black-bfd8e?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -8298,17 +8298,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/8b7fcd6f-843a-4f43-9ed7-23b395be8bf8.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=%2FDlw6vuOqivafUfdw6v7C4DC%2BeM%3D&amp;x-signature-webp=XqSjEtQLI0zm48Uet5i4XKZ3awc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/8b7fcd6f-843a-4f43-9ed7-23b395be8bf8.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=mMohfA2XJHXtTvv6VNtWJLU1pk8%3D&amp;x-signature-webp=Ygu9pyg1ikDVGCXWCXvHj0dcCK4%3D</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\eab7fd671bcc4771a5a358a12ab26118.jpeg</t>
+          <t>Lib\hardware\data\images\7ffcf9be5a784b218da824bc3f87da38.jpeg</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-bag-black-1731594664039319238?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-bag-black-1731594664039319238?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -8347,17 +8347,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/32274fe1-96e5-4c4b-b9a1-8a54ed3cd196.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=kfD%2Bo6ViaJ1hUYFP9dvyRPKy06w%3D&amp;x-signature-webp=pz%2BKKowIiacIIfvvrFUWxP%2FEEi8%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/1/3/32274fe1-96e5-4c4b-b9a1-8a54ed3cd196.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=AIhDvFi9LxwO9qoDX0WCmJwjWFs%3D&amp;x-signature-webp=sPWX1OgUqLZQmOGSUrMc8TWPoe4%3D</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\1b975a00a55f429c9fd8a5dcad2c86fe.jpeg</t>
+          <t>Lib\hardware\data\images\98938c53d5d948299b3e331171eb6d5f.jpeg</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-sleeve-1731594608912926406?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/xd-design-laptop-sleeve-1731594608912926406?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/20/d1423af4-f39b-45ce-a5e1-4e98654a57a9.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=7yL8JPerLSpxRz4nOqP9rTw3pJI%3D&amp;x-signature-webp=5sONKb7%2FYbo2LiEzroEb5D4dA0E%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/6/20/d1423af4-f39b-45ce-a5e1-4e98654a57a9.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=js0ah1PuxQtKJ98TSTNdRyZSbkc%3D&amp;x-signature-webp=EHqkAfa%2FfVlixhg84uCYBrsovEU%3D</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7b01f268038241fba71c45fd017a3d5c.jpeg</t>
+          <t>Lib\hardware\data\images\c8ca7b61efc4464cb57f912a935f491c.jpeg</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/xddesign/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-laptop-original-off-white-987cc?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/xddesign/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-laptop-original-off-white-987cc?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -8445,17 +8445,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/74672521-d63c-4345-8d7c-1a4c6d44107d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=tFxZdfAqJeATTBVXpjj62qa1p8Y%3D&amp;x-signature-webp=FgJYJ6PH73F57QEqjUhOxe8CNpY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/74672521-d63c-4345-8d7c-1a4c6d44107d.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=f%2FgR3EyeyJJR7SHneExgCY9Rskg%3D&amp;x-signature-webp=gk3%2B23VVsybZf3PG8Y3QU2GGCYY%3D</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\82c1b3e52e1c4ba6a9a382f60e9c5753.jpeg</t>
+          <t>Lib\hardware\data\images\136974c0e52b4cffaa656fa9e6f7ff2a.jpeg</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-14-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-14-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -8494,17 +8494,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/0cb9f188-7016-4eff-b964-b13b4f39e7be.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=A8bxQ44CBfSS4s39l1bBi%2BBPf1k%3D&amp;x-signature-webp=WRsuUtL84p02WYZvyhmERQuFGWc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2025/2/27/0cb9f188-7016-4eff-b964-b13b4f39e7be.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=m5rPMOLRYCAZUi2WlUhpLeAcPHs%3D&amp;x-signature-webp=kGUKs4UIFcOghe6zlWw2B1guPRY%3D</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\97e51951c0a8418ca6fd17c3874248a7.jpeg</t>
+          <t>Lib\hardware\data\images\497f3a2ae0774dc98847651c856c0a0b.jpeg</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-15-6-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/tanaga/wiwu-minimalist-laptop-bag-15-6-inch-simple-design-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -8543,17 +8543,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=Tjv7UFx%2FQYtMeU7soCcwTCzMAsQ%3D&amp;x-signature-webp=qej7m8r5TbxqqA6pMQ8WT7qaWZ0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/12/26/69dc73cf-8cda-40ca-b701-0dd3fe91f7aa.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=gBGe5br8WEH0TuBmv60ZU9ubrso%3D&amp;x-signature-webp=8GOepbi3B%2BWFGCjYcUZkkcx88GI%3D</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\858c149d0e784970be5cea899f27eec9.png</t>
+          <t>Lib\hardware\data\images\63d57b721d3648559378fead278d852f.png</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-kabel-usb-portable-office-business-ergonomic-design-untuk-pc-laptop-mou21-blue-8bc5c?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -8592,17 +8592,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/4/211ca921-7a59-4d54-b8a4-b0a866a8a1fc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=2JKMG5gLGaXkSceGB3Rb7whMdfU%3D&amp;x-signature-webp=eImU0q2IyB0bTELKV9axKp4xGUY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/11/4/211ca921-7a59-4d54-b8a4-b0a866a8a1fc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=EehNxZU3V6yBJhoooN60XH3Zs7I%3D&amp;x-signature-webp=g04WX96EOGXSJOoOu%2B2ACMTOu3E%3D</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b1166d276588406abd4c8d47ce948791.jpeg</t>
+          <t>Lib\hardware\data\images\4dfad0bd5ef043dd93c7a40ef3ca3300.jpeg</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-2-4g-wireless-optical-mous-1600dpi-ergonomic-design-for-pc-laptop-portable-usb-receiver-connection-mou19-blue-549c3?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/olyps-official/olyps-mouse-2-4g-wireless-optical-mous-1600dpi-ergonomic-design-for-pc-laptop-portable-usb-receiver-connection-mou19-blue-549c3?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3f70bf285cdd4ba78101ac0ce308ca29~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=n%2Fh5ahTKXWlwwIaiPMb6IVXYV9Q%3D&amp;x-signature-webp=8MEY0DIB3b07aupBIaopEk4KMr4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3f70bf285cdd4ba78101ac0ce308ca29~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=guPywMU3FRzuvn5L168BiBdu9DE%3D&amp;x-signature-webp=sok3mXUI%2FC86RH0naLXgZuCfOYA%3D</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\359d85f041954c258d705d838508e072.jpeg</t>
+          <t>Lib\hardware\data\images\405c1f7e1dfd47bdaa81de54a8ecfb86.jpeg</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/poloalvisofficial/polo-alvis-urban-stanford-tas-ransel-waterproof-laptop-15-inch-sma-kampus-cowok-23-l-minimalis-design-1732445419512170430?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/poloalvisofficial/polo-alvis-urban-stanford-tas-ransel-waterproof-laptop-15-inch-sma-kampus-cowok-23-l-minimalis-design-1732445419512170430?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -8693,17 +8693,17 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/66c11c4fd34d4d6882e98ed086d9b763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=uhQ%2B%2BSmPmjbaDN7p8l0Rwdv9ra0%3D&amp;x-signature-webp=F4sMYf8ihYFhOhYaUvxj1bQxpc4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/66c11c4fd34d4d6882e98ed086d9b763~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=f6WyuuANxOsCrceHrq7%2B6WgbjYA%3D&amp;x-signature-webp=yjZOK9saDGlQRDup4bk8poLtDFg%3D</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\fef11a388167408ba26830f2b92c5510.jpeg</t>
+          <t>Lib\hardware\data\images\f69ba235a2894975ba9924d1233d4f0a.jpeg</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/asterosofficial/ugreen-mouse-wireless-2-4gh-dongle-slim-design-silent-click-4-level-dpi-for-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/asterosofficial/ugreen-mouse-wireless-2-4gh-dongle-slim-design-silent-click-4-level-dpi-for-pc-laptop?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -8745,17 +8745,17 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4cebea9086a44f65b64de3af3ab65a97~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=PsBRkl45b18Vw7IueiNW8lHG0xo%3D&amp;x-signature-webp=GiO9zB%2FDJOV61gCAqEMqcoWW4mM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4cebea9086a44f65b64de3af3ab65a97~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=%2FEpCtRPuFeN1Li6q9wSxIpJcPZc%3D&amp;x-signature-webp=3FQlqepbjeexCIyVYFmtH5XH%2BN4%3D</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\9fa0b2bf218b450b8e18a08ec22178ff.jpeg</t>
+          <t>Lib\hardware\data\images\830dbad09ed74072b8af89641089bfdc.jpeg</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-koper-2-in-1-mini-14-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charge-1731259158583739685?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/forgui/forgui-kapasitas-besar-koper-24-inch-20-22-inch-koper-2-in-1-mini-14-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charge-1731259158583739685?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -8794,17 +8794,17 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/2/12/79679dee-c94c-4311-bcd5-4f2eff9ffde0.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=AojSBVJq39dGoPH8ykxxrQl7otk%3D&amp;x-signature-webp=msTICFu9vS4fGqN9QsuGXDAkeqY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/2/12/79679dee-c94c-4311-bcd5-4f2eff9ffde0.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=ff9tGP4lHYHy%2FjmPsEX8i6eS1Sc%3D&amp;x-signature-webp=zn1liQJb3Eq%2BAVjAmMdTaJQT4rE%3D</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\e4f6c32a200348a789f5c59d2d990105.png</t>
+          <t>Lib\hardware\data\images\2fa5c947f3bf42769e85727ef20a3907.png</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/mitra-visual-store/magnus-computer-hand-elbow-bracket-ergonomic-design-untuk-laptop-dengan-kapasitas-beban-50kg-instalasi-tanpa-lubang-dan-desain-penyimpanan-aman-dan-terpercaya-1730001110731359391?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/mitra-visual-store/magnus-computer-hand-elbow-bracket-ergonomic-design-untuk-laptop-dengan-kapasitas-beban-50kg-instalasi-tanpa-lubang-dan-desain-penyimpanan-aman-dan-terpercaya-1730001110731359391?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -8846,17 +8846,17 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/619af75ea7304f43b85045a7eb5d04d6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=QOaJ7gKiSNdo0l5O7v7FED1duMw%3D&amp;x-signature-webp=2hHGya7hikfpwZRh5kubFudo3Ds%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/619af75ea7304f43b85045a7eb5d04d6~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=QyMF6JcWyTpmguzbVx4RQKK1dRk%3D&amp;x-signature-webp=H8oN%2BhaiO50lSBEepmnnWQfG6R0%3D</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6520c3280d2d4b5296265723fd099fd4.jpeg</t>
+          <t>Lib\hardware\data\images\1c6736fbe8874bf8ac07187c27dfe87d.jpeg</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotpcoffcial/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732093254842418725?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robotpcoffcial/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732093254842418725?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -8898,17 +8898,17 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/551a82aed56c47eb9e3ee0fba57f90b2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=cVnxYn6yclEEkmJbSF1IEjX4hiQ%3D&amp;x-signature-webp=lg5OajJqtKHciV%2Fx2PbTfGP16gY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/551a82aed56c47eb9e3ee0fba57f90b2~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=AN%2FKwaGIrW9I5p6%2BXNCxp1iVNVk%3D&amp;x-signature-webp=EJJmKYuKHM5UwOG1BA7L9g0A17Y%3D</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c9d6d7003a6e4020907b3e578df8a395.jpeg</t>
+          <t>Lib\hardware\data\images\5ffa85661ec54341be78cc3f0541bdb7.jpeg</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/freeknight/freeknight-tas-ransel-pria-jumbo-tas-backpack-rain-cover-scalable-design-tas-laptop-anti-air-kokoh-expandable-usb-anti-maling-for-working-traveling-kulit-sekolah-hitam-tr748-1731255717575886209?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/freeknight/freeknight-tas-ransel-pria-jumbo-tas-backpack-rain-cover-scalable-design-tas-laptop-anti-air-kokoh-expandable-usb-anti-maling-for-working-traveling-kulit-sekolah-hitam-tr748-1731255717575886209?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -8950,17 +8950,17 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4fcd798501a442ba8d7d822ab4ca3653~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=bfGmryYw3%2FuWvKKjju%2B%2F4xPoDXY%3D&amp;x-signature-webp=wBMpkQclioVlciPso8FFIExSx1M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4fcd798501a442ba8d7d822ab4ca3653~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=Zu2OGIvTMaCfOqWAdl4AnVSY58Q%3D&amp;x-signature-webp=1zXLXWfYoDraqt58yzAmotZgQNc%3D</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2cbe5a2f1d0941d5a817b45c79f4a651.jpeg</t>
+          <t>Lib\hardware\data\images\3e5df9d571c7448d83f7fe72926af46e.jpeg</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1731286329775916501?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1731286329775916501?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9002,17 +9002,17 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4a7f13da9aad455ab9fdba3f50b1c198~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=l0g1eeN0TC87SKfzEbK%2BRo9QHzM%3D&amp;x-signature-webp=yS31ETEqfU21gVCrBf1I%2FkauSFk%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/4a7f13da9aad455ab9fdba3f50b1c198~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=3127TgwsyMuOf%2Bo1ZlalxZssDFI%3D&amp;x-signature-webp=PzEbq6lGkVwncmfxsFl1RzeapBo%3D</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5e5df43b4ca0426d9d8a49f2fe12f6e8.jpeg</t>
+          <t>Lib\hardware\data\images\b76a3c5f22414464968b3182af3ee756.jpeg</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-koper-2-in-1mini-14-inch-1730797361031578784?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-koper-2-in-1mini-14-inch-1730797361031578784?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3252748fff24ac1b364458644770abc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=I5BIJNT3rhbOwbq49PCgREQuulM%3D&amp;x-signature-webp=aZMutTiN4mI52wYLsL2GvLtNUQY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/d3252748fff24ac1b364458644770abc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=MbO0baLjmZ4TF6d%2FoWJgxYt7iDc%3D&amp;x-signature-webp=TsqlmXm5D9ueyLdmTbpIreQ0hFw%3D</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c513b9f659e24613b7d8e0d11b649059.jpeg</t>
+          <t>Lib\hardware\data\images\f2cd71413b1a4ea5bdb937fd1d9be13e.jpeg</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-laptop-komputer-a909-design-ergonomic-with-volume-control-pc-spiker-speker-bass-1729384758482863585?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-laptop-komputer-a909-design-ergonomic-with-volume-control-pc-spiker-speker-bass-1729384758482863585?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -9106,17 +9106,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfeae6c1c6224919b5aa8184f6d941d3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=njkFfcoPlHaZxdJjBaYb3wOFnWI%3D&amp;x-signature-webp=2%2B%2Fga14EPbA%2B84ZcI6O00LAMzxE%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cfeae6c1c6224919b5aa8184f6d941d3~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=z%2F8KULr%2B3K%2BBtfic7YXRC%2B1f5Rc%3D&amp;x-signature-webp=3ApAGNhCijINtH12dxRHMwDuQ1w%3D</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d08cc151d7f14a64bae7715c25448251.jpeg</t>
+          <t>Lib\hardware\data\images\8b61a015578a4b998c193cdb220e6875.jpeg</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robot-powerbank-indonesia/robot-m315-mouse-pc-laptop-computer-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-bergaransi-resmi-1-tahun-1732091684148970925?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/robot-powerbank-indonesia/robot-m315-mouse-pc-laptop-computer-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-bergaransi-resmi-1-tahun-1732091684148970925?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/761cf6e500cc429b8864a69dc5572e5c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=pLnU145EOweGRKXEL1r1NkIKv6Q%3D&amp;x-signature-webp=VLCh4VPQT4eo1m1p05rl%2Bzt5ecg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/761cf6e500cc429b8864a69dc5572e5c~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=8MTIVlTtQ1l9geDXVtnjMMm0cI4%3D&amp;x-signature-webp=Ol0bE1hxK4qiJoZPVsoP8xHDvZA%3D</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\083da5c572bf4ecda8b1f86cb4578f6e.jpeg</t>
+          <t>Lib\hardware\data\images\30c6555f339545f3be6168e055d12036.jpeg</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robotsmartpower/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732092778590929924?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch%26whid%3D18553152</t>
+          <t>https://www.tokopedia.com/robotsmartpower/robot-m315-mouse-wireless-2-4g-2400-dpi-mouse-pc-computer-laptop-mouse-silent-click-komputer-6d-design-ergonomis-original-garansi-1-tahun-bisa-cod-1732092778590929924?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch%26whid%3D18553152</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -9210,17 +9210,17 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1cfc199626c74270b7f2df4afa4837df~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=wILPQu0VenFdRmiLgAPW2q1%2FRJ0%3D&amp;x-signature-webp=Zes1F9XYP%2FY9tK9vBDVoeoxGyF0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/1cfc199626c74270b7f2df4afa4837df~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=Zmv8pQAMrKes73wqjwsEOSOB5t8%3D&amp;x-signature-webp=DK93EAg25w5%2F%2B%2FVZRFXS7TmnLV4%3D</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\18fd1161acb44e55b269a90cc2729b12.jpeg</t>
+          <t>Lib\hardware\data\images\ac932c3298a0494e8b5e46a698e27271.jpeg</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/robot-official-surabaya/robot-mouse-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-robot-m315-mouse-nirkabel-kompatibel-pc-computer-laptop-original-bergaransi-resmi-1-tahun-1732189678655407803?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch%26whid%3D20644317</t>
+          <t>https://www.tokopedia.com/robot-official-surabaya/robot-mouse-wireless-2-4g-2400-dpi-silent-click-6d-design-ergonomis-robot-m315-mouse-nirkabel-kompatibel-pc-computer-laptop-original-bergaransi-resmi-1-tahun-1732189678655407803?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch%26whid%3D20644317</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -9262,17 +9262,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cdba5499d0c541eabd966bd3251dd080~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=svi6NMQI0lQfa0CDTBU0s%2FooX1s%3D&amp;x-signature-webp=peEGF23ZwukEhlPTn0O5FExzr6M%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/cdba5499d0c541eabd966bd3251dd080~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=BqK6qwpUscwDcytivi5yeBDY3OI%3D&amp;x-signature-webp=vbdeaRb7mer70ebchtaXM0OFr1k%3D</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\38f0ac1ba7db49eabd6944098d2c18d6.jpeg</t>
+          <t>Lib\hardware\data\images\e233b3437af94a00afd918252dbd8c4d.jpeg</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731285332222182869?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1731285332222182869?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -9314,17 +9314,17 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/736c25698fe647b7b3a2740fc3a0941d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=fMb%2F4ju1T8EmpMTQJKZdK6R%2BBMs%3D&amp;x-signature-webp=QP41l6LXfTf8Vc1Mj0ONYj7RLeg%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/736c25698fe647b7b3a2740fc3a0941d~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=Bixx3Y1KwFH%2BIt8a5K6COUBloKs%3D&amp;x-signature-webp=lX0fe%2BjSn4pP2YTkE2nI6fL0iLA%3D</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\27b064c4a3c7488b9316d19a375f7c59.jpeg</t>
+          <t>Lib\hardware\data\images\f8dd511efe024381abe3472f30a840d5.jpeg</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730915957094909397?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730915957094909397?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -9366,17 +9366,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/38dcad3fe4a041af8676ce38b7af63c5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=zZZybHssT7qH%2F3najUjj57P93jc%3D&amp;x-signature-webp=aQE0qi4Aa%2FnfOAa1I5%2BsMEcLbDM%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/38dcad3fe4a041af8676ce38b7af63c5~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=HaAs5S%2F7S82tWRKt7bqiKCoaCgY%3D&amp;x-signature-webp=FyR9A5Hc4F4aDrnVhmtmWGTYdC0%3D</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5a4dfc50a0694531a11c2508c7778ec6.jpeg</t>
+          <t>Lib\hardware\data\images\6656eb397ba74b388811da8e60b29a11.jpeg</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1730932169696708053?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-koper-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-1730932169696708053?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -9418,17 +9418,17 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0765aa228c7e4eb98f5cddffb3cd161e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=unJN2oGT13W%2FPEZtGmw19kP7pxw%3D&amp;x-signature-webp=6T4z7u%2FI4qbh5837g2LS8GNeZgw%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/0765aa228c7e4eb98f5cddffb3cd161e~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=7z%2BTtvVzO2lE2DHvJs7OUcV6ips%3D&amp;x-signature-webp=E%2FA7pOe%2FI0MrDu0qT%2BhpYMSHL%2B8%3D</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6be02d29b617417b8bd6c5d512f7eb02.jpeg</t>
+          <t>Lib\hardware\data\images\0a11daf3c49c42ca9e67626273df10ca.jpeg</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730797091346285728?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730797091346285728?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -9470,17 +9470,17 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/15dbf2c96f3e48028a7d92838124dd06~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=6pX0ZP8iINP6jt6WVapXU6zh90U%3D&amp;x-signature-webp=qBHRzgBpoVmHUdmpt9WZmVYo%2FdM%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/15dbf2c96f3e48028a7d92838124dd06~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=6j%2B%2FNIzRhpHqzIxD%2FX0qWaKJEjQ%3D&amp;x-signature-webp=basD8lT8SuZIzqVd%2Bhe6wmBbQ1M%3D</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\61b6b79809e14d838cf64c56e6dc27d1.jpeg</t>
+          <t>Lib\hardware\data\images\f151371726c642dfbac9966992d78dad.jpeg</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-led-for-laptop-komputer-pc-cpu-i560-1729692448934234593?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-led-for-laptop-komputer-pc-cpu-i560-1729692448934234593?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -9522,17 +9522,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/6/559a865b-d5dc-46a6-b4cc-1cbcaac99452.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=TsICb1nFARUIyJNt97DXCqhtFYg%3D&amp;x-signature-webp=EZKkR3u%2FGmIs5dDSfAnu4B14Ypo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/5/6/559a865b-d5dc-46a6-b4cc-1cbcaac99452.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=ANHT07jCPaxeauNPEV%2FmghA3eFc%3D&amp;x-signature-webp=U68Bq1CH0QYQjZb7N0LkMfhK8hE%3D</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b9415393f7f044c2830bfc609d84f5cf.jpeg</t>
+          <t>Lib\hardware\data\images\b0b4981d66ea4a5eb20282bbdeca3249.jpeg</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-for-laptop-komputer-pc-i600-1730809914258851297?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-speaker-design-long-strip-for-laptop-komputer-pc-i600-1730809914258851297?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -9574,17 +9574,17 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9b778382d9e042acbbf6fc51f0b4b3cc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=pd1MQGbP8K8XbRu6b77g7zgMsPo%3D&amp;x-signature-webp=PhP3DlSo17lXJRHDDhm1enc%2FPrY%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9b778382d9e042acbbf6fc51f0b4b3cc~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=Hh6%2FaQdoohbNb%2FyPvnOn2nDbH%2Fk%3D&amp;x-signature-webp=A%2BKMDO%2FJZOSWNuzQpe38%2FvYcxAw%3D</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\4ad70f8ec2894f7a9a363fc1a46811a9.jpeg</t>
+          <t>Lib\hardware\data\images\7aa62c29099c42d4909a6cc48d833211.jpeg</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-soundbar-laptop-pc-komputer-i520-design-long-strip-with-volume-control-1729384483568911841?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/kisonli-id/kisonli-gaming-speaker-soundbar-laptop-pc-komputer-i520-design-long-strip-with-volume-control-1729384483568911841?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -9626,17 +9626,17 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/08a5710421f849f0ba33f538d160f9fb~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=XS25Uxnt3rK8bARZYncMIpD0Tvs%3D&amp;x-signature-webp=hCQlKikJLdMInERRJenAK9%2B9YQQ%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/08a5710421f849f0ba33f538d160f9fb~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=epEkM16OitXgAbLyNQkcdcesHDs%3D&amp;x-signature-webp=b8G2mSG7E%2Fc2XAqiafiA8kAtOUo%3D</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\8768a67f00ab437d95e55dbb41201ffa.jpeg</t>
+          <t>Lib\hardware\data\images\77798fd6c92b403590e96396ce94ef39.jpeg</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-1730797282857354400?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/lovebirdkoper/love-bird-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-bagasi-stand-cup-charger-1730797282857354400?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -9678,17 +9678,17 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3a7b9972f596402094058c182b8ba340~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=9P369b5dX2zFLSdjtRtc8iJVQPk%3D&amp;x-signature-webp=VmFSTQaRQPhWOyOz4ck0vi5h868%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/3a7b9972f596402094058c182b8ba340~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=iwRqNqrctG9M%2FYFtblGz5YNXZTU%3D&amp;x-signature-webp=3L3op9kYQgTLAF4MNSS9nGSMBTk%3D</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\d07d6372fba44cec88759f018a460a62.jpeg</t>
+          <t>Lib\hardware\data\images\2d8e23c0812b437899240c360aa04bdc.jpeg</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730755375298348501?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/laoshidaishuu/laoshidaishu-kapasitas-besar-koper-24-inch-20-22-inch-travel-kabin-bagasi-laptop-new-design-stand-cup-charger-koper-2-in-1mini-14-inch-1730755375298348501?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/92ffb7bcb5ba4243bf5aa5c96cd90e61~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=hHyPACPqx8UkdLOW%2F0e2lLIbiYk%3D&amp;x-signature-webp=6CRMINryflSqPGUfwckrVvwzN7g%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/92ffb7bcb5ba4243bf5aa5c96cd90e61~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=IqOD0aNcr30jw5kIHu%2BgYq4dC3Y%3D&amp;x-signature-webp=r47AcazEuLyd2AvrfpACqou9EpI%3D</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\da18c90ff15a4a1ba8c5e160fe4cdecd.jpeg</t>
+          <t>Lib\hardware\data\images\6ad0b3f444d64b4d95bfa757d7f85983.jpeg</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/orashare/orashare-a01-decorative-assorted-cartoon-stickers-for-power-bank-wall-charger-laptop-tablet-aquaflask-and-so-on-decoration-long-lasting-waterproof-aesthetic-cute-cartoon-design-magic-paper-stickers-random-1pc-sticker-1732799857834428193?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/orashare/orashare-a01-decorative-assorted-cartoon-stickers-for-power-bank-wall-charger-laptop-tablet-aquaflask-and-so-on-decoration-long-lasting-waterproof-aesthetic-cute-cartoon-design-magic-paper-stickers-random-1pc-sticker-1732799857834428193?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -9776,17 +9776,17 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/9/14/e90d0ad0-232f-4503-9d30-433258dedbd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=gjqWdnkFK%2BN%2FwneBQvwMN8LXZyM%3D&amp;x-signature-webp=E5ECwSMo8%2Bae%2Fh8Nmu8nfw9aEKM%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2022/9/14/e90d0ad0-232f-4503-9d30-433258dedbd4.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=7MDCPgvHEvtz3DXJ2lGhMtHbRbA%3D&amp;x-signature-webp=pUKMwcnAT83D9NnojIzF966H5%2B4%3D</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\5f8c033abca546dbac5b77ea6dd8b6c3.jpeg</t>
+          <t>Lib\hardware\data\images\095449a867ab49a99e20584c07b851a1.jpeg</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-bobby-explore-backpack-by-xd-design-for-laptop-17-inch-ransel-original-1731176351546115751?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-bobby-explore-backpack-by-xd-design-for-laptop-17-inch-ransel-original-1731176351546115751?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -9825,17 +9825,17 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/19/3048426c-97a8-4891-ad6a-9d3335136017.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=EfLF%2BK9VXrvvu2at5bYopUzcYxI%3D&amp;x-signature-webp=W%2Fw3AcYgLdE1%2FaMvZPwTBQvQRaY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/10/19/3048426c-97a8-4891-ad6a-9d3335136017.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=DJO59qoHQqfidjPlbFB08GdnQ%2FQ%3D&amp;x-signature-webp=597MIDYB2ijO2%2B2sKNQr0l%2FVayc%3D</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\6a36f0b33fbe48a0860e19dd5800c533.jpeg</t>
+          <t>Lib\hardware\data\images\dc91f11c48574728a32bee43fb4f2ab5.jpeg</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-ransel-eco-flex-bag-for-laptop-untuk-kerja-sekolah-original-water-resistant-original-xd-design-1731176336923592359?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-ransel-eco-flex-bag-for-laptop-untuk-kerja-sekolah-original-water-resistant-original-xd-design-1731176336923592359?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/7/15/2a8e3008-0cc1-456c-a1eb-8712b4e3afef.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=7%2FPnbic7sBAmk3okEeEKAsnyb%2BI%3D&amp;x-signature-webp=yak5YcxwOPXoTI%2FhljClKyT9uQY%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/7/15/2a8e3008-0cc1-456c-a1eb-8712b4e3afef.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=1py03EDbMF2HnH1BWO0O%2FLfd4zA%3D&amp;x-signature-webp=%2F80m8ccQbc2CA8k9d1%2ByQLpv1ZY%3D</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\0bea127c2a384c96be62b366985c0482.jpeg</t>
+          <t>Lib\hardware\data\images\cc4a900ea5ee41aaafdf01bcf52b27cc.jpeg</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-2-0-anti-theft-backpack-briefcase-for-laptop-1731176367656371879?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-2-0-anti-theft-backpack-briefcase-for-laptop-1731176367656371879?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/26/3934712d-a1d2-4f48-af1b-0b1037ea9e26.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=kn3tTDPHBBZjf7dsWcjHO%2FnJuNc%3D&amp;x-signature-webp=%2BxQX0HXPqYTbWJjeQ%2BM4GfzGK0s%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/26/3934712d-a1d2-4f48-af1b-0b1037ea9e26.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=0ElOch52WzHbXx92U9Wv4iP6TpE%3D&amp;x-signature-webp=Lw6bET3VRWyXstWVRQkIbV0LQbs%3D</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\718839f416b74589bb569739dce73db2.jpeg</t>
+          <t>Lib\hardware\data\images\2b02582a85bc46d78405fda6bbf3aa57.jpeg</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-backpack-for-laptop-original-1731176301652117159?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/bobby-edge-anti-theft-backpack-by-xd-design-tas-ransel-backpack-for-laptop-original-1731176301652117159?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e0cb31b7859943a7818f516b7a76c398~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=aRaxNEpKTZcnqRS9lI%2FtSpk7U2Q%3D&amp;x-signature-webp=bA2U0qh1sYqtl5YZtFR3AR%2Ft7GQ%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e0cb31b7859943a7818f516b7a76c398~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=ZQkssoA4P%2FGDI1Zxq6WCHLt2xF4%3D&amp;x-signature-webp=K5tuZkHRD9%2FUuqMo9FlW%2BrIshW8%3D</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\26ef3f6b87b247fa8118823a1289d271.jpeg</t>
+          <t>Lib\hardware\data\images\c25cf85956f349919ba0df8b4877fa75.jpeg</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/prodesign/pro-design-patron-patslt-50-meja-samping-nakas-meja-laptop-1729384439739745584?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/prodesign/pro-design-patron-patslt-50-meja-samping-nakas-meja-laptop-1729384439739745584?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -10027,17 +10027,17 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e100902e37f5405f95ab14ceca042fbe~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=1SIOoxOSope0sEiQD5cZ3ceiUeE%3D&amp;x-signature-webp=r61RaMW%2B1t9%2FqzB4J56JUTi4JKY%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/e100902e37f5405f95ab14ceca042fbe~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=ZKmD%2FOyMieWL9SiXP5p4Xg6tBWw%3D&amp;x-signature-webp=fJ2CSzoXYYzPSgfKomklVM4XKKw%3D</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\66ea92593ed943ce9170ab5888de6251.jpeg</t>
+          <t>Lib\hardware\data\images\d4605f677811472d8d1fbcfd2443e500.jpeg</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/unomax/sleeve-nillkin-versatile-for-laptop-notebook-macbook-horizontal-design-1729542909144501215?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/unomax/sleeve-nillkin-versatile-for-laptop-notebook-macbook-horizontal-design-1729542909144501215?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -10076,17 +10076,17 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/4/12/4a196eba-99a6-4d86-ba5d-42198ae0ae47.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=TbRaip26l3pWT%2BYkRGHp6y2jSi0%3D&amp;x-signature-webp=R1ovOHvHKC0MTAvnkhD0wHd11sc%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2023/4/12/4a196eba-99a6-4d86-ba5d-42198ae0ae47.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=pvWXjrVdgsPAoEvUZ9KWT0vYOjU%3D&amp;x-signature-webp=gQR9XXjBlz4BjN20OtWwPwB55Cs%3D</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\a08dc59520bd41d59fc095ba4cd6a923.jpeg</t>
+          <t>Lib\hardware\data\images\9e21626d5c9f43488b8a178edf94ed80.jpeg</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-anti-theft-backpack-briefcase-for-laptop-15-1731176360280164007?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/original-xd-design-bobby-bizz-anti-theft-backpack-briefcase-for-laptop-15-1731176360280164007?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/65b3b9f2049f476ba5c95f176912c01f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=jFoEROsQRG2rjiZLRAJK%2F0dzatE%3D&amp;x-signature-webp=q%2BS3d5UOBopLIffqpkoZoIPkKds%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/65b3b9f2049f476ba5c95f176912c01f~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=LPfmDn5a6SWDr%2FC5ndo3QVNCLRg%3D&amp;x-signature-webp=U5hJF2NeirMrg6tsFf%2BupJbZeWg%3D</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3e4403f4430349268775b906798eb42a.jpeg</t>
+          <t>Lib\hardware\data\images\2402b35a35d6488aae53f33a351744ae.jpeg</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/wia-official/wia-xd-design-bobby-edge-anti-theft-backpack-tas-ransel-laptop-unisex-original-1729752607370544988?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/wia-official/wia-xd-design-bobby-edge-anti-theft-backpack-tas-ransel-laptop-unisex-original-1729752607370544988?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -10174,17 +10174,17 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/1/16/61242af3-3630-4531-8d25-e625e9e80dea.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=ijldVPog0iMal9CI0%2BNjgqo3W9k%3D&amp;x-signature-webp=fYyLHNyI8qKi2jrWH8XR8JbVwvY%3D</t>
+          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2024/1/16/61242af3-3630-4531-8d25-e625e9e80dea.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=Y567NPOC9n%2Bb4FuTpovOtdqQ5HA%3D&amp;x-signature-webp=ASHAZNFzMCOoDbBzjJ2nuPDiHGk%3D</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\3d786c14abe04234a272b597165a6f36.jpeg</t>
+          <t>Lib\hardware\data\images\c049aa9c2c5b4019bd2de92f5a141bd3.jpeg</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/primarycaresofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black-80565?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/primarycaresofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black-80565?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://p19-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/1d2dc8699f1a427e82b9077ea324a552~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=J%2BwV9JQZ4cKekzb%2B5jg5NgWIOxM%3D&amp;x-signature-webp=D%2B%2BXxDEZS3KF%2BRNIa9VH%2FisLbG4%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/1d2dc8699f1a427e82b9077ea324a552~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=gocfF3ciL9XDOeBgGeSbDvw2IF0%3D&amp;x-signature-webp=wHxH1OEh40vpxWSPbPlz%2FGjhey8%3D</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\c34bc9e3f3734a4cbbaccf7d93df3cae.jpeg</t>
+          <t>Lib\hardware\data\images\1895b971feab4d53a3cd412cf885f2ec.jpeg</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/sempanabags/polo-goden-62194-2b-tas-ransel-backpack-tas-punggung-tas-laptop-tas-kantor-tas-kerja-premium-material-sleek-design-multi-compartment-banyak-tempat-penyimpanan-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/sempanabags/polo-goden-62194-2b-tas-ransel-backpack-tas-punggung-tas-laptop-tas-kantor-tas-kerja-premium-material-sleek-design-multi-compartment-banyak-tempat-penyimpanan-hitam?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -10278,17 +10278,17 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a04b8b3b3b064a0fa6aaf3e379856c92~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=U5%2FfGRNZ%2FS0XVqczo%2B9eK991UPc%3D&amp;x-signature-webp=ITcgDAxiK7tNGznhxoaF%2BokMD1k%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/a04b8b3b3b064a0fa6aaf3e379856c92~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=%2BhDaVc%2FgYQ5MpnMDWs%2FROMc8RMk%3D&amp;x-signature-webp=70adEotJwsJGSkx6fVTJ9cja4o4%3D</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\76fb77b891a741fc8604ea51ad351cc1.jpeg</t>
+          <t>Lib\hardware\data\images\0f948cf4500840bc994ed544a18547a0.jpeg</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/advan-by-urbanlife/advan-laptop-workplus-heritage-amd-ryzen-5-7535hs-8gb-ddr4-upgrade-512gb-ssd-upgrade-amd-radeon-660m-win-11-14-wuxga-16-10-megamendung-batik-design-1731557661886154575?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/advan-by-urbanlife/advan-laptop-workplus-heritage-amd-ryzen-5-7535hs-8gb-ddr4-upgrade-512gb-ssd-upgrade-amd-radeon-660m-win-11-14-wuxga-16-10-megamendung-batik-design-1731557661886154575?extParam=ivf%3Dtrue%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -10327,17 +10327,17 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://p19-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/12/ffd6e4db-90b2-4e80-b558-4833df06bfc3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=cDLtRdCyvev5KpoUBhWJ2oTmKx0%3D&amp;x-signature-webp=U4exwXrEBpmjOAxndFOJJrulLwc%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2024/8/12/ffd6e4db-90b2-4e80-b558-4833df06bfc3.png~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=2vTg3BjTZSbDnbrn207FYDP3zZs%3D&amp;x-signature-webp=K%2FurdLXsTHdY4RYdw236aHKyPrc%3D</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\7314291999a443bda3963e174de8f659.png</t>
+          <t>Lib\hardware\data\images\3640faf3ab5a44609664a9664db8414e.png</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/deermatech/ugreen-ergonomic-premium-mouse-pad-with-arm-rest-design-bantal-tangan-anti-slip-mousepad-untuk-kerja-kantor-meja-komputer-pc-laptop-black-faf99?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/deermatech/ugreen-ergonomic-premium-mouse-pad-with-arm-rest-design-bantal-tangan-anti-slip-mousepad-untuk-kerja-kantor-meja-komputer-pc-laptop-black-faf99?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -10379,17 +10379,17 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/af145de2fcdb4ec3a9dc41740a920a72~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=0%2F0I%2BLrOh80NAmZzEN%2FatEtLwwQ%3D&amp;x-signature-webp=%2FZ3J%2F%2FxFTESJOxy%2BsadNhOmqwuY%3D</t>
+          <t>https://p16-images-common-sign-sg.tokopedia-static.net/tos-maliva-i-o3syd03w52-us/af145de2fcdb4ec3a9dc41740a920a72~tplv-o3syd03w52-resize-jpeg:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=U9VHy5VERITx6GIM9CvQOzPjU3U%3D&amp;x-signature-webp=5en%2BVhnpYIkPDmvumOtmfXOx0DE%3D</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\62a73f9287ee4a7384b409b0eece30bb.jpeg</t>
+          <t>Lib\hardware\data\images\9874d366a37042879442a8dafe794e82.jpeg</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/usea/taffhome-meja-lipat-serbaguna-laptop-portable-desk-minimalist-design-i042767-1731655641388386299?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/usea/taffhome-meja-lipat-serbaguna-laptop-portable-desk-minimalist-design-i042767-1731655641388386299?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9d59757d49a84775a35c06bdeb14cede~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=zzZSbYhTZBrsbuVF8m%2BchOXHDtw%3D&amp;x-signature-webp=Tl1%2F3DqD3fiM08AYTdfDqIQPma0%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/9d59757d49a84775a35c06bdeb14cede~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=dX1O7Gyj0pyKMnOryG8xP3HYzy8%3D&amp;x-signature-webp=ckpP63jfiw6IgJBYF11STcFqt7w%3D</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2b2baad911294308b5976944168d688f.jpeg</t>
+          <t>Lib\hardware\data\images\16ecc3d9a54f473f9ebbd803bcbc079f.jpeg</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/wia-official/wia-xd-design-14-16-laptop-sleeve-black-tas-pelindung-laptop-original-1729909128724056924?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/wia-official/wia-xd-design-14-16-laptop-sleeve-black-tas-pelindung-laptop-original-1729909128724056924?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -10477,17 +10477,17 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/8/dd821518-9132-4894-82f2-34caf0bb2acc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=IdKApFJotvhcyx4xFGCorAA0SFs%3D&amp;x-signature-webp=XMRn9ECR6P3u8ifcqt7kRO%2FxZ%2B4%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/VqbcmM/2021/11/8/dd821518-9132-4894-82f2-34caf0bb2acc.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=LmKYmKyKRI1RJBESldPR6djedFM%3D&amp;x-signature-webp=hxlOwPTafMZ%2Ft%2FiOuwdQqb7Fbh8%3D</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\2e56d226e7f642eeb82dbb2e97ad7fd0.jpeg</t>
+          <t>Lib\hardware\data\images\1bd033e97e0c42c6a5945d545111c063.jpeg</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/luxer/tas-bobby-hero-anti-theft-backpack-xl-17-inch-bag-for-laptop-xd-design-ori-1731176367509243559?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/luxer/tas-bobby-hero-anti-theft-backpack-xl-17-inch-bag-for-laptop-xd-design-ori-1731176367509243559?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -10526,17 +10526,17 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/12/9/54c88793-1151-49b3-ae07-078a15223f01.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047520&amp;x-signature=DV9779apLss9WjUzHXHjDd%2FWj1E%3D&amp;x-signature-webp=SpGViU%2F8XZqruH1DVf3n0GSOt%2Bo%3D</t>
+          <t>https://p16-images-sign-sg.tokopedia-static.net/tos-alisg-i-aphluv4xwc-sg/img/hDjmkQ/2022/12/9/54c88793-1151-49b3-ae07-078a15223f01.jpg~tplv-aphluv4xwc-white-pad-v1:200:200.jpeg?lk3s=a74d0a5d&amp;x-expires=1764047813&amp;x-signature=ku1OWUlnHJbaKitep%2FcpWrcHjTk%3D&amp;x-signature-webp=MaiXrAzpxzf7SooBDOjMxSgHmSo%3D</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Lib\hardware\data\images\b1a81cc67fc94f948bd0250e2ec0cb8e.jpeg</t>
+          <t>Lib\hardware\data\images\a842dcbbe4204e36955ecb9eec6a8fc3.jpeg</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>https://www.tokopedia.com/supcaseofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D20251125041200371BCE7DC83817148W32%26src%3Dsearch</t>
+          <t>https://www.tokopedia.com/supcaseofficial/vrs-design-ark-backpack-organize-laptop-carry-bag-multi-use-up-to-15-6-black?extParam=ivf%3Dfalse%26keyword%3Dlaptop+design%26search_id%3D2025112504165337BC2F75BF1BCF0C6XUL%26src%3Dsearch</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
